--- a/Horario_Facultad.xlsx
+++ b/Horario_Facultad.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -508,77 +508,81 @@
       <c r="O1" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+      <c r="A2" s="1" t="inlineStr"/>
+      <c r="B2" s="1" t="inlineStr"/>
+      <c r="C2" s="1" t="inlineStr"/>
+      <c r="D2" s="1" t="inlineStr"/>
+      <c r="E2" s="1" t="inlineStr"/>
+      <c r="F2" s="1" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2">
+        <f>(J2-L2)</f>
+        <v/>
+      </c>
+      <c r="L2" s="2">
+        <f>COUNTIF($B$2:$F$19,H2)</f>
+        <v/>
+      </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr"/>
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Martes</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Miercoles</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>Jueves</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Viernes</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Abrev</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Asignaturas</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Frec</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Faltan</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Asignadas</t>
-        </is>
+      <c r="K3" s="2">
+        <f>(J3-L3)</f>
+        <v/>
+      </c>
+      <c r="L3" s="2">
+        <f>COUNTIF($B$2:$F$19,H3)</f>
+        <v/>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>Aulas</t>
         </is>
@@ -627,17 +631,15 @@
           <t>Álgebra Lineal</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="J4" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="K4" s="2">
         <f>(J4-L4)</f>
         <v/>
       </c>
       <c r="L4" s="2">
-        <f>COUNTIF($B$4:$F$15,H4)</f>
+        <f>COUNTIF($B$2:$F$19,H4)</f>
         <v/>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -686,17 +688,15 @@
           <t>Lógica</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J5" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K5" s="2">
         <f>(J5-L5)</f>
         <v/>
       </c>
       <c r="L5" s="2">
-        <f>COUNTIF($B$4:$F$15,H5)</f>
+        <f>COUNTIF($B$2:$F$19,H5)</f>
         <v/>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -745,17 +745,15 @@
           <t>Introducción a la Programación</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J6" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K6" s="2">
         <f>(J6-L6)</f>
         <v/>
       </c>
       <c r="L6" s="2">
-        <f>COUNTIF($B$4:$F$15,H6)</f>
+        <f>COUNTIF($B$2:$F$19,H6)</f>
         <v/>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -800,17 +798,15 @@
           <t>Análisis Matemático I</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J7" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K7" s="2">
         <f>(J7-L7)</f>
         <v/>
       </c>
       <c r="L7" s="2">
-        <f>COUNTIF($B$4:$F$15,H7)</f>
+        <f>COUNTIF($B$2:$F$19,H7)</f>
         <v/>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -859,17 +855,15 @@
           <t>Introducción a la Ciencia de Datos</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J8" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K8" s="2">
         <f>(J8-L8)</f>
         <v/>
       </c>
       <c r="L8" s="2">
-        <f>COUNTIF($B$4:$F$15,H8)</f>
+        <f>COUNTIF($B$2:$F$19,H8)</f>
         <v/>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -914,17 +908,15 @@
           <t>Filosofía</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J9" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K9" s="2">
         <f>(J9-L9)</f>
         <v/>
       </c>
       <c r="L9" s="2">
-        <f>COUNTIF($B$4:$F$15,H9)</f>
+        <f>COUNTIF($B$2:$F$19,H9)</f>
         <v/>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -950,8 +942,14 @@
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr"/>
+      <c r="K10" s="2">
+        <f>(J10-L10)</f>
+        <v/>
+      </c>
+      <c r="L10" s="2">
+        <f>COUNTIF($B$2:$F$19,H10)</f>
+        <v/>
+      </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr">
         <is>
@@ -1074,26 +1072,26 @@
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
+      <c r="A16" s="1" t="inlineStr"/>
+      <c r="B16" s="1" t="inlineStr"/>
+      <c r="C16" s="1" t="inlineStr"/>
+      <c r="D16" s="1" t="inlineStr"/>
+      <c r="E16" s="1" t="inlineStr"/>
+      <c r="F16" s="1" t="inlineStr"/>
       <c r="G16">
         <f>"Total:"</f>
         <v/>
       </c>
-      <c r="H16">
-        <f>COUNTA($H$4:$H$15)</f>
-        <v/>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+      <c r="H16" s="2">
+        <f>COUNTA($H$2:$H$19)</f>
+        <v/>
+      </c>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>Lab</t>
         </is>
@@ -1101,14 +1099,53 @@
       <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="F17">
+      <c r="A17" s="3" t="n"/>
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3" t="n"/>
+      <c r="F17" s="3">
         <f>"Σ Frec:"</f>
         <v/>
       </c>
       <c r="G17">
-        <f>SUM($J$4:$J$15)</f>
-        <v/>
-      </c>
+        <f>SUM($J$2:$J$19)</f>
+        <v/>
+      </c>
+      <c r="H17" s="2" t="n"/>
+      <c r="I17" s="2" t="n"/>
+      <c r="J17" s="2" t="n"/>
+      <c r="K17" s="2" t="n"/>
+      <c r="L17" s="2" t="n"/>
+      <c r="N17" s="2" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="1" t="n"/>
+      <c r="C18" s="1" t="n"/>
+      <c r="D18" s="1" t="n"/>
+      <c r="E18" s="1" t="n"/>
+      <c r="F18" s="1" t="n"/>
+      <c r="H18" s="2" t="n"/>
+      <c r="I18" s="2" t="n"/>
+      <c r="J18" s="2" t="n"/>
+      <c r="K18" s="2" t="n"/>
+      <c r="L18" s="2" t="n"/>
+      <c r="N18" s="2" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n"/>
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="n"/>
+      <c r="H19" s="2" t="n"/>
+      <c r="I19" s="2" t="n"/>
+      <c r="J19" s="2" t="n"/>
+      <c r="K19" s="2" t="n"/>
+      <c r="L19" s="2" t="n"/>
+      <c r="N19" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1121,7 +1158,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1160,77 +1197,81 @@
       <c r="O1" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+      <c r="A2" s="1" t="inlineStr"/>
+      <c r="B2" s="1" t="inlineStr"/>
+      <c r="C2" s="1" t="inlineStr"/>
+      <c r="D2" s="1" t="inlineStr"/>
+      <c r="E2" s="1" t="inlineStr"/>
+      <c r="F2" s="1" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2">
+        <f>(J2-L2)</f>
+        <v/>
+      </c>
+      <c r="L2" s="2">
+        <f>COUNTIF($B$2:$F$19,H2)</f>
+        <v/>
+      </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr"/>
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Martes</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Miercoles</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>Jueves</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Viernes</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Abrev</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Asignaturas</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Frec</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Faltan</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Asignadas</t>
-        </is>
+      <c r="K3" s="2">
+        <f>(J3-L3)</f>
+        <v/>
+      </c>
+      <c r="L3" s="2">
+        <f>COUNTIF($B$2:$F$19,H3)</f>
+        <v/>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>Aulas</t>
         </is>
@@ -1275,17 +1316,15 @@
           <t>Redes de Computadoras</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J4" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K4" s="2">
         <f>(J4-L4)</f>
         <v/>
       </c>
       <c r="L4" s="2">
-        <f>COUNTIF($B$4:$F$15,H4)</f>
+        <f>COUNTIF($B$2:$F$19,H4)</f>
         <v/>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -1330,17 +1369,15 @@
           <t>Ingeniería de Software</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J5" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K5" s="2">
         <f>(J5-L5)</f>
         <v/>
       </c>
       <c r="L5" s="2">
-        <f>COUNTIF($B$4:$F$15,H5)</f>
+        <f>COUNTIF($B$2:$F$19,H5)</f>
         <v/>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -1389,17 +1426,15 @@
           <t>Modelos de Optimización</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J6" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K6" s="2">
         <f>(J6-L6)</f>
         <v/>
       </c>
       <c r="L6" s="2">
-        <f>COUNTIF($B$4:$F$15,H6)</f>
+        <f>COUNTIF($B$2:$F$19,H6)</f>
         <v/>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -1444,17 +1479,15 @@
           <t>Bases de Datos II</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J7" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K7" s="2">
         <f>(J7-L7)</f>
         <v/>
       </c>
       <c r="L7" s="2">
-        <f>COUNTIF($B$4:$F$15,H7)</f>
+        <f>COUNTIF($B$2:$F$19,H7)</f>
         <v/>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -1503,17 +1536,15 @@
           <t>Programación Declarativa</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J8" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K8" s="2">
         <f>(J8-L8)</f>
         <v/>
       </c>
       <c r="L8" s="2">
-        <f>COUNTIF($B$4:$F$15,H8)</f>
+        <f>COUNTIF($B$2:$F$19,H8)</f>
         <v/>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -1558,17 +1589,15 @@
           <t>Estadística</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J9" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K9" s="2">
         <f>(J9-L9)</f>
         <v/>
       </c>
       <c r="L9" s="2">
-        <f>COUNTIF($B$4:$F$15,H9)</f>
+        <f>COUNTIF($B$2:$F$19,H9)</f>
         <v/>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -1594,8 +1623,14 @@
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr"/>
+      <c r="K10" s="2">
+        <f>(J10-L10)</f>
+        <v/>
+      </c>
+      <c r="L10" s="2">
+        <f>COUNTIF($B$2:$F$19,H10)</f>
+        <v/>
+      </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr">
         <is>
@@ -1718,24 +1753,74 @@
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
+      <c r="A16" s="1" t="n"/>
+      <c r="B16" s="1" t="n"/>
+      <c r="C16" s="1" t="n"/>
+      <c r="D16" s="1" t="n"/>
+      <c r="E16" s="1" t="n"/>
+      <c r="F16" s="1" t="n"/>
       <c r="G16">
         <f>"Total:"</f>
         <v/>
       </c>
-      <c r="H16">
-        <f>COUNTA($H$4:$H$15)</f>
-        <v/>
-      </c>
+      <c r="H16" s="2">
+        <f>COUNTA($H$2:$H$19)</f>
+        <v/>
+      </c>
+      <c r="I16" s="2" t="n"/>
+      <c r="J16" s="2" t="n"/>
+      <c r="K16" s="2" t="n"/>
+      <c r="L16" s="2" t="n"/>
+      <c r="N16" s="2" t="n"/>
     </row>
     <row r="17">
-      <c r="F17">
+      <c r="A17" s="3" t="n"/>
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3" t="n"/>
+      <c r="F17" s="3">
         <f>"Σ Frec:"</f>
         <v/>
       </c>
       <c r="G17">
-        <f>SUM($J$4:$J$15)</f>
-        <v/>
-      </c>
+        <f>SUM($J$2:$J$19)</f>
+        <v/>
+      </c>
+      <c r="H17" s="2" t="n"/>
+      <c r="I17" s="2" t="n"/>
+      <c r="J17" s="2" t="n"/>
+      <c r="K17" s="2" t="n"/>
+      <c r="L17" s="2" t="n"/>
+      <c r="N17" s="2" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="1" t="n"/>
+      <c r="C18" s="1" t="n"/>
+      <c r="D18" s="1" t="n"/>
+      <c r="E18" s="1" t="n"/>
+      <c r="F18" s="1" t="n"/>
+      <c r="H18" s="2" t="n"/>
+      <c r="I18" s="2" t="n"/>
+      <c r="J18" s="2" t="n"/>
+      <c r="K18" s="2" t="n"/>
+      <c r="L18" s="2" t="n"/>
+      <c r="N18" s="2" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n"/>
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="n"/>
+      <c r="H19" s="2" t="n"/>
+      <c r="I19" s="2" t="n"/>
+      <c r="J19" s="2" t="n"/>
+      <c r="K19" s="2" t="n"/>
+      <c r="L19" s="2" t="n"/>
+      <c r="N19" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1748,7 +1833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1787,77 +1872,81 @@
       <c r="O1" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+      <c r="A2" s="1" t="inlineStr"/>
+      <c r="B2" s="1" t="inlineStr"/>
+      <c r="C2" s="1" t="inlineStr"/>
+      <c r="D2" s="1" t="inlineStr"/>
+      <c r="E2" s="1" t="inlineStr"/>
+      <c r="F2" s="1" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2">
+        <f>(J2-L2)</f>
+        <v/>
+      </c>
+      <c r="L2" s="2">
+        <f>COUNTIF($B$2:$F$19,H2)</f>
+        <v/>
+      </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr"/>
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Martes</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Miercoles</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>Jueves</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Viernes</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Abrev</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Asignaturas</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Frec</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Faltan</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Asignadas</t>
-        </is>
+      <c r="K3" s="2">
+        <f>(J3-L3)</f>
+        <v/>
+      </c>
+      <c r="L3" s="2">
+        <f>COUNTIF($B$2:$F$19,H3)</f>
+        <v/>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>Aulas</t>
         </is>
@@ -1902,17 +1991,15 @@
           <t>Redes de Computadoras</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J4" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K4" s="2">
         <f>(J4-L4)</f>
         <v/>
       </c>
       <c r="L4" s="2">
-        <f>COUNTIF($B$4:$F$15,H4)</f>
+        <f>COUNTIF($B$2:$F$19,H4)</f>
         <v/>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -1957,17 +2044,15 @@
           <t>Ingeniería de Software</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J5" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K5" s="2">
         <f>(J5-L5)</f>
         <v/>
       </c>
       <c r="L5" s="2">
-        <f>COUNTIF($B$4:$F$15,H5)</f>
+        <f>COUNTIF($B$2:$F$19,H5)</f>
         <v/>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -2016,17 +2101,15 @@
           <t>Modelos de Optimización</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J6" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K6" s="2">
         <f>(J6-L6)</f>
         <v/>
       </c>
       <c r="L6" s="2">
-        <f>COUNTIF($B$4:$F$15,H6)</f>
+        <f>COUNTIF($B$2:$F$19,H6)</f>
         <v/>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -2071,17 +2154,15 @@
           <t>Bases de Datos II</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J7" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K7" s="2">
         <f>(J7-L7)</f>
         <v/>
       </c>
       <c r="L7" s="2">
-        <f>COUNTIF($B$4:$F$15,H7)</f>
+        <f>COUNTIF($B$2:$F$19,H7)</f>
         <v/>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -2130,17 +2211,15 @@
           <t>Programación Declarativa</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J8" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K8" s="2">
         <f>(J8-L8)</f>
         <v/>
       </c>
       <c r="L8" s="2">
-        <f>COUNTIF($B$4:$F$15,H8)</f>
+        <f>COUNTIF($B$2:$F$19,H8)</f>
         <v/>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -2185,17 +2264,15 @@
           <t>Estadística</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J9" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K9" s="2">
         <f>(J9-L9)</f>
         <v/>
       </c>
       <c r="L9" s="2">
-        <f>COUNTIF($B$4:$F$15,H9)</f>
+        <f>COUNTIF($B$2:$F$19,H9)</f>
         <v/>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -2221,8 +2298,14 @@
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr"/>
+      <c r="K10" s="2">
+        <f>(J10-L10)</f>
+        <v/>
+      </c>
+      <c r="L10" s="2">
+        <f>COUNTIF($B$2:$F$19,H10)</f>
+        <v/>
+      </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr">
         <is>
@@ -2345,24 +2428,74 @@
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
+      <c r="A16" s="1" t="n"/>
+      <c r="B16" s="1" t="n"/>
+      <c r="C16" s="1" t="n"/>
+      <c r="D16" s="1" t="n"/>
+      <c r="E16" s="1" t="n"/>
+      <c r="F16" s="1" t="n"/>
       <c r="G16">
         <f>"Total:"</f>
         <v/>
       </c>
-      <c r="H16">
-        <f>COUNTA($H$4:$H$15)</f>
-        <v/>
-      </c>
+      <c r="H16" s="2">
+        <f>COUNTA($H$2:$H$19)</f>
+        <v/>
+      </c>
+      <c r="I16" s="2" t="n"/>
+      <c r="J16" s="2" t="n"/>
+      <c r="K16" s="2" t="n"/>
+      <c r="L16" s="2" t="n"/>
+      <c r="N16" s="2" t="n"/>
     </row>
     <row r="17">
-      <c r="F17">
+      <c r="A17" s="3" t="n"/>
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3" t="n"/>
+      <c r="F17" s="3">
         <f>"Σ Frec:"</f>
         <v/>
       </c>
       <c r="G17">
-        <f>SUM($J$4:$J$15)</f>
-        <v/>
-      </c>
+        <f>SUM($J$2:$J$19)</f>
+        <v/>
+      </c>
+      <c r="H17" s="2" t="n"/>
+      <c r="I17" s="2" t="n"/>
+      <c r="J17" s="2" t="n"/>
+      <c r="K17" s="2" t="n"/>
+      <c r="L17" s="2" t="n"/>
+      <c r="N17" s="2" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="1" t="n"/>
+      <c r="C18" s="1" t="n"/>
+      <c r="D18" s="1" t="n"/>
+      <c r="E18" s="1" t="n"/>
+      <c r="F18" s="1" t="n"/>
+      <c r="H18" s="2" t="n"/>
+      <c r="I18" s="2" t="n"/>
+      <c r="J18" s="2" t="n"/>
+      <c r="K18" s="2" t="n"/>
+      <c r="L18" s="2" t="n"/>
+      <c r="N18" s="2" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n"/>
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="n"/>
+      <c r="H19" s="2" t="n"/>
+      <c r="I19" s="2" t="n"/>
+      <c r="J19" s="2" t="n"/>
+      <c r="K19" s="2" t="n"/>
+      <c r="L19" s="2" t="n"/>
+      <c r="N19" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2375,7 +2508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2414,77 +2547,81 @@
       <c r="O1" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+      <c r="A2" s="1" t="inlineStr"/>
+      <c r="B2" s="1" t="inlineStr"/>
+      <c r="C2" s="1" t="inlineStr"/>
+      <c r="D2" s="1" t="inlineStr"/>
+      <c r="E2" s="1" t="inlineStr"/>
+      <c r="F2" s="1" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2">
+        <f>(J2-L2)</f>
+        <v/>
+      </c>
+      <c r="L2" s="2">
+        <f>COUNTIF($B$2:$F$19,H2)</f>
+        <v/>
+      </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr"/>
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Martes</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Miercoles</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>Jueves</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Viernes</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Abrev</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Asignaturas</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Frec</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Faltan</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Asignadas</t>
-        </is>
+      <c r="K3" s="2">
+        <f>(J3-L3)</f>
+        <v/>
+      </c>
+      <c r="L3" s="2">
+        <f>COUNTIF($B$2:$F$19,H3)</f>
+        <v/>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>Aulas</t>
         </is>
@@ -2513,17 +2650,15 @@
           <t>Aprendizaje de Máquinas</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J4" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K4" s="2">
         <f>(J4-L4)</f>
         <v/>
       </c>
       <c r="L4" s="2">
-        <f>COUNTIF($B$4:$F$15,H4)</f>
+        <f>COUNTIF($B$2:$F$19,H4)</f>
         <v/>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -2552,17 +2687,15 @@
           <t>Diseño y Análisis de Algoritmos</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J5" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K5" s="2">
         <f>(J5-L5)</f>
         <v/>
       </c>
       <c r="L5" s="2">
-        <f>COUNTIF($B$4:$F$15,H5)</f>
+        <f>COUNTIF($B$2:$F$19,H5)</f>
         <v/>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -2595,17 +2728,15 @@
           <t>Sistemas Distribuidos</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J6" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K6" s="2">
         <f>(J6-L6)</f>
         <v/>
       </c>
       <c r="L6" s="2">
-        <f>COUNTIF($B$4:$F$15,H6)</f>
+        <f>COUNTIF($B$2:$F$19,H6)</f>
         <v/>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -2634,17 +2765,15 @@
           <t>Asignatura Electiva</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J7" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K7" s="2">
         <f>(J7-L7)</f>
         <v/>
       </c>
       <c r="L7" s="2">
-        <f>COUNTIF($B$4:$F$15,H7)</f>
+        <f>COUNTIF($B$2:$F$19,H7)</f>
         <v/>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -2677,17 +2806,15 @@
           <t>Estudios de Ciencia, Tecnología y Sociedad</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J8" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K8" s="2">
         <f>(J8-L8)</f>
         <v/>
       </c>
       <c r="L8" s="2">
-        <f>COUNTIF($B$4:$F$15,H8)</f>
+        <f>COUNTIF($B$2:$F$19,H8)</f>
         <v/>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -2716,17 +2843,15 @@
           <t>Seguridad Nacional / Defensa Nacionaol</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J9" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K9" s="2">
         <f>(J9-L9)</f>
         <v/>
       </c>
       <c r="L9" s="2">
-        <f>COUNTIF($B$4:$F$15,H9)</f>
+        <f>COUNTIF($B$2:$F$19,H9)</f>
         <v/>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -2768,8 +2893,14 @@
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr"/>
+      <c r="K10" s="2">
+        <f>(J10-L10)</f>
+        <v/>
+      </c>
+      <c r="L10" s="2">
+        <f>COUNTIF($B$2:$F$19,H10)</f>
+        <v/>
+      </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -2920,24 +3051,74 @@
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
+      <c r="A16" s="1" t="n"/>
+      <c r="B16" s="1" t="n"/>
+      <c r="C16" s="1" t="n"/>
+      <c r="D16" s="1" t="n"/>
+      <c r="E16" s="1" t="n"/>
+      <c r="F16" s="1" t="n"/>
       <c r="G16">
         <f>"Total:"</f>
         <v/>
       </c>
-      <c r="H16">
-        <f>COUNTA($H$4:$H$15)</f>
-        <v/>
-      </c>
+      <c r="H16" s="2">
+        <f>COUNTA($H$2:$H$19)</f>
+        <v/>
+      </c>
+      <c r="I16" s="2" t="n"/>
+      <c r="J16" s="2" t="n"/>
+      <c r="K16" s="2" t="n"/>
+      <c r="L16" s="2" t="n"/>
+      <c r="N16" s="2" t="n"/>
     </row>
     <row r="17">
-      <c r="F17">
+      <c r="A17" s="3" t="n"/>
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3" t="n"/>
+      <c r="F17" s="3">
         <f>"Σ Frec:"</f>
         <v/>
       </c>
       <c r="G17">
-        <f>SUM($J$4:$J$15)</f>
-        <v/>
-      </c>
+        <f>SUM($J$2:$J$19)</f>
+        <v/>
+      </c>
+      <c r="H17" s="2" t="n"/>
+      <c r="I17" s="2" t="n"/>
+      <c r="J17" s="2" t="n"/>
+      <c r="K17" s="2" t="n"/>
+      <c r="L17" s="2" t="n"/>
+      <c r="N17" s="2" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="1" t="n"/>
+      <c r="C18" s="1" t="n"/>
+      <c r="D18" s="1" t="n"/>
+      <c r="E18" s="1" t="n"/>
+      <c r="F18" s="1" t="n"/>
+      <c r="H18" s="2" t="n"/>
+      <c r="I18" s="2" t="n"/>
+      <c r="J18" s="2" t="n"/>
+      <c r="K18" s="2" t="n"/>
+      <c r="L18" s="2" t="n"/>
+      <c r="N18" s="2" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n"/>
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="n"/>
+      <c r="H19" s="2" t="n"/>
+      <c r="I19" s="2" t="n"/>
+      <c r="J19" s="2" t="n"/>
+      <c r="K19" s="2" t="n"/>
+      <c r="L19" s="2" t="n"/>
+      <c r="N19" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2950,7 +3131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2989,77 +3170,81 @@
       <c r="O1" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+      <c r="A2" s="1" t="inlineStr"/>
+      <c r="B2" s="1" t="inlineStr"/>
+      <c r="C2" s="1" t="inlineStr"/>
+      <c r="D2" s="1" t="inlineStr"/>
+      <c r="E2" s="1" t="inlineStr"/>
+      <c r="F2" s="1" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2">
+        <f>(J2-L2)</f>
+        <v/>
+      </c>
+      <c r="L2" s="2">
+        <f>COUNTIF($B$2:$F$19,H2)</f>
+        <v/>
+      </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr"/>
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Martes</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Miercoles</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>Jueves</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Viernes</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Abrev</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Asignaturas</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Frec</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Faltan</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Asignadas</t>
-        </is>
+      <c r="K3" s="2">
+        <f>(J3-L3)</f>
+        <v/>
+      </c>
+      <c r="L3" s="2">
+        <f>COUNTIF($B$2:$F$19,H3)</f>
+        <v/>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>Aulas</t>
         </is>
@@ -3088,17 +3273,15 @@
           <t>Aprendizaje de Máquinas</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J4" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K4" s="2">
         <f>(J4-L4)</f>
         <v/>
       </c>
       <c r="L4" s="2">
-        <f>COUNTIF($B$4:$F$15,H4)</f>
+        <f>COUNTIF($B$2:$F$19,H4)</f>
         <v/>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -3127,17 +3310,15 @@
           <t>Diseño y Análisis de Algoritmos</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J5" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K5" s="2">
         <f>(J5-L5)</f>
         <v/>
       </c>
       <c r="L5" s="2">
-        <f>COUNTIF($B$4:$F$15,H5)</f>
+        <f>COUNTIF($B$2:$F$19,H5)</f>
         <v/>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -3170,17 +3351,15 @@
           <t>Sistemas Distribuidos</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J6" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K6" s="2">
         <f>(J6-L6)</f>
         <v/>
       </c>
       <c r="L6" s="2">
-        <f>COUNTIF($B$4:$F$15,H6)</f>
+        <f>COUNTIF($B$2:$F$19,H6)</f>
         <v/>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -3209,17 +3388,15 @@
           <t>Asignatura Electiva</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J7" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K7" s="2">
         <f>(J7-L7)</f>
         <v/>
       </c>
       <c r="L7" s="2">
-        <f>COUNTIF($B$4:$F$15,H7)</f>
+        <f>COUNTIF($B$2:$F$19,H7)</f>
         <v/>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -3252,17 +3429,15 @@
           <t>Estudios de Ciencia, Tecnología y Sociedad</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J8" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K8" s="2">
         <f>(J8-L8)</f>
         <v/>
       </c>
       <c r="L8" s="2">
-        <f>COUNTIF($B$4:$F$15,H8)</f>
+        <f>COUNTIF($B$2:$F$19,H8)</f>
         <v/>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -3291,17 +3466,15 @@
           <t>Seguridad Nacional / Defensa Nacionaol</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J9" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K9" s="2">
         <f>(J9-L9)</f>
         <v/>
       </c>
       <c r="L9" s="2">
-        <f>COUNTIF($B$4:$F$15,H9)</f>
+        <f>COUNTIF($B$2:$F$19,H9)</f>
         <v/>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -3339,8 +3512,14 @@
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr"/>
+      <c r="K10" s="2">
+        <f>(J10-L10)</f>
+        <v/>
+      </c>
+      <c r="L10" s="2">
+        <f>COUNTIF($B$2:$F$19,H10)</f>
+        <v/>
+      </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -3487,24 +3666,74 @@
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
+      <c r="A16" s="1" t="n"/>
+      <c r="B16" s="1" t="n"/>
+      <c r="C16" s="1" t="n"/>
+      <c r="D16" s="1" t="n"/>
+      <c r="E16" s="1" t="n"/>
+      <c r="F16" s="1" t="n"/>
       <c r="G16">
         <f>"Total:"</f>
         <v/>
       </c>
-      <c r="H16">
-        <f>COUNTA($H$4:$H$15)</f>
-        <v/>
-      </c>
+      <c r="H16" s="2">
+        <f>COUNTA($H$2:$H$19)</f>
+        <v/>
+      </c>
+      <c r="I16" s="2" t="n"/>
+      <c r="J16" s="2" t="n"/>
+      <c r="K16" s="2" t="n"/>
+      <c r="L16" s="2" t="n"/>
+      <c r="N16" s="2" t="n"/>
     </row>
     <row r="17">
-      <c r="F17">
+      <c r="A17" s="3" t="n"/>
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3" t="n"/>
+      <c r="F17" s="3">
         <f>"Σ Frec:"</f>
         <v/>
       </c>
       <c r="G17">
-        <f>SUM($J$4:$J$15)</f>
-        <v/>
-      </c>
+        <f>SUM($J$2:$J$19)</f>
+        <v/>
+      </c>
+      <c r="H17" s="2" t="n"/>
+      <c r="I17" s="2" t="n"/>
+      <c r="J17" s="2" t="n"/>
+      <c r="K17" s="2" t="n"/>
+      <c r="L17" s="2" t="n"/>
+      <c r="N17" s="2" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="1" t="n"/>
+      <c r="C18" s="1" t="n"/>
+      <c r="D18" s="1" t="n"/>
+      <c r="E18" s="1" t="n"/>
+      <c r="F18" s="1" t="n"/>
+      <c r="H18" s="2" t="n"/>
+      <c r="I18" s="2" t="n"/>
+      <c r="J18" s="2" t="n"/>
+      <c r="K18" s="2" t="n"/>
+      <c r="L18" s="2" t="n"/>
+      <c r="N18" s="2" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n"/>
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="n"/>
+      <c r="H19" s="2" t="n"/>
+      <c r="I19" s="2" t="n"/>
+      <c r="J19" s="2" t="n"/>
+      <c r="K19" s="2" t="n"/>
+      <c r="L19" s="2" t="n"/>
+      <c r="N19" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3517,7 +3746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3556,77 +3785,81 @@
       <c r="O1" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+      <c r="A2" s="1" t="inlineStr"/>
+      <c r="B2" s="1" t="inlineStr"/>
+      <c r="C2" s="1" t="inlineStr"/>
+      <c r="D2" s="1" t="inlineStr"/>
+      <c r="E2" s="1" t="inlineStr"/>
+      <c r="F2" s="1" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2">
+        <f>(J2-L2)</f>
+        <v/>
+      </c>
+      <c r="L2" s="2">
+        <f>COUNTIF($B$2:$F$19,H2)</f>
+        <v/>
+      </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr"/>
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Martes</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Miercoles</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>Jueves</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Viernes</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Abrev</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Asignaturas</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Frec</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Faltan</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Asignadas</t>
-        </is>
+      <c r="K3" s="2">
+        <f>(J3-L3)</f>
+        <v/>
+      </c>
+      <c r="L3" s="2">
+        <f>COUNTIF($B$2:$F$19,H3)</f>
+        <v/>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>Aulas</t>
         </is>
@@ -3675,17 +3908,15 @@
           <t>Introducción al Análisis Matemático</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="J4" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="K4" s="2">
         <f>(J4-L4)</f>
         <v/>
       </c>
       <c r="L4" s="2">
-        <f>COUNTIF($B$4:$F$15,H4)</f>
+        <f>COUNTIF($B$2:$F$19,H4)</f>
         <v/>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -3734,17 +3965,15 @@
           <t>Introducción al Álgebra</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="J5" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="K5" s="2">
         <f>(J5-L5)</f>
         <v/>
       </c>
       <c r="L5" s="2">
-        <f>COUNTIF($B$4:$F$15,H5)</f>
+        <f>COUNTIF($B$2:$F$19,H5)</f>
         <v/>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -3797,17 +4026,15 @@
           <t>Geometría Analítica</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J6" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K6" s="2">
         <f>(J6-L6)</f>
         <v/>
       </c>
       <c r="L6" s="2">
-        <f>COUNTIF($B$4:$F$15,H6)</f>
+        <f>COUNTIF($B$2:$F$19,H6)</f>
         <v/>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -3856,17 +4083,15 @@
           <t>Programación y Algoritmos</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J7" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K7" s="2">
         <f>(J7-L7)</f>
         <v/>
       </c>
       <c r="L7" s="2">
-        <f>COUNTIF($B$4:$F$15,H7)</f>
+        <f>COUNTIF($B$2:$F$19,H7)</f>
         <v/>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -3915,17 +4140,15 @@
           <t>Introducción a la Matemática</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J8" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K8" s="2">
         <f>(J8-L8)</f>
         <v/>
       </c>
       <c r="L8" s="2">
-        <f>COUNTIF($B$4:$F$15,H8)</f>
+        <f>COUNTIF($B$2:$F$19,H8)</f>
         <v/>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -3966,17 +4189,15 @@
           <t>Filosofía</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J9" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K9" s="2">
         <f>(J9-L9)</f>
         <v/>
       </c>
       <c r="L9" s="2">
-        <f>COUNTIF($B$4:$F$15,H9)</f>
+        <f>COUNTIF($B$2:$F$19,H9)</f>
         <v/>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -4002,8 +4223,14 @@
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr"/>
+      <c r="K10" s="2">
+        <f>(J10-L10)</f>
+        <v/>
+      </c>
+      <c r="L10" s="2">
+        <f>COUNTIF($B$2:$F$19,H10)</f>
+        <v/>
+      </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr">
         <is>
@@ -4126,26 +4353,26 @@
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
+      <c r="A16" s="1" t="inlineStr"/>
+      <c r="B16" s="1" t="inlineStr"/>
+      <c r="C16" s="1" t="inlineStr"/>
+      <c r="D16" s="1" t="inlineStr"/>
+      <c r="E16" s="1" t="inlineStr"/>
+      <c r="F16" s="1" t="inlineStr"/>
       <c r="G16">
         <f>"Total:"</f>
         <v/>
       </c>
-      <c r="H16">
-        <f>COUNTA($H$4:$H$15)</f>
-        <v/>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+      <c r="H16" s="2">
+        <f>COUNTA($H$2:$H$19)</f>
+        <v/>
+      </c>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>Aula 8</t>
         </is>
@@ -4153,14 +4380,53 @@
       <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="F17">
+      <c r="A17" s="3" t="n"/>
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3" t="n"/>
+      <c r="F17" s="3">
         <f>"Σ Frec:"</f>
         <v/>
       </c>
       <c r="G17">
-        <f>SUM($J$4:$J$15)</f>
-        <v/>
-      </c>
+        <f>SUM($J$2:$J$19)</f>
+        <v/>
+      </c>
+      <c r="H17" s="2" t="n"/>
+      <c r="I17" s="2" t="n"/>
+      <c r="J17" s="2" t="n"/>
+      <c r="K17" s="2" t="n"/>
+      <c r="L17" s="2" t="n"/>
+      <c r="N17" s="2" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="1" t="n"/>
+      <c r="C18" s="1" t="n"/>
+      <c r="D18" s="1" t="n"/>
+      <c r="E18" s="1" t="n"/>
+      <c r="F18" s="1" t="n"/>
+      <c r="H18" s="2" t="n"/>
+      <c r="I18" s="2" t="n"/>
+      <c r="J18" s="2" t="n"/>
+      <c r="K18" s="2" t="n"/>
+      <c r="L18" s="2" t="n"/>
+      <c r="N18" s="2" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n"/>
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="n"/>
+      <c r="H19" s="2" t="n"/>
+      <c r="I19" s="2" t="n"/>
+      <c r="J19" s="2" t="n"/>
+      <c r="K19" s="2" t="n"/>
+      <c r="L19" s="2" t="n"/>
+      <c r="N19" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4173,7 +4439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4212,77 +4478,81 @@
       <c r="O1" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+      <c r="A2" s="1" t="inlineStr"/>
+      <c r="B2" s="1" t="inlineStr"/>
+      <c r="C2" s="1" t="inlineStr"/>
+      <c r="D2" s="1" t="inlineStr"/>
+      <c r="E2" s="1" t="inlineStr"/>
+      <c r="F2" s="1" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2">
+        <f>(J2-L2)</f>
+        <v/>
+      </c>
+      <c r="L2" s="2">
+        <f>COUNTIF($B$2:$F$19,H2)</f>
+        <v/>
+      </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr"/>
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Martes</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Miercoles</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>Jueves</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Viernes</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Abrev</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Asignaturas</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Frec</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Faltan</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Asignadas</t>
-        </is>
+      <c r="K3" s="2">
+        <f>(J3-L3)</f>
+        <v/>
+      </c>
+      <c r="L3" s="2">
+        <f>COUNTIF($B$2:$F$19,H3)</f>
+        <v/>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>Aulas</t>
         </is>
@@ -4311,17 +4581,15 @@
           <t>Funciones de Varias Variables</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="J4" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="K4" s="2">
         <f>(J4-L4)</f>
         <v/>
       </c>
       <c r="L4" s="2">
-        <f>COUNTIF($B$4:$F$15,H4)</f>
+        <f>COUNTIF($B$2:$F$19,H4)</f>
         <v/>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -4350,17 +4618,15 @@
           <t>Complementos de Álgebra Lineal</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="J5" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="K5" s="2">
         <f>(J5-L5)</f>
         <v/>
       </c>
       <c r="L5" s="2">
-        <f>COUNTIF($B$4:$F$15,H5)</f>
+        <f>COUNTIF($B$2:$F$19,H5)</f>
         <v/>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -4393,17 +4659,15 @@
           <t>Seminario de Problemas II</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J6" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K6" s="2">
         <f>(J6-L6)</f>
         <v/>
       </c>
       <c r="L6" s="2">
-        <f>COUNTIF($B$4:$F$15,H6)</f>
+        <f>COUNTIF($B$2:$F$19,H6)</f>
         <v/>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -4432,17 +4696,15 @@
           <t>Asignatura Electiva I</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J7" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K7" s="2">
         <f>(J7-L7)</f>
         <v/>
       </c>
       <c r="L7" s="2">
-        <f>COUNTIF($B$4:$F$15,H7)</f>
+        <f>COUNTIF($B$2:$F$19,H7)</f>
         <v/>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -4483,17 +4745,15 @@
           <t>Economía Política</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J8" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K8" s="2">
         <f>(J8-L8)</f>
         <v/>
       </c>
       <c r="L8" s="2">
-        <f>COUNTIF($B$4:$F$15,H8)</f>
+        <f>COUNTIF($B$2:$F$19,H8)</f>
         <v/>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -4530,17 +4790,15 @@
           <t>Educación Física III</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J9" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K9" s="2">
         <f>(J9-L9)</f>
         <v/>
       </c>
       <c r="L9" s="2">
-        <f>COUNTIF($B$4:$F$15,H9)</f>
+        <f>COUNTIF($B$2:$F$19,H9)</f>
         <v/>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -4582,8 +4840,14 @@
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr"/>
+      <c r="K10" s="2">
+        <f>(J10-L10)</f>
+        <v/>
+      </c>
+      <c r="L10" s="2">
+        <f>COUNTIF($B$2:$F$19,H10)</f>
+        <v/>
+      </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr">
         <is>
@@ -4750,24 +5014,74 @@
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
+      <c r="A16" s="1" t="n"/>
+      <c r="B16" s="1" t="n"/>
+      <c r="C16" s="1" t="n"/>
+      <c r="D16" s="1" t="n"/>
+      <c r="E16" s="1" t="n"/>
+      <c r="F16" s="1" t="n"/>
       <c r="G16">
         <f>"Total:"</f>
         <v/>
       </c>
-      <c r="H16">
-        <f>COUNTA($H$4:$H$15)</f>
-        <v/>
-      </c>
+      <c r="H16" s="2">
+        <f>COUNTA($H$2:$H$19)</f>
+        <v/>
+      </c>
+      <c r="I16" s="2" t="n"/>
+      <c r="J16" s="2" t="n"/>
+      <c r="K16" s="2" t="n"/>
+      <c r="L16" s="2" t="n"/>
+      <c r="N16" s="2" t="n"/>
     </row>
     <row r="17">
-      <c r="F17">
+      <c r="A17" s="3" t="n"/>
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3" t="n"/>
+      <c r="F17" s="3">
         <f>"Σ Frec:"</f>
         <v/>
       </c>
       <c r="G17">
-        <f>SUM($J$4:$J$15)</f>
-        <v/>
-      </c>
+        <f>SUM($J$2:$J$19)</f>
+        <v/>
+      </c>
+      <c r="H17" s="2" t="n"/>
+      <c r="I17" s="2" t="n"/>
+      <c r="J17" s="2" t="n"/>
+      <c r="K17" s="2" t="n"/>
+      <c r="L17" s="2" t="n"/>
+      <c r="N17" s="2" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="1" t="n"/>
+      <c r="C18" s="1" t="n"/>
+      <c r="D18" s="1" t="n"/>
+      <c r="E18" s="1" t="n"/>
+      <c r="F18" s="1" t="n"/>
+      <c r="H18" s="2" t="n"/>
+      <c r="I18" s="2" t="n"/>
+      <c r="J18" s="2" t="n"/>
+      <c r="K18" s="2" t="n"/>
+      <c r="L18" s="2" t="n"/>
+      <c r="N18" s="2" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n"/>
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="n"/>
+      <c r="H19" s="2" t="n"/>
+      <c r="I19" s="2" t="n"/>
+      <c r="J19" s="2" t="n"/>
+      <c r="K19" s="2" t="n"/>
+      <c r="L19" s="2" t="n"/>
+      <c r="N19" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4780,7 +5094,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4819,77 +5133,81 @@
       <c r="O1" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+      <c r="A2" s="1" t="inlineStr"/>
+      <c r="B2" s="1" t="inlineStr"/>
+      <c r="C2" s="1" t="inlineStr"/>
+      <c r="D2" s="1" t="inlineStr"/>
+      <c r="E2" s="1" t="inlineStr"/>
+      <c r="F2" s="1" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2">
+        <f>(J2-L2)</f>
+        <v/>
+      </c>
+      <c r="L2" s="2">
+        <f>COUNTIF($B$2:$F$19,H2)</f>
+        <v/>
+      </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr"/>
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Martes</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Miercoles</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>Jueves</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Viernes</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Abrev</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Asignaturas</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Frec</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Faltan</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Asignadas</t>
-        </is>
+      <c r="K3" s="2">
+        <f>(J3-L3)</f>
+        <v/>
+      </c>
+      <c r="L3" s="2">
+        <f>COUNTIF($B$2:$F$19,H3)</f>
+        <v/>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>Aulas</t>
         </is>
@@ -4938,17 +5256,15 @@
           <t>Funciones de variable Compleja</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J4" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K4" s="2">
         <f>(J4-L4)</f>
         <v/>
       </c>
       <c r="L4" s="2">
-        <f>COUNTIF($B$4:$F$15,H4)</f>
+        <f>COUNTIF($B$2:$F$19,H4)</f>
         <v/>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -4997,17 +5313,15 @@
           <t>Inferencia Estadística</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="J5" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="K5" s="2">
         <f>(J5-L5)</f>
         <v/>
       </c>
       <c r="L5" s="2">
-        <f>COUNTIF($B$4:$F$15,H5)</f>
+        <f>COUNTIF($B$2:$F$19,H5)</f>
         <v/>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -5060,17 +5374,15 @@
           <t>Ecuaciones Diferenciales Ordinarias</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="J6" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="K6" s="2">
         <f>(J6-L6)</f>
         <v/>
       </c>
       <c r="L6" s="2">
-        <f>COUNTIF($B$4:$F$15,H6)</f>
+        <f>COUNTIF($B$2:$F$19,H6)</f>
         <v/>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -5119,17 +5431,15 @@
           <t>Matemática Numérica</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J7" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K7" s="2">
         <f>(J7-L7)</f>
         <v/>
       </c>
       <c r="L7" s="2">
-        <f>COUNTIF($B$4:$F$15,H7)</f>
+        <f>COUNTIF($B$2:$F$19,H7)</f>
         <v/>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -5178,17 +5488,15 @@
           <t>Optimización Matemática I</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J8" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K8" s="2">
         <f>(J8-L8)</f>
         <v/>
       </c>
       <c r="L8" s="2">
-        <f>COUNTIF($B$4:$F$15,H8)</f>
+        <f>COUNTIF($B$2:$F$19,H8)</f>
         <v/>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -5233,17 +5541,15 @@
           <t>Teoría Política</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J9" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K9" s="2">
         <f>(J9-L9)</f>
         <v/>
       </c>
       <c r="L9" s="2">
-        <f>COUNTIF($B$4:$F$15,H9)</f>
+        <f>COUNTIF($B$2:$F$19,H9)</f>
         <v/>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -5269,8 +5575,14 @@
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr"/>
+      <c r="K10" s="2">
+        <f>(J10-L10)</f>
+        <v/>
+      </c>
+      <c r="L10" s="2">
+        <f>COUNTIF($B$2:$F$19,H10)</f>
+        <v/>
+      </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr">
         <is>
@@ -5393,26 +5705,26 @@
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
+      <c r="A16" s="1" t="inlineStr"/>
+      <c r="B16" s="1" t="inlineStr"/>
+      <c r="C16" s="1" t="inlineStr"/>
+      <c r="D16" s="1" t="inlineStr"/>
+      <c r="E16" s="1" t="inlineStr"/>
+      <c r="F16" s="1" t="inlineStr"/>
       <c r="G16">
         <f>"Total:"</f>
         <v/>
       </c>
-      <c r="H16">
-        <f>COUNTA($H$4:$H$15)</f>
-        <v/>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+      <c r="H16" s="2">
+        <f>COUNTA($H$2:$H$19)</f>
+        <v/>
+      </c>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>Aula 4</t>
         </is>
@@ -5420,31 +5732,59 @@
       <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17">
+      <c r="A17" s="3" t="inlineStr"/>
+      <c r="B17" s="3" t="inlineStr"/>
+      <c r="C17" s="3" t="inlineStr"/>
+      <c r="D17" s="3" t="inlineStr"/>
+      <c r="E17" s="3" t="inlineStr"/>
+      <c r="F17" s="3">
         <f>"Σ Frec:"</f>
         <v/>
       </c>
       <c r="G17">
-        <f>SUM($J$4:$J$15)</f>
-        <v/>
-      </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+        <f>SUM($J$2:$J$19)</f>
+        <v/>
+      </c>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>Aula 4</t>
         </is>
       </c>
       <c r="O17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="1" t="n"/>
+      <c r="C18" s="1" t="n"/>
+      <c r="D18" s="1" t="n"/>
+      <c r="E18" s="1" t="n"/>
+      <c r="F18" s="1" t="n"/>
+      <c r="H18" s="2" t="n"/>
+      <c r="I18" s="2" t="n"/>
+      <c r="J18" s="2" t="n"/>
+      <c r="K18" s="2" t="n"/>
+      <c r="L18" s="2" t="n"/>
+      <c r="N18" s="2" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n"/>
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="n"/>
+      <c r="H19" s="2" t="n"/>
+      <c r="I19" s="2" t="n"/>
+      <c r="J19" s="2" t="n"/>
+      <c r="K19" s="2" t="n"/>
+      <c r="L19" s="2" t="n"/>
+      <c r="N19" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5457,7 +5797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5496,77 +5836,81 @@
       <c r="O1" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+      <c r="A2" s="1" t="inlineStr"/>
+      <c r="B2" s="1" t="inlineStr"/>
+      <c r="C2" s="1" t="inlineStr"/>
+      <c r="D2" s="1" t="inlineStr"/>
+      <c r="E2" s="1" t="inlineStr"/>
+      <c r="F2" s="1" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2">
+        <f>(J2-L2)</f>
+        <v/>
+      </c>
+      <c r="L2" s="2">
+        <f>COUNTIF($B$2:$F$19,H2)</f>
+        <v/>
+      </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr"/>
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Martes</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Miercoles</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>Jueves</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Viernes</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Abrev</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Asignaturas</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Frec</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Faltan</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Asignadas</t>
-        </is>
+      <c r="K3" s="2">
+        <f>(J3-L3)</f>
+        <v/>
+      </c>
+      <c r="L3" s="2">
+        <f>COUNTIF($B$2:$F$19,H3)</f>
+        <v/>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>Aulas</t>
         </is>
@@ -5595,17 +5939,15 @@
           <t>Medida e Integración</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J4" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K4" s="2">
         <f>(J4-L4)</f>
         <v/>
       </c>
       <c r="L4" s="2">
-        <f>COUNTIF($B$4:$F$15,H4)</f>
+        <f>COUNTIF($B$2:$F$19,H4)</f>
         <v/>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -5634,17 +5976,15 @@
           <t>Geometría Diferencial</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J5" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K5" s="2">
         <f>(J5-L5)</f>
         <v/>
       </c>
       <c r="L5" s="2">
-        <f>COUNTIF($B$4:$F$15,H5)</f>
+        <f>COUNTIF($B$2:$F$19,H5)</f>
         <v/>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -5677,17 +6017,15 @@
           <t>Historia de la Matemática</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J6" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K6" s="2">
         <f>(J6-L6)</f>
         <v/>
       </c>
       <c r="L6" s="2">
-        <f>COUNTIF($B$4:$F$15,H6)</f>
+        <f>COUNTIF($B$2:$F$19,H6)</f>
         <v/>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -5716,17 +6054,15 @@
           <t>Estudios de Ciencia, Tecnología y Sociedad</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J7" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K7" s="2">
         <f>(J7-L7)</f>
         <v/>
       </c>
       <c r="L7" s="2">
-        <f>COUNTIF($B$4:$F$15,H7)</f>
+        <f>COUNTIF($B$2:$F$19,H7)</f>
         <v/>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -5759,17 +6095,15 @@
           <t>Asignatura Optativa II</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J8" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K8" s="2">
         <f>(J8-L8)</f>
         <v/>
       </c>
       <c r="L8" s="2">
-        <f>COUNTIF($B$4:$F$15,H8)</f>
+        <f>COUNTIF($B$2:$F$19,H8)</f>
         <v/>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -5798,17 +6132,15 @@
           <t>Asignatura Optativa III</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J9" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K9" s="2">
         <f>(J9-L9)</f>
         <v/>
       </c>
       <c r="L9" s="2">
-        <f>COUNTIF($B$4:$F$15,H9)</f>
+        <f>COUNTIF($B$2:$F$19,H9)</f>
         <v/>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -5850,8 +6182,14 @@
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr"/>
+      <c r="K10" s="2">
+        <f>(J10-L10)</f>
+        <v/>
+      </c>
+      <c r="L10" s="2">
+        <f>COUNTIF($B$2:$F$19,H10)</f>
+        <v/>
+      </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr">
         <is>
@@ -6030,24 +6368,74 @@
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
+      <c r="A16" s="1" t="n"/>
+      <c r="B16" s="1" t="n"/>
+      <c r="C16" s="1" t="n"/>
+      <c r="D16" s="1" t="n"/>
+      <c r="E16" s="1" t="n"/>
+      <c r="F16" s="1" t="n"/>
       <c r="G16">
         <f>"Total:"</f>
         <v/>
       </c>
-      <c r="H16">
-        <f>COUNTA($H$4:$H$15)</f>
-        <v/>
-      </c>
+      <c r="H16" s="2">
+        <f>COUNTA($H$2:$H$19)</f>
+        <v/>
+      </c>
+      <c r="I16" s="2" t="n"/>
+      <c r="J16" s="2" t="n"/>
+      <c r="K16" s="2" t="n"/>
+      <c r="L16" s="2" t="n"/>
+      <c r="N16" s="2" t="n"/>
     </row>
     <row r="17">
-      <c r="F17">
+      <c r="A17" s="3" t="n"/>
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3" t="n"/>
+      <c r="F17" s="3">
         <f>"Σ Frec:"</f>
         <v/>
       </c>
       <c r="G17">
-        <f>SUM($J$4:$J$15)</f>
-        <v/>
-      </c>
+        <f>SUM($J$2:$J$19)</f>
+        <v/>
+      </c>
+      <c r="H17" s="2" t="n"/>
+      <c r="I17" s="2" t="n"/>
+      <c r="J17" s="2" t="n"/>
+      <c r="K17" s="2" t="n"/>
+      <c r="L17" s="2" t="n"/>
+      <c r="N17" s="2" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="1" t="n"/>
+      <c r="C18" s="1" t="n"/>
+      <c r="D18" s="1" t="n"/>
+      <c r="E18" s="1" t="n"/>
+      <c r="F18" s="1" t="n"/>
+      <c r="H18" s="2" t="n"/>
+      <c r="I18" s="2" t="n"/>
+      <c r="J18" s="2" t="n"/>
+      <c r="K18" s="2" t="n"/>
+      <c r="L18" s="2" t="n"/>
+      <c r="N18" s="2" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n"/>
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="n"/>
+      <c r="H19" s="2" t="n"/>
+      <c r="I19" s="2" t="n"/>
+      <c r="J19" s="2" t="n"/>
+      <c r="K19" s="2" t="n"/>
+      <c r="L19" s="2" t="n"/>
+      <c r="N19" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6060,7 +6448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L39"/>
+  <dimension ref="A1:L40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6423,17 +6811,47 @@
       <c r="L7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="2">
+        <f>SUBSTITUTE(TRIM(IF(D111!$B$17="Aula 1",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$17="Aula 1",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$17="Aula 1",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$17="Aula 1",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$17="Aula 1",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$17="Aula 1",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$17="Aula 1",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$17="Aula 1",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$17="Aula 1",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$17="Aula 1",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$17="Aula 1",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$17="Aula 1",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$17="Aula 1",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$17="Aula 1",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$17="Aula 1",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$17="Aula 1",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$17="Aula 1",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="C8" s="2">
+        <f>SUBSTITUTE(TRIM(IF(D111!$B$17="Aula 2",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$17="Aula 2",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$17="Aula 2",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$17="Aula 2",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$17="Aula 2",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$17="Aula 2",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$17="Aula 2",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$17="Aula 2",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$17="Aula 2",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$17="Aula 2",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$17="Aula 2",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$17="Aula 2",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$17="Aula 2",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$17="Aula 2",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$17="Aula 2",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$17="Aula 2",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$17="Aula 2",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="D8" s="2">
+        <f>SUBSTITUTE(TRIM(IF(D111!$B$17="Aula 3",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$17="Aula 3",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$17="Aula 3",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$17="Aula 3",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$17="Aula 3",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$17="Aula 3",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$17="Aula 3",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$17="Aula 3",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$17="Aula 3",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$17="Aula 3",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$17="Aula 3",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$17="Aula 3",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$17="Aula 3",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$17="Aula 3",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$17="Aula 3",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$17="Aula 3",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$17="Aula 3",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="E8" s="2">
+        <f>SUBSTITUTE(TRIM(IF(D111!$B$17="Aula 4",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$17="Aula 4",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$17="Aula 4",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$17="Aula 4",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$17="Aula 4",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$17="Aula 4",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$17="Aula 4",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$17="Aula 4",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$17="Aula 4",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$17="Aula 4",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$17="Aula 4",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$17="Aula 4",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$17="Aula 4",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$17="Aula 4",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$17="Aula 4",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$17="Aula 4",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$17="Aula 4",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="F8" s="2">
+        <f>SUBSTITUTE(TRIM(IF(D111!$B$17="Aula 5",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$17="Aula 5",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$17="Aula 5",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$17="Aula 5",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$17="Aula 5",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$17="Aula 5",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$17="Aula 5",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$17="Aula 5",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$17="Aula 5",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$17="Aula 5",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$17="Aula 5",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$17="Aula 5",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$17="Aula 5",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$17="Aula 5",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$17="Aula 5",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$17="Aula 5",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$17="Aula 5",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="G8" s="2">
+        <f>SUBSTITUTE(TRIM(IF(D111!$B$17="Aula 6",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$17="Aula 6",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$17="Aula 6",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$17="Aula 6",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$17="Aula 6",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$17="Aula 6",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$17="Aula 6",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$17="Aula 6",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$17="Aula 6",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$17="Aula 6",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$17="Aula 6",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$17="Aula 6",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$17="Aula 6",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$17="Aula 6",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$17="Aula 6",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$17="Aula 6",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$17="Aula 6",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="H8" s="2">
+        <f>SUBSTITUTE(TRIM(IF(D111!$B$17="Aula 7",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$17="Aula 7",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$17="Aula 7",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$17="Aula 7",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$17="Aula 7",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$17="Aula 7",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$17="Aula 7",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$17="Aula 7",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$17="Aula 7",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$17="Aula 7",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$17="Aula 7",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$17="Aula 7",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$17="Aula 7",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$17="Aula 7",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$17="Aula 7",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$17="Aula 7",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$17="Aula 7",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="I8" s="2">
+        <f>SUBSTITUTE(TRIM(IF(D111!$B$17="Aula 8",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$17="Aula 8",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$17="Aula 8",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$17="Aula 8",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$17="Aula 8",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$17="Aula 8",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$17="Aula 8",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$17="Aula 8",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$17="Aula 8",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$17="Aula 8",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$17="Aula 8",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$17="Aula 8",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$17="Aula 8",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$17="Aula 8",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$17="Aula 8",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$17="Aula 8",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$17="Aula 8",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="J8" s="2">
+        <f>SUBSTITUTE(TRIM(IF(D111!$B$17="Aula 9",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$17="Aula 9",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$17="Aula 9",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$17="Aula 9",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$17="Aula 9",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$17="Aula 9",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$17="Aula 9",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$17="Aula 9",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$17="Aula 9",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$17="Aula 9",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$17="Aula 9",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$17="Aula 9",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$17="Aula 9",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$17="Aula 9",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$17="Aula 9",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$17="Aula 9",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$17="Aula 9",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="K8" s="2">
+        <f>SUBSTITUTE(TRIM(IF(D111!$B$17="Lab",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$17="Lab",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$17="Lab",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$17="Lab",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$17="Lab",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$17="Lab",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$17="Lab",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$17="Lab",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$17="Lab",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$17="Lab",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$17="Lab",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$17="Lab",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$17="Lab",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$17="Lab",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$17="Lab",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$17="Lab",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$17="Lab",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <v/>
+      </c>
       <c r="L8" t="inlineStr"/>
     </row>
     <row r="9">
@@ -6783,17 +7201,47 @@
       <c r="L15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2">
+        <f>SUBSTITUTE(TRIM(IF(D111!$C$17="Aula 1",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$17="Aula 1",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$17="Aula 1",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$17="Aula 1",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$17="Aula 1",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$17="Aula 1",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$17="Aula 1",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$17="Aula 1",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$17="Aula 1",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$17="Aula 1",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$17="Aula 1",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$17="Aula 1",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$17="Aula 1",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$17="Aula 1",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$17="Aula 1",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$17="Aula 1",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$17="Aula 1",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="C16" s="2">
+        <f>SUBSTITUTE(TRIM(IF(D111!$C$17="Aula 2",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$17="Aula 2",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$17="Aula 2",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$17="Aula 2",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$17="Aula 2",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$17="Aula 2",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$17="Aula 2",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$17="Aula 2",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$17="Aula 2",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$17="Aula 2",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$17="Aula 2",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$17="Aula 2",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$17="Aula 2",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$17="Aula 2",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$17="Aula 2",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$17="Aula 2",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$17="Aula 2",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="D16" s="2">
+        <f>SUBSTITUTE(TRIM(IF(D111!$C$17="Aula 3",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$17="Aula 3",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$17="Aula 3",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$17="Aula 3",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$17="Aula 3",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$17="Aula 3",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$17="Aula 3",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$17="Aula 3",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$17="Aula 3",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$17="Aula 3",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$17="Aula 3",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$17="Aula 3",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$17="Aula 3",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$17="Aula 3",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$17="Aula 3",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$17="Aula 3",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$17="Aula 3",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="E16" s="2">
+        <f>SUBSTITUTE(TRIM(IF(D111!$C$17="Aula 4",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$17="Aula 4",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$17="Aula 4",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$17="Aula 4",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$17="Aula 4",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$17="Aula 4",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$17="Aula 4",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$17="Aula 4",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$17="Aula 4",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$17="Aula 4",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$17="Aula 4",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$17="Aula 4",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$17="Aula 4",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$17="Aula 4",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$17="Aula 4",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$17="Aula 4",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$17="Aula 4",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="F16" s="2">
+        <f>SUBSTITUTE(TRIM(IF(D111!$C$17="Aula 5",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$17="Aula 5",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$17="Aula 5",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$17="Aula 5",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$17="Aula 5",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$17="Aula 5",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$17="Aula 5",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$17="Aula 5",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$17="Aula 5",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$17="Aula 5",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$17="Aula 5",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$17="Aula 5",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$17="Aula 5",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$17="Aula 5",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$17="Aula 5",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$17="Aula 5",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$17="Aula 5",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="G16" s="2">
+        <f>SUBSTITUTE(TRIM(IF(D111!$C$17="Aula 6",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$17="Aula 6",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$17="Aula 6",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$17="Aula 6",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$17="Aula 6",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$17="Aula 6",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$17="Aula 6",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$17="Aula 6",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$17="Aula 6",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$17="Aula 6",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$17="Aula 6",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$17="Aula 6",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$17="Aula 6",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$17="Aula 6",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$17="Aula 6",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$17="Aula 6",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$17="Aula 6",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="H16" s="2">
+        <f>SUBSTITUTE(TRIM(IF(D111!$C$17="Aula 7",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$17="Aula 7",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$17="Aula 7",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$17="Aula 7",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$17="Aula 7",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$17="Aula 7",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$17="Aula 7",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$17="Aula 7",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$17="Aula 7",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$17="Aula 7",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$17="Aula 7",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$17="Aula 7",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$17="Aula 7",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$17="Aula 7",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$17="Aula 7",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$17="Aula 7",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$17="Aula 7",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="I16" s="2">
+        <f>SUBSTITUTE(TRIM(IF(D111!$C$17="Aula 8",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$17="Aula 8",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$17="Aula 8",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$17="Aula 8",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$17="Aula 8",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$17="Aula 8",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$17="Aula 8",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$17="Aula 8",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$17="Aula 8",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$17="Aula 8",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$17="Aula 8",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$17="Aula 8",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$17="Aula 8",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$17="Aula 8",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$17="Aula 8",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$17="Aula 8",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$17="Aula 8",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="J16" s="2">
+        <f>SUBSTITUTE(TRIM(IF(D111!$C$17="Aula 9",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$17="Aula 9",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$17="Aula 9",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$17="Aula 9",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$17="Aula 9",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$17="Aula 9",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$17="Aula 9",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$17="Aula 9",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$17="Aula 9",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$17="Aula 9",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$17="Aula 9",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$17="Aula 9",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$17="Aula 9",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$17="Aula 9",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$17="Aula 9",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$17="Aula 9",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$17="Aula 9",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="K16" s="2">
+        <f>SUBSTITUTE(TRIM(IF(D111!$C$17="Lab",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$17="Lab",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$17="Lab",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$17="Lab",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$17="Lab",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$17="Lab",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$17="Lab",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$17="Lab",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$17="Lab",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$17="Lab",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$17="Lab",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$17="Lab",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$17="Lab",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$17="Lab",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$17="Lab",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$17="Lab",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$17="Lab",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <v/>
+      </c>
       <c r="L16" t="inlineStr"/>
     </row>
     <row r="17">
@@ -7143,17 +7591,47 @@
       <c r="L23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2">
+        <f>SUBSTITUTE(TRIM(IF(D111!$D$17="Aula 1",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$17="Aula 1",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$17="Aula 1",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$17="Aula 1",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$17="Aula 1",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$17="Aula 1",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$17="Aula 1",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$17="Aula 1",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$17="Aula 1",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$17="Aula 1",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$17="Aula 1",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$17="Aula 1",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$17="Aula 1",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$17="Aula 1",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$17="Aula 1",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$17="Aula 1",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$17="Aula 1",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="C24" s="2">
+        <f>SUBSTITUTE(TRIM(IF(D111!$D$17="Aula 2",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$17="Aula 2",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$17="Aula 2",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$17="Aula 2",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$17="Aula 2",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$17="Aula 2",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$17="Aula 2",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$17="Aula 2",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$17="Aula 2",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$17="Aula 2",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$17="Aula 2",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$17="Aula 2",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$17="Aula 2",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$17="Aula 2",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$17="Aula 2",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$17="Aula 2",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$17="Aula 2",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="D24" s="2">
+        <f>SUBSTITUTE(TRIM(IF(D111!$D$17="Aula 3",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$17="Aula 3",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$17="Aula 3",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$17="Aula 3",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$17="Aula 3",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$17="Aula 3",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$17="Aula 3",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$17="Aula 3",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$17="Aula 3",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$17="Aula 3",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$17="Aula 3",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$17="Aula 3",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$17="Aula 3",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$17="Aula 3",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$17="Aula 3",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$17="Aula 3",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$17="Aula 3",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="E24" s="2">
+        <f>SUBSTITUTE(TRIM(IF(D111!$D$17="Aula 4",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$17="Aula 4",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$17="Aula 4",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$17="Aula 4",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$17="Aula 4",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$17="Aula 4",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$17="Aula 4",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$17="Aula 4",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$17="Aula 4",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$17="Aula 4",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$17="Aula 4",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$17="Aula 4",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$17="Aula 4",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$17="Aula 4",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$17="Aula 4",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$17="Aula 4",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$17="Aula 4",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="F24" s="2">
+        <f>SUBSTITUTE(TRIM(IF(D111!$D$17="Aula 5",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$17="Aula 5",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$17="Aula 5",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$17="Aula 5",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$17="Aula 5",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$17="Aula 5",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$17="Aula 5",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$17="Aula 5",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$17="Aula 5",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$17="Aula 5",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$17="Aula 5",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$17="Aula 5",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$17="Aula 5",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$17="Aula 5",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$17="Aula 5",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$17="Aula 5",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$17="Aula 5",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="G24" s="2">
+        <f>SUBSTITUTE(TRIM(IF(D111!$D$17="Aula 6",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$17="Aula 6",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$17="Aula 6",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$17="Aula 6",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$17="Aula 6",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$17="Aula 6",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$17="Aula 6",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$17="Aula 6",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$17="Aula 6",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$17="Aula 6",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$17="Aula 6",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$17="Aula 6",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$17="Aula 6",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$17="Aula 6",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$17="Aula 6",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$17="Aula 6",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$17="Aula 6",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="H24" s="2">
+        <f>SUBSTITUTE(TRIM(IF(D111!$D$17="Aula 7",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$17="Aula 7",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$17="Aula 7",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$17="Aula 7",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$17="Aula 7",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$17="Aula 7",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$17="Aula 7",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$17="Aula 7",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$17="Aula 7",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$17="Aula 7",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$17="Aula 7",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$17="Aula 7",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$17="Aula 7",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$17="Aula 7",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$17="Aula 7",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$17="Aula 7",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$17="Aula 7",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="I24" s="2">
+        <f>SUBSTITUTE(TRIM(IF(D111!$D$17="Aula 8",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$17="Aula 8",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$17="Aula 8",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$17="Aula 8",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$17="Aula 8",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$17="Aula 8",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$17="Aula 8",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$17="Aula 8",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$17="Aula 8",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$17="Aula 8",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$17="Aula 8",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$17="Aula 8",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$17="Aula 8",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$17="Aula 8",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$17="Aula 8",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$17="Aula 8",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$17="Aula 8",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="J24" s="2">
+        <f>SUBSTITUTE(TRIM(IF(D111!$D$17="Aula 9",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$17="Aula 9",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$17="Aula 9",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$17="Aula 9",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$17="Aula 9",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$17="Aula 9",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$17="Aula 9",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$17="Aula 9",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$17="Aula 9",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$17="Aula 9",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$17="Aula 9",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$17="Aula 9",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$17="Aula 9",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$17="Aula 9",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$17="Aula 9",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$17="Aula 9",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$17="Aula 9",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="K24" s="2">
+        <f>SUBSTITUTE(TRIM(IF(D111!$D$17="Lab",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$17="Lab",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$17="Lab",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$17="Lab",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$17="Lab",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$17="Lab",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$17="Lab",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$17="Lab",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$17="Lab",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$17="Lab",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$17="Lab",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$17="Lab",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$17="Lab",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$17="Lab",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$17="Lab",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$17="Lab",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$17="Lab",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <v/>
+      </c>
       <c r="L24" t="inlineStr"/>
     </row>
     <row r="25">
@@ -7503,17 +7981,47 @@
       <c r="L31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2">
+        <f>SUBSTITUTE(TRIM(IF(D111!$E$17="Aula 1",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$17="Aula 1",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$17="Aula 1",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$17="Aula 1",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$17="Aula 1",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$17="Aula 1",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$17="Aula 1",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$17="Aula 1",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$17="Aula 1",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$17="Aula 1",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$17="Aula 1",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$17="Aula 1",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$17="Aula 1",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$17="Aula 1",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$17="Aula 1",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$17="Aula 1",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$17="Aula 1",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="C32" s="2">
+        <f>SUBSTITUTE(TRIM(IF(D111!$E$17="Aula 2",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$17="Aula 2",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$17="Aula 2",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$17="Aula 2",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$17="Aula 2",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$17="Aula 2",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$17="Aula 2",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$17="Aula 2",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$17="Aula 2",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$17="Aula 2",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$17="Aula 2",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$17="Aula 2",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$17="Aula 2",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$17="Aula 2",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$17="Aula 2",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$17="Aula 2",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$17="Aula 2",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="D32" s="2">
+        <f>SUBSTITUTE(TRIM(IF(D111!$E$17="Aula 3",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$17="Aula 3",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$17="Aula 3",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$17="Aula 3",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$17="Aula 3",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$17="Aula 3",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$17="Aula 3",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$17="Aula 3",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$17="Aula 3",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$17="Aula 3",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$17="Aula 3",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$17="Aula 3",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$17="Aula 3",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$17="Aula 3",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$17="Aula 3",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$17="Aula 3",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$17="Aula 3",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="E32" s="2">
+        <f>SUBSTITUTE(TRIM(IF(D111!$E$17="Aula 4",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$17="Aula 4",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$17="Aula 4",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$17="Aula 4",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$17="Aula 4",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$17="Aula 4",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$17="Aula 4",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$17="Aula 4",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$17="Aula 4",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$17="Aula 4",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$17="Aula 4",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$17="Aula 4",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$17="Aula 4",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$17="Aula 4",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$17="Aula 4",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$17="Aula 4",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$17="Aula 4",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="F32" s="2">
+        <f>SUBSTITUTE(TRIM(IF(D111!$E$17="Aula 5",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$17="Aula 5",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$17="Aula 5",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$17="Aula 5",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$17="Aula 5",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$17="Aula 5",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$17="Aula 5",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$17="Aula 5",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$17="Aula 5",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$17="Aula 5",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$17="Aula 5",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$17="Aula 5",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$17="Aula 5",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$17="Aula 5",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$17="Aula 5",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$17="Aula 5",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$17="Aula 5",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="G32" s="2">
+        <f>SUBSTITUTE(TRIM(IF(D111!$E$17="Aula 6",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$17="Aula 6",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$17="Aula 6",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$17="Aula 6",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$17="Aula 6",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$17="Aula 6",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$17="Aula 6",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$17="Aula 6",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$17="Aula 6",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$17="Aula 6",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$17="Aula 6",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$17="Aula 6",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$17="Aula 6",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$17="Aula 6",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$17="Aula 6",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$17="Aula 6",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$17="Aula 6",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="H32" s="2">
+        <f>SUBSTITUTE(TRIM(IF(D111!$E$17="Aula 7",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$17="Aula 7",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$17="Aula 7",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$17="Aula 7",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$17="Aula 7",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$17="Aula 7",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$17="Aula 7",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$17="Aula 7",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$17="Aula 7",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$17="Aula 7",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$17="Aula 7",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$17="Aula 7",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$17="Aula 7",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$17="Aula 7",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$17="Aula 7",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$17="Aula 7",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$17="Aula 7",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="I32" s="2">
+        <f>SUBSTITUTE(TRIM(IF(D111!$E$17="Aula 8",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$17="Aula 8",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$17="Aula 8",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$17="Aula 8",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$17="Aula 8",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$17="Aula 8",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$17="Aula 8",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$17="Aula 8",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$17="Aula 8",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$17="Aula 8",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$17="Aula 8",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$17="Aula 8",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$17="Aula 8",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$17="Aula 8",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$17="Aula 8",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$17="Aula 8",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$17="Aula 8",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="J32" s="2">
+        <f>SUBSTITUTE(TRIM(IF(D111!$E$17="Aula 9",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$17="Aula 9",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$17="Aula 9",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$17="Aula 9",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$17="Aula 9",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$17="Aula 9",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$17="Aula 9",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$17="Aula 9",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$17="Aula 9",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$17="Aula 9",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$17="Aula 9",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$17="Aula 9",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$17="Aula 9",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$17="Aula 9",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$17="Aula 9",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$17="Aula 9",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$17="Aula 9",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="K32" s="2">
+        <f>SUBSTITUTE(TRIM(IF(D111!$E$17="Lab",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$17="Lab",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$17="Lab",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$17="Lab",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$17="Lab",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$17="Lab",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$17="Lab",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$17="Lab",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$17="Lab",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$17="Lab",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$17="Lab",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$17="Lab",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$17="Lab",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$17="Lab",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$17="Lab",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$17="Lab",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$17="Lab",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <v/>
+      </c>
       <c r="L32" t="inlineStr"/>
     </row>
     <row r="33">
@@ -7861,6 +8369,49 @@
         <v/>
       </c>
       <c r="L39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n"/>
+      <c r="B40" s="2">
+        <f>SUBSTITUTE(TRIM(IF(D111!$F$17="Aula 1",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$17="Aula 1",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$17="Aula 1",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$17="Aula 1",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$17="Aula 1",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$17="Aula 1",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$17="Aula 1",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$17="Aula 1",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$17="Aula 1",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$17="Aula 1",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$17="Aula 1",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$17="Aula 1",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$17="Aula 1",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$17="Aula 1",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$17="Aula 1",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$17="Aula 1",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$17="Aula 1",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="C40" s="2">
+        <f>SUBSTITUTE(TRIM(IF(D111!$F$17="Aula 2",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$17="Aula 2",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$17="Aula 2",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$17="Aula 2",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$17="Aula 2",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$17="Aula 2",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$17="Aula 2",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$17="Aula 2",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$17="Aula 2",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$17="Aula 2",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$17="Aula 2",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$17="Aula 2",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$17="Aula 2",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$17="Aula 2",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$17="Aula 2",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$17="Aula 2",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$17="Aula 2",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="D40" s="2">
+        <f>SUBSTITUTE(TRIM(IF(D111!$F$17="Aula 3",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$17="Aula 3",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$17="Aula 3",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$17="Aula 3",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$17="Aula 3",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$17="Aula 3",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$17="Aula 3",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$17="Aula 3",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$17="Aula 3",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$17="Aula 3",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$17="Aula 3",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$17="Aula 3",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$17="Aula 3",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$17="Aula 3",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$17="Aula 3",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$17="Aula 3",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$17="Aula 3",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="E40" s="2">
+        <f>SUBSTITUTE(TRIM(IF(D111!$F$17="Aula 4",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$17="Aula 4",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$17="Aula 4",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$17="Aula 4",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$17="Aula 4",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$17="Aula 4",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$17="Aula 4",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$17="Aula 4",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$17="Aula 4",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$17="Aula 4",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$17="Aula 4",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$17="Aula 4",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$17="Aula 4",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$17="Aula 4",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$17="Aula 4",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$17="Aula 4",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$17="Aula 4",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="F40" s="2">
+        <f>SUBSTITUTE(TRIM(IF(D111!$F$17="Aula 5",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$17="Aula 5",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$17="Aula 5",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$17="Aula 5",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$17="Aula 5",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$17="Aula 5",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$17="Aula 5",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$17="Aula 5",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$17="Aula 5",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$17="Aula 5",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$17="Aula 5",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$17="Aula 5",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$17="Aula 5",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$17="Aula 5",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$17="Aula 5",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$17="Aula 5",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$17="Aula 5",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="G40" s="2">
+        <f>SUBSTITUTE(TRIM(IF(D111!$F$17="Aula 6",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$17="Aula 6",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$17="Aula 6",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$17="Aula 6",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$17="Aula 6",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$17="Aula 6",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$17="Aula 6",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$17="Aula 6",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$17="Aula 6",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$17="Aula 6",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$17="Aula 6",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$17="Aula 6",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$17="Aula 6",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$17="Aula 6",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$17="Aula 6",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$17="Aula 6",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$17="Aula 6",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="H40" s="2">
+        <f>SUBSTITUTE(TRIM(IF(D111!$F$17="Aula 7",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$17="Aula 7",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$17="Aula 7",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$17="Aula 7",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$17="Aula 7",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$17="Aula 7",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$17="Aula 7",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$17="Aula 7",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$17="Aula 7",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$17="Aula 7",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$17="Aula 7",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$17="Aula 7",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$17="Aula 7",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$17="Aula 7",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$17="Aula 7",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$17="Aula 7",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$17="Aula 7",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="I40" s="2">
+        <f>SUBSTITUTE(TRIM(IF(D111!$F$17="Aula 8",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$17="Aula 8",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$17="Aula 8",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$17="Aula 8",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$17="Aula 8",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$17="Aula 8",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$17="Aula 8",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$17="Aula 8",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$17="Aula 8",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$17="Aula 8",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$17="Aula 8",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$17="Aula 8",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$17="Aula 8",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$17="Aula 8",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$17="Aula 8",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$17="Aula 8",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$17="Aula 8",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="J40" s="2">
+        <f>SUBSTITUTE(TRIM(IF(D111!$F$17="Aula 9",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$17="Aula 9",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$17="Aula 9",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$17="Aula 9",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$17="Aula 9",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$17="Aula 9",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$17="Aula 9",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$17="Aula 9",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$17="Aula 9",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$17="Aula 9",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$17="Aula 9",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$17="Aula 9",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$17="Aula 9",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$17="Aula 9",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$17="Aula 9",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$17="Aula 9",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$17="Aula 9",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <v/>
+      </c>
+      <c r="K40" s="2">
+        <f>SUBSTITUTE(TRIM(IF(D111!$F$17="Lab",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$17="Lab",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$17="Lab",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$17="Lab",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$17="Lab",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$17="Lab",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$17="Lab",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$17="Lab",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$17="Lab",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$17="Lab",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$17="Lab",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$17="Lab",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$17="Lab",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$17="Lab",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$17="Lab",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$17="Lab",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$17="Lab",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7873,7 +8424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7912,77 +8463,81 @@
       <c r="O1" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+      <c r="A2" s="1" t="inlineStr"/>
+      <c r="B2" s="1" t="inlineStr"/>
+      <c r="C2" s="1" t="inlineStr"/>
+      <c r="D2" s="1" t="inlineStr"/>
+      <c r="E2" s="1" t="inlineStr"/>
+      <c r="F2" s="1" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2">
+        <f>(J2-L2)</f>
+        <v/>
+      </c>
+      <c r="L2" s="2">
+        <f>COUNTIF($B$2:$F$19,H2)</f>
+        <v/>
+      </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr"/>
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Martes</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Miercoles</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>Jueves</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Viernes</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Abrev</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Asignaturas</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Frec</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Faltan</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Asignadas</t>
-        </is>
+      <c r="K3" s="2">
+        <f>(J3-L3)</f>
+        <v/>
+      </c>
+      <c r="L3" s="2">
+        <f>COUNTIF($B$2:$F$19,H3)</f>
+        <v/>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>Aulas</t>
         </is>
@@ -8011,17 +8566,15 @@
           <t>Matemática y Aplicaciones</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J4" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K4" s="2">
         <f>(J4-L4)</f>
         <v/>
       </c>
       <c r="L4" s="2">
-        <f>COUNTIF($B$4:$F$15,H4)</f>
+        <f>COUNTIF($B$2:$F$19,H4)</f>
         <v/>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -8050,17 +8603,15 @@
           <t>Probabilidades</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J5" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K5" s="2">
         <f>(J5-L5)</f>
         <v/>
       </c>
       <c r="L5" s="2">
-        <f>COUNTIF($B$4:$F$15,H5)</f>
+        <f>COUNTIF($B$2:$F$19,H5)</f>
         <v/>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -8093,17 +8644,15 @@
           <t>Bases de Datos</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J6" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K6" s="2">
         <f>(J6-L6)</f>
         <v/>
       </c>
       <c r="L6" s="2">
-        <f>COUNTIF($B$4:$F$15,H6)</f>
+        <f>COUNTIF($B$2:$F$19,H6)</f>
         <v/>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -8132,17 +8681,15 @@
           <t>Estructura de Datos</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J7" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K7" s="2">
         <f>(J7-L7)</f>
         <v/>
       </c>
       <c r="L7" s="2">
-        <f>COUNTIF($B$4:$F$15,H7)</f>
+        <f>COUNTIF($B$2:$F$19,H7)</f>
         <v/>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -8175,17 +8722,15 @@
           <t>Visualización de Datos</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J8" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K8" s="2">
         <f>(J8-L8)</f>
         <v/>
       </c>
       <c r="L8" s="2">
-        <f>COUNTIF($B$4:$F$15,H8)</f>
+        <f>COUNTIF($B$2:$F$19,H8)</f>
         <v/>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -8214,17 +8759,15 @@
           <t>Economía Política</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J9" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K9" s="2">
         <f>(J9-L9)</f>
         <v/>
       </c>
       <c r="L9" s="2">
-        <f>COUNTIF($B$4:$F$15,H9)</f>
+        <f>COUNTIF($B$2:$F$19,H9)</f>
         <v/>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -8266,8 +8809,14 @@
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr"/>
+      <c r="K10" s="2">
+        <f>(J10-L10)</f>
+        <v/>
+      </c>
+      <c r="L10" s="2">
+        <f>COUNTIF($B$2:$F$19,H10)</f>
+        <v/>
+      </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr">
         <is>
@@ -8462,24 +9011,74 @@
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
+      <c r="A16" s="1" t="n"/>
+      <c r="B16" s="1" t="n"/>
+      <c r="C16" s="1" t="n"/>
+      <c r="D16" s="1" t="n"/>
+      <c r="E16" s="1" t="n"/>
+      <c r="F16" s="1" t="n"/>
       <c r="G16">
         <f>"Total:"</f>
         <v/>
       </c>
-      <c r="H16">
-        <f>COUNTA($H$4:$H$15)</f>
-        <v/>
-      </c>
+      <c r="H16" s="2">
+        <f>COUNTA($H$2:$H$19)</f>
+        <v/>
+      </c>
+      <c r="I16" s="2" t="n"/>
+      <c r="J16" s="2" t="n"/>
+      <c r="K16" s="2" t="n"/>
+      <c r="L16" s="2" t="n"/>
+      <c r="N16" s="2" t="n"/>
     </row>
     <row r="17">
-      <c r="F17">
+      <c r="A17" s="3" t="n"/>
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3" t="n"/>
+      <c r="F17" s="3">
         <f>"Σ Frec:"</f>
         <v/>
       </c>
       <c r="G17">
-        <f>SUM($J$4:$J$15)</f>
-        <v/>
-      </c>
+        <f>SUM($J$2:$J$19)</f>
+        <v/>
+      </c>
+      <c r="H17" s="2" t="n"/>
+      <c r="I17" s="2" t="n"/>
+      <c r="J17" s="2" t="n"/>
+      <c r="K17" s="2" t="n"/>
+      <c r="L17" s="2" t="n"/>
+      <c r="N17" s="2" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="1" t="n"/>
+      <c r="C18" s="1" t="n"/>
+      <c r="D18" s="1" t="n"/>
+      <c r="E18" s="1" t="n"/>
+      <c r="F18" s="1" t="n"/>
+      <c r="H18" s="2" t="n"/>
+      <c r="I18" s="2" t="n"/>
+      <c r="J18" s="2" t="n"/>
+      <c r="K18" s="2" t="n"/>
+      <c r="L18" s="2" t="n"/>
+      <c r="N18" s="2" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n"/>
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="n"/>
+      <c r="H19" s="2" t="n"/>
+      <c r="I19" s="2" t="n"/>
+      <c r="J19" s="2" t="n"/>
+      <c r="K19" s="2" t="n"/>
+      <c r="L19" s="2" t="n"/>
+      <c r="N19" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8492,7 +9091,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8531,77 +9130,81 @@
       <c r="O1" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+      <c r="A2" s="1" t="inlineStr"/>
+      <c r="B2" s="1" t="inlineStr"/>
+      <c r="C2" s="1" t="inlineStr"/>
+      <c r="D2" s="1" t="inlineStr"/>
+      <c r="E2" s="1" t="inlineStr"/>
+      <c r="F2" s="1" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2">
+        <f>(J2-L2)</f>
+        <v/>
+      </c>
+      <c r="L2" s="2">
+        <f>COUNTIF($B$2:$F$19,H2)</f>
+        <v/>
+      </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr"/>
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Martes</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Miercoles</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>Jueves</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Viernes</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Abrev</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Asignaturas</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Frec</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Faltan</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Asignadas</t>
-        </is>
+      <c r="K3" s="2">
+        <f>(J3-L3)</f>
+        <v/>
+      </c>
+      <c r="L3" s="2">
+        <f>COUNTIF($B$2:$F$19,H3)</f>
+        <v/>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>Aulas</t>
         </is>
@@ -8642,17 +9245,15 @@
           <t>Análisis Estadístico II</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J4" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K4" s="2">
         <f>(J4-L4)</f>
         <v/>
       </c>
       <c r="L4" s="2">
-        <f>COUNTIF($B$4:$F$15,H4)</f>
+        <f>COUNTIF($B$2:$F$19,H4)</f>
         <v/>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -8689,17 +9290,15 @@
           <t>Muestreo y Diseño de Experimentos</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J5" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K5" s="2">
         <f>(J5-L5)</f>
         <v/>
       </c>
       <c r="L5" s="2">
-        <f>COUNTIF($B$4:$F$15,H5)</f>
+        <f>COUNTIF($B$2:$F$19,H5)</f>
         <v/>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -8748,17 +9347,15 @@
           <t>Redes Neuronales</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J6" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K6" s="2">
         <f>(J6-L6)</f>
         <v/>
       </c>
       <c r="L6" s="2">
-        <f>COUNTIF($B$4:$F$15,H6)</f>
+        <f>COUNTIF($B$2:$F$19,H6)</f>
         <v/>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -8803,17 +9400,15 @@
           <t>Procesamiento del Lenguaje</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J7" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K7" s="2">
         <f>(J7-L7)</f>
         <v/>
       </c>
       <c r="L7" s="2">
-        <f>COUNTIF($B$4:$F$15,H7)</f>
+        <f>COUNTIF($B$2:$F$19,H7)</f>
         <v/>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -8862,17 +9457,15 @@
           <t>Procesamiento de Grandes Volúmenes de Datos</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J8" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K8" s="2">
         <f>(J8-L8)</f>
         <v/>
       </c>
       <c r="L8" s="2">
-        <f>COUNTIF($B$4:$F$15,H8)</f>
+        <f>COUNTIF($B$2:$F$19,H8)</f>
         <v/>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -8917,17 +9510,15 @@
           <t>Teoría Política</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J9" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K9" s="2">
         <f>(J9-L9)</f>
         <v/>
       </c>
       <c r="L9" s="2">
-        <f>COUNTIF($B$4:$F$15,H9)</f>
+        <f>COUNTIF($B$2:$F$19,H9)</f>
         <v/>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -8953,8 +9544,14 @@
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr"/>
+      <c r="K10" s="2">
+        <f>(J10-L10)</f>
+        <v/>
+      </c>
+      <c r="L10" s="2">
+        <f>COUNTIF($B$2:$F$19,H10)</f>
+        <v/>
+      </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr">
         <is>
@@ -9069,24 +9666,74 @@
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
+      <c r="A16" s="1" t="n"/>
+      <c r="B16" s="1" t="n"/>
+      <c r="C16" s="1" t="n"/>
+      <c r="D16" s="1" t="n"/>
+      <c r="E16" s="1" t="n"/>
+      <c r="F16" s="1" t="n"/>
       <c r="G16">
         <f>"Total:"</f>
         <v/>
       </c>
-      <c r="H16">
-        <f>COUNTA($H$4:$H$15)</f>
-        <v/>
-      </c>
+      <c r="H16" s="2">
+        <f>COUNTA($H$2:$H$19)</f>
+        <v/>
+      </c>
+      <c r="I16" s="2" t="n"/>
+      <c r="J16" s="2" t="n"/>
+      <c r="K16" s="2" t="n"/>
+      <c r="L16" s="2" t="n"/>
+      <c r="N16" s="2" t="n"/>
     </row>
     <row r="17">
-      <c r="F17">
+      <c r="A17" s="3" t="n"/>
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3" t="n"/>
+      <c r="F17" s="3">
         <f>"Σ Frec:"</f>
         <v/>
       </c>
       <c r="G17">
-        <f>SUM($J$4:$J$15)</f>
-        <v/>
-      </c>
+        <f>SUM($J$2:$J$19)</f>
+        <v/>
+      </c>
+      <c r="H17" s="2" t="n"/>
+      <c r="I17" s="2" t="n"/>
+      <c r="J17" s="2" t="n"/>
+      <c r="K17" s="2" t="n"/>
+      <c r="L17" s="2" t="n"/>
+      <c r="N17" s="2" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="1" t="n"/>
+      <c r="C18" s="1" t="n"/>
+      <c r="D18" s="1" t="n"/>
+      <c r="E18" s="1" t="n"/>
+      <c r="F18" s="1" t="n"/>
+      <c r="H18" s="2" t="n"/>
+      <c r="I18" s="2" t="n"/>
+      <c r="J18" s="2" t="n"/>
+      <c r="K18" s="2" t="n"/>
+      <c r="L18" s="2" t="n"/>
+      <c r="N18" s="2" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n"/>
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="n"/>
+      <c r="H19" s="2" t="n"/>
+      <c r="I19" s="2" t="n"/>
+      <c r="J19" s="2" t="n"/>
+      <c r="K19" s="2" t="n"/>
+      <c r="L19" s="2" t="n"/>
+      <c r="N19" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9099,7 +9746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9138,77 +9785,81 @@
       <c r="O1" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+      <c r="A2" s="1" t="inlineStr"/>
+      <c r="B2" s="1" t="inlineStr"/>
+      <c r="C2" s="1" t="inlineStr"/>
+      <c r="D2" s="1" t="inlineStr"/>
+      <c r="E2" s="1" t="inlineStr"/>
+      <c r="F2" s="1" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2">
+        <f>(J2-L2)</f>
+        <v/>
+      </c>
+      <c r="L2" s="2">
+        <f>COUNTIF($B$2:$F$19,H2)</f>
+        <v/>
+      </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr"/>
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Martes</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Miercoles</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>Jueves</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Viernes</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Abrev</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Asignaturas</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Frec</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Faltan</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Asignadas</t>
-        </is>
+      <c r="K3" s="2">
+        <f>(J3-L3)</f>
+        <v/>
+      </c>
+      <c r="L3" s="2">
+        <f>COUNTIF($B$2:$F$19,H3)</f>
+        <v/>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>Aulas</t>
         </is>
@@ -9245,17 +9896,15 @@
           <t>Inteligencia de Negocios</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J4" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K4" s="2">
         <f>(J4-L4)</f>
         <v/>
       </c>
       <c r="L4" s="2">
-        <f>COUNTIF($B$4:$F$15,H4)</f>
+        <f>COUNTIF($B$2:$F$19,H4)</f>
         <v/>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -9300,17 +9949,15 @@
           <t>Elementos de Inteligencia Artificial</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J5" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K5" s="2">
         <f>(J5-L5)</f>
         <v/>
       </c>
       <c r="L5" s="2">
-        <f>COUNTIF($B$4:$F$15,H5)</f>
+        <f>COUNTIF($B$2:$F$19,H5)</f>
         <v/>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -9359,17 +10006,15 @@
           <t>Ciberseguridad y Privacidad</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J6" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K6" s="2">
         <f>(J6-L6)</f>
         <v/>
       </c>
       <c r="L6" s="2">
-        <f>COUNTIF($B$4:$F$15,H6)</f>
+        <f>COUNTIF($B$2:$F$19,H6)</f>
         <v/>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -9414,17 +10059,15 @@
           <t>Curso Optativo II</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J7" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K7" s="2">
         <f>(J7-L7)</f>
         <v/>
       </c>
       <c r="L7" s="2">
-        <f>COUNTIF($B$4:$F$15,H7)</f>
+        <f>COUNTIF($B$2:$F$19,H7)</f>
         <v/>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -9469,17 +10112,15 @@
           <t>Estudios de Ciencia, Tecnología y Sociedad</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J8" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K8" s="2">
         <f>(J8-L8)</f>
         <v/>
       </c>
       <c r="L8" s="2">
-        <f>COUNTIF($B$4:$F$15,H8)</f>
+        <f>COUNTIF($B$2:$F$19,H8)</f>
         <v/>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -9516,17 +10157,15 @@
           <t>Seguridad Nacional / Defensa Nacional</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J9" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K9" s="2">
         <f>(J9-L9)</f>
         <v/>
       </c>
       <c r="L9" s="2">
-        <f>COUNTIF($B$4:$F$15,H9)</f>
+        <f>COUNTIF($B$2:$F$19,H9)</f>
         <v/>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -9552,8 +10191,14 @@
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr"/>
+      <c r="K10" s="2">
+        <f>(J10-L10)</f>
+        <v/>
+      </c>
+      <c r="L10" s="2">
+        <f>COUNTIF($B$2:$F$19,H10)</f>
+        <v/>
+      </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr">
         <is>
@@ -9668,24 +10313,74 @@
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
+      <c r="A16" s="1" t="n"/>
+      <c r="B16" s="1" t="n"/>
+      <c r="C16" s="1" t="n"/>
+      <c r="D16" s="1" t="n"/>
+      <c r="E16" s="1" t="n"/>
+      <c r="F16" s="1" t="n"/>
       <c r="G16">
         <f>"Total:"</f>
         <v/>
       </c>
-      <c r="H16">
-        <f>COUNTA($H$4:$H$15)</f>
-        <v/>
-      </c>
+      <c r="H16" s="2">
+        <f>COUNTA($H$2:$H$19)</f>
+        <v/>
+      </c>
+      <c r="I16" s="2" t="n"/>
+      <c r="J16" s="2" t="n"/>
+      <c r="K16" s="2" t="n"/>
+      <c r="L16" s="2" t="n"/>
+      <c r="N16" s="2" t="n"/>
     </row>
     <row r="17">
-      <c r="F17">
+      <c r="A17" s="3" t="n"/>
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3" t="n"/>
+      <c r="F17" s="3">
         <f>"Σ Frec:"</f>
         <v/>
       </c>
       <c r="G17">
-        <f>SUM($J$4:$J$15)</f>
-        <v/>
-      </c>
+        <f>SUM($J$2:$J$19)</f>
+        <v/>
+      </c>
+      <c r="H17" s="2" t="n"/>
+      <c r="I17" s="2" t="n"/>
+      <c r="J17" s="2" t="n"/>
+      <c r="K17" s="2" t="n"/>
+      <c r="L17" s="2" t="n"/>
+      <c r="N17" s="2" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="1" t="n"/>
+      <c r="C18" s="1" t="n"/>
+      <c r="D18" s="1" t="n"/>
+      <c r="E18" s="1" t="n"/>
+      <c r="F18" s="1" t="n"/>
+      <c r="H18" s="2" t="n"/>
+      <c r="I18" s="2" t="n"/>
+      <c r="J18" s="2" t="n"/>
+      <c r="K18" s="2" t="n"/>
+      <c r="L18" s="2" t="n"/>
+      <c r="N18" s="2" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n"/>
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="n"/>
+      <c r="H19" s="2" t="n"/>
+      <c r="I19" s="2" t="n"/>
+      <c r="J19" s="2" t="n"/>
+      <c r="K19" s="2" t="n"/>
+      <c r="L19" s="2" t="n"/>
+      <c r="N19" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9698,7 +10393,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9737,77 +10432,81 @@
       <c r="O1" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+      <c r="A2" s="1" t="inlineStr"/>
+      <c r="B2" s="1" t="inlineStr"/>
+      <c r="C2" s="1" t="inlineStr"/>
+      <c r="D2" s="1" t="inlineStr"/>
+      <c r="E2" s="1" t="inlineStr"/>
+      <c r="F2" s="1" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2">
+        <f>(J2-L2)</f>
+        <v/>
+      </c>
+      <c r="L2" s="2">
+        <f>COUNTIF($B$2:$F$19,H2)</f>
+        <v/>
+      </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr"/>
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Martes</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Miercoles</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>Jueves</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Viernes</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Abrev</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Asignaturas</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Frec</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Faltan</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Asignadas</t>
-        </is>
+      <c r="K3" s="2">
+        <f>(J3-L3)</f>
+        <v/>
+      </c>
+      <c r="L3" s="2">
+        <f>COUNTIF($B$2:$F$19,H3)</f>
+        <v/>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>Aulas</t>
         </is>
@@ -9852,17 +10551,15 @@
           <t>Álgebra I</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="J4" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="K4" s="2">
         <f>(J4-L4)</f>
         <v/>
       </c>
       <c r="L4" s="2">
-        <f>COUNTIF($B$4:$F$15,H4)</f>
+        <f>COUNTIF($B$2:$F$19,H4)</f>
         <v/>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -9907,17 +10604,15 @@
           <t>Lógica</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J5" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K5" s="2">
         <f>(J5-L5)</f>
         <v/>
       </c>
       <c r="L5" s="2">
-        <f>COUNTIF($B$4:$F$15,H5)</f>
+        <f>COUNTIF($B$2:$F$19,H5)</f>
         <v/>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -9970,17 +10665,15 @@
           <t>Programación</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="J6" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="K6" s="2">
         <f>(J6-L6)</f>
         <v/>
       </c>
       <c r="L6" s="2">
-        <f>COUNTIF($B$4:$F$15,H6)</f>
+        <f>COUNTIF($B$2:$F$19,H6)</f>
         <v/>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -10029,17 +10722,15 @@
           <t>Análisis Matemático I</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J7" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K7" s="2">
         <f>(J7-L7)</f>
         <v/>
       </c>
       <c r="L7" s="2">
-        <f>COUNTIF($B$4:$F$15,H7)</f>
+        <f>COUNTIF($B$2:$F$19,H7)</f>
         <v/>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -10092,17 +10783,15 @@
           <t>Filosofía</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J8" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K8" s="2">
         <f>(J8-L8)</f>
         <v/>
       </c>
       <c r="L8" s="2">
-        <f>COUNTIF($B$4:$F$15,H8)</f>
+        <f>COUNTIF($B$2:$F$19,H8)</f>
         <v/>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -10151,17 +10840,15 @@
           <t>Educación Física I</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J9" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K9" s="2">
         <f>(J9-L9)</f>
         <v/>
       </c>
       <c r="L9" s="2">
-        <f>COUNTIF($B$4:$F$15,H9)</f>
+        <f>COUNTIF($B$2:$F$19,H9)</f>
         <v/>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -10187,8 +10874,14 @@
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr"/>
+      <c r="K10" s="2">
+        <f>(J10-L10)</f>
+        <v/>
+      </c>
+      <c r="L10" s="2">
+        <f>COUNTIF($B$2:$F$19,H10)</f>
+        <v/>
+      </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr">
         <is>
@@ -10311,26 +11004,26 @@
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
+      <c r="A16" s="1" t="inlineStr"/>
+      <c r="B16" s="1" t="inlineStr"/>
+      <c r="C16" s="1" t="inlineStr"/>
+      <c r="D16" s="1" t="inlineStr"/>
+      <c r="E16" s="1" t="inlineStr"/>
+      <c r="F16" s="1" t="inlineStr"/>
       <c r="G16">
         <f>"Total:"</f>
         <v/>
       </c>
-      <c r="H16">
-        <f>COUNTA($H$4:$H$15)</f>
-        <v/>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+      <c r="H16" s="2">
+        <f>COUNTA($H$2:$H$19)</f>
+        <v/>
+      </c>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>Aula 6</t>
         </is>
@@ -10338,31 +11031,59 @@
       <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17">
+      <c r="A17" s="3" t="inlineStr"/>
+      <c r="B17" s="3" t="inlineStr"/>
+      <c r="C17" s="3" t="inlineStr"/>
+      <c r="D17" s="3" t="inlineStr"/>
+      <c r="E17" s="3" t="inlineStr"/>
+      <c r="F17" s="3">
         <f>"Σ Frec:"</f>
         <v/>
       </c>
       <c r="G17">
-        <f>SUM($J$4:$J$15)</f>
-        <v/>
-      </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+        <f>SUM($J$2:$J$19)</f>
+        <v/>
+      </c>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>Lab</t>
         </is>
       </c>
       <c r="O17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="1" t="n"/>
+      <c r="C18" s="1" t="n"/>
+      <c r="D18" s="1" t="n"/>
+      <c r="E18" s="1" t="n"/>
+      <c r="F18" s="1" t="n"/>
+      <c r="H18" s="2" t="n"/>
+      <c r="I18" s="2" t="n"/>
+      <c r="J18" s="2" t="n"/>
+      <c r="K18" s="2" t="n"/>
+      <c r="L18" s="2" t="n"/>
+      <c r="N18" s="2" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n"/>
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="n"/>
+      <c r="H19" s="2" t="n"/>
+      <c r="I19" s="2" t="n"/>
+      <c r="J19" s="2" t="n"/>
+      <c r="K19" s="2" t="n"/>
+      <c r="L19" s="2" t="n"/>
+      <c r="N19" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10375,7 +11096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -10414,77 +11135,81 @@
       <c r="O1" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+      <c r="A2" s="1" t="inlineStr"/>
+      <c r="B2" s="1" t="inlineStr"/>
+      <c r="C2" s="1" t="inlineStr"/>
+      <c r="D2" s="1" t="inlineStr"/>
+      <c r="E2" s="1" t="inlineStr"/>
+      <c r="F2" s="1" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2">
+        <f>(J2-L2)</f>
+        <v/>
+      </c>
+      <c r="L2" s="2">
+        <f>COUNTIF($B$2:$F$19,H2)</f>
+        <v/>
+      </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr"/>
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Martes</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Miercoles</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>Jueves</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Viernes</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Abrev</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Asignaturas</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Frec</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Faltan</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Asignadas</t>
-        </is>
+      <c r="K3" s="2">
+        <f>(J3-L3)</f>
+        <v/>
+      </c>
+      <c r="L3" s="2">
+        <f>COUNTIF($B$2:$F$19,H3)</f>
+        <v/>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>Aulas</t>
         </is>
@@ -10533,17 +11258,15 @@
           <t>Álgebra I</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="J4" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="K4" s="2">
         <f>(J4-L4)</f>
         <v/>
       </c>
       <c r="L4" s="2">
-        <f>COUNTIF($B$4:$F$15,H4)</f>
+        <f>COUNTIF($B$2:$F$19,H4)</f>
         <v/>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -10592,17 +11315,15 @@
           <t>Lógica</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J5" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K5" s="2">
         <f>(J5-L5)</f>
         <v/>
       </c>
       <c r="L5" s="2">
-        <f>COUNTIF($B$4:$F$15,H5)</f>
+        <f>COUNTIF($B$2:$F$19,H5)</f>
         <v/>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -10655,17 +11376,15 @@
           <t>Programación</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="J6" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="K6" s="2">
         <f>(J6-L6)</f>
         <v/>
       </c>
       <c r="L6" s="2">
-        <f>COUNTIF($B$4:$F$15,H6)</f>
+        <f>COUNTIF($B$2:$F$19,H6)</f>
         <v/>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -10714,17 +11433,15 @@
           <t>Análisis Matemático I</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J7" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K7" s="2">
         <f>(J7-L7)</f>
         <v/>
       </c>
       <c r="L7" s="2">
-        <f>COUNTIF($B$4:$F$15,H7)</f>
+        <f>COUNTIF($B$2:$F$19,H7)</f>
         <v/>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -10773,17 +11490,15 @@
           <t>Filosofía</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J8" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K8" s="2">
         <f>(J8-L8)</f>
         <v/>
       </c>
       <c r="L8" s="2">
-        <f>COUNTIF($B$4:$F$15,H8)</f>
+        <f>COUNTIF($B$2:$F$19,H8)</f>
         <v/>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -10828,17 +11543,15 @@
           <t>Educación Física I</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J9" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K9" s="2">
         <f>(J9-L9)</f>
         <v/>
       </c>
       <c r="L9" s="2">
-        <f>COUNTIF($B$4:$F$15,H9)</f>
+        <f>COUNTIF($B$2:$F$19,H9)</f>
         <v/>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -10864,8 +11577,14 @@
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr"/>
+      <c r="K10" s="2">
+        <f>(J10-L10)</f>
+        <v/>
+      </c>
+      <c r="L10" s="2">
+        <f>COUNTIF($B$2:$F$19,H10)</f>
+        <v/>
+      </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr">
         <is>
@@ -10988,26 +11707,26 @@
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
+      <c r="A16" s="1" t="inlineStr"/>
+      <c r="B16" s="1" t="inlineStr"/>
+      <c r="C16" s="1" t="inlineStr"/>
+      <c r="D16" s="1" t="inlineStr"/>
+      <c r="E16" s="1" t="inlineStr"/>
+      <c r="F16" s="1" t="inlineStr"/>
       <c r="G16">
         <f>"Total:"</f>
         <v/>
       </c>
-      <c r="H16">
-        <f>COUNTA($H$4:$H$15)</f>
-        <v/>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+      <c r="H16" s="2">
+        <f>COUNTA($H$2:$H$19)</f>
+        <v/>
+      </c>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>Aula 5</t>
         </is>
@@ -11015,31 +11734,59 @@
       <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17">
+      <c r="A17" s="3" t="inlineStr"/>
+      <c r="B17" s="3" t="inlineStr"/>
+      <c r="C17" s="3" t="inlineStr"/>
+      <c r="D17" s="3" t="inlineStr"/>
+      <c r="E17" s="3" t="inlineStr"/>
+      <c r="F17" s="3">
         <f>"Σ Frec:"</f>
         <v/>
       </c>
       <c r="G17">
-        <f>SUM($J$4:$J$15)</f>
-        <v/>
-      </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+        <f>SUM($J$2:$J$19)</f>
+        <v/>
+      </c>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>Aula 5</t>
         </is>
       </c>
       <c r="O17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="1" t="n"/>
+      <c r="C18" s="1" t="n"/>
+      <c r="D18" s="1" t="n"/>
+      <c r="E18" s="1" t="n"/>
+      <c r="F18" s="1" t="n"/>
+      <c r="H18" s="2" t="n"/>
+      <c r="I18" s="2" t="n"/>
+      <c r="J18" s="2" t="n"/>
+      <c r="K18" s="2" t="n"/>
+      <c r="L18" s="2" t="n"/>
+      <c r="N18" s="2" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n"/>
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="n"/>
+      <c r="H19" s="2" t="n"/>
+      <c r="I19" s="2" t="n"/>
+      <c r="J19" s="2" t="n"/>
+      <c r="K19" s="2" t="n"/>
+      <c r="L19" s="2" t="n"/>
+      <c r="N19" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11052,7 +11799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -11091,77 +11838,81 @@
       <c r="O1" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+      <c r="A2" s="1" t="inlineStr"/>
+      <c r="B2" s="1" t="inlineStr"/>
+      <c r="C2" s="1" t="inlineStr"/>
+      <c r="D2" s="1" t="inlineStr"/>
+      <c r="E2" s="1" t="inlineStr"/>
+      <c r="F2" s="1" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2">
+        <f>(J2-L2)</f>
+        <v/>
+      </c>
+      <c r="L2" s="2">
+        <f>COUNTIF($B$2:$F$19,H2)</f>
+        <v/>
+      </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr"/>
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Martes</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Miercoles</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>Jueves</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Viernes</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Abrev</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Asignaturas</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Frec</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Faltan</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Asignadas</t>
-        </is>
+      <c r="K3" s="2">
+        <f>(J3-L3)</f>
+        <v/>
+      </c>
+      <c r="L3" s="2">
+        <f>COUNTIF($B$2:$F$19,H3)</f>
+        <v/>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>Aulas</t>
         </is>
@@ -11210,17 +11961,15 @@
           <t>Álgebra I</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="J4" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="K4" s="2">
         <f>(J4-L4)</f>
         <v/>
       </c>
       <c r="L4" s="2">
-        <f>COUNTIF($B$4:$F$15,H4)</f>
+        <f>COUNTIF($B$2:$F$19,H4)</f>
         <v/>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -11269,17 +12018,15 @@
           <t>Lógica</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J5" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K5" s="2">
         <f>(J5-L5)</f>
         <v/>
       </c>
       <c r="L5" s="2">
-        <f>COUNTIF($B$4:$F$15,H5)</f>
+        <f>COUNTIF($B$2:$F$19,H5)</f>
         <v/>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -11332,17 +12079,15 @@
           <t>Programación</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="J6" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="K6" s="2">
         <f>(J6-L6)</f>
         <v/>
       </c>
       <c r="L6" s="2">
-        <f>COUNTIF($B$4:$F$15,H6)</f>
+        <f>COUNTIF($B$2:$F$19,H6)</f>
         <v/>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -11391,17 +12136,15 @@
           <t>Análisis Matemático I</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J7" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K7" s="2">
         <f>(J7-L7)</f>
         <v/>
       </c>
       <c r="L7" s="2">
-        <f>COUNTIF($B$4:$F$15,H7)</f>
+        <f>COUNTIF($B$2:$F$19,H7)</f>
         <v/>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -11450,17 +12193,15 @@
           <t>Filosofía</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J8" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K8" s="2">
         <f>(J8-L8)</f>
         <v/>
       </c>
       <c r="L8" s="2">
-        <f>COUNTIF($B$4:$F$15,H8)</f>
+        <f>COUNTIF($B$2:$F$19,H8)</f>
         <v/>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -11505,17 +12246,15 @@
           <t>Educación Física I</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J9" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K9" s="2">
         <f>(J9-L9)</f>
         <v/>
       </c>
       <c r="L9" s="2">
-        <f>COUNTIF($B$4:$F$15,H9)</f>
+        <f>COUNTIF($B$2:$F$19,H9)</f>
         <v/>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -11541,8 +12280,14 @@
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr"/>
+      <c r="K10" s="2">
+        <f>(J10-L10)</f>
+        <v/>
+      </c>
+      <c r="L10" s="2">
+        <f>COUNTIF($B$2:$F$19,H10)</f>
+        <v/>
+      </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr">
         <is>
@@ -11665,26 +12410,26 @@
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
+      <c r="A16" s="1" t="inlineStr"/>
+      <c r="B16" s="1" t="inlineStr"/>
+      <c r="C16" s="1" t="inlineStr"/>
+      <c r="D16" s="1" t="inlineStr"/>
+      <c r="E16" s="1" t="inlineStr"/>
+      <c r="F16" s="1" t="inlineStr"/>
       <c r="G16">
         <f>"Total:"</f>
         <v/>
       </c>
-      <c r="H16">
-        <f>COUNTA($H$4:$H$15)</f>
-        <v/>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+      <c r="H16" s="2">
+        <f>COUNTA($H$2:$H$19)</f>
+        <v/>
+      </c>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>Aula 1</t>
         </is>
@@ -11692,31 +12437,59 @@
       <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17">
+      <c r="A17" s="3" t="inlineStr"/>
+      <c r="B17" s="3" t="inlineStr"/>
+      <c r="C17" s="3" t="inlineStr"/>
+      <c r="D17" s="3" t="inlineStr"/>
+      <c r="E17" s="3" t="inlineStr"/>
+      <c r="F17" s="3">
         <f>"Σ Frec:"</f>
         <v/>
       </c>
       <c r="G17">
-        <f>SUM($J$4:$J$15)</f>
-        <v/>
-      </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+        <f>SUM($J$2:$J$19)</f>
+        <v/>
+      </c>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>Aula 5</t>
         </is>
       </c>
       <c r="O17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="1" t="n"/>
+      <c r="C18" s="1" t="n"/>
+      <c r="D18" s="1" t="n"/>
+      <c r="E18" s="1" t="n"/>
+      <c r="F18" s="1" t="n"/>
+      <c r="H18" s="2" t="n"/>
+      <c r="I18" s="2" t="n"/>
+      <c r="J18" s="2" t="n"/>
+      <c r="K18" s="2" t="n"/>
+      <c r="L18" s="2" t="n"/>
+      <c r="N18" s="2" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n"/>
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="n"/>
+      <c r="H19" s="2" t="n"/>
+      <c r="I19" s="2" t="n"/>
+      <c r="J19" s="2" t="n"/>
+      <c r="K19" s="2" t="n"/>
+      <c r="L19" s="2" t="n"/>
+      <c r="N19" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11729,7 +12502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -11768,77 +12541,81 @@
       <c r="O1" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+      <c r="A2" s="1" t="inlineStr"/>
+      <c r="B2" s="1" t="inlineStr"/>
+      <c r="C2" s="1" t="inlineStr"/>
+      <c r="D2" s="1" t="inlineStr"/>
+      <c r="E2" s="1" t="inlineStr"/>
+      <c r="F2" s="1" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2">
+        <f>(J2-L2)</f>
+        <v/>
+      </c>
+      <c r="L2" s="2">
+        <f>COUNTIF($B$2:$F$19,H2)</f>
+        <v/>
+      </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr"/>
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Martes</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Miercoles</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>Jueves</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Viernes</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Abrev</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Asignaturas</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Frec</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Faltan</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Asignadas</t>
-        </is>
+      <c r="K3" s="2">
+        <f>(J3-L3)</f>
+        <v/>
+      </c>
+      <c r="L3" s="2">
+        <f>COUNTIF($B$2:$F$19,H3)</f>
+        <v/>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>Aulas</t>
         </is>
@@ -11867,17 +12644,15 @@
           <t>Estructuras de Datos y Algoritmos I</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J4" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K4" s="2">
         <f>(J4-L4)</f>
         <v/>
       </c>
       <c r="L4" s="2">
-        <f>COUNTIF($B$4:$F$15,H4)</f>
+        <f>COUNTIF($B$2:$F$19,H4)</f>
         <v/>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -11906,17 +12681,15 @@
           <t>Matemática Discreta I</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J5" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K5" s="2">
         <f>(J5-L5)</f>
         <v/>
       </c>
       <c r="L5" s="2">
-        <f>COUNTIF($B$4:$F$15,H5)</f>
+        <f>COUNTIF($B$2:$F$19,H5)</f>
         <v/>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -11949,17 +12722,15 @@
           <t>Arquitectura de computadoras</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J6" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K6" s="2">
         <f>(J6-L6)</f>
         <v/>
       </c>
       <c r="L6" s="2">
-        <f>COUNTIF($B$4:$F$15,H6)</f>
+        <f>COUNTIF($B$2:$F$19,H6)</f>
         <v/>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -11988,17 +12759,15 @@
           <t>Ecuaciones Diferenciales Ordinarias</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J7" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K7" s="2">
         <f>(J7-L7)</f>
         <v/>
       </c>
       <c r="L7" s="2">
-        <f>COUNTIF($B$4:$F$15,H7)</f>
+        <f>COUNTIF($B$2:$F$19,H7)</f>
         <v/>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -12031,17 +12800,15 @@
           <t>Matemática Numérica</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J8" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K8" s="2">
         <f>(J8-L8)</f>
         <v/>
       </c>
       <c r="L8" s="2">
-        <f>COUNTIF($B$4:$F$15,H8)</f>
+        <f>COUNTIF($B$2:$F$19,H8)</f>
         <v/>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -12070,17 +12837,15 @@
           <t>Teoría Política</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J9" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K9" s="2">
         <f>(J9-L9)</f>
         <v/>
       </c>
       <c r="L9" s="2">
-        <f>COUNTIF($B$4:$F$15,H9)</f>
+        <f>COUNTIF($B$2:$F$19,H9)</f>
         <v/>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -12126,8 +12891,14 @@
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr"/>
+      <c r="K10" s="2">
+        <f>(J10-L10)</f>
+        <v/>
+      </c>
+      <c r="L10" s="2">
+        <f>COUNTIF($B$2:$F$19,H10)</f>
+        <v/>
+      </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr">
         <is>
@@ -12330,24 +13101,74 @@
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
+      <c r="A16" s="1" t="n"/>
+      <c r="B16" s="1" t="n"/>
+      <c r="C16" s="1" t="n"/>
+      <c r="D16" s="1" t="n"/>
+      <c r="E16" s="1" t="n"/>
+      <c r="F16" s="1" t="n"/>
       <c r="G16">
         <f>"Total:"</f>
         <v/>
       </c>
-      <c r="H16">
-        <f>COUNTA($H$4:$H$15)</f>
-        <v/>
-      </c>
+      <c r="H16" s="2">
+        <f>COUNTA($H$2:$H$19)</f>
+        <v/>
+      </c>
+      <c r="I16" s="2" t="n"/>
+      <c r="J16" s="2" t="n"/>
+      <c r="K16" s="2" t="n"/>
+      <c r="L16" s="2" t="n"/>
+      <c r="N16" s="2" t="n"/>
     </row>
     <row r="17">
-      <c r="F17">
+      <c r="A17" s="3" t="n"/>
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3" t="n"/>
+      <c r="F17" s="3">
         <f>"Σ Frec:"</f>
         <v/>
       </c>
       <c r="G17">
-        <f>SUM($J$4:$J$15)</f>
-        <v/>
-      </c>
+        <f>SUM($J$2:$J$19)</f>
+        <v/>
+      </c>
+      <c r="H17" s="2" t="n"/>
+      <c r="I17" s="2" t="n"/>
+      <c r="J17" s="2" t="n"/>
+      <c r="K17" s="2" t="n"/>
+      <c r="L17" s="2" t="n"/>
+      <c r="N17" s="2" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="1" t="n"/>
+      <c r="C18" s="1" t="n"/>
+      <c r="D18" s="1" t="n"/>
+      <c r="E18" s="1" t="n"/>
+      <c r="F18" s="1" t="n"/>
+      <c r="H18" s="2" t="n"/>
+      <c r="I18" s="2" t="n"/>
+      <c r="J18" s="2" t="n"/>
+      <c r="K18" s="2" t="n"/>
+      <c r="L18" s="2" t="n"/>
+      <c r="N18" s="2" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n"/>
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="n"/>
+      <c r="H19" s="2" t="n"/>
+      <c r="I19" s="2" t="n"/>
+      <c r="J19" s="2" t="n"/>
+      <c r="K19" s="2" t="n"/>
+      <c r="L19" s="2" t="n"/>
+      <c r="N19" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12360,7 +13181,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -12399,77 +13220,81 @@
       <c r="O1" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+      <c r="A2" s="1" t="inlineStr"/>
+      <c r="B2" s="1" t="inlineStr"/>
+      <c r="C2" s="1" t="inlineStr"/>
+      <c r="D2" s="1" t="inlineStr"/>
+      <c r="E2" s="1" t="inlineStr"/>
+      <c r="F2" s="1" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2">
+        <f>(J2-L2)</f>
+        <v/>
+      </c>
+      <c r="L2" s="2">
+        <f>COUNTIF($B$2:$F$19,H2)</f>
+        <v/>
+      </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr"/>
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Martes</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Miercoles</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>Jueves</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Viernes</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Abrev</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Asignaturas</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Frec</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Faltan</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Asignadas</t>
-        </is>
+      <c r="K3" s="2">
+        <f>(J3-L3)</f>
+        <v/>
+      </c>
+      <c r="L3" s="2">
+        <f>COUNTIF($B$2:$F$19,H3)</f>
+        <v/>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>Aulas</t>
         </is>
@@ -12498,17 +13323,15 @@
           <t>Estructuras de Datos y Algoritmos I</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J4" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K4" s="2">
         <f>(J4-L4)</f>
         <v/>
       </c>
       <c r="L4" s="2">
-        <f>COUNTIF($B$4:$F$15,H4)</f>
+        <f>COUNTIF($B$2:$F$19,H4)</f>
         <v/>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -12537,17 +13360,15 @@
           <t>Matemática Discreta I</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J5" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K5" s="2">
         <f>(J5-L5)</f>
         <v/>
       </c>
       <c r="L5" s="2">
-        <f>COUNTIF($B$4:$F$15,H5)</f>
+        <f>COUNTIF($B$2:$F$19,H5)</f>
         <v/>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -12580,17 +13401,15 @@
           <t>Arquitectura de computadoras</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J6" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K6" s="2">
         <f>(J6-L6)</f>
         <v/>
       </c>
       <c r="L6" s="2">
-        <f>COUNTIF($B$4:$F$15,H6)</f>
+        <f>COUNTIF($B$2:$F$19,H6)</f>
         <v/>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -12619,17 +13438,15 @@
           <t>Ecuaciones Diferenciales Ordinarias</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J7" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K7" s="2">
         <f>(J7-L7)</f>
         <v/>
       </c>
       <c r="L7" s="2">
-        <f>COUNTIF($B$4:$F$15,H7)</f>
+        <f>COUNTIF($B$2:$F$19,H7)</f>
         <v/>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -12662,17 +13479,15 @@
           <t>Matemática Numérica</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J8" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K8" s="2">
         <f>(J8-L8)</f>
         <v/>
       </c>
       <c r="L8" s="2">
-        <f>COUNTIF($B$4:$F$15,H8)</f>
+        <f>COUNTIF($B$2:$F$19,H8)</f>
         <v/>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -12701,17 +13516,15 @@
           <t>Teoría Política</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="J9" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="K9" s="2">
         <f>(J9-L9)</f>
         <v/>
       </c>
       <c r="L9" s="2">
-        <f>COUNTIF($B$4:$F$15,H9)</f>
+        <f>COUNTIF($B$2:$F$19,H9)</f>
         <v/>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -12757,8 +13570,14 @@
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr"/>
+      <c r="K10" s="2">
+        <f>(J10-L10)</f>
+        <v/>
+      </c>
+      <c r="L10" s="2">
+        <f>COUNTIF($B$2:$F$19,H10)</f>
+        <v/>
+      </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr">
         <is>
@@ -12961,24 +13780,74 @@
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
+      <c r="A16" s="1" t="n"/>
+      <c r="B16" s="1" t="n"/>
+      <c r="C16" s="1" t="n"/>
+      <c r="D16" s="1" t="n"/>
+      <c r="E16" s="1" t="n"/>
+      <c r="F16" s="1" t="n"/>
       <c r="G16">
         <f>"Total:"</f>
         <v/>
       </c>
-      <c r="H16">
-        <f>COUNTA($H$4:$H$15)</f>
-        <v/>
-      </c>
+      <c r="H16" s="2">
+        <f>COUNTA($H$2:$H$19)</f>
+        <v/>
+      </c>
+      <c r="I16" s="2" t="n"/>
+      <c r="J16" s="2" t="n"/>
+      <c r="K16" s="2" t="n"/>
+      <c r="L16" s="2" t="n"/>
+      <c r="N16" s="2" t="n"/>
     </row>
     <row r="17">
-      <c r="F17">
+      <c r="A17" s="3" t="n"/>
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3" t="n"/>
+      <c r="F17" s="3">
         <f>"Σ Frec:"</f>
         <v/>
       </c>
       <c r="G17">
-        <f>SUM($J$4:$J$15)</f>
-        <v/>
-      </c>
+        <f>SUM($J$2:$J$19)</f>
+        <v/>
+      </c>
+      <c r="H17" s="2" t="n"/>
+      <c r="I17" s="2" t="n"/>
+      <c r="J17" s="2" t="n"/>
+      <c r="K17" s="2" t="n"/>
+      <c r="L17" s="2" t="n"/>
+      <c r="N17" s="2" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="1" t="n"/>
+      <c r="C18" s="1" t="n"/>
+      <c r="D18" s="1" t="n"/>
+      <c r="E18" s="1" t="n"/>
+      <c r="F18" s="1" t="n"/>
+      <c r="H18" s="2" t="n"/>
+      <c r="I18" s="2" t="n"/>
+      <c r="J18" s="2" t="n"/>
+      <c r="K18" s="2" t="n"/>
+      <c r="L18" s="2" t="n"/>
+      <c r="N18" s="2" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n"/>
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="n"/>
+      <c r="H19" s="2" t="n"/>
+      <c r="I19" s="2" t="n"/>
+      <c r="J19" s="2" t="n"/>
+      <c r="K19" s="2" t="n"/>
+      <c r="L19" s="2" t="n"/>
+      <c r="N19" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Horario_Facultad.xlsx
+++ b/Horario_Facultad.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -508,81 +508,77 @@
       <c r="O1" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr"/>
-      <c r="B2" s="1" t="inlineStr"/>
-      <c r="C2" s="1" t="inlineStr"/>
-      <c r="D2" s="1" t="inlineStr"/>
-      <c r="E2" s="1" t="inlineStr"/>
-      <c r="F2" s="1" t="inlineStr"/>
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="2">
-        <f>(J2-L2)</f>
-        <v/>
-      </c>
-      <c r="L2" s="2">
-        <f>COUNTIF($B$2:$F$19,H2)</f>
-        <v/>
-      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr"/>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Martes</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Miercoles</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Jueves</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Viernes</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Abrev</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Asignaturas</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Frec</t>
         </is>
       </c>
-      <c r="K3" s="2">
-        <f>(J3-L3)</f>
-        <v/>
-      </c>
-      <c r="L3" s="2">
-        <f>COUNTIF($B$2:$F$19,H3)</f>
-        <v/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Faltan</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Asignadas</t>
+        </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Aulas</t>
         </is>
@@ -639,7 +635,7 @@
         <v/>
       </c>
       <c r="L4" s="2">
-        <f>COUNTIF($B$2:$F$19,H4)</f>
+        <f>COUNTIF($B$4:$F$15,H4)</f>
         <v/>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -696,7 +692,7 @@
         <v/>
       </c>
       <c r="L5" s="2">
-        <f>COUNTIF($B$2:$F$19,H5)</f>
+        <f>COUNTIF($B$4:$F$15,H5)</f>
         <v/>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -753,7 +749,7 @@
         <v/>
       </c>
       <c r="L6" s="2">
-        <f>COUNTIF($B$2:$F$19,H6)</f>
+        <f>COUNTIF($B$4:$F$15,H6)</f>
         <v/>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -806,7 +802,7 @@
         <v/>
       </c>
       <c r="L7" s="2">
-        <f>COUNTIF($B$2:$F$19,H7)</f>
+        <f>COUNTIF($B$4:$F$15,H7)</f>
         <v/>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -863,7 +859,7 @@
         <v/>
       </c>
       <c r="L8" s="2">
-        <f>COUNTIF($B$2:$F$19,H8)</f>
+        <f>COUNTIF($B$4:$F$15,H8)</f>
         <v/>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -916,7 +912,7 @@
         <v/>
       </c>
       <c r="L9" s="2">
-        <f>COUNTIF($B$2:$F$19,H9)</f>
+        <f>COUNTIF($B$4:$F$15,H9)</f>
         <v/>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -939,17 +935,14 @@
       <c r="E10" s="1" t="inlineStr"/>
       <c r="F10" s="1" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr"/>
+      <c r="H10" s="2">
+        <f>COUNTA($H$4:$H$9)</f>
+        <v/>
+      </c>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2">
-        <f>(J10-L10)</f>
-        <v/>
-      </c>
-      <c r="L10" s="2">
-        <f>COUNTIF($B$2:$F$19,H10)</f>
-        <v/>
-      </c>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr">
         <is>
@@ -1072,26 +1065,23 @@
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr"/>
-      <c r="B16" s="1" t="inlineStr"/>
-      <c r="C16" s="1" t="inlineStr"/>
-      <c r="D16" s="1" t="inlineStr"/>
-      <c r="E16" s="1" t="inlineStr"/>
-      <c r="F16" s="1" t="inlineStr"/>
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
       <c r="G16">
         <f>"Total:"</f>
         <v/>
       </c>
-      <c r="H16" s="2">
-        <f>COUNTA($H$2:$H$19)</f>
-        <v/>
-      </c>
-      <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="2" t="inlineStr"/>
-      <c r="L16" s="2" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>Lab</t>
         </is>
@@ -1099,53 +1089,14 @@
       <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n"/>
-      <c r="B17" s="3" t="n"/>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="3" t="n"/>
-      <c r="E17" s="3" t="n"/>
-      <c r="F17" s="3">
-        <f>"Σ Frec:"</f>
+      <c r="F17">
+        <f>"Sigma Frec:"</f>
         <v/>
       </c>
       <c r="G17">
-        <f>SUM($J$2:$J$19)</f>
-        <v/>
-      </c>
-      <c r="H17" s="2" t="n"/>
-      <c r="I17" s="2" t="n"/>
-      <c r="J17" s="2" t="n"/>
-      <c r="K17" s="2" t="n"/>
-      <c r="L17" s="2" t="n"/>
-      <c r="N17" s="2" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n"/>
-      <c r="B18" s="1" t="n"/>
-      <c r="C18" s="1" t="n"/>
-      <c r="D18" s="1" t="n"/>
-      <c r="E18" s="1" t="n"/>
-      <c r="F18" s="1" t="n"/>
-      <c r="H18" s="2" t="n"/>
-      <c r="I18" s="2" t="n"/>
-      <c r="J18" s="2" t="n"/>
-      <c r="K18" s="2" t="n"/>
-      <c r="L18" s="2" t="n"/>
-      <c r="N18" s="2" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="n"/>
-      <c r="B19" s="3" t="n"/>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="3" t="n"/>
-      <c r="E19" s="3" t="n"/>
-      <c r="F19" s="3" t="n"/>
-      <c r="H19" s="2" t="n"/>
-      <c r="I19" s="2" t="n"/>
-      <c r="J19" s="2" t="n"/>
-      <c r="K19" s="2" t="n"/>
-      <c r="L19" s="2" t="n"/>
-      <c r="N19" s="2" t="n"/>
+        <f>SUM($J$4:$J$9)</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1158,7 +1109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1197,81 +1148,77 @@
       <c r="O1" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr"/>
-      <c r="B2" s="1" t="inlineStr"/>
-      <c r="C2" s="1" t="inlineStr"/>
-      <c r="D2" s="1" t="inlineStr"/>
-      <c r="E2" s="1" t="inlineStr"/>
-      <c r="F2" s="1" t="inlineStr"/>
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="2">
-        <f>(J2-L2)</f>
-        <v/>
-      </c>
-      <c r="L2" s="2">
-        <f>COUNTIF($B$2:$F$19,H2)</f>
-        <v/>
-      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr"/>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Martes</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Miercoles</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Jueves</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Viernes</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Abrev</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Asignaturas</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Frec</t>
         </is>
       </c>
-      <c r="K3" s="2">
-        <f>(J3-L3)</f>
-        <v/>
-      </c>
-      <c r="L3" s="2">
-        <f>COUNTIF($B$2:$F$19,H3)</f>
-        <v/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Faltan</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Asignadas</t>
+        </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Aulas</t>
         </is>
@@ -1324,7 +1271,7 @@
         <v/>
       </c>
       <c r="L4" s="2">
-        <f>COUNTIF($B$2:$F$19,H4)</f>
+        <f>COUNTIF($B$4:$F$15,H4)</f>
         <v/>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -1377,7 +1324,7 @@
         <v/>
       </c>
       <c r="L5" s="2">
-        <f>COUNTIF($B$2:$F$19,H5)</f>
+        <f>COUNTIF($B$4:$F$15,H5)</f>
         <v/>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -1434,7 +1381,7 @@
         <v/>
       </c>
       <c r="L6" s="2">
-        <f>COUNTIF($B$2:$F$19,H6)</f>
+        <f>COUNTIF($B$4:$F$15,H6)</f>
         <v/>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -1487,7 +1434,7 @@
         <v/>
       </c>
       <c r="L7" s="2">
-        <f>COUNTIF($B$2:$F$19,H7)</f>
+        <f>COUNTIF($B$4:$F$15,H7)</f>
         <v/>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -1544,7 +1491,7 @@
         <v/>
       </c>
       <c r="L8" s="2">
-        <f>COUNTIF($B$2:$F$19,H8)</f>
+        <f>COUNTIF($B$4:$F$15,H8)</f>
         <v/>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -1597,7 +1544,7 @@
         <v/>
       </c>
       <c r="L9" s="2">
-        <f>COUNTIF($B$2:$F$19,H9)</f>
+        <f>COUNTIF($B$4:$F$15,H9)</f>
         <v/>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -1620,17 +1567,14 @@
       <c r="E10" s="1" t="inlineStr"/>
       <c r="F10" s="1" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr"/>
+      <c r="H10" s="2">
+        <f>COUNTA($H$4:$H$9)</f>
+        <v/>
+      </c>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2">
-        <f>(J10-L10)</f>
-        <v/>
-      </c>
-      <c r="L10" s="2">
-        <f>COUNTIF($B$2:$F$19,H10)</f>
-        <v/>
-      </c>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr">
         <is>
@@ -1753,74 +1697,20 @@
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n"/>
-      <c r="B16" s="1" t="n"/>
-      <c r="C16" s="1" t="n"/>
-      <c r="D16" s="1" t="n"/>
-      <c r="E16" s="1" t="n"/>
-      <c r="F16" s="1" t="n"/>
       <c r="G16">
         <f>"Total:"</f>
         <v/>
       </c>
-      <c r="H16" s="2">
-        <f>COUNTA($H$2:$H$19)</f>
-        <v/>
-      </c>
-      <c r="I16" s="2" t="n"/>
-      <c r="J16" s="2" t="n"/>
-      <c r="K16" s="2" t="n"/>
-      <c r="L16" s="2" t="n"/>
-      <c r="N16" s="2" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n"/>
-      <c r="B17" s="3" t="n"/>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="3" t="n"/>
-      <c r="E17" s="3" t="n"/>
-      <c r="F17" s="3">
-        <f>"Σ Frec:"</f>
+      <c r="F17">
+        <f>"Sigma Frec:"</f>
         <v/>
       </c>
       <c r="G17">
-        <f>SUM($J$2:$J$19)</f>
-        <v/>
-      </c>
-      <c r="H17" s="2" t="n"/>
-      <c r="I17" s="2" t="n"/>
-      <c r="J17" s="2" t="n"/>
-      <c r="K17" s="2" t="n"/>
-      <c r="L17" s="2" t="n"/>
-      <c r="N17" s="2" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n"/>
-      <c r="B18" s="1" t="n"/>
-      <c r="C18" s="1" t="n"/>
-      <c r="D18" s="1" t="n"/>
-      <c r="E18" s="1" t="n"/>
-      <c r="F18" s="1" t="n"/>
-      <c r="H18" s="2" t="n"/>
-      <c r="I18" s="2" t="n"/>
-      <c r="J18" s="2" t="n"/>
-      <c r="K18" s="2" t="n"/>
-      <c r="L18" s="2" t="n"/>
-      <c r="N18" s="2" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="n"/>
-      <c r="B19" s="3" t="n"/>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="3" t="n"/>
-      <c r="E19" s="3" t="n"/>
-      <c r="F19" s="3" t="n"/>
-      <c r="H19" s="2" t="n"/>
-      <c r="I19" s="2" t="n"/>
-      <c r="J19" s="2" t="n"/>
-      <c r="K19" s="2" t="n"/>
-      <c r="L19" s="2" t="n"/>
-      <c r="N19" s="2" t="n"/>
+        <f>SUM($J$4:$J$9)</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1833,7 +1723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1872,81 +1762,77 @@
       <c r="O1" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr"/>
-      <c r="B2" s="1" t="inlineStr"/>
-      <c r="C2" s="1" t="inlineStr"/>
-      <c r="D2" s="1" t="inlineStr"/>
-      <c r="E2" s="1" t="inlineStr"/>
-      <c r="F2" s="1" t="inlineStr"/>
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="2">
-        <f>(J2-L2)</f>
-        <v/>
-      </c>
-      <c r="L2" s="2">
-        <f>COUNTIF($B$2:$F$19,H2)</f>
-        <v/>
-      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr"/>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Martes</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Miercoles</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Jueves</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Viernes</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Abrev</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Asignaturas</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Frec</t>
         </is>
       </c>
-      <c r="K3" s="2">
-        <f>(J3-L3)</f>
-        <v/>
-      </c>
-      <c r="L3" s="2">
-        <f>COUNTIF($B$2:$F$19,H3)</f>
-        <v/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Faltan</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Asignadas</t>
+        </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Aulas</t>
         </is>
@@ -1999,7 +1885,7 @@
         <v/>
       </c>
       <c r="L4" s="2">
-        <f>COUNTIF($B$2:$F$19,H4)</f>
+        <f>COUNTIF($B$4:$F$15,H4)</f>
         <v/>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -2052,7 +1938,7 @@
         <v/>
       </c>
       <c r="L5" s="2">
-        <f>COUNTIF($B$2:$F$19,H5)</f>
+        <f>COUNTIF($B$4:$F$15,H5)</f>
         <v/>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -2109,7 +1995,7 @@
         <v/>
       </c>
       <c r="L6" s="2">
-        <f>COUNTIF($B$2:$F$19,H6)</f>
+        <f>COUNTIF($B$4:$F$15,H6)</f>
         <v/>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -2162,7 +2048,7 @@
         <v/>
       </c>
       <c r="L7" s="2">
-        <f>COUNTIF($B$2:$F$19,H7)</f>
+        <f>COUNTIF($B$4:$F$15,H7)</f>
         <v/>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -2219,7 +2105,7 @@
         <v/>
       </c>
       <c r="L8" s="2">
-        <f>COUNTIF($B$2:$F$19,H8)</f>
+        <f>COUNTIF($B$4:$F$15,H8)</f>
         <v/>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -2272,7 +2158,7 @@
         <v/>
       </c>
       <c r="L9" s="2">
-        <f>COUNTIF($B$2:$F$19,H9)</f>
+        <f>COUNTIF($B$4:$F$15,H9)</f>
         <v/>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -2295,17 +2181,14 @@
       <c r="E10" s="1" t="inlineStr"/>
       <c r="F10" s="1" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr"/>
+      <c r="H10" s="2">
+        <f>COUNTA($H$4:$H$9)</f>
+        <v/>
+      </c>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2">
-        <f>(J10-L10)</f>
-        <v/>
-      </c>
-      <c r="L10" s="2">
-        <f>COUNTIF($B$2:$F$19,H10)</f>
-        <v/>
-      </c>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr">
         <is>
@@ -2428,74 +2311,20 @@
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n"/>
-      <c r="B16" s="1" t="n"/>
-      <c r="C16" s="1" t="n"/>
-      <c r="D16" s="1" t="n"/>
-      <c r="E16" s="1" t="n"/>
-      <c r="F16" s="1" t="n"/>
       <c r="G16">
         <f>"Total:"</f>
         <v/>
       </c>
-      <c r="H16" s="2">
-        <f>COUNTA($H$2:$H$19)</f>
-        <v/>
-      </c>
-      <c r="I16" s="2" t="n"/>
-      <c r="J16" s="2" t="n"/>
-      <c r="K16" s="2" t="n"/>
-      <c r="L16" s="2" t="n"/>
-      <c r="N16" s="2" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n"/>
-      <c r="B17" s="3" t="n"/>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="3" t="n"/>
-      <c r="E17" s="3" t="n"/>
-      <c r="F17" s="3">
-        <f>"Σ Frec:"</f>
+      <c r="F17">
+        <f>"Sigma Frec:"</f>
         <v/>
       </c>
       <c r="G17">
-        <f>SUM($J$2:$J$19)</f>
-        <v/>
-      </c>
-      <c r="H17" s="2" t="n"/>
-      <c r="I17" s="2" t="n"/>
-      <c r="J17" s="2" t="n"/>
-      <c r="K17" s="2" t="n"/>
-      <c r="L17" s="2" t="n"/>
-      <c r="N17" s="2" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n"/>
-      <c r="B18" s="1" t="n"/>
-      <c r="C18" s="1" t="n"/>
-      <c r="D18" s="1" t="n"/>
-      <c r="E18" s="1" t="n"/>
-      <c r="F18" s="1" t="n"/>
-      <c r="H18" s="2" t="n"/>
-      <c r="I18" s="2" t="n"/>
-      <c r="J18" s="2" t="n"/>
-      <c r="K18" s="2" t="n"/>
-      <c r="L18" s="2" t="n"/>
-      <c r="N18" s="2" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="n"/>
-      <c r="B19" s="3" t="n"/>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="3" t="n"/>
-      <c r="E19" s="3" t="n"/>
-      <c r="F19" s="3" t="n"/>
-      <c r="H19" s="2" t="n"/>
-      <c r="I19" s="2" t="n"/>
-      <c r="J19" s="2" t="n"/>
-      <c r="K19" s="2" t="n"/>
-      <c r="L19" s="2" t="n"/>
-      <c r="N19" s="2" t="n"/>
+        <f>SUM($J$4:$J$9)</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2508,7 +2337,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2547,81 +2376,77 @@
       <c r="O1" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr"/>
-      <c r="B2" s="1" t="inlineStr"/>
-      <c r="C2" s="1" t="inlineStr"/>
-      <c r="D2" s="1" t="inlineStr"/>
-      <c r="E2" s="1" t="inlineStr"/>
-      <c r="F2" s="1" t="inlineStr"/>
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="2">
-        <f>(J2-L2)</f>
-        <v/>
-      </c>
-      <c r="L2" s="2">
-        <f>COUNTIF($B$2:$F$19,H2)</f>
-        <v/>
-      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr"/>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Martes</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Miercoles</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Jueves</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Viernes</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Abrev</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Asignaturas</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Frec</t>
         </is>
       </c>
-      <c r="K3" s="2">
-        <f>(J3-L3)</f>
-        <v/>
-      </c>
-      <c r="L3" s="2">
-        <f>COUNTIF($B$2:$F$19,H3)</f>
-        <v/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Faltan</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Asignadas</t>
+        </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Aulas</t>
         </is>
@@ -2658,7 +2483,7 @@
         <v/>
       </c>
       <c r="L4" s="2">
-        <f>COUNTIF($B$2:$F$19,H4)</f>
+        <f>COUNTIF($B$4:$F$15,H4)</f>
         <v/>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -2695,7 +2520,7 @@
         <v/>
       </c>
       <c r="L5" s="2">
-        <f>COUNTIF($B$2:$F$19,H5)</f>
+        <f>COUNTIF($B$4:$F$15,H5)</f>
         <v/>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -2736,7 +2561,7 @@
         <v/>
       </c>
       <c r="L6" s="2">
-        <f>COUNTIF($B$2:$F$19,H6)</f>
+        <f>COUNTIF($B$4:$F$15,H6)</f>
         <v/>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -2773,7 +2598,7 @@
         <v/>
       </c>
       <c r="L7" s="2">
-        <f>COUNTIF($B$2:$F$19,H7)</f>
+        <f>COUNTIF($B$4:$F$15,H7)</f>
         <v/>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -2814,7 +2639,7 @@
         <v/>
       </c>
       <c r="L8" s="2">
-        <f>COUNTIF($B$2:$F$19,H8)</f>
+        <f>COUNTIF($B$4:$F$15,H8)</f>
         <v/>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -2851,7 +2676,7 @@
         <v/>
       </c>
       <c r="L9" s="2">
-        <f>COUNTIF($B$2:$F$19,H9)</f>
+        <f>COUNTIF($B$4:$F$15,H9)</f>
         <v/>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -2890,17 +2715,14 @@
       </c>
       <c r="F10" s="1" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr"/>
+      <c r="H10" s="2">
+        <f>COUNTA($H$4:$H$9)</f>
+        <v/>
+      </c>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2">
-        <f>(J10-L10)</f>
-        <v/>
-      </c>
-      <c r="L10" s="2">
-        <f>COUNTIF($B$2:$F$19,H10)</f>
-        <v/>
-      </c>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -3051,74 +2873,20 @@
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n"/>
-      <c r="B16" s="1" t="n"/>
-      <c r="C16" s="1" t="n"/>
-      <c r="D16" s="1" t="n"/>
-      <c r="E16" s="1" t="n"/>
-      <c r="F16" s="1" t="n"/>
       <c r="G16">
         <f>"Total:"</f>
         <v/>
       </c>
-      <c r="H16" s="2">
-        <f>COUNTA($H$2:$H$19)</f>
-        <v/>
-      </c>
-      <c r="I16" s="2" t="n"/>
-      <c r="J16" s="2" t="n"/>
-      <c r="K16" s="2" t="n"/>
-      <c r="L16" s="2" t="n"/>
-      <c r="N16" s="2" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n"/>
-      <c r="B17" s="3" t="n"/>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="3" t="n"/>
-      <c r="E17" s="3" t="n"/>
-      <c r="F17" s="3">
-        <f>"Σ Frec:"</f>
+      <c r="F17">
+        <f>"Sigma Frec:"</f>
         <v/>
       </c>
       <c r="G17">
-        <f>SUM($J$2:$J$19)</f>
-        <v/>
-      </c>
-      <c r="H17" s="2" t="n"/>
-      <c r="I17" s="2" t="n"/>
-      <c r="J17" s="2" t="n"/>
-      <c r="K17" s="2" t="n"/>
-      <c r="L17" s="2" t="n"/>
-      <c r="N17" s="2" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n"/>
-      <c r="B18" s="1" t="n"/>
-      <c r="C18" s="1" t="n"/>
-      <c r="D18" s="1" t="n"/>
-      <c r="E18" s="1" t="n"/>
-      <c r="F18" s="1" t="n"/>
-      <c r="H18" s="2" t="n"/>
-      <c r="I18" s="2" t="n"/>
-      <c r="J18" s="2" t="n"/>
-      <c r="K18" s="2" t="n"/>
-      <c r="L18" s="2" t="n"/>
-      <c r="N18" s="2" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="n"/>
-      <c r="B19" s="3" t="n"/>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="3" t="n"/>
-      <c r="E19" s="3" t="n"/>
-      <c r="F19" s="3" t="n"/>
-      <c r="H19" s="2" t="n"/>
-      <c r="I19" s="2" t="n"/>
-      <c r="J19" s="2" t="n"/>
-      <c r="K19" s="2" t="n"/>
-      <c r="L19" s="2" t="n"/>
-      <c r="N19" s="2" t="n"/>
+        <f>SUM($J$4:$J$9)</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3131,7 +2899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3170,81 +2938,77 @@
       <c r="O1" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr"/>
-      <c r="B2" s="1" t="inlineStr"/>
-      <c r="C2" s="1" t="inlineStr"/>
-      <c r="D2" s="1" t="inlineStr"/>
-      <c r="E2" s="1" t="inlineStr"/>
-      <c r="F2" s="1" t="inlineStr"/>
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="2">
-        <f>(J2-L2)</f>
-        <v/>
-      </c>
-      <c r="L2" s="2">
-        <f>COUNTIF($B$2:$F$19,H2)</f>
-        <v/>
-      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr"/>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Martes</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Miercoles</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Jueves</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Viernes</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Abrev</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Asignaturas</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Frec</t>
         </is>
       </c>
-      <c r="K3" s="2">
-        <f>(J3-L3)</f>
-        <v/>
-      </c>
-      <c r="L3" s="2">
-        <f>COUNTIF($B$2:$F$19,H3)</f>
-        <v/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Faltan</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Asignadas</t>
+        </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Aulas</t>
         </is>
@@ -3281,7 +3045,7 @@
         <v/>
       </c>
       <c r="L4" s="2">
-        <f>COUNTIF($B$2:$F$19,H4)</f>
+        <f>COUNTIF($B$4:$F$15,H4)</f>
         <v/>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -3318,7 +3082,7 @@
         <v/>
       </c>
       <c r="L5" s="2">
-        <f>COUNTIF($B$2:$F$19,H5)</f>
+        <f>COUNTIF($B$4:$F$15,H5)</f>
         <v/>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -3359,7 +3123,7 @@
         <v/>
       </c>
       <c r="L6" s="2">
-        <f>COUNTIF($B$2:$F$19,H6)</f>
+        <f>COUNTIF($B$4:$F$15,H6)</f>
         <v/>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -3396,7 +3160,7 @@
         <v/>
       </c>
       <c r="L7" s="2">
-        <f>COUNTIF($B$2:$F$19,H7)</f>
+        <f>COUNTIF($B$4:$F$15,H7)</f>
         <v/>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -3437,7 +3201,7 @@
         <v/>
       </c>
       <c r="L8" s="2">
-        <f>COUNTIF($B$2:$F$19,H8)</f>
+        <f>COUNTIF($B$4:$F$15,H8)</f>
         <v/>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -3474,7 +3238,7 @@
         <v/>
       </c>
       <c r="L9" s="2">
-        <f>COUNTIF($B$2:$F$19,H9)</f>
+        <f>COUNTIF($B$4:$F$15,H9)</f>
         <v/>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -3509,17 +3273,14 @@
       </c>
       <c r="F10" s="1" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr"/>
+      <c r="H10" s="2">
+        <f>COUNTA($H$4:$H$9)</f>
+        <v/>
+      </c>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2">
-        <f>(J10-L10)</f>
-        <v/>
-      </c>
-      <c r="L10" s="2">
-        <f>COUNTIF($B$2:$F$19,H10)</f>
-        <v/>
-      </c>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -3666,74 +3427,20 @@
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n"/>
-      <c r="B16" s="1" t="n"/>
-      <c r="C16" s="1" t="n"/>
-      <c r="D16" s="1" t="n"/>
-      <c r="E16" s="1" t="n"/>
-      <c r="F16" s="1" t="n"/>
       <c r="G16">
         <f>"Total:"</f>
         <v/>
       </c>
-      <c r="H16" s="2">
-        <f>COUNTA($H$2:$H$19)</f>
-        <v/>
-      </c>
-      <c r="I16" s="2" t="n"/>
-      <c r="J16" s="2" t="n"/>
-      <c r="K16" s="2" t="n"/>
-      <c r="L16" s="2" t="n"/>
-      <c r="N16" s="2" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n"/>
-      <c r="B17" s="3" t="n"/>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="3" t="n"/>
-      <c r="E17" s="3" t="n"/>
-      <c r="F17" s="3">
-        <f>"Σ Frec:"</f>
+      <c r="F17">
+        <f>"Sigma Frec:"</f>
         <v/>
       </c>
       <c r="G17">
-        <f>SUM($J$2:$J$19)</f>
-        <v/>
-      </c>
-      <c r="H17" s="2" t="n"/>
-      <c r="I17" s="2" t="n"/>
-      <c r="J17" s="2" t="n"/>
-      <c r="K17" s="2" t="n"/>
-      <c r="L17" s="2" t="n"/>
-      <c r="N17" s="2" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n"/>
-      <c r="B18" s="1" t="n"/>
-      <c r="C18" s="1" t="n"/>
-      <c r="D18" s="1" t="n"/>
-      <c r="E18" s="1" t="n"/>
-      <c r="F18" s="1" t="n"/>
-      <c r="H18" s="2" t="n"/>
-      <c r="I18" s="2" t="n"/>
-      <c r="J18" s="2" t="n"/>
-      <c r="K18" s="2" t="n"/>
-      <c r="L18" s="2" t="n"/>
-      <c r="N18" s="2" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="n"/>
-      <c r="B19" s="3" t="n"/>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="3" t="n"/>
-      <c r="E19" s="3" t="n"/>
-      <c r="F19" s="3" t="n"/>
-      <c r="H19" s="2" t="n"/>
-      <c r="I19" s="2" t="n"/>
-      <c r="J19" s="2" t="n"/>
-      <c r="K19" s="2" t="n"/>
-      <c r="L19" s="2" t="n"/>
-      <c r="N19" s="2" t="n"/>
+        <f>SUM($J$4:$J$9)</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3746,7 +3453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3785,81 +3492,77 @@
       <c r="O1" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr"/>
-      <c r="B2" s="1" t="inlineStr"/>
-      <c r="C2" s="1" t="inlineStr"/>
-      <c r="D2" s="1" t="inlineStr"/>
-      <c r="E2" s="1" t="inlineStr"/>
-      <c r="F2" s="1" t="inlineStr"/>
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="2">
-        <f>(J2-L2)</f>
-        <v/>
-      </c>
-      <c r="L2" s="2">
-        <f>COUNTIF($B$2:$F$19,H2)</f>
-        <v/>
-      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr"/>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Martes</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Miercoles</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Jueves</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Viernes</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Abrev</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Asignaturas</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Frec</t>
         </is>
       </c>
-      <c r="K3" s="2">
-        <f>(J3-L3)</f>
-        <v/>
-      </c>
-      <c r="L3" s="2">
-        <f>COUNTIF($B$2:$F$19,H3)</f>
-        <v/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Faltan</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Asignadas</t>
+        </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Aulas</t>
         </is>
@@ -3916,7 +3619,7 @@
         <v/>
       </c>
       <c r="L4" s="2">
-        <f>COUNTIF($B$2:$F$19,H4)</f>
+        <f>COUNTIF($B$4:$F$15,H4)</f>
         <v/>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -3973,7 +3676,7 @@
         <v/>
       </c>
       <c r="L5" s="2">
-        <f>COUNTIF($B$2:$F$19,H5)</f>
+        <f>COUNTIF($B$4:$F$15,H5)</f>
         <v/>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -4034,7 +3737,7 @@
         <v/>
       </c>
       <c r="L6" s="2">
-        <f>COUNTIF($B$2:$F$19,H6)</f>
+        <f>COUNTIF($B$4:$F$15,H6)</f>
         <v/>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -4091,7 +3794,7 @@
         <v/>
       </c>
       <c r="L7" s="2">
-        <f>COUNTIF($B$2:$F$19,H7)</f>
+        <f>COUNTIF($B$4:$F$15,H7)</f>
         <v/>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -4148,7 +3851,7 @@
         <v/>
       </c>
       <c r="L8" s="2">
-        <f>COUNTIF($B$2:$F$19,H8)</f>
+        <f>COUNTIF($B$4:$F$15,H8)</f>
         <v/>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -4197,7 +3900,7 @@
         <v/>
       </c>
       <c r="L9" s="2">
-        <f>COUNTIF($B$2:$F$19,H9)</f>
+        <f>COUNTIF($B$4:$F$15,H9)</f>
         <v/>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -4220,17 +3923,14 @@
       <c r="E10" s="1" t="inlineStr"/>
       <c r="F10" s="1" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr"/>
+      <c r="H10" s="2">
+        <f>COUNTA($H$4:$H$9)</f>
+        <v/>
+      </c>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2">
-        <f>(J10-L10)</f>
-        <v/>
-      </c>
-      <c r="L10" s="2">
-        <f>COUNTIF($B$2:$F$19,H10)</f>
-        <v/>
-      </c>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr">
         <is>
@@ -4353,26 +4053,23 @@
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr"/>
-      <c r="B16" s="1" t="inlineStr"/>
-      <c r="C16" s="1" t="inlineStr"/>
-      <c r="D16" s="1" t="inlineStr"/>
-      <c r="E16" s="1" t="inlineStr"/>
-      <c r="F16" s="1" t="inlineStr"/>
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
       <c r="G16">
         <f>"Total:"</f>
         <v/>
       </c>
-      <c r="H16" s="2">
-        <f>COUNTA($H$2:$H$19)</f>
-        <v/>
-      </c>
-      <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="2" t="inlineStr"/>
-      <c r="L16" s="2" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>Aula 8</t>
         </is>
@@ -4380,53 +4077,14 @@
       <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n"/>
-      <c r="B17" s="3" t="n"/>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="3" t="n"/>
-      <c r="E17" s="3" t="n"/>
-      <c r="F17" s="3">
-        <f>"Σ Frec:"</f>
+      <c r="F17">
+        <f>"Sigma Frec:"</f>
         <v/>
       </c>
       <c r="G17">
-        <f>SUM($J$2:$J$19)</f>
-        <v/>
-      </c>
-      <c r="H17" s="2" t="n"/>
-      <c r="I17" s="2" t="n"/>
-      <c r="J17" s="2" t="n"/>
-      <c r="K17" s="2" t="n"/>
-      <c r="L17" s="2" t="n"/>
-      <c r="N17" s="2" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n"/>
-      <c r="B18" s="1" t="n"/>
-      <c r="C18" s="1" t="n"/>
-      <c r="D18" s="1" t="n"/>
-      <c r="E18" s="1" t="n"/>
-      <c r="F18" s="1" t="n"/>
-      <c r="H18" s="2" t="n"/>
-      <c r="I18" s="2" t="n"/>
-      <c r="J18" s="2" t="n"/>
-      <c r="K18" s="2" t="n"/>
-      <c r="L18" s="2" t="n"/>
-      <c r="N18" s="2" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="n"/>
-      <c r="B19" s="3" t="n"/>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="3" t="n"/>
-      <c r="E19" s="3" t="n"/>
-      <c r="F19" s="3" t="n"/>
-      <c r="H19" s="2" t="n"/>
-      <c r="I19" s="2" t="n"/>
-      <c r="J19" s="2" t="n"/>
-      <c r="K19" s="2" t="n"/>
-      <c r="L19" s="2" t="n"/>
-      <c r="N19" s="2" t="n"/>
+        <f>SUM($J$4:$J$9)</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4439,7 +4097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4478,81 +4136,77 @@
       <c r="O1" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr"/>
-      <c r="B2" s="1" t="inlineStr"/>
-      <c r="C2" s="1" t="inlineStr"/>
-      <c r="D2" s="1" t="inlineStr"/>
-      <c r="E2" s="1" t="inlineStr"/>
-      <c r="F2" s="1" t="inlineStr"/>
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="2">
-        <f>(J2-L2)</f>
-        <v/>
-      </c>
-      <c r="L2" s="2">
-        <f>COUNTIF($B$2:$F$19,H2)</f>
-        <v/>
-      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr"/>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Martes</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Miercoles</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Jueves</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Viernes</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Abrev</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Asignaturas</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Frec</t>
         </is>
       </c>
-      <c r="K3" s="2">
-        <f>(J3-L3)</f>
-        <v/>
-      </c>
-      <c r="L3" s="2">
-        <f>COUNTIF($B$2:$F$19,H3)</f>
-        <v/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Faltan</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Asignadas</t>
+        </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Aulas</t>
         </is>
@@ -4589,7 +4243,7 @@
         <v/>
       </c>
       <c r="L4" s="2">
-        <f>COUNTIF($B$2:$F$19,H4)</f>
+        <f>COUNTIF($B$4:$F$15,H4)</f>
         <v/>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -4626,7 +4280,7 @@
         <v/>
       </c>
       <c r="L5" s="2">
-        <f>COUNTIF($B$2:$F$19,H5)</f>
+        <f>COUNTIF($B$4:$F$15,H5)</f>
         <v/>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -4667,7 +4321,7 @@
         <v/>
       </c>
       <c r="L6" s="2">
-        <f>COUNTIF($B$2:$F$19,H6)</f>
+        <f>COUNTIF($B$4:$F$15,H6)</f>
         <v/>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -4704,7 +4358,7 @@
         <v/>
       </c>
       <c r="L7" s="2">
-        <f>COUNTIF($B$2:$F$19,H7)</f>
+        <f>COUNTIF($B$4:$F$15,H7)</f>
         <v/>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -4753,7 +4407,7 @@
         <v/>
       </c>
       <c r="L8" s="2">
-        <f>COUNTIF($B$2:$F$19,H8)</f>
+        <f>COUNTIF($B$4:$F$15,H8)</f>
         <v/>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -4798,7 +4452,7 @@
         <v/>
       </c>
       <c r="L9" s="2">
-        <f>COUNTIF($B$2:$F$19,H9)</f>
+        <f>COUNTIF($B$4:$F$15,H9)</f>
         <v/>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -4837,17 +4491,14 @@
       </c>
       <c r="F10" s="1" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr"/>
+      <c r="H10" s="2">
+        <f>COUNTA($H$4:$H$9)</f>
+        <v/>
+      </c>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2">
-        <f>(J10-L10)</f>
-        <v/>
-      </c>
-      <c r="L10" s="2">
-        <f>COUNTIF($B$2:$F$19,H10)</f>
-        <v/>
-      </c>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr">
         <is>
@@ -5014,74 +4665,20 @@
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n"/>
-      <c r="B16" s="1" t="n"/>
-      <c r="C16" s="1" t="n"/>
-      <c r="D16" s="1" t="n"/>
-      <c r="E16" s="1" t="n"/>
-      <c r="F16" s="1" t="n"/>
       <c r="G16">
         <f>"Total:"</f>
         <v/>
       </c>
-      <c r="H16" s="2">
-        <f>COUNTA($H$2:$H$19)</f>
-        <v/>
-      </c>
-      <c r="I16" s="2" t="n"/>
-      <c r="J16" s="2" t="n"/>
-      <c r="K16" s="2" t="n"/>
-      <c r="L16" s="2" t="n"/>
-      <c r="N16" s="2" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n"/>
-      <c r="B17" s="3" t="n"/>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="3" t="n"/>
-      <c r="E17" s="3" t="n"/>
-      <c r="F17" s="3">
-        <f>"Σ Frec:"</f>
+      <c r="F17">
+        <f>"Sigma Frec:"</f>
         <v/>
       </c>
       <c r="G17">
-        <f>SUM($J$2:$J$19)</f>
-        <v/>
-      </c>
-      <c r="H17" s="2" t="n"/>
-      <c r="I17" s="2" t="n"/>
-      <c r="J17" s="2" t="n"/>
-      <c r="K17" s="2" t="n"/>
-      <c r="L17" s="2" t="n"/>
-      <c r="N17" s="2" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n"/>
-      <c r="B18" s="1" t="n"/>
-      <c r="C18" s="1" t="n"/>
-      <c r="D18" s="1" t="n"/>
-      <c r="E18" s="1" t="n"/>
-      <c r="F18" s="1" t="n"/>
-      <c r="H18" s="2" t="n"/>
-      <c r="I18" s="2" t="n"/>
-      <c r="J18" s="2" t="n"/>
-      <c r="K18" s="2" t="n"/>
-      <c r="L18" s="2" t="n"/>
-      <c r="N18" s="2" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="n"/>
-      <c r="B19" s="3" t="n"/>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="3" t="n"/>
-      <c r="E19" s="3" t="n"/>
-      <c r="F19" s="3" t="n"/>
-      <c r="H19" s="2" t="n"/>
-      <c r="I19" s="2" t="n"/>
-      <c r="J19" s="2" t="n"/>
-      <c r="K19" s="2" t="n"/>
-      <c r="L19" s="2" t="n"/>
-      <c r="N19" s="2" t="n"/>
+        <f>SUM($J$4:$J$9)</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5094,7 +4691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5133,81 +4730,77 @@
       <c r="O1" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr"/>
-      <c r="B2" s="1" t="inlineStr"/>
-      <c r="C2" s="1" t="inlineStr"/>
-      <c r="D2" s="1" t="inlineStr"/>
-      <c r="E2" s="1" t="inlineStr"/>
-      <c r="F2" s="1" t="inlineStr"/>
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="2">
-        <f>(J2-L2)</f>
-        <v/>
-      </c>
-      <c r="L2" s="2">
-        <f>COUNTIF($B$2:$F$19,H2)</f>
-        <v/>
-      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr"/>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Martes</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Miercoles</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Jueves</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Viernes</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Abrev</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Asignaturas</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Frec</t>
         </is>
       </c>
-      <c r="K3" s="2">
-        <f>(J3-L3)</f>
-        <v/>
-      </c>
-      <c r="L3" s="2">
-        <f>COUNTIF($B$2:$F$19,H3)</f>
-        <v/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Faltan</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Asignadas</t>
+        </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Aulas</t>
         </is>
@@ -5264,7 +4857,7 @@
         <v/>
       </c>
       <c r="L4" s="2">
-        <f>COUNTIF($B$2:$F$19,H4)</f>
+        <f>COUNTIF($B$4:$F$15,H4)</f>
         <v/>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -5321,7 +4914,7 @@
         <v/>
       </c>
       <c r="L5" s="2">
-        <f>COUNTIF($B$2:$F$19,H5)</f>
+        <f>COUNTIF($B$4:$F$15,H5)</f>
         <v/>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -5382,7 +4975,7 @@
         <v/>
       </c>
       <c r="L6" s="2">
-        <f>COUNTIF($B$2:$F$19,H6)</f>
+        <f>COUNTIF($B$4:$F$15,H6)</f>
         <v/>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -5439,7 +5032,7 @@
         <v/>
       </c>
       <c r="L7" s="2">
-        <f>COUNTIF($B$2:$F$19,H7)</f>
+        <f>COUNTIF($B$4:$F$15,H7)</f>
         <v/>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -5496,7 +5089,7 @@
         <v/>
       </c>
       <c r="L8" s="2">
-        <f>COUNTIF($B$2:$F$19,H8)</f>
+        <f>COUNTIF($B$4:$F$15,H8)</f>
         <v/>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -5549,7 +5142,7 @@
         <v/>
       </c>
       <c r="L9" s="2">
-        <f>COUNTIF($B$2:$F$19,H9)</f>
+        <f>COUNTIF($B$4:$F$15,H9)</f>
         <v/>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -5572,17 +5165,14 @@
       <c r="E10" s="1" t="inlineStr"/>
       <c r="F10" s="1" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr"/>
+      <c r="H10" s="2">
+        <f>COUNTA($H$4:$H$9)</f>
+        <v/>
+      </c>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2">
-        <f>(J10-L10)</f>
-        <v/>
-      </c>
-      <c r="L10" s="2">
-        <f>COUNTIF($B$2:$F$19,H10)</f>
-        <v/>
-      </c>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr">
         <is>
@@ -5705,26 +5295,23 @@
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr"/>
-      <c r="B16" s="1" t="inlineStr"/>
-      <c r="C16" s="1" t="inlineStr"/>
-      <c r="D16" s="1" t="inlineStr"/>
-      <c r="E16" s="1" t="inlineStr"/>
-      <c r="F16" s="1" t="inlineStr"/>
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
       <c r="G16">
         <f>"Total:"</f>
         <v/>
       </c>
-      <c r="H16" s="2">
-        <f>COUNTA($H$2:$H$19)</f>
-        <v/>
-      </c>
-      <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="2" t="inlineStr"/>
-      <c r="L16" s="2" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>Aula 4</t>
         </is>
@@ -5732,59 +5319,31 @@
       <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr"/>
-      <c r="B17" s="3" t="inlineStr"/>
-      <c r="C17" s="3" t="inlineStr"/>
-      <c r="D17" s="3" t="inlineStr"/>
-      <c r="E17" s="3" t="inlineStr"/>
-      <c r="F17" s="3">
-        <f>"Σ Frec:"</f>
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17">
+        <f>"Sigma Frec:"</f>
         <v/>
       </c>
       <c r="G17">
-        <f>SUM($J$2:$J$19)</f>
-        <v/>
-      </c>
-      <c r="H17" s="2" t="inlineStr"/>
-      <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr"/>
-      <c r="K17" s="2" t="inlineStr"/>
-      <c r="L17" s="2" t="inlineStr"/>
+        <f>SUM($J$4:$J$9)</f>
+        <v/>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>Aula 4</t>
         </is>
       </c>
       <c r="O17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n"/>
-      <c r="B18" s="1" t="n"/>
-      <c r="C18" s="1" t="n"/>
-      <c r="D18" s="1" t="n"/>
-      <c r="E18" s="1" t="n"/>
-      <c r="F18" s="1" t="n"/>
-      <c r="H18" s="2" t="n"/>
-      <c r="I18" s="2" t="n"/>
-      <c r="J18" s="2" t="n"/>
-      <c r="K18" s="2" t="n"/>
-      <c r="L18" s="2" t="n"/>
-      <c r="N18" s="2" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="n"/>
-      <c r="B19" s="3" t="n"/>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="3" t="n"/>
-      <c r="E19" s="3" t="n"/>
-      <c r="F19" s="3" t="n"/>
-      <c r="H19" s="2" t="n"/>
-      <c r="I19" s="2" t="n"/>
-      <c r="J19" s="2" t="n"/>
-      <c r="K19" s="2" t="n"/>
-      <c r="L19" s="2" t="n"/>
-      <c r="N19" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5797,7 +5356,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5836,81 +5395,77 @@
       <c r="O1" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr"/>
-      <c r="B2" s="1" t="inlineStr"/>
-      <c r="C2" s="1" t="inlineStr"/>
-      <c r="D2" s="1" t="inlineStr"/>
-      <c r="E2" s="1" t="inlineStr"/>
-      <c r="F2" s="1" t="inlineStr"/>
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="2">
-        <f>(J2-L2)</f>
-        <v/>
-      </c>
-      <c r="L2" s="2">
-        <f>COUNTIF($B$2:$F$19,H2)</f>
-        <v/>
-      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr"/>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Martes</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Miercoles</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Jueves</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Viernes</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Abrev</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Asignaturas</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Frec</t>
         </is>
       </c>
-      <c r="K3" s="2">
-        <f>(J3-L3)</f>
-        <v/>
-      </c>
-      <c r="L3" s="2">
-        <f>COUNTIF($B$2:$F$19,H3)</f>
-        <v/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Faltan</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Asignadas</t>
+        </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Aulas</t>
         </is>
@@ -5947,7 +5502,7 @@
         <v/>
       </c>
       <c r="L4" s="2">
-        <f>COUNTIF($B$2:$F$19,H4)</f>
+        <f>COUNTIF($B$4:$F$15,H4)</f>
         <v/>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -5984,7 +5539,7 @@
         <v/>
       </c>
       <c r="L5" s="2">
-        <f>COUNTIF($B$2:$F$19,H5)</f>
+        <f>COUNTIF($B$4:$F$15,H5)</f>
         <v/>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -6025,7 +5580,7 @@
         <v/>
       </c>
       <c r="L6" s="2">
-        <f>COUNTIF($B$2:$F$19,H6)</f>
+        <f>COUNTIF($B$4:$F$15,H6)</f>
         <v/>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -6062,7 +5617,7 @@
         <v/>
       </c>
       <c r="L7" s="2">
-        <f>COUNTIF($B$2:$F$19,H7)</f>
+        <f>COUNTIF($B$4:$F$15,H7)</f>
         <v/>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -6103,7 +5658,7 @@
         <v/>
       </c>
       <c r="L8" s="2">
-        <f>COUNTIF($B$2:$F$19,H8)</f>
+        <f>COUNTIF($B$4:$F$15,H8)</f>
         <v/>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -6140,7 +5695,7 @@
         <v/>
       </c>
       <c r="L9" s="2">
-        <f>COUNTIF($B$2:$F$19,H9)</f>
+        <f>COUNTIF($B$4:$F$15,H9)</f>
         <v/>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -6179,17 +5734,14 @@
       </c>
       <c r="F10" s="1" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr"/>
+      <c r="H10" s="2">
+        <f>COUNTA($H$4:$H$9)</f>
+        <v/>
+      </c>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2">
-        <f>(J10-L10)</f>
-        <v/>
-      </c>
-      <c r="L10" s="2">
-        <f>COUNTIF($B$2:$F$19,H10)</f>
-        <v/>
-      </c>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr">
         <is>
@@ -6368,74 +5920,20 @@
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n"/>
-      <c r="B16" s="1" t="n"/>
-      <c r="C16" s="1" t="n"/>
-      <c r="D16" s="1" t="n"/>
-      <c r="E16" s="1" t="n"/>
-      <c r="F16" s="1" t="n"/>
       <c r="G16">
         <f>"Total:"</f>
         <v/>
       </c>
-      <c r="H16" s="2">
-        <f>COUNTA($H$2:$H$19)</f>
-        <v/>
-      </c>
-      <c r="I16" s="2" t="n"/>
-      <c r="J16" s="2" t="n"/>
-      <c r="K16" s="2" t="n"/>
-      <c r="L16" s="2" t="n"/>
-      <c r="N16" s="2" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n"/>
-      <c r="B17" s="3" t="n"/>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="3" t="n"/>
-      <c r="E17" s="3" t="n"/>
-      <c r="F17" s="3">
-        <f>"Σ Frec:"</f>
+      <c r="F17">
+        <f>"Sigma Frec:"</f>
         <v/>
       </c>
       <c r="G17">
-        <f>SUM($J$2:$J$19)</f>
-        <v/>
-      </c>
-      <c r="H17" s="2" t="n"/>
-      <c r="I17" s="2" t="n"/>
-      <c r="J17" s="2" t="n"/>
-      <c r="K17" s="2" t="n"/>
-      <c r="L17" s="2" t="n"/>
-      <c r="N17" s="2" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n"/>
-      <c r="B18" s="1" t="n"/>
-      <c r="C18" s="1" t="n"/>
-      <c r="D18" s="1" t="n"/>
-      <c r="E18" s="1" t="n"/>
-      <c r="F18" s="1" t="n"/>
-      <c r="H18" s="2" t="n"/>
-      <c r="I18" s="2" t="n"/>
-      <c r="J18" s="2" t="n"/>
-      <c r="K18" s="2" t="n"/>
-      <c r="L18" s="2" t="n"/>
-      <c r="N18" s="2" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="n"/>
-      <c r="B19" s="3" t="n"/>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="3" t="n"/>
-      <c r="E19" s="3" t="n"/>
-      <c r="F19" s="3" t="n"/>
-      <c r="H19" s="2" t="n"/>
-      <c r="I19" s="2" t="n"/>
-      <c r="J19" s="2" t="n"/>
-      <c r="K19" s="2" t="n"/>
-      <c r="L19" s="2" t="n"/>
-      <c r="N19" s="2" t="n"/>
+        <f>SUM($J$4:$J$9)</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6448,7 +5946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L40"/>
+  <dimension ref="A1:L39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6811,47 +6309,17 @@
       <c r="L7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr"/>
-      <c r="B8" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$B$17="Aula 1",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$17="Aula 1",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$17="Aula 1",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$17="Aula 1",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$17="Aula 1",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$17="Aula 1",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$17="Aula 1",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$17="Aula 1",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$17="Aula 1",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$17="Aula 1",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$17="Aula 1",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$17="Aula 1",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$17="Aula 1",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$17="Aula 1",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$17="Aula 1",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$17="Aula 1",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$17="Aula 1",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="C8" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$B$17="Aula 2",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$17="Aula 2",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$17="Aula 2",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$17="Aula 2",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$17="Aula 2",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$17="Aula 2",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$17="Aula 2",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$17="Aula 2",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$17="Aula 2",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$17="Aula 2",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$17="Aula 2",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$17="Aula 2",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$17="Aula 2",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$17="Aula 2",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$17="Aula 2",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$17="Aula 2",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$17="Aula 2",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="D8" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$B$17="Aula 3",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$17="Aula 3",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$17="Aula 3",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$17="Aula 3",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$17="Aula 3",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$17="Aula 3",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$17="Aula 3",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$17="Aula 3",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$17="Aula 3",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$17="Aula 3",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$17="Aula 3",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$17="Aula 3",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$17="Aula 3",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$17="Aula 3",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$17="Aula 3",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$17="Aula 3",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$17="Aula 3",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="E8" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$B$17="Aula 4",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$17="Aula 4",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$17="Aula 4",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$17="Aula 4",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$17="Aula 4",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$17="Aula 4",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$17="Aula 4",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$17="Aula 4",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$17="Aula 4",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$17="Aula 4",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$17="Aula 4",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$17="Aula 4",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$17="Aula 4",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$17="Aula 4",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$17="Aula 4",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$17="Aula 4",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$17="Aula 4",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="F8" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$B$17="Aula 5",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$17="Aula 5",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$17="Aula 5",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$17="Aula 5",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$17="Aula 5",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$17="Aula 5",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$17="Aula 5",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$17="Aula 5",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$17="Aula 5",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$17="Aula 5",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$17="Aula 5",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$17="Aula 5",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$17="Aula 5",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$17="Aula 5",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$17="Aula 5",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$17="Aula 5",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$17="Aula 5",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="G8" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$B$17="Aula 6",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$17="Aula 6",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$17="Aula 6",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$17="Aula 6",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$17="Aula 6",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$17="Aula 6",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$17="Aula 6",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$17="Aula 6",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$17="Aula 6",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$17="Aula 6",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$17="Aula 6",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$17="Aula 6",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$17="Aula 6",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$17="Aula 6",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$17="Aula 6",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$17="Aula 6",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$17="Aula 6",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="H8" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$B$17="Aula 7",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$17="Aula 7",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$17="Aula 7",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$17="Aula 7",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$17="Aula 7",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$17="Aula 7",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$17="Aula 7",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$17="Aula 7",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$17="Aula 7",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$17="Aula 7",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$17="Aula 7",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$17="Aula 7",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$17="Aula 7",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$17="Aula 7",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$17="Aula 7",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$17="Aula 7",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$17="Aula 7",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="I8" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$B$17="Aula 8",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$17="Aula 8",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$17="Aula 8",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$17="Aula 8",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$17="Aula 8",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$17="Aula 8",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$17="Aula 8",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$17="Aula 8",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$17="Aula 8",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$17="Aula 8",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$17="Aula 8",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$17="Aula 8",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$17="Aula 8",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$17="Aula 8",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$17="Aula 8",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$17="Aula 8",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$17="Aula 8",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="J8" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$B$17="Aula 9",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$17="Aula 9",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$17="Aula 9",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$17="Aula 9",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$17="Aula 9",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$17="Aula 9",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$17="Aula 9",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$17="Aula 9",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$17="Aula 9",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$17="Aula 9",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$17="Aula 9",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$17="Aula 9",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$17="Aula 9",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$17="Aula 9",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$17="Aula 9",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$17="Aula 9",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$17="Aula 9",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="K8" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$B$17="Lab",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$17="Lab",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$17="Lab",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$17="Lab",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$17="Lab",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$17="Lab",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$17="Lab",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$17="Lab",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$17="Lab",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$17="Lab",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$17="Lab",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$17="Lab",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$17="Lab",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$17="Lab",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$17="Lab",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$17="Lab",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$17="Lab",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
     </row>
     <row r="9">
@@ -7201,47 +6669,17 @@
       <c r="L15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr"/>
-      <c r="B16" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$C$17="Aula 1",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$17="Aula 1",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$17="Aula 1",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$17="Aula 1",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$17="Aula 1",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$17="Aula 1",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$17="Aula 1",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$17="Aula 1",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$17="Aula 1",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$17="Aula 1",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$17="Aula 1",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$17="Aula 1",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$17="Aula 1",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$17="Aula 1",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$17="Aula 1",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$17="Aula 1",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$17="Aula 1",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="C16" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$C$17="Aula 2",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$17="Aula 2",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$17="Aula 2",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$17="Aula 2",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$17="Aula 2",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$17="Aula 2",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$17="Aula 2",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$17="Aula 2",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$17="Aula 2",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$17="Aula 2",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$17="Aula 2",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$17="Aula 2",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$17="Aula 2",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$17="Aula 2",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$17="Aula 2",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$17="Aula 2",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$17="Aula 2",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="D16" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$C$17="Aula 3",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$17="Aula 3",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$17="Aula 3",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$17="Aula 3",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$17="Aula 3",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$17="Aula 3",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$17="Aula 3",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$17="Aula 3",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$17="Aula 3",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$17="Aula 3",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$17="Aula 3",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$17="Aula 3",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$17="Aula 3",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$17="Aula 3",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$17="Aula 3",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$17="Aula 3",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$17="Aula 3",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="E16" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$C$17="Aula 4",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$17="Aula 4",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$17="Aula 4",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$17="Aula 4",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$17="Aula 4",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$17="Aula 4",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$17="Aula 4",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$17="Aula 4",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$17="Aula 4",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$17="Aula 4",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$17="Aula 4",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$17="Aula 4",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$17="Aula 4",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$17="Aula 4",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$17="Aula 4",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$17="Aula 4",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$17="Aula 4",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="F16" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$C$17="Aula 5",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$17="Aula 5",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$17="Aula 5",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$17="Aula 5",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$17="Aula 5",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$17="Aula 5",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$17="Aula 5",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$17="Aula 5",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$17="Aula 5",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$17="Aula 5",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$17="Aula 5",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$17="Aula 5",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$17="Aula 5",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$17="Aula 5",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$17="Aula 5",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$17="Aula 5",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$17="Aula 5",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="G16" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$C$17="Aula 6",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$17="Aula 6",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$17="Aula 6",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$17="Aula 6",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$17="Aula 6",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$17="Aula 6",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$17="Aula 6",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$17="Aula 6",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$17="Aula 6",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$17="Aula 6",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$17="Aula 6",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$17="Aula 6",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$17="Aula 6",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$17="Aula 6",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$17="Aula 6",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$17="Aula 6",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$17="Aula 6",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="H16" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$C$17="Aula 7",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$17="Aula 7",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$17="Aula 7",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$17="Aula 7",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$17="Aula 7",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$17="Aula 7",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$17="Aula 7",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$17="Aula 7",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$17="Aula 7",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$17="Aula 7",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$17="Aula 7",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$17="Aula 7",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$17="Aula 7",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$17="Aula 7",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$17="Aula 7",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$17="Aula 7",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$17="Aula 7",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="I16" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$C$17="Aula 8",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$17="Aula 8",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$17="Aula 8",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$17="Aula 8",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$17="Aula 8",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$17="Aula 8",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$17="Aula 8",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$17="Aula 8",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$17="Aula 8",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$17="Aula 8",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$17="Aula 8",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$17="Aula 8",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$17="Aula 8",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$17="Aula 8",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$17="Aula 8",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$17="Aula 8",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$17="Aula 8",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="J16" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$C$17="Aula 9",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$17="Aula 9",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$17="Aula 9",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$17="Aula 9",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$17="Aula 9",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$17="Aula 9",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$17="Aula 9",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$17="Aula 9",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$17="Aula 9",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$17="Aula 9",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$17="Aula 9",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$17="Aula 9",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$17="Aula 9",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$17="Aula 9",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$17="Aula 9",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$17="Aula 9",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$17="Aula 9",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="K16" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$C$17="Lab",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$17="Lab",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$17="Lab",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$17="Lab",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$17="Lab",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$17="Lab",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$17="Lab",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$17="Lab",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$17="Lab",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$17="Lab",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$17="Lab",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$17="Lab",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$17="Lab",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$17="Lab",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$17="Lab",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$17="Lab",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$17="Lab",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
     </row>
     <row r="17">
@@ -7591,47 +7029,17 @@
       <c r="L23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr"/>
-      <c r="B24" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$D$17="Aula 1",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$17="Aula 1",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$17="Aula 1",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$17="Aula 1",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$17="Aula 1",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$17="Aula 1",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$17="Aula 1",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$17="Aula 1",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$17="Aula 1",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$17="Aula 1",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$17="Aula 1",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$17="Aula 1",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$17="Aula 1",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$17="Aula 1",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$17="Aula 1",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$17="Aula 1",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$17="Aula 1",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="C24" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$D$17="Aula 2",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$17="Aula 2",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$17="Aula 2",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$17="Aula 2",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$17="Aula 2",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$17="Aula 2",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$17="Aula 2",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$17="Aula 2",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$17="Aula 2",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$17="Aula 2",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$17="Aula 2",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$17="Aula 2",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$17="Aula 2",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$17="Aula 2",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$17="Aula 2",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$17="Aula 2",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$17="Aula 2",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="D24" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$D$17="Aula 3",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$17="Aula 3",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$17="Aula 3",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$17="Aula 3",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$17="Aula 3",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$17="Aula 3",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$17="Aula 3",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$17="Aula 3",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$17="Aula 3",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$17="Aula 3",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$17="Aula 3",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$17="Aula 3",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$17="Aula 3",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$17="Aula 3",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$17="Aula 3",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$17="Aula 3",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$17="Aula 3",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="E24" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$D$17="Aula 4",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$17="Aula 4",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$17="Aula 4",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$17="Aula 4",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$17="Aula 4",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$17="Aula 4",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$17="Aula 4",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$17="Aula 4",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$17="Aula 4",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$17="Aula 4",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$17="Aula 4",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$17="Aula 4",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$17="Aula 4",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$17="Aula 4",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$17="Aula 4",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$17="Aula 4",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$17="Aula 4",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="F24" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$D$17="Aula 5",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$17="Aula 5",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$17="Aula 5",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$17="Aula 5",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$17="Aula 5",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$17="Aula 5",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$17="Aula 5",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$17="Aula 5",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$17="Aula 5",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$17="Aula 5",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$17="Aula 5",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$17="Aula 5",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$17="Aula 5",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$17="Aula 5",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$17="Aula 5",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$17="Aula 5",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$17="Aula 5",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="G24" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$D$17="Aula 6",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$17="Aula 6",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$17="Aula 6",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$17="Aula 6",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$17="Aula 6",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$17="Aula 6",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$17="Aula 6",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$17="Aula 6",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$17="Aula 6",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$17="Aula 6",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$17="Aula 6",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$17="Aula 6",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$17="Aula 6",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$17="Aula 6",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$17="Aula 6",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$17="Aula 6",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$17="Aula 6",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="H24" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$D$17="Aula 7",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$17="Aula 7",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$17="Aula 7",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$17="Aula 7",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$17="Aula 7",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$17="Aula 7",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$17="Aula 7",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$17="Aula 7",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$17="Aula 7",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$17="Aula 7",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$17="Aula 7",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$17="Aula 7",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$17="Aula 7",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$17="Aula 7",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$17="Aula 7",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$17="Aula 7",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$17="Aula 7",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="I24" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$D$17="Aula 8",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$17="Aula 8",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$17="Aula 8",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$17="Aula 8",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$17="Aula 8",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$17="Aula 8",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$17="Aula 8",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$17="Aula 8",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$17="Aula 8",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$17="Aula 8",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$17="Aula 8",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$17="Aula 8",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$17="Aula 8",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$17="Aula 8",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$17="Aula 8",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$17="Aula 8",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$17="Aula 8",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="J24" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$D$17="Aula 9",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$17="Aula 9",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$17="Aula 9",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$17="Aula 9",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$17="Aula 9",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$17="Aula 9",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$17="Aula 9",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$17="Aula 9",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$17="Aula 9",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$17="Aula 9",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$17="Aula 9",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$17="Aula 9",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$17="Aula 9",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$17="Aula 9",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$17="Aula 9",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$17="Aula 9",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$17="Aula 9",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="K24" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$D$17="Lab",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$17="Lab",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$17="Lab",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$17="Lab",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$17="Lab",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$17="Lab",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$17="Lab",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$17="Lab",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$17="Lab",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$17="Lab",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$17="Lab",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$17="Lab",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$17="Lab",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$17="Lab",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$17="Lab",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$17="Lab",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$17="Lab",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
     </row>
     <row r="25">
@@ -7981,47 +7389,17 @@
       <c r="L31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr"/>
-      <c r="B32" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$E$17="Aula 1",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$17="Aula 1",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$17="Aula 1",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$17="Aula 1",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$17="Aula 1",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$17="Aula 1",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$17="Aula 1",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$17="Aula 1",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$17="Aula 1",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$17="Aula 1",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$17="Aula 1",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$17="Aula 1",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$17="Aula 1",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$17="Aula 1",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$17="Aula 1",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$17="Aula 1",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$17="Aula 1",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="C32" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$E$17="Aula 2",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$17="Aula 2",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$17="Aula 2",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$17="Aula 2",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$17="Aula 2",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$17="Aula 2",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$17="Aula 2",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$17="Aula 2",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$17="Aula 2",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$17="Aula 2",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$17="Aula 2",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$17="Aula 2",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$17="Aula 2",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$17="Aula 2",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$17="Aula 2",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$17="Aula 2",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$17="Aula 2",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="D32" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$E$17="Aula 3",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$17="Aula 3",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$17="Aula 3",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$17="Aula 3",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$17="Aula 3",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$17="Aula 3",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$17="Aula 3",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$17="Aula 3",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$17="Aula 3",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$17="Aula 3",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$17="Aula 3",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$17="Aula 3",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$17="Aula 3",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$17="Aula 3",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$17="Aula 3",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$17="Aula 3",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$17="Aula 3",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="E32" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$E$17="Aula 4",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$17="Aula 4",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$17="Aula 4",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$17="Aula 4",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$17="Aula 4",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$17="Aula 4",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$17="Aula 4",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$17="Aula 4",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$17="Aula 4",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$17="Aula 4",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$17="Aula 4",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$17="Aula 4",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$17="Aula 4",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$17="Aula 4",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$17="Aula 4",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$17="Aula 4",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$17="Aula 4",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="F32" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$E$17="Aula 5",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$17="Aula 5",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$17="Aula 5",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$17="Aula 5",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$17="Aula 5",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$17="Aula 5",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$17="Aula 5",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$17="Aula 5",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$17="Aula 5",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$17="Aula 5",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$17="Aula 5",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$17="Aula 5",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$17="Aula 5",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$17="Aula 5",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$17="Aula 5",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$17="Aula 5",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$17="Aula 5",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="G32" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$E$17="Aula 6",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$17="Aula 6",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$17="Aula 6",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$17="Aula 6",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$17="Aula 6",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$17="Aula 6",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$17="Aula 6",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$17="Aula 6",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$17="Aula 6",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$17="Aula 6",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$17="Aula 6",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$17="Aula 6",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$17="Aula 6",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$17="Aula 6",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$17="Aula 6",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$17="Aula 6",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$17="Aula 6",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="H32" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$E$17="Aula 7",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$17="Aula 7",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$17="Aula 7",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$17="Aula 7",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$17="Aula 7",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$17="Aula 7",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$17="Aula 7",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$17="Aula 7",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$17="Aula 7",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$17="Aula 7",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$17="Aula 7",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$17="Aula 7",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$17="Aula 7",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$17="Aula 7",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$17="Aula 7",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$17="Aula 7",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$17="Aula 7",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="I32" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$E$17="Aula 8",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$17="Aula 8",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$17="Aula 8",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$17="Aula 8",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$17="Aula 8",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$17="Aula 8",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$17="Aula 8",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$17="Aula 8",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$17="Aula 8",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$17="Aula 8",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$17="Aula 8",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$17="Aula 8",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$17="Aula 8",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$17="Aula 8",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$17="Aula 8",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$17="Aula 8",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$17="Aula 8",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="J32" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$E$17="Aula 9",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$17="Aula 9",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$17="Aula 9",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$17="Aula 9",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$17="Aula 9",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$17="Aula 9",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$17="Aula 9",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$17="Aula 9",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$17="Aula 9",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$17="Aula 9",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$17="Aula 9",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$17="Aula 9",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$17="Aula 9",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$17="Aula 9",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$17="Aula 9",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$17="Aula 9",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$17="Aula 9",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="K32" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$E$17="Lab",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$17="Lab",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$17="Lab",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$17="Lab",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$17="Lab",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$17="Lab",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$17="Lab",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$17="Lab",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$17="Lab",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$17="Lab",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$17="Lab",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$17="Lab",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$17="Lab",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$17="Lab",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$17="Lab",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$17="Lab",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$17="Lab",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
     </row>
     <row r="33">
@@ -8369,49 +7747,6 @@
         <v/>
       </c>
       <c r="L39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="n"/>
-      <c r="B40" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$F$17="Aula 1",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$17="Aula 1",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$17="Aula 1",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$17="Aula 1",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$17="Aula 1",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$17="Aula 1",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$17="Aula 1",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$17="Aula 1",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$17="Aula 1",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$17="Aula 1",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$17="Aula 1",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$17="Aula 1",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$17="Aula 1",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$17="Aula 1",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$17="Aula 1",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$17="Aula 1",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$17="Aula 1",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="C40" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$F$17="Aula 2",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$17="Aula 2",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$17="Aula 2",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$17="Aula 2",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$17="Aula 2",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$17="Aula 2",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$17="Aula 2",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$17="Aula 2",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$17="Aula 2",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$17="Aula 2",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$17="Aula 2",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$17="Aula 2",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$17="Aula 2",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$17="Aula 2",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$17="Aula 2",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$17="Aula 2",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$17="Aula 2",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="D40" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$F$17="Aula 3",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$17="Aula 3",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$17="Aula 3",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$17="Aula 3",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$17="Aula 3",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$17="Aula 3",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$17="Aula 3",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$17="Aula 3",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$17="Aula 3",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$17="Aula 3",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$17="Aula 3",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$17="Aula 3",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$17="Aula 3",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$17="Aula 3",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$17="Aula 3",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$17="Aula 3",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$17="Aula 3",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="E40" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$F$17="Aula 4",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$17="Aula 4",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$17="Aula 4",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$17="Aula 4",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$17="Aula 4",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$17="Aula 4",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$17="Aula 4",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$17="Aula 4",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$17="Aula 4",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$17="Aula 4",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$17="Aula 4",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$17="Aula 4",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$17="Aula 4",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$17="Aula 4",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$17="Aula 4",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$17="Aula 4",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$17="Aula 4",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="F40" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$F$17="Aula 5",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$17="Aula 5",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$17="Aula 5",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$17="Aula 5",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$17="Aula 5",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$17="Aula 5",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$17="Aula 5",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$17="Aula 5",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$17="Aula 5",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$17="Aula 5",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$17="Aula 5",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$17="Aula 5",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$17="Aula 5",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$17="Aula 5",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$17="Aula 5",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$17="Aula 5",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$17="Aula 5",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="G40" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$F$17="Aula 6",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$17="Aula 6",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$17="Aula 6",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$17="Aula 6",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$17="Aula 6",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$17="Aula 6",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$17="Aula 6",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$17="Aula 6",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$17="Aula 6",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$17="Aula 6",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$17="Aula 6",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$17="Aula 6",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$17="Aula 6",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$17="Aula 6",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$17="Aula 6",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$17="Aula 6",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$17="Aula 6",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="H40" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$F$17="Aula 7",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$17="Aula 7",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$17="Aula 7",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$17="Aula 7",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$17="Aula 7",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$17="Aula 7",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$17="Aula 7",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$17="Aula 7",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$17="Aula 7",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$17="Aula 7",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$17="Aula 7",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$17="Aula 7",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$17="Aula 7",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$17="Aula 7",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$17="Aula 7",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$17="Aula 7",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$17="Aula 7",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="I40" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$F$17="Aula 8",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$17="Aula 8",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$17="Aula 8",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$17="Aula 8",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$17="Aula 8",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$17="Aula 8",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$17="Aula 8",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$17="Aula 8",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$17="Aula 8",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$17="Aula 8",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$17="Aula 8",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$17="Aula 8",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$17="Aula 8",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$17="Aula 8",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$17="Aula 8",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$17="Aula 8",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$17="Aula 8",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="J40" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$F$17="Aula 9",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$17="Aula 9",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$17="Aula 9",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$17="Aula 9",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$17="Aula 9",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$17="Aula 9",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$17="Aula 9",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$17="Aula 9",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$17="Aula 9",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$17="Aula 9",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$17="Aula 9",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$17="Aula 9",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$17="Aula 9",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$17="Aula 9",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$17="Aula 9",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$17="Aula 9",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$17="Aula 9",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="K40" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$F$17="Lab",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$17="Lab",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$17="Lab",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$17="Lab",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$17="Lab",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$17="Lab",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$17="Lab",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$17="Lab",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$17="Lab",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$17="Lab",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$17="Lab",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$17="Lab",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$17="Lab",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$17="Lab",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$17="Lab",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$17="Lab",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$17="Lab",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8424,7 +7759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8463,81 +7798,77 @@
       <c r="O1" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr"/>
-      <c r="B2" s="1" t="inlineStr"/>
-      <c r="C2" s="1" t="inlineStr"/>
-      <c r="D2" s="1" t="inlineStr"/>
-      <c r="E2" s="1" t="inlineStr"/>
-      <c r="F2" s="1" t="inlineStr"/>
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="2">
-        <f>(J2-L2)</f>
-        <v/>
-      </c>
-      <c r="L2" s="2">
-        <f>COUNTIF($B$2:$F$19,H2)</f>
-        <v/>
-      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr"/>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Martes</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Miercoles</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Jueves</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Viernes</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Abrev</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Asignaturas</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Frec</t>
         </is>
       </c>
-      <c r="K3" s="2">
-        <f>(J3-L3)</f>
-        <v/>
-      </c>
-      <c r="L3" s="2">
-        <f>COUNTIF($B$2:$F$19,H3)</f>
-        <v/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Faltan</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Asignadas</t>
+        </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Aulas</t>
         </is>
@@ -8574,7 +7905,7 @@
         <v/>
       </c>
       <c r="L4" s="2">
-        <f>COUNTIF($B$2:$F$19,H4)</f>
+        <f>COUNTIF($B$4:$F$15,H4)</f>
         <v/>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -8611,7 +7942,7 @@
         <v/>
       </c>
       <c r="L5" s="2">
-        <f>COUNTIF($B$2:$F$19,H5)</f>
+        <f>COUNTIF($B$4:$F$15,H5)</f>
         <v/>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -8652,7 +7983,7 @@
         <v/>
       </c>
       <c r="L6" s="2">
-        <f>COUNTIF($B$2:$F$19,H6)</f>
+        <f>COUNTIF($B$4:$F$15,H6)</f>
         <v/>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -8689,7 +8020,7 @@
         <v/>
       </c>
       <c r="L7" s="2">
-        <f>COUNTIF($B$2:$F$19,H7)</f>
+        <f>COUNTIF($B$4:$F$15,H7)</f>
         <v/>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -8730,7 +8061,7 @@
         <v/>
       </c>
       <c r="L8" s="2">
-        <f>COUNTIF($B$2:$F$19,H8)</f>
+        <f>COUNTIF($B$4:$F$15,H8)</f>
         <v/>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -8767,7 +8098,7 @@
         <v/>
       </c>
       <c r="L9" s="2">
-        <f>COUNTIF($B$2:$F$19,H9)</f>
+        <f>COUNTIF($B$4:$F$15,H9)</f>
         <v/>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -8806,17 +8137,14 @@
       </c>
       <c r="F10" s="1" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr"/>
+      <c r="H10" s="2">
+        <f>COUNTA($H$4:$H$9)</f>
+        <v/>
+      </c>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2">
-        <f>(J10-L10)</f>
-        <v/>
-      </c>
-      <c r="L10" s="2">
-        <f>COUNTIF($B$2:$F$19,H10)</f>
-        <v/>
-      </c>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr">
         <is>
@@ -9011,74 +8339,20 @@
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n"/>
-      <c r="B16" s="1" t="n"/>
-      <c r="C16" s="1" t="n"/>
-      <c r="D16" s="1" t="n"/>
-      <c r="E16" s="1" t="n"/>
-      <c r="F16" s="1" t="n"/>
       <c r="G16">
         <f>"Total:"</f>
         <v/>
       </c>
-      <c r="H16" s="2">
-        <f>COUNTA($H$2:$H$19)</f>
-        <v/>
-      </c>
-      <c r="I16" s="2" t="n"/>
-      <c r="J16" s="2" t="n"/>
-      <c r="K16" s="2" t="n"/>
-      <c r="L16" s="2" t="n"/>
-      <c r="N16" s="2" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n"/>
-      <c r="B17" s="3" t="n"/>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="3" t="n"/>
-      <c r="E17" s="3" t="n"/>
-      <c r="F17" s="3">
-        <f>"Σ Frec:"</f>
+      <c r="F17">
+        <f>"Sigma Frec:"</f>
         <v/>
       </c>
       <c r="G17">
-        <f>SUM($J$2:$J$19)</f>
-        <v/>
-      </c>
-      <c r="H17" s="2" t="n"/>
-      <c r="I17" s="2" t="n"/>
-      <c r="J17" s="2" t="n"/>
-      <c r="K17" s="2" t="n"/>
-      <c r="L17" s="2" t="n"/>
-      <c r="N17" s="2" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n"/>
-      <c r="B18" s="1" t="n"/>
-      <c r="C18" s="1" t="n"/>
-      <c r="D18" s="1" t="n"/>
-      <c r="E18" s="1" t="n"/>
-      <c r="F18" s="1" t="n"/>
-      <c r="H18" s="2" t="n"/>
-      <c r="I18" s="2" t="n"/>
-      <c r="J18" s="2" t="n"/>
-      <c r="K18" s="2" t="n"/>
-      <c r="L18" s="2" t="n"/>
-      <c r="N18" s="2" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="n"/>
-      <c r="B19" s="3" t="n"/>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="3" t="n"/>
-      <c r="E19" s="3" t="n"/>
-      <c r="F19" s="3" t="n"/>
-      <c r="H19" s="2" t="n"/>
-      <c r="I19" s="2" t="n"/>
-      <c r="J19" s="2" t="n"/>
-      <c r="K19" s="2" t="n"/>
-      <c r="L19" s="2" t="n"/>
-      <c r="N19" s="2" t="n"/>
+        <f>SUM($J$4:$J$9)</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9091,7 +8365,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9130,81 +8404,77 @@
       <c r="O1" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr"/>
-      <c r="B2" s="1" t="inlineStr"/>
-      <c r="C2" s="1" t="inlineStr"/>
-      <c r="D2" s="1" t="inlineStr"/>
-      <c r="E2" s="1" t="inlineStr"/>
-      <c r="F2" s="1" t="inlineStr"/>
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="2">
-        <f>(J2-L2)</f>
-        <v/>
-      </c>
-      <c r="L2" s="2">
-        <f>COUNTIF($B$2:$F$19,H2)</f>
-        <v/>
-      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr"/>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Martes</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Miercoles</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Jueves</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Viernes</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Abrev</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Asignaturas</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Frec</t>
         </is>
       </c>
-      <c r="K3" s="2">
-        <f>(J3-L3)</f>
-        <v/>
-      </c>
-      <c r="L3" s="2">
-        <f>COUNTIF($B$2:$F$19,H3)</f>
-        <v/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Faltan</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Asignadas</t>
+        </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Aulas</t>
         </is>
@@ -9253,7 +8523,7 @@
         <v/>
       </c>
       <c r="L4" s="2">
-        <f>COUNTIF($B$2:$F$19,H4)</f>
+        <f>COUNTIF($B$4:$F$15,H4)</f>
         <v/>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -9298,7 +8568,7 @@
         <v/>
       </c>
       <c r="L5" s="2">
-        <f>COUNTIF($B$2:$F$19,H5)</f>
+        <f>COUNTIF($B$4:$F$15,H5)</f>
         <v/>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -9355,7 +8625,7 @@
         <v/>
       </c>
       <c r="L6" s="2">
-        <f>COUNTIF($B$2:$F$19,H6)</f>
+        <f>COUNTIF($B$4:$F$15,H6)</f>
         <v/>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -9408,7 +8678,7 @@
         <v/>
       </c>
       <c r="L7" s="2">
-        <f>COUNTIF($B$2:$F$19,H7)</f>
+        <f>COUNTIF($B$4:$F$15,H7)</f>
         <v/>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -9465,7 +8735,7 @@
         <v/>
       </c>
       <c r="L8" s="2">
-        <f>COUNTIF($B$2:$F$19,H8)</f>
+        <f>COUNTIF($B$4:$F$15,H8)</f>
         <v/>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -9518,7 +8788,7 @@
         <v/>
       </c>
       <c r="L9" s="2">
-        <f>COUNTIF($B$2:$F$19,H9)</f>
+        <f>COUNTIF($B$4:$F$15,H9)</f>
         <v/>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -9541,17 +8811,14 @@
       <c r="E10" s="1" t="inlineStr"/>
       <c r="F10" s="1" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr"/>
+      <c r="H10" s="2">
+        <f>COUNTA($H$4:$H$9)</f>
+        <v/>
+      </c>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2">
-        <f>(J10-L10)</f>
-        <v/>
-      </c>
-      <c r="L10" s="2">
-        <f>COUNTIF($B$2:$F$19,H10)</f>
-        <v/>
-      </c>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr">
         <is>
@@ -9666,74 +8933,20 @@
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n"/>
-      <c r="B16" s="1" t="n"/>
-      <c r="C16" s="1" t="n"/>
-      <c r="D16" s="1" t="n"/>
-      <c r="E16" s="1" t="n"/>
-      <c r="F16" s="1" t="n"/>
       <c r="G16">
         <f>"Total:"</f>
         <v/>
       </c>
-      <c r="H16" s="2">
-        <f>COUNTA($H$2:$H$19)</f>
-        <v/>
-      </c>
-      <c r="I16" s="2" t="n"/>
-      <c r="J16" s="2" t="n"/>
-      <c r="K16" s="2" t="n"/>
-      <c r="L16" s="2" t="n"/>
-      <c r="N16" s="2" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n"/>
-      <c r="B17" s="3" t="n"/>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="3" t="n"/>
-      <c r="E17" s="3" t="n"/>
-      <c r="F17" s="3">
-        <f>"Σ Frec:"</f>
+      <c r="F17">
+        <f>"Sigma Frec:"</f>
         <v/>
       </c>
       <c r="G17">
-        <f>SUM($J$2:$J$19)</f>
-        <v/>
-      </c>
-      <c r="H17" s="2" t="n"/>
-      <c r="I17" s="2" t="n"/>
-      <c r="J17" s="2" t="n"/>
-      <c r="K17" s="2" t="n"/>
-      <c r="L17" s="2" t="n"/>
-      <c r="N17" s="2" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n"/>
-      <c r="B18" s="1" t="n"/>
-      <c r="C18" s="1" t="n"/>
-      <c r="D18" s="1" t="n"/>
-      <c r="E18" s="1" t="n"/>
-      <c r="F18" s="1" t="n"/>
-      <c r="H18" s="2" t="n"/>
-      <c r="I18" s="2" t="n"/>
-      <c r="J18" s="2" t="n"/>
-      <c r="K18" s="2" t="n"/>
-      <c r="L18" s="2" t="n"/>
-      <c r="N18" s="2" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="n"/>
-      <c r="B19" s="3" t="n"/>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="3" t="n"/>
-      <c r="E19" s="3" t="n"/>
-      <c r="F19" s="3" t="n"/>
-      <c r="H19" s="2" t="n"/>
-      <c r="I19" s="2" t="n"/>
-      <c r="J19" s="2" t="n"/>
-      <c r="K19" s="2" t="n"/>
-      <c r="L19" s="2" t="n"/>
-      <c r="N19" s="2" t="n"/>
+        <f>SUM($J$4:$J$9)</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9746,7 +8959,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9785,81 +8998,77 @@
       <c r="O1" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr"/>
-      <c r="B2" s="1" t="inlineStr"/>
-      <c r="C2" s="1" t="inlineStr"/>
-      <c r="D2" s="1" t="inlineStr"/>
-      <c r="E2" s="1" t="inlineStr"/>
-      <c r="F2" s="1" t="inlineStr"/>
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="2">
-        <f>(J2-L2)</f>
-        <v/>
-      </c>
-      <c r="L2" s="2">
-        <f>COUNTIF($B$2:$F$19,H2)</f>
-        <v/>
-      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr"/>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Martes</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Miercoles</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Jueves</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Viernes</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Abrev</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Asignaturas</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Frec</t>
         </is>
       </c>
-      <c r="K3" s="2">
-        <f>(J3-L3)</f>
-        <v/>
-      </c>
-      <c r="L3" s="2">
-        <f>COUNTIF($B$2:$F$19,H3)</f>
-        <v/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Faltan</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Asignadas</t>
+        </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Aulas</t>
         </is>
@@ -9904,7 +9113,7 @@
         <v/>
       </c>
       <c r="L4" s="2">
-        <f>COUNTIF($B$2:$F$19,H4)</f>
+        <f>COUNTIF($B$4:$F$15,H4)</f>
         <v/>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -9957,7 +9166,7 @@
         <v/>
       </c>
       <c r="L5" s="2">
-        <f>COUNTIF($B$2:$F$19,H5)</f>
+        <f>COUNTIF($B$4:$F$15,H5)</f>
         <v/>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -10014,7 +9223,7 @@
         <v/>
       </c>
       <c r="L6" s="2">
-        <f>COUNTIF($B$2:$F$19,H6)</f>
+        <f>COUNTIF($B$4:$F$15,H6)</f>
         <v/>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -10067,7 +9276,7 @@
         <v/>
       </c>
       <c r="L7" s="2">
-        <f>COUNTIF($B$2:$F$19,H7)</f>
+        <f>COUNTIF($B$4:$F$15,H7)</f>
         <v/>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -10120,7 +9329,7 @@
         <v/>
       </c>
       <c r="L8" s="2">
-        <f>COUNTIF($B$2:$F$19,H8)</f>
+        <f>COUNTIF($B$4:$F$15,H8)</f>
         <v/>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -10165,7 +9374,7 @@
         <v/>
       </c>
       <c r="L9" s="2">
-        <f>COUNTIF($B$2:$F$19,H9)</f>
+        <f>COUNTIF($B$4:$F$15,H9)</f>
         <v/>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -10188,17 +9397,14 @@
       <c r="E10" s="1" t="inlineStr"/>
       <c r="F10" s="1" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr"/>
+      <c r="H10" s="2">
+        <f>COUNTA($H$4:$H$9)</f>
+        <v/>
+      </c>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2">
-        <f>(J10-L10)</f>
-        <v/>
-      </c>
-      <c r="L10" s="2">
-        <f>COUNTIF($B$2:$F$19,H10)</f>
-        <v/>
-      </c>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr">
         <is>
@@ -10313,74 +9519,20 @@
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n"/>
-      <c r="B16" s="1" t="n"/>
-      <c r="C16" s="1" t="n"/>
-      <c r="D16" s="1" t="n"/>
-      <c r="E16" s="1" t="n"/>
-      <c r="F16" s="1" t="n"/>
       <c r="G16">
         <f>"Total:"</f>
         <v/>
       </c>
-      <c r="H16" s="2">
-        <f>COUNTA($H$2:$H$19)</f>
-        <v/>
-      </c>
-      <c r="I16" s="2" t="n"/>
-      <c r="J16" s="2" t="n"/>
-      <c r="K16" s="2" t="n"/>
-      <c r="L16" s="2" t="n"/>
-      <c r="N16" s="2" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n"/>
-      <c r="B17" s="3" t="n"/>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="3" t="n"/>
-      <c r="E17" s="3" t="n"/>
-      <c r="F17" s="3">
-        <f>"Σ Frec:"</f>
+      <c r="F17">
+        <f>"Sigma Frec:"</f>
         <v/>
       </c>
       <c r="G17">
-        <f>SUM($J$2:$J$19)</f>
-        <v/>
-      </c>
-      <c r="H17" s="2" t="n"/>
-      <c r="I17" s="2" t="n"/>
-      <c r="J17" s="2" t="n"/>
-      <c r="K17" s="2" t="n"/>
-      <c r="L17" s="2" t="n"/>
-      <c r="N17" s="2" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n"/>
-      <c r="B18" s="1" t="n"/>
-      <c r="C18" s="1" t="n"/>
-      <c r="D18" s="1" t="n"/>
-      <c r="E18" s="1" t="n"/>
-      <c r="F18" s="1" t="n"/>
-      <c r="H18" s="2" t="n"/>
-      <c r="I18" s="2" t="n"/>
-      <c r="J18" s="2" t="n"/>
-      <c r="K18" s="2" t="n"/>
-      <c r="L18" s="2" t="n"/>
-      <c r="N18" s="2" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="n"/>
-      <c r="B19" s="3" t="n"/>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="3" t="n"/>
-      <c r="E19" s="3" t="n"/>
-      <c r="F19" s="3" t="n"/>
-      <c r="H19" s="2" t="n"/>
-      <c r="I19" s="2" t="n"/>
-      <c r="J19" s="2" t="n"/>
-      <c r="K19" s="2" t="n"/>
-      <c r="L19" s="2" t="n"/>
-      <c r="N19" s="2" t="n"/>
+        <f>SUM($J$4:$J$9)</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10393,7 +9545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -10432,81 +9584,77 @@
       <c r="O1" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr"/>
-      <c r="B2" s="1" t="inlineStr"/>
-      <c r="C2" s="1" t="inlineStr"/>
-      <c r="D2" s="1" t="inlineStr"/>
-      <c r="E2" s="1" t="inlineStr"/>
-      <c r="F2" s="1" t="inlineStr"/>
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="2">
-        <f>(J2-L2)</f>
-        <v/>
-      </c>
-      <c r="L2" s="2">
-        <f>COUNTIF($B$2:$F$19,H2)</f>
-        <v/>
-      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr"/>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Martes</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Miercoles</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Jueves</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Viernes</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Abrev</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Asignaturas</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Frec</t>
         </is>
       </c>
-      <c r="K3" s="2">
-        <f>(J3-L3)</f>
-        <v/>
-      </c>
-      <c r="L3" s="2">
-        <f>COUNTIF($B$2:$F$19,H3)</f>
-        <v/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Faltan</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Asignadas</t>
+        </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Aulas</t>
         </is>
@@ -10559,7 +9707,7 @@
         <v/>
       </c>
       <c r="L4" s="2">
-        <f>COUNTIF($B$2:$F$19,H4)</f>
+        <f>COUNTIF($B$4:$F$15,H4)</f>
         <v/>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -10612,7 +9760,7 @@
         <v/>
       </c>
       <c r="L5" s="2">
-        <f>COUNTIF($B$2:$F$19,H5)</f>
+        <f>COUNTIF($B$4:$F$15,H5)</f>
         <v/>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -10673,7 +9821,7 @@
         <v/>
       </c>
       <c r="L6" s="2">
-        <f>COUNTIF($B$2:$F$19,H6)</f>
+        <f>COUNTIF($B$4:$F$15,H6)</f>
         <v/>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -10730,7 +9878,7 @@
         <v/>
       </c>
       <c r="L7" s="2">
-        <f>COUNTIF($B$2:$F$19,H7)</f>
+        <f>COUNTIF($B$4:$F$15,H7)</f>
         <v/>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -10791,7 +9939,7 @@
         <v/>
       </c>
       <c r="L8" s="2">
-        <f>COUNTIF($B$2:$F$19,H8)</f>
+        <f>COUNTIF($B$4:$F$15,H8)</f>
         <v/>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -10848,7 +9996,7 @@
         <v/>
       </c>
       <c r="L9" s="2">
-        <f>COUNTIF($B$2:$F$19,H9)</f>
+        <f>COUNTIF($B$4:$F$15,H9)</f>
         <v/>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -10871,17 +10019,14 @@
       <c r="E10" s="1" t="inlineStr"/>
       <c r="F10" s="1" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr"/>
+      <c r="H10" s="2">
+        <f>COUNTA($H$4:$H$9)</f>
+        <v/>
+      </c>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2">
-        <f>(J10-L10)</f>
-        <v/>
-      </c>
-      <c r="L10" s="2">
-        <f>COUNTIF($B$2:$F$19,H10)</f>
-        <v/>
-      </c>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr">
         <is>
@@ -11004,26 +10149,23 @@
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr"/>
-      <c r="B16" s="1" t="inlineStr"/>
-      <c r="C16" s="1" t="inlineStr"/>
-      <c r="D16" s="1" t="inlineStr"/>
-      <c r="E16" s="1" t="inlineStr"/>
-      <c r="F16" s="1" t="inlineStr"/>
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
       <c r="G16">
         <f>"Total:"</f>
         <v/>
       </c>
-      <c r="H16" s="2">
-        <f>COUNTA($H$2:$H$19)</f>
-        <v/>
-      </c>
-      <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="2" t="inlineStr"/>
-      <c r="L16" s="2" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>Aula 6</t>
         </is>
@@ -11031,59 +10173,31 @@
       <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr"/>
-      <c r="B17" s="3" t="inlineStr"/>
-      <c r="C17" s="3" t="inlineStr"/>
-      <c r="D17" s="3" t="inlineStr"/>
-      <c r="E17" s="3" t="inlineStr"/>
-      <c r="F17" s="3">
-        <f>"Σ Frec:"</f>
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17">
+        <f>"Sigma Frec:"</f>
         <v/>
       </c>
       <c r="G17">
-        <f>SUM($J$2:$J$19)</f>
-        <v/>
-      </c>
-      <c r="H17" s="2" t="inlineStr"/>
-      <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr"/>
-      <c r="K17" s="2" t="inlineStr"/>
-      <c r="L17" s="2" t="inlineStr"/>
+        <f>SUM($J$4:$J$9)</f>
+        <v/>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>Lab</t>
         </is>
       </c>
       <c r="O17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n"/>
-      <c r="B18" s="1" t="n"/>
-      <c r="C18" s="1" t="n"/>
-      <c r="D18" s="1" t="n"/>
-      <c r="E18" s="1" t="n"/>
-      <c r="F18" s="1" t="n"/>
-      <c r="H18" s="2" t="n"/>
-      <c r="I18" s="2" t="n"/>
-      <c r="J18" s="2" t="n"/>
-      <c r="K18" s="2" t="n"/>
-      <c r="L18" s="2" t="n"/>
-      <c r="N18" s="2" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="n"/>
-      <c r="B19" s="3" t="n"/>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="3" t="n"/>
-      <c r="E19" s="3" t="n"/>
-      <c r="F19" s="3" t="n"/>
-      <c r="H19" s="2" t="n"/>
-      <c r="I19" s="2" t="n"/>
-      <c r="J19" s="2" t="n"/>
-      <c r="K19" s="2" t="n"/>
-      <c r="L19" s="2" t="n"/>
-      <c r="N19" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11096,7 +10210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -11135,81 +10249,77 @@
       <c r="O1" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr"/>
-      <c r="B2" s="1" t="inlineStr"/>
-      <c r="C2" s="1" t="inlineStr"/>
-      <c r="D2" s="1" t="inlineStr"/>
-      <c r="E2" s="1" t="inlineStr"/>
-      <c r="F2" s="1" t="inlineStr"/>
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="2">
-        <f>(J2-L2)</f>
-        <v/>
-      </c>
-      <c r="L2" s="2">
-        <f>COUNTIF($B$2:$F$19,H2)</f>
-        <v/>
-      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr"/>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Martes</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Miercoles</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Jueves</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Viernes</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Abrev</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Asignaturas</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Frec</t>
         </is>
       </c>
-      <c r="K3" s="2">
-        <f>(J3-L3)</f>
-        <v/>
-      </c>
-      <c r="L3" s="2">
-        <f>COUNTIF($B$2:$F$19,H3)</f>
-        <v/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Faltan</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Asignadas</t>
+        </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Aulas</t>
         </is>
@@ -11266,7 +10376,7 @@
         <v/>
       </c>
       <c r="L4" s="2">
-        <f>COUNTIF($B$2:$F$19,H4)</f>
+        <f>COUNTIF($B$4:$F$15,H4)</f>
         <v/>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -11323,7 +10433,7 @@
         <v/>
       </c>
       <c r="L5" s="2">
-        <f>COUNTIF($B$2:$F$19,H5)</f>
+        <f>COUNTIF($B$4:$F$15,H5)</f>
         <v/>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -11384,7 +10494,7 @@
         <v/>
       </c>
       <c r="L6" s="2">
-        <f>COUNTIF($B$2:$F$19,H6)</f>
+        <f>COUNTIF($B$4:$F$15,H6)</f>
         <v/>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -11441,7 +10551,7 @@
         <v/>
       </c>
       <c r="L7" s="2">
-        <f>COUNTIF($B$2:$F$19,H7)</f>
+        <f>COUNTIF($B$4:$F$15,H7)</f>
         <v/>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -11498,7 +10608,7 @@
         <v/>
       </c>
       <c r="L8" s="2">
-        <f>COUNTIF($B$2:$F$19,H8)</f>
+        <f>COUNTIF($B$4:$F$15,H8)</f>
         <v/>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -11551,7 +10661,7 @@
         <v/>
       </c>
       <c r="L9" s="2">
-        <f>COUNTIF($B$2:$F$19,H9)</f>
+        <f>COUNTIF($B$4:$F$15,H9)</f>
         <v/>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -11574,17 +10684,14 @@
       <c r="E10" s="1" t="inlineStr"/>
       <c r="F10" s="1" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr"/>
+      <c r="H10" s="2">
+        <f>COUNTA($H$4:$H$9)</f>
+        <v/>
+      </c>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2">
-        <f>(J10-L10)</f>
-        <v/>
-      </c>
-      <c r="L10" s="2">
-        <f>COUNTIF($B$2:$F$19,H10)</f>
-        <v/>
-      </c>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr">
         <is>
@@ -11707,26 +10814,23 @@
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr"/>
-      <c r="B16" s="1" t="inlineStr"/>
-      <c r="C16" s="1" t="inlineStr"/>
-      <c r="D16" s="1" t="inlineStr"/>
-      <c r="E16" s="1" t="inlineStr"/>
-      <c r="F16" s="1" t="inlineStr"/>
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
       <c r="G16">
         <f>"Total:"</f>
         <v/>
       </c>
-      <c r="H16" s="2">
-        <f>COUNTA($H$2:$H$19)</f>
-        <v/>
-      </c>
-      <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="2" t="inlineStr"/>
-      <c r="L16" s="2" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>Aula 5</t>
         </is>
@@ -11734,59 +10838,31 @@
       <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr"/>
-      <c r="B17" s="3" t="inlineStr"/>
-      <c r="C17" s="3" t="inlineStr"/>
-      <c r="D17" s="3" t="inlineStr"/>
-      <c r="E17" s="3" t="inlineStr"/>
-      <c r="F17" s="3">
-        <f>"Σ Frec:"</f>
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17">
+        <f>"Sigma Frec:"</f>
         <v/>
       </c>
       <c r="G17">
-        <f>SUM($J$2:$J$19)</f>
-        <v/>
-      </c>
-      <c r="H17" s="2" t="inlineStr"/>
-      <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr"/>
-      <c r="K17" s="2" t="inlineStr"/>
-      <c r="L17" s="2" t="inlineStr"/>
+        <f>SUM($J$4:$J$9)</f>
+        <v/>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>Aula 5</t>
         </is>
       </c>
       <c r="O17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n"/>
-      <c r="B18" s="1" t="n"/>
-      <c r="C18" s="1" t="n"/>
-      <c r="D18" s="1" t="n"/>
-      <c r="E18" s="1" t="n"/>
-      <c r="F18" s="1" t="n"/>
-      <c r="H18" s="2" t="n"/>
-      <c r="I18" s="2" t="n"/>
-      <c r="J18" s="2" t="n"/>
-      <c r="K18" s="2" t="n"/>
-      <c r="L18" s="2" t="n"/>
-      <c r="N18" s="2" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="n"/>
-      <c r="B19" s="3" t="n"/>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="3" t="n"/>
-      <c r="E19" s="3" t="n"/>
-      <c r="F19" s="3" t="n"/>
-      <c r="H19" s="2" t="n"/>
-      <c r="I19" s="2" t="n"/>
-      <c r="J19" s="2" t="n"/>
-      <c r="K19" s="2" t="n"/>
-      <c r="L19" s="2" t="n"/>
-      <c r="N19" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11799,7 +10875,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -11838,81 +10914,77 @@
       <c r="O1" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr"/>
-      <c r="B2" s="1" t="inlineStr"/>
-      <c r="C2" s="1" t="inlineStr"/>
-      <c r="D2" s="1" t="inlineStr"/>
-      <c r="E2" s="1" t="inlineStr"/>
-      <c r="F2" s="1" t="inlineStr"/>
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="2">
-        <f>(J2-L2)</f>
-        <v/>
-      </c>
-      <c r="L2" s="2">
-        <f>COUNTIF($B$2:$F$19,H2)</f>
-        <v/>
-      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr"/>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Martes</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Miercoles</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Jueves</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Viernes</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Abrev</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Asignaturas</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Frec</t>
         </is>
       </c>
-      <c r="K3" s="2">
-        <f>(J3-L3)</f>
-        <v/>
-      </c>
-      <c r="L3" s="2">
-        <f>COUNTIF($B$2:$F$19,H3)</f>
-        <v/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Faltan</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Asignadas</t>
+        </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Aulas</t>
         </is>
@@ -11969,7 +11041,7 @@
         <v/>
       </c>
       <c r="L4" s="2">
-        <f>COUNTIF($B$2:$F$19,H4)</f>
+        <f>COUNTIF($B$4:$F$15,H4)</f>
         <v/>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -12026,7 +11098,7 @@
         <v/>
       </c>
       <c r="L5" s="2">
-        <f>COUNTIF($B$2:$F$19,H5)</f>
+        <f>COUNTIF($B$4:$F$15,H5)</f>
         <v/>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -12087,7 +11159,7 @@
         <v/>
       </c>
       <c r="L6" s="2">
-        <f>COUNTIF($B$2:$F$19,H6)</f>
+        <f>COUNTIF($B$4:$F$15,H6)</f>
         <v/>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -12144,7 +11216,7 @@
         <v/>
       </c>
       <c r="L7" s="2">
-        <f>COUNTIF($B$2:$F$19,H7)</f>
+        <f>COUNTIF($B$4:$F$15,H7)</f>
         <v/>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -12201,7 +11273,7 @@
         <v/>
       </c>
       <c r="L8" s="2">
-        <f>COUNTIF($B$2:$F$19,H8)</f>
+        <f>COUNTIF($B$4:$F$15,H8)</f>
         <v/>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -12254,7 +11326,7 @@
         <v/>
       </c>
       <c r="L9" s="2">
-        <f>COUNTIF($B$2:$F$19,H9)</f>
+        <f>COUNTIF($B$4:$F$15,H9)</f>
         <v/>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -12277,17 +11349,14 @@
       <c r="E10" s="1" t="inlineStr"/>
       <c r="F10" s="1" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr"/>
+      <c r="H10" s="2">
+        <f>COUNTA($H$4:$H$9)</f>
+        <v/>
+      </c>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2">
-        <f>(J10-L10)</f>
-        <v/>
-      </c>
-      <c r="L10" s="2">
-        <f>COUNTIF($B$2:$F$19,H10)</f>
-        <v/>
-      </c>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr">
         <is>
@@ -12410,26 +11479,23 @@
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr"/>
-      <c r="B16" s="1" t="inlineStr"/>
-      <c r="C16" s="1" t="inlineStr"/>
-      <c r="D16" s="1" t="inlineStr"/>
-      <c r="E16" s="1" t="inlineStr"/>
-      <c r="F16" s="1" t="inlineStr"/>
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
       <c r="G16">
         <f>"Total:"</f>
         <v/>
       </c>
-      <c r="H16" s="2">
-        <f>COUNTA($H$2:$H$19)</f>
-        <v/>
-      </c>
-      <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="2" t="inlineStr"/>
-      <c r="L16" s="2" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>Aula 1</t>
         </is>
@@ -12437,59 +11503,31 @@
       <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr"/>
-      <c r="B17" s="3" t="inlineStr"/>
-      <c r="C17" s="3" t="inlineStr"/>
-      <c r="D17" s="3" t="inlineStr"/>
-      <c r="E17" s="3" t="inlineStr"/>
-      <c r="F17" s="3">
-        <f>"Σ Frec:"</f>
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17">
+        <f>"Sigma Frec:"</f>
         <v/>
       </c>
       <c r="G17">
-        <f>SUM($J$2:$J$19)</f>
-        <v/>
-      </c>
-      <c r="H17" s="2" t="inlineStr"/>
-      <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr"/>
-      <c r="K17" s="2" t="inlineStr"/>
-      <c r="L17" s="2" t="inlineStr"/>
+        <f>SUM($J$4:$J$9)</f>
+        <v/>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>Aula 5</t>
         </is>
       </c>
       <c r="O17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n"/>
-      <c r="B18" s="1" t="n"/>
-      <c r="C18" s="1" t="n"/>
-      <c r="D18" s="1" t="n"/>
-      <c r="E18" s="1" t="n"/>
-      <c r="F18" s="1" t="n"/>
-      <c r="H18" s="2" t="n"/>
-      <c r="I18" s="2" t="n"/>
-      <c r="J18" s="2" t="n"/>
-      <c r="K18" s="2" t="n"/>
-      <c r="L18" s="2" t="n"/>
-      <c r="N18" s="2" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="n"/>
-      <c r="B19" s="3" t="n"/>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="3" t="n"/>
-      <c r="E19" s="3" t="n"/>
-      <c r="F19" s="3" t="n"/>
-      <c r="H19" s="2" t="n"/>
-      <c r="I19" s="2" t="n"/>
-      <c r="J19" s="2" t="n"/>
-      <c r="K19" s="2" t="n"/>
-      <c r="L19" s="2" t="n"/>
-      <c r="N19" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12502,7 +11540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -12541,81 +11579,77 @@
       <c r="O1" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr"/>
-      <c r="B2" s="1" t="inlineStr"/>
-      <c r="C2" s="1" t="inlineStr"/>
-      <c r="D2" s="1" t="inlineStr"/>
-      <c r="E2" s="1" t="inlineStr"/>
-      <c r="F2" s="1" t="inlineStr"/>
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="2">
-        <f>(J2-L2)</f>
-        <v/>
-      </c>
-      <c r="L2" s="2">
-        <f>COUNTIF($B$2:$F$19,H2)</f>
-        <v/>
-      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr"/>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Martes</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Miercoles</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Jueves</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Viernes</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Abrev</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Asignaturas</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Frec</t>
         </is>
       </c>
-      <c r="K3" s="2">
-        <f>(J3-L3)</f>
-        <v/>
-      </c>
-      <c r="L3" s="2">
-        <f>COUNTIF($B$2:$F$19,H3)</f>
-        <v/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Faltan</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Asignadas</t>
+        </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Aulas</t>
         </is>
@@ -12652,7 +11686,7 @@
         <v/>
       </c>
       <c r="L4" s="2">
-        <f>COUNTIF($B$2:$F$19,H4)</f>
+        <f>COUNTIF($B$4:$F$15,H4)</f>
         <v/>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -12689,7 +11723,7 @@
         <v/>
       </c>
       <c r="L5" s="2">
-        <f>COUNTIF($B$2:$F$19,H5)</f>
+        <f>COUNTIF($B$4:$F$15,H5)</f>
         <v/>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -12730,7 +11764,7 @@
         <v/>
       </c>
       <c r="L6" s="2">
-        <f>COUNTIF($B$2:$F$19,H6)</f>
+        <f>COUNTIF($B$4:$F$15,H6)</f>
         <v/>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -12767,7 +11801,7 @@
         <v/>
       </c>
       <c r="L7" s="2">
-        <f>COUNTIF($B$2:$F$19,H7)</f>
+        <f>COUNTIF($B$4:$F$15,H7)</f>
         <v/>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -12808,7 +11842,7 @@
         <v/>
       </c>
       <c r="L8" s="2">
-        <f>COUNTIF($B$2:$F$19,H8)</f>
+        <f>COUNTIF($B$4:$F$15,H8)</f>
         <v/>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -12845,7 +11879,7 @@
         <v/>
       </c>
       <c r="L9" s="2">
-        <f>COUNTIF($B$2:$F$19,H9)</f>
+        <f>COUNTIF($B$4:$F$15,H9)</f>
         <v/>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -12888,17 +11922,14 @@
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr"/>
+      <c r="H10" s="2">
+        <f>COUNTA($H$4:$H$9)</f>
+        <v/>
+      </c>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2">
-        <f>(J10-L10)</f>
-        <v/>
-      </c>
-      <c r="L10" s="2">
-        <f>COUNTIF($B$2:$F$19,H10)</f>
-        <v/>
-      </c>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr">
         <is>
@@ -13101,74 +12132,20 @@
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n"/>
-      <c r="B16" s="1" t="n"/>
-      <c r="C16" s="1" t="n"/>
-      <c r="D16" s="1" t="n"/>
-      <c r="E16" s="1" t="n"/>
-      <c r="F16" s="1" t="n"/>
       <c r="G16">
         <f>"Total:"</f>
         <v/>
       </c>
-      <c r="H16" s="2">
-        <f>COUNTA($H$2:$H$19)</f>
-        <v/>
-      </c>
-      <c r="I16" s="2" t="n"/>
-      <c r="J16" s="2" t="n"/>
-      <c r="K16" s="2" t="n"/>
-      <c r="L16" s="2" t="n"/>
-      <c r="N16" s="2" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n"/>
-      <c r="B17" s="3" t="n"/>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="3" t="n"/>
-      <c r="E17" s="3" t="n"/>
-      <c r="F17" s="3">
-        <f>"Σ Frec:"</f>
+      <c r="F17">
+        <f>"Sigma Frec:"</f>
         <v/>
       </c>
       <c r="G17">
-        <f>SUM($J$2:$J$19)</f>
-        <v/>
-      </c>
-      <c r="H17" s="2" t="n"/>
-      <c r="I17" s="2" t="n"/>
-      <c r="J17" s="2" t="n"/>
-      <c r="K17" s="2" t="n"/>
-      <c r="L17" s="2" t="n"/>
-      <c r="N17" s="2" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n"/>
-      <c r="B18" s="1" t="n"/>
-      <c r="C18" s="1" t="n"/>
-      <c r="D18" s="1" t="n"/>
-      <c r="E18" s="1" t="n"/>
-      <c r="F18" s="1" t="n"/>
-      <c r="H18" s="2" t="n"/>
-      <c r="I18" s="2" t="n"/>
-      <c r="J18" s="2" t="n"/>
-      <c r="K18" s="2" t="n"/>
-      <c r="L18" s="2" t="n"/>
-      <c r="N18" s="2" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="n"/>
-      <c r="B19" s="3" t="n"/>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="3" t="n"/>
-      <c r="E19" s="3" t="n"/>
-      <c r="F19" s="3" t="n"/>
-      <c r="H19" s="2" t="n"/>
-      <c r="I19" s="2" t="n"/>
-      <c r="J19" s="2" t="n"/>
-      <c r="K19" s="2" t="n"/>
-      <c r="L19" s="2" t="n"/>
-      <c r="N19" s="2" t="n"/>
+        <f>SUM($J$4:$J$9)</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13181,7 +12158,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -13220,81 +12197,77 @@
       <c r="O1" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr"/>
-      <c r="B2" s="1" t="inlineStr"/>
-      <c r="C2" s="1" t="inlineStr"/>
-      <c r="D2" s="1" t="inlineStr"/>
-      <c r="E2" s="1" t="inlineStr"/>
-      <c r="F2" s="1" t="inlineStr"/>
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="2">
-        <f>(J2-L2)</f>
-        <v/>
-      </c>
-      <c r="L2" s="2">
-        <f>COUNTIF($B$2:$F$19,H2)</f>
-        <v/>
-      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr"/>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Martes</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Miercoles</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Jueves</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Viernes</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Abrev</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Asignaturas</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Frec</t>
         </is>
       </c>
-      <c r="K3" s="2">
-        <f>(J3-L3)</f>
-        <v/>
-      </c>
-      <c r="L3" s="2">
-        <f>COUNTIF($B$2:$F$19,H3)</f>
-        <v/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Faltan</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Asignadas</t>
+        </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Aulas</t>
         </is>
@@ -13331,7 +12304,7 @@
         <v/>
       </c>
       <c r="L4" s="2">
-        <f>COUNTIF($B$2:$F$19,H4)</f>
+        <f>COUNTIF($B$4:$F$15,H4)</f>
         <v/>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -13368,7 +12341,7 @@
         <v/>
       </c>
       <c r="L5" s="2">
-        <f>COUNTIF($B$2:$F$19,H5)</f>
+        <f>COUNTIF($B$4:$F$15,H5)</f>
         <v/>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -13409,7 +12382,7 @@
         <v/>
       </c>
       <c r="L6" s="2">
-        <f>COUNTIF($B$2:$F$19,H6)</f>
+        <f>COUNTIF($B$4:$F$15,H6)</f>
         <v/>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -13446,7 +12419,7 @@
         <v/>
       </c>
       <c r="L7" s="2">
-        <f>COUNTIF($B$2:$F$19,H7)</f>
+        <f>COUNTIF($B$4:$F$15,H7)</f>
         <v/>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -13487,7 +12460,7 @@
         <v/>
       </c>
       <c r="L8" s="2">
-        <f>COUNTIF($B$2:$F$19,H8)</f>
+        <f>COUNTIF($B$4:$F$15,H8)</f>
         <v/>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -13524,7 +12497,7 @@
         <v/>
       </c>
       <c r="L9" s="2">
-        <f>COUNTIF($B$2:$F$19,H9)</f>
+        <f>COUNTIF($B$4:$F$15,H9)</f>
         <v/>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -13567,17 +12540,14 @@
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr"/>
+      <c r="H10" s="2">
+        <f>COUNTA($H$4:$H$9)</f>
+        <v/>
+      </c>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2">
-        <f>(J10-L10)</f>
-        <v/>
-      </c>
-      <c r="L10" s="2">
-        <f>COUNTIF($B$2:$F$19,H10)</f>
-        <v/>
-      </c>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr">
         <is>
@@ -13780,74 +12750,20 @@
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n"/>
-      <c r="B16" s="1" t="n"/>
-      <c r="C16" s="1" t="n"/>
-      <c r="D16" s="1" t="n"/>
-      <c r="E16" s="1" t="n"/>
-      <c r="F16" s="1" t="n"/>
       <c r="G16">
         <f>"Total:"</f>
         <v/>
       </c>
-      <c r="H16" s="2">
-        <f>COUNTA($H$2:$H$19)</f>
-        <v/>
-      </c>
-      <c r="I16" s="2" t="n"/>
-      <c r="J16" s="2" t="n"/>
-      <c r="K16" s="2" t="n"/>
-      <c r="L16" s="2" t="n"/>
-      <c r="N16" s="2" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n"/>
-      <c r="B17" s="3" t="n"/>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="3" t="n"/>
-      <c r="E17" s="3" t="n"/>
-      <c r="F17" s="3">
-        <f>"Σ Frec:"</f>
+      <c r="F17">
+        <f>"Sigma Frec:"</f>
         <v/>
       </c>
       <c r="G17">
-        <f>SUM($J$2:$J$19)</f>
-        <v/>
-      </c>
-      <c r="H17" s="2" t="n"/>
-      <c r="I17" s="2" t="n"/>
-      <c r="J17" s="2" t="n"/>
-      <c r="K17" s="2" t="n"/>
-      <c r="L17" s="2" t="n"/>
-      <c r="N17" s="2" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n"/>
-      <c r="B18" s="1" t="n"/>
-      <c r="C18" s="1" t="n"/>
-      <c r="D18" s="1" t="n"/>
-      <c r="E18" s="1" t="n"/>
-      <c r="F18" s="1" t="n"/>
-      <c r="H18" s="2" t="n"/>
-      <c r="I18" s="2" t="n"/>
-      <c r="J18" s="2" t="n"/>
-      <c r="K18" s="2" t="n"/>
-      <c r="L18" s="2" t="n"/>
-      <c r="N18" s="2" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="n"/>
-      <c r="B19" s="3" t="n"/>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="3" t="n"/>
-      <c r="E19" s="3" t="n"/>
-      <c r="F19" s="3" t="n"/>
-      <c r="H19" s="2" t="n"/>
-      <c r="I19" s="2" t="n"/>
-      <c r="J19" s="2" t="n"/>
-      <c r="K19" s="2" t="n"/>
-      <c r="L19" s="2" t="n"/>
-      <c r="N19" s="2" t="n"/>
+        <f>SUM($J$4:$J$9)</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Horario_Facultad.xlsx
+++ b/Horario_Facultad.xlsx
@@ -108,6 +108,32 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="3">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF4444"/>
+          <bgColor rgb="FFFF4444"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF44BB44"/>
+          <bgColor rgb="FF44BB44"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF4488FF"/>
+          <bgColor rgb="FF4488FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -935,14 +961,14 @@
       <c r="E10" s="1" t="inlineStr"/>
       <c r="F10" s="1" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" s="2">
+      <c r="H10">
         <f>COUNTA($H$4:$H$9)</f>
         <v/>
       </c>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr">
         <is>
@@ -959,11 +985,11 @@
       <c r="E11" s="3" t="inlineStr"/>
       <c r="F11" s="3" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="2" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -984,11 +1010,11 @@
       <c r="E12" s="1" t="inlineStr"/>
       <c r="F12" s="1" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -1005,11 +1031,11 @@
       <c r="E13" s="3" t="inlineStr"/>
       <c r="F13" s="3" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr"/>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="2" t="inlineStr"/>
-      <c r="L13" s="2" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -1030,11 +1056,11 @@
       <c r="E14" s="1" t="inlineStr"/>
       <c r="F14" s="1" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr"/>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr"/>
-      <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="2" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1051,11 +1077,11 @@
       <c r="E15" s="3" t="inlineStr"/>
       <c r="F15" s="3" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="2" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1081,7 +1107,7 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>Lab</t>
         </is>
@@ -1099,6 +1125,17 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="I4:I9">
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
+      <formula>L4&gt;J4</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="0">
+      <formula>L4=J4</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="2" stopIfTrue="0">
+      <formula>L4&lt;J4</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1109,7 +1146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1567,14 +1604,11 @@
       <c r="E10" s="1" t="inlineStr"/>
       <c r="F10" s="1" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" s="2">
-        <f>COUNTA($H$4:$H$9)</f>
-        <v/>
-      </c>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr">
         <is>
@@ -1591,11 +1625,11 @@
       <c r="E11" s="3" t="inlineStr"/>
       <c r="F11" s="3" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="2" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -1616,11 +1650,11 @@
       <c r="E12" s="1" t="inlineStr"/>
       <c r="F12" s="1" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -1637,11 +1671,11 @@
       <c r="E13" s="3" t="inlineStr"/>
       <c r="F13" s="3" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr"/>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="2" t="inlineStr"/>
-      <c r="L13" s="2" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -1662,11 +1696,11 @@
       <c r="E14" s="1" t="inlineStr"/>
       <c r="F14" s="1" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr"/>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr"/>
-      <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="2" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1683,11 +1717,11 @@
       <c r="E15" s="3" t="inlineStr"/>
       <c r="F15" s="3" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="2" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1696,23 +1730,18 @@
       </c>
       <c r="O15" t="inlineStr"/>
     </row>
-    <row r="16">
-      <c r="G16">
-        <f>"Total:"</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="F17">
-        <f>"Sigma Frec:"</f>
-        <v/>
-      </c>
-      <c r="G17">
-        <f>SUM($J$4:$J$9)</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
+  <conditionalFormatting sqref="I4:I9">
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
+      <formula>L4&gt;J4</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="0">
+      <formula>L4=J4</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="2" stopIfTrue="0">
+      <formula>L4&lt;J4</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1723,7 +1752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2181,14 +2210,11 @@
       <c r="E10" s="1" t="inlineStr"/>
       <c r="F10" s="1" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" s="2">
-        <f>COUNTA($H$4:$H$9)</f>
-        <v/>
-      </c>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr">
         <is>
@@ -2205,11 +2231,11 @@
       <c r="E11" s="3" t="inlineStr"/>
       <c r="F11" s="3" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="2" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -2230,11 +2256,11 @@
       <c r="E12" s="1" t="inlineStr"/>
       <c r="F12" s="1" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -2251,11 +2277,11 @@
       <c r="E13" s="3" t="inlineStr"/>
       <c r="F13" s="3" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr"/>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="2" t="inlineStr"/>
-      <c r="L13" s="2" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -2276,11 +2302,11 @@
       <c r="E14" s="1" t="inlineStr"/>
       <c r="F14" s="1" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr"/>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr"/>
-      <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="2" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -2297,11 +2323,11 @@
       <c r="E15" s="3" t="inlineStr"/>
       <c r="F15" s="3" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="2" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -2310,23 +2336,18 @@
       </c>
       <c r="O15" t="inlineStr"/>
     </row>
-    <row r="16">
-      <c r="G16">
-        <f>"Total:"</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="F17">
-        <f>"Sigma Frec:"</f>
-        <v/>
-      </c>
-      <c r="G17">
-        <f>SUM($J$4:$J$9)</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
+  <conditionalFormatting sqref="I4:I9">
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
+      <formula>L4&gt;J4</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="0">
+      <formula>L4=J4</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="2" stopIfTrue="0">
+      <formula>L4&lt;J4</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2337,7 +2358,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2715,16 +2736,13 @@
       </c>
       <c r="F10" s="1" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" s="2">
-        <f>COUNTA($H$4:$H$9)</f>
-        <v/>
-      </c>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" s="2" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
@@ -2747,13 +2765,13 @@
       <c r="E11" s="3" t="inlineStr"/>
       <c r="F11" s="3" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="2" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" s="2" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
@@ -2784,13 +2802,13 @@
       </c>
       <c r="F12" s="1" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" s="2" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
@@ -2805,13 +2823,13 @@
       <c r="E13" s="3" t="inlineStr"/>
       <c r="F13" s="3" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr"/>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="2" t="inlineStr"/>
-      <c r="L13" s="2" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" s="2" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
@@ -2838,13 +2856,13 @@
       <c r="E14" s="1" t="inlineStr"/>
       <c r="F14" s="1" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr"/>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr"/>
-      <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="2" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" s="2" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
@@ -2863,32 +2881,27 @@
       <c r="E15" s="3" t="inlineStr"/>
       <c r="F15" s="3" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="2" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" s="2" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
     </row>
-    <row r="16">
-      <c r="G16">
-        <f>"Total:"</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="F17">
-        <f>"Sigma Frec:"</f>
-        <v/>
-      </c>
-      <c r="G17">
-        <f>SUM($J$4:$J$9)</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
+  <conditionalFormatting sqref="I4:I9">
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
+      <formula>L4&gt;J4</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="0">
+      <formula>L4=J4</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="2" stopIfTrue="0">
+      <formula>L4&lt;J4</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2899,7 +2912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3242,7 +3255,7 @@
         <v/>
       </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" s="2" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
@@ -3273,16 +3286,13 @@
       </c>
       <c r="F10" s="1" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" s="2">
-        <f>COUNTA($H$4:$H$9)</f>
-        <v/>
-      </c>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" s="2" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
@@ -3305,13 +3315,13 @@
       <c r="E11" s="3" t="inlineStr"/>
       <c r="F11" s="3" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="2" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" s="2" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
@@ -3342,13 +3352,13 @@
       </c>
       <c r="F12" s="1" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" s="2" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
@@ -3363,13 +3373,13 @@
       <c r="E13" s="3" t="inlineStr"/>
       <c r="F13" s="3" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr"/>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="2" t="inlineStr"/>
-      <c r="L13" s="2" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" s="2" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
@@ -3396,13 +3406,13 @@
       <c r="E14" s="1" t="inlineStr"/>
       <c r="F14" s="1" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr"/>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr"/>
-      <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="2" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" s="2" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
@@ -3417,32 +3427,27 @@
       <c r="E15" s="3" t="inlineStr"/>
       <c r="F15" s="3" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="2" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" s="2" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
     </row>
-    <row r="16">
-      <c r="G16">
-        <f>"Total:"</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="F17">
-        <f>"Sigma Frec:"</f>
-        <v/>
-      </c>
-      <c r="G17">
-        <f>SUM($J$4:$J$9)</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
+  <conditionalFormatting sqref="I4:I9">
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
+      <formula>L4&gt;J4</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="0">
+      <formula>L4=J4</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="2" stopIfTrue="0">
+      <formula>L4&lt;J4</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3453,7 +3458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3923,14 +3928,11 @@
       <c r="E10" s="1" t="inlineStr"/>
       <c r="F10" s="1" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" s="2">
-        <f>COUNTA($H$4:$H$9)</f>
-        <v/>
-      </c>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr">
         <is>
@@ -3947,11 +3949,11 @@
       <c r="E11" s="3" t="inlineStr"/>
       <c r="F11" s="3" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="2" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -3972,11 +3974,11 @@
       <c r="E12" s="1" t="inlineStr"/>
       <c r="F12" s="1" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -3993,11 +3995,11 @@
       <c r="E13" s="3" t="inlineStr"/>
       <c r="F13" s="3" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr"/>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="2" t="inlineStr"/>
-      <c r="L13" s="2" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -4018,11 +4020,11 @@
       <c r="E14" s="1" t="inlineStr"/>
       <c r="F14" s="1" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr"/>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr"/>
-      <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="2" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -4039,11 +4041,11 @@
       <c r="E15" s="3" t="inlineStr"/>
       <c r="F15" s="3" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="2" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -4059,34 +4061,32 @@
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
-      <c r="G16">
-        <f>"Total:"</f>
-        <v/>
-      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>Aula 8</t>
         </is>
       </c>
       <c r="O16" t="inlineStr"/>
     </row>
-    <row r="17">
-      <c r="F17">
-        <f>"Sigma Frec:"</f>
-        <v/>
-      </c>
-      <c r="G17">
-        <f>SUM($J$4:$J$9)</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
+  <conditionalFormatting sqref="I4:I9">
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
+      <formula>L4&gt;J4</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="0">
+      <formula>L4=J4</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="2" stopIfTrue="0">
+      <formula>L4&lt;J4</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4097,7 +4097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4491,14 +4491,11 @@
       </c>
       <c r="F10" s="1" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" s="2">
-        <f>COUNTA($H$4:$H$9)</f>
-        <v/>
-      </c>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr">
         <is>
@@ -4531,11 +4528,11 @@
       </c>
       <c r="F11" s="3" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="2" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -4568,11 +4565,11 @@
       <c r="E12" s="1" t="inlineStr"/>
       <c r="F12" s="1" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -4601,11 +4598,11 @@
       <c r="E13" s="3" t="inlineStr"/>
       <c r="F13" s="3" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr"/>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="2" t="inlineStr"/>
-      <c r="L13" s="2" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -4634,13 +4631,13 @@
       <c r="E14" s="1" t="inlineStr"/>
       <c r="F14" s="1" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr"/>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr"/>
-      <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="2" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" s="2" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
@@ -4655,32 +4652,27 @@
       <c r="E15" s="3" t="inlineStr"/>
       <c r="F15" s="3" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="2" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" s="2" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
     </row>
-    <row r="16">
-      <c r="G16">
-        <f>"Total:"</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="F17">
-        <f>"Sigma Frec:"</f>
-        <v/>
-      </c>
-      <c r="G17">
-        <f>SUM($J$4:$J$9)</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
+  <conditionalFormatting sqref="I4:I9">
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
+      <formula>L4&gt;J4</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="0">
+      <formula>L4=J4</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="2" stopIfTrue="0">
+      <formula>L4&lt;J4</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5165,14 +5157,11 @@
       <c r="E10" s="1" t="inlineStr"/>
       <c r="F10" s="1" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" s="2">
-        <f>COUNTA($H$4:$H$9)</f>
-        <v/>
-      </c>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr">
         <is>
@@ -5189,11 +5178,11 @@
       <c r="E11" s="3" t="inlineStr"/>
       <c r="F11" s="3" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="2" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -5214,11 +5203,11 @@
       <c r="E12" s="1" t="inlineStr"/>
       <c r="F12" s="1" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -5235,11 +5224,11 @@
       <c r="E13" s="3" t="inlineStr"/>
       <c r="F13" s="3" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr"/>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="2" t="inlineStr"/>
-      <c r="L13" s="2" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -5260,11 +5249,11 @@
       <c r="E14" s="1" t="inlineStr"/>
       <c r="F14" s="1" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr"/>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr"/>
-      <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="2" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -5281,11 +5270,11 @@
       <c r="E15" s="3" t="inlineStr"/>
       <c r="F15" s="3" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="2" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -5301,17 +5290,14 @@
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
-      <c r="G16">
-        <f>"Total:"</f>
-        <v/>
-      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>Aula 4</t>
         </is>
@@ -5324,21 +5310,15 @@
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
-      <c r="F17">
-        <f>"Sigma Frec:"</f>
-        <v/>
-      </c>
-      <c r="G17">
-        <f>SUM($J$4:$J$9)</f>
-        <v/>
-      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>Aula 4</t>
         </is>
@@ -5346,6 +5326,17 @@
       <c r="O17" t="inlineStr"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="I4:I9">
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
+      <formula>L4&gt;J4</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="0">
+      <formula>L4=J4</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="2" stopIfTrue="0">
+      <formula>L4&lt;J4</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5356,7 +5347,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5734,14 +5725,11 @@
       </c>
       <c r="F10" s="1" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" s="2">
-        <f>COUNTA($H$4:$H$9)</f>
-        <v/>
-      </c>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr">
         <is>
@@ -5774,11 +5762,11 @@
       </c>
       <c r="F11" s="3" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="2" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -5815,11 +5803,11 @@
       </c>
       <c r="F12" s="1" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -5852,11 +5840,11 @@
       </c>
       <c r="F13" s="3" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr"/>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="2" t="inlineStr"/>
-      <c r="L13" s="2" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -5885,13 +5873,13 @@
       <c r="E14" s="1" t="inlineStr"/>
       <c r="F14" s="1" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr"/>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr"/>
-      <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="2" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" s="2" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
@@ -5910,32 +5898,27 @@
       <c r="E15" s="3" t="inlineStr"/>
       <c r="F15" s="3" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="2" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" s="2" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
     </row>
-    <row r="16">
-      <c r="G16">
-        <f>"Total:"</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="F17">
-        <f>"Sigma Frec:"</f>
-        <v/>
-      </c>
-      <c r="G17">
-        <f>SUM($J$4:$J$9)</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
+  <conditionalFormatting sqref="I4:I9">
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
+      <formula>L4&gt;J4</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="0">
+      <formula>L4=J4</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="2" stopIfTrue="0">
+      <formula>L4&lt;J4</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6021,99 +6004,55 @@
       <c r="L1" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B2" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$B$5="Aula 1",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$5="Aula 1",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$5="Aula 1",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$5="Aula 1",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$5="Aula 1",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$5="Aula 1",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$5="Aula 1",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$5="Aula 1",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$5="Aula 1",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$5="Aula 1",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$5="Aula 1",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$5="Aula 1",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$5="Aula 1",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$5="Aula 1",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$5="Aula 1",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$5="Aula 1",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$5="Aula 1",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="C2" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$B$5="Aula 2",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$5="Aula 2",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$5="Aula 2",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$5="Aula 2",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$5="Aula 2",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$5="Aula 2",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$5="Aula 2",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$5="Aula 2",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$5="Aula 2",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$5="Aula 2",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$5="Aula 2",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$5="Aula 2",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$5="Aula 2",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$5="Aula 2",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$5="Aula 2",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$5="Aula 2",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$5="Aula 2",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="D2" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$B$5="Aula 3",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$5="Aula 3",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$5="Aula 3",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$5="Aula 3",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$5="Aula 3",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$5="Aula 3",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$5="Aula 3",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$5="Aula 3",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$5="Aula 3",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$5="Aula 3",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$5="Aula 3",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$5="Aula 3",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$5="Aula 3",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$5="Aula 3",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$5="Aula 3",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$5="Aula 3",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$5="Aula 3",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="E2" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$B$5="Aula 4",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$5="Aula 4",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$5="Aula 4",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$5="Aula 4",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$5="Aula 4",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$5="Aula 4",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$5="Aula 4",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$5="Aula 4",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$5="Aula 4",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$5="Aula 4",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$5="Aula 4",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$5="Aula 4",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$5="Aula 4",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$5="Aula 4",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$5="Aula 4",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$5="Aula 4",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$5="Aula 4",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="F2" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$B$5="Aula 5",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$5="Aula 5",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$5="Aula 5",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$5="Aula 5",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$5="Aula 5",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$5="Aula 5",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$5="Aula 5",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$5="Aula 5",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$5="Aula 5",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$5="Aula 5",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$5="Aula 5",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$5="Aula 5",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$5="Aula 5",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$5="Aula 5",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$5="Aula 5",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$5="Aula 5",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$5="Aula 5",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="G2" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$B$5="Aula 6",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$5="Aula 6",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$5="Aula 6",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$5="Aula 6",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$5="Aula 6",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$5="Aula 6",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$5="Aula 6",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$5="Aula 6",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$5="Aula 6",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$5="Aula 6",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$5="Aula 6",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$5="Aula 6",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$5="Aula 6",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$5="Aula 6",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$5="Aula 6",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$5="Aula 6",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$5="Aula 6",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="H2" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$B$5="Aula 7",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$5="Aula 7",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$5="Aula 7",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$5="Aula 7",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$5="Aula 7",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$5="Aula 7",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$5="Aula 7",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$5="Aula 7",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$5="Aula 7",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$5="Aula 7",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$5="Aula 7",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$5="Aula 7",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$5="Aula 7",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$5="Aula 7",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$5="Aula 7",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$5="Aula 7",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$5="Aula 7",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="I2" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$B$5="Aula 8",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$5="Aula 8",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$5="Aula 8",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$5="Aula 8",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$5="Aula 8",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$5="Aula 8",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$5="Aula 8",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$5="Aula 8",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$5="Aula 8",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$5="Aula 8",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$5="Aula 8",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$5="Aula 8",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$5="Aula 8",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$5="Aula 8",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$5="Aula 8",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$5="Aula 8",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$5="Aula 8",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="J2" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$B$5="Aula 9",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$5="Aula 9",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$5="Aula 9",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$5="Aula 9",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$5="Aula 9",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$5="Aula 9",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$5="Aula 9",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$5="Aula 9",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$5="Aula 9",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$5="Aula 9",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$5="Aula 9",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$5="Aula 9",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$5="Aula 9",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$5="Aula 9",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$5="Aula 9",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$5="Aula 9",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$5="Aula 9",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="K2" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$B$5="Lab",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$5="Lab",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$5="Lab",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$5="Lab",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$5="Lab",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$5="Lab",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$5="Lab",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$5="Lab",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$5="Lab",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$5="Lab",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$5="Lab",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$5="Lab",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$5="Lab",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$5="Lab",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$5="Lab",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$5="Lab",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$5="Lab",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>C111,C112</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>C113</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B3" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$B$7="Aula 1",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$7="Aula 1",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$7="Aula 1",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$7="Aula 1",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$7="Aula 1",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$7="Aula 1",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$7="Aula 1",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$7="Aula 1",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$7="Aula 1",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$7="Aula 1",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$7="Aula 1",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$7="Aula 1",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$7="Aula 1",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$7="Aula 1",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$7="Aula 1",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$7="Aula 1",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$7="Aula 1",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="C3" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$B$7="Aula 2",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$7="Aula 2",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$7="Aula 2",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$7="Aula 2",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$7="Aula 2",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$7="Aula 2",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$7="Aula 2",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$7="Aula 2",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$7="Aula 2",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$7="Aula 2",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$7="Aula 2",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$7="Aula 2",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$7="Aula 2",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$7="Aula 2",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$7="Aula 2",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$7="Aula 2",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$7="Aula 2",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="D3" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$B$7="Aula 3",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$7="Aula 3",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$7="Aula 3",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$7="Aula 3",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$7="Aula 3",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$7="Aula 3",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$7="Aula 3",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$7="Aula 3",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$7="Aula 3",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$7="Aula 3",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$7="Aula 3",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$7="Aula 3",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$7="Aula 3",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$7="Aula 3",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$7="Aula 3",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$7="Aula 3",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$7="Aula 3",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="E3" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$B$7="Aula 4",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$7="Aula 4",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$7="Aula 4",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$7="Aula 4",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$7="Aula 4",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$7="Aula 4",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$7="Aula 4",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$7="Aula 4",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$7="Aula 4",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$7="Aula 4",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$7="Aula 4",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$7="Aula 4",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$7="Aula 4",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$7="Aula 4",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$7="Aula 4",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$7="Aula 4",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$7="Aula 4",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="F3" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$B$7="Aula 5",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$7="Aula 5",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$7="Aula 5",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$7="Aula 5",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$7="Aula 5",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$7="Aula 5",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$7="Aula 5",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$7="Aula 5",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$7="Aula 5",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$7="Aula 5",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$7="Aula 5",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$7="Aula 5",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$7="Aula 5",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$7="Aula 5",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$7="Aula 5",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$7="Aula 5",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$7="Aula 5",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="G3" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$B$7="Aula 6",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$7="Aula 6",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$7="Aula 6",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$7="Aula 6",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$7="Aula 6",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$7="Aula 6",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$7="Aula 6",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$7="Aula 6",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$7="Aula 6",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$7="Aula 6",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$7="Aula 6",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$7="Aula 6",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$7="Aula 6",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$7="Aula 6",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$7="Aula 6",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$7="Aula 6",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$7="Aula 6",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="H3" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$B$7="Aula 7",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$7="Aula 7",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$7="Aula 7",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$7="Aula 7",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$7="Aula 7",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$7="Aula 7",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$7="Aula 7",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$7="Aula 7",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$7="Aula 7",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$7="Aula 7",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$7="Aula 7",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$7="Aula 7",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$7="Aula 7",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$7="Aula 7",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$7="Aula 7",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$7="Aula 7",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$7="Aula 7",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="I3" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$B$7="Aula 8",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$7="Aula 8",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$7="Aula 8",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$7="Aula 8",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$7="Aula 8",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$7="Aula 8",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$7="Aula 8",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$7="Aula 8",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$7="Aula 8",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$7="Aula 8",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$7="Aula 8",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$7="Aula 8",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$7="Aula 8",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$7="Aula 8",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$7="Aula 8",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$7="Aula 8",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$7="Aula 8",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="J3" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$B$7="Aula 9",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$7="Aula 9",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$7="Aula 9",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$7="Aula 9",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$7="Aula 9",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$7="Aula 9",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$7="Aula 9",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$7="Aula 9",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$7="Aula 9",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$7="Aula 9",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$7="Aula 9",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$7="Aula 9",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$7="Aula 9",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$7="Aula 9",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$7="Aula 9",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$7="Aula 9",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$7="Aula 9",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="K3" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$B$7="Lab",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$7="Lab",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$7="Lab",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$7="Lab",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$7="Lab",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$7="Lab",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$7="Lab",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$7="Lab",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$7="Lab",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$7="Lab",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$7="Lab",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$7="Lab",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$7="Lab",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$7="Lab",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$7="Lab",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$7="Lab",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$7="Lab",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>C112</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>C113</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
     </row>
     <row r="4">
@@ -6123,43 +6062,43 @@
         </is>
       </c>
       <c r="B4" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$B$9="Aula 1",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$9="Aula 1",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$9="Aula 1",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$9="Aula 1",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$9="Aula 1",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$9="Aula 1",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$9="Aula 1",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$9="Aula 1",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$9="Aula 1",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$9="Aula 1",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$9="Aula 1",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$9="Aula 1",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$9="Aula 1",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$9="Aula 1",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$9="Aula 1",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$9="Aula 1",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$9="Aula 1",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$B$5="Aula 1",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$5="Aula 1",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$5="Aula 1",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$5="Aula 1",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$5="Aula 1",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$5="Aula 1",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$5="Aula 1",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$5="Aula 1",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$5="Aula 1",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$5="Aula 1",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$5="Aula 1",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$5="Aula 1",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$5="Aula 1",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$5="Aula 1",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$5="Aula 1",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$5="Aula 1",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$5="Aula 1",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="C4" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$B$9="Aula 2",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$9="Aula 2",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$9="Aula 2",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$9="Aula 2",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$9="Aula 2",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$9="Aula 2",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$9="Aula 2",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$9="Aula 2",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$9="Aula 2",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$9="Aula 2",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$9="Aula 2",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$9="Aula 2",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$9="Aula 2",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$9="Aula 2",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$9="Aula 2",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$9="Aula 2",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$9="Aula 2",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$B$5="Aula 2",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$5="Aula 2",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$5="Aula 2",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$5="Aula 2",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$5="Aula 2",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$5="Aula 2",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$5="Aula 2",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$5="Aula 2",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$5="Aula 2",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$5="Aula 2",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$5="Aula 2",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$5="Aula 2",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$5="Aula 2",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$5="Aula 2",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$5="Aula 2",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$5="Aula 2",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$5="Aula 2",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="D4" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$B$9="Aula 3",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$9="Aula 3",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$9="Aula 3",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$9="Aula 3",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$9="Aula 3",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$9="Aula 3",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$9="Aula 3",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$9="Aula 3",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$9="Aula 3",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$9="Aula 3",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$9="Aula 3",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$9="Aula 3",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$9="Aula 3",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$9="Aula 3",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$9="Aula 3",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$9="Aula 3",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$9="Aula 3",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$B$5="Aula 3",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$5="Aula 3",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$5="Aula 3",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$5="Aula 3",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$5="Aula 3",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$5="Aula 3",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$5="Aula 3",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$5="Aula 3",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$5="Aula 3",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$5="Aula 3",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$5="Aula 3",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$5="Aula 3",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$5="Aula 3",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$5="Aula 3",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$5="Aula 3",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$5="Aula 3",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$5="Aula 3",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="E4" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$B$9="Aula 4",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$9="Aula 4",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$9="Aula 4",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$9="Aula 4",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$9="Aula 4",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$9="Aula 4",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$9="Aula 4",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$9="Aula 4",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$9="Aula 4",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$9="Aula 4",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$9="Aula 4",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$9="Aula 4",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$9="Aula 4",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$9="Aula 4",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$9="Aula 4",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$9="Aula 4",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$9="Aula 4",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$B$5="Aula 4",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$5="Aula 4",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$5="Aula 4",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$5="Aula 4",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$5="Aula 4",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$5="Aula 4",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$5="Aula 4",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$5="Aula 4",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$5="Aula 4",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$5="Aula 4",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$5="Aula 4",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$5="Aula 4",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$5="Aula 4",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$5="Aula 4",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$5="Aula 4",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$5="Aula 4",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$5="Aula 4",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="F4" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$B$9="Aula 5",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$9="Aula 5",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$9="Aula 5",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$9="Aula 5",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$9="Aula 5",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$9="Aula 5",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$9="Aula 5",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$9="Aula 5",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$9="Aula 5",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$9="Aula 5",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$9="Aula 5",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$9="Aula 5",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$9="Aula 5",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$9="Aula 5",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$9="Aula 5",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$9="Aula 5",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$9="Aula 5",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$B$5="Aula 5",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$5="Aula 5",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$5="Aula 5",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$5="Aula 5",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$5="Aula 5",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$5="Aula 5",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$5="Aula 5",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$5="Aula 5",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$5="Aula 5",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$5="Aula 5",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$5="Aula 5",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$5="Aula 5",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$5="Aula 5",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$5="Aula 5",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$5="Aula 5",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$5="Aula 5",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$5="Aula 5",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="G4" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$B$9="Aula 6",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$9="Aula 6",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$9="Aula 6",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$9="Aula 6",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$9="Aula 6",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$9="Aula 6",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$9="Aula 6",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$9="Aula 6",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$9="Aula 6",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$9="Aula 6",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$9="Aula 6",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$9="Aula 6",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$9="Aula 6",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$9="Aula 6",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$9="Aula 6",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$9="Aula 6",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$9="Aula 6",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$B$5="Aula 6",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$5="Aula 6",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$5="Aula 6",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$5="Aula 6",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$5="Aula 6",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$5="Aula 6",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$5="Aula 6",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$5="Aula 6",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$5="Aula 6",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$5="Aula 6",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$5="Aula 6",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$5="Aula 6",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$5="Aula 6",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$5="Aula 6",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$5="Aula 6",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$5="Aula 6",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$5="Aula 6",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="H4" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$B$9="Aula 7",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$9="Aula 7",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$9="Aula 7",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$9="Aula 7",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$9="Aula 7",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$9="Aula 7",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$9="Aula 7",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$9="Aula 7",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$9="Aula 7",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$9="Aula 7",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$9="Aula 7",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$9="Aula 7",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$9="Aula 7",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$9="Aula 7",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$9="Aula 7",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$9="Aula 7",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$9="Aula 7",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$B$5="Aula 7",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$5="Aula 7",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$5="Aula 7",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$5="Aula 7",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$5="Aula 7",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$5="Aula 7",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$5="Aula 7",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$5="Aula 7",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$5="Aula 7",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$5="Aula 7",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$5="Aula 7",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$5="Aula 7",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$5="Aula 7",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$5="Aula 7",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$5="Aula 7",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$5="Aula 7",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$5="Aula 7",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="I4" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$B$9="Aula 8",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$9="Aula 8",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$9="Aula 8",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$9="Aula 8",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$9="Aula 8",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$9="Aula 8",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$9="Aula 8",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$9="Aula 8",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$9="Aula 8",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$9="Aula 8",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$9="Aula 8",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$9="Aula 8",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$9="Aula 8",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$9="Aula 8",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$9="Aula 8",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$9="Aula 8",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$9="Aula 8",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$B$5="Aula 8",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$5="Aula 8",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$5="Aula 8",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$5="Aula 8",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$5="Aula 8",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$5="Aula 8",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$5="Aula 8",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$5="Aula 8",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$5="Aula 8",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$5="Aula 8",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$5="Aula 8",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$5="Aula 8",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$5="Aula 8",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$5="Aula 8",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$5="Aula 8",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$5="Aula 8",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$5="Aula 8",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="J4" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$B$9="Aula 9",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$9="Aula 9",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$9="Aula 9",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$9="Aula 9",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$9="Aula 9",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$9="Aula 9",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$9="Aula 9",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$9="Aula 9",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$9="Aula 9",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$9="Aula 9",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$9="Aula 9",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$9="Aula 9",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$9="Aula 9",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$9="Aula 9",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$9="Aula 9",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$9="Aula 9",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$9="Aula 9",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$B$5="Aula 9",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$5="Aula 9",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$5="Aula 9",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$5="Aula 9",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$5="Aula 9",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$5="Aula 9",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$5="Aula 9",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$5="Aula 9",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$5="Aula 9",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$5="Aula 9",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$5="Aula 9",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$5="Aula 9",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$5="Aula 9",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$5="Aula 9",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$5="Aula 9",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$5="Aula 9",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$5="Aula 9",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="K4" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$B$9="Lab",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$9="Lab",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$9="Lab",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$9="Lab",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$9="Lab",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$9="Lab",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$9="Lab",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$9="Lab",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$9="Lab",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$9="Lab",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$9="Lab",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$9="Lab",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$9="Lab",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$9="Lab",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$9="Lab",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$9="Lab",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$9="Lab",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$B$5="Lab",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$5="Lab",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$5="Lab",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$5="Lab",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$5="Lab",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$5="Lab",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$5="Lab",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$5="Lab",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$5="Lab",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$5="Lab",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$5="Lab",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$5="Lab",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$5="Lab",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$5="Lab",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$5="Lab",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$5="Lab",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$5="Lab",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -6171,43 +6110,43 @@
         </is>
       </c>
       <c r="B5" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$B$11="Aula 1",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$11="Aula 1",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$11="Aula 1",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$11="Aula 1",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$11="Aula 1",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$11="Aula 1",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$11="Aula 1",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$11="Aula 1",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$11="Aula 1",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$11="Aula 1",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$11="Aula 1",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$11="Aula 1",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$11="Aula 1",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$11="Aula 1",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$11="Aula 1",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$11="Aula 1",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$11="Aula 1",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$B$7="Aula 1",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$7="Aula 1",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$7="Aula 1",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$7="Aula 1",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$7="Aula 1",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$7="Aula 1",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$7="Aula 1",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$7="Aula 1",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$7="Aula 1",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$7="Aula 1",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$7="Aula 1",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$7="Aula 1",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$7="Aula 1",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$7="Aula 1",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$7="Aula 1",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$7="Aula 1",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$7="Aula 1",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="C5" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$B$11="Aula 2",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$11="Aula 2",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$11="Aula 2",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$11="Aula 2",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$11="Aula 2",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$11="Aula 2",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$11="Aula 2",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$11="Aula 2",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$11="Aula 2",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$11="Aula 2",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$11="Aula 2",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$11="Aula 2",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$11="Aula 2",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$11="Aula 2",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$11="Aula 2",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$11="Aula 2",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$11="Aula 2",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$B$7="Aula 2",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$7="Aula 2",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$7="Aula 2",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$7="Aula 2",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$7="Aula 2",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$7="Aula 2",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$7="Aula 2",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$7="Aula 2",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$7="Aula 2",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$7="Aula 2",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$7="Aula 2",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$7="Aula 2",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$7="Aula 2",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$7="Aula 2",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$7="Aula 2",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$7="Aula 2",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$7="Aula 2",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$B$11="Aula 3",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$11="Aula 3",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$11="Aula 3",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$11="Aula 3",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$11="Aula 3",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$11="Aula 3",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$11="Aula 3",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$11="Aula 3",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$11="Aula 3",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$11="Aula 3",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$11="Aula 3",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$11="Aula 3",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$11="Aula 3",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$11="Aula 3",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$11="Aula 3",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$11="Aula 3",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$11="Aula 3",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$B$7="Aula 3",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$7="Aula 3",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$7="Aula 3",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$7="Aula 3",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$7="Aula 3",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$7="Aula 3",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$7="Aula 3",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$7="Aula 3",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$7="Aula 3",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$7="Aula 3",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$7="Aula 3",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$7="Aula 3",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$7="Aula 3",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$7="Aula 3",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$7="Aula 3",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$7="Aula 3",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$7="Aula 3",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$B$11="Aula 4",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$11="Aula 4",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$11="Aula 4",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$11="Aula 4",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$11="Aula 4",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$11="Aula 4",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$11="Aula 4",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$11="Aula 4",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$11="Aula 4",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$11="Aula 4",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$11="Aula 4",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$11="Aula 4",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$11="Aula 4",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$11="Aula 4",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$11="Aula 4",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$11="Aula 4",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$11="Aula 4",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$B$7="Aula 4",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$7="Aula 4",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$7="Aula 4",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$7="Aula 4",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$7="Aula 4",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$7="Aula 4",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$7="Aula 4",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$7="Aula 4",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$7="Aula 4",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$7="Aula 4",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$7="Aula 4",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$7="Aula 4",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$7="Aula 4",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$7="Aula 4",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$7="Aula 4",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$7="Aula 4",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$7="Aula 4",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$B$11="Aula 5",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$11="Aula 5",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$11="Aula 5",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$11="Aula 5",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$11="Aula 5",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$11="Aula 5",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$11="Aula 5",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$11="Aula 5",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$11="Aula 5",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$11="Aula 5",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$11="Aula 5",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$11="Aula 5",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$11="Aula 5",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$11="Aula 5",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$11="Aula 5",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$11="Aula 5",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$11="Aula 5",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$B$7="Aula 5",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$7="Aula 5",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$7="Aula 5",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$7="Aula 5",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$7="Aula 5",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$7="Aula 5",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$7="Aula 5",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$7="Aula 5",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$7="Aula 5",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$7="Aula 5",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$7="Aula 5",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$7="Aula 5",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$7="Aula 5",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$7="Aula 5",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$7="Aula 5",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$7="Aula 5",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$7="Aula 5",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="G5" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$B$11="Aula 6",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$11="Aula 6",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$11="Aula 6",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$11="Aula 6",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$11="Aula 6",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$11="Aula 6",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$11="Aula 6",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$11="Aula 6",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$11="Aula 6",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$11="Aula 6",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$11="Aula 6",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$11="Aula 6",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$11="Aula 6",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$11="Aula 6",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$11="Aula 6",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$11="Aula 6",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$11="Aula 6",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$B$7="Aula 6",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$7="Aula 6",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$7="Aula 6",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$7="Aula 6",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$7="Aula 6",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$7="Aula 6",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$7="Aula 6",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$7="Aula 6",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$7="Aula 6",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$7="Aula 6",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$7="Aula 6",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$7="Aula 6",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$7="Aula 6",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$7="Aula 6",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$7="Aula 6",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$7="Aula 6",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$7="Aula 6",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="H5" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$B$11="Aula 7",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$11="Aula 7",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$11="Aula 7",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$11="Aula 7",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$11="Aula 7",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$11="Aula 7",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$11="Aula 7",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$11="Aula 7",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$11="Aula 7",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$11="Aula 7",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$11="Aula 7",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$11="Aula 7",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$11="Aula 7",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$11="Aula 7",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$11="Aula 7",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$11="Aula 7",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$11="Aula 7",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$B$7="Aula 7",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$7="Aula 7",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$7="Aula 7",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$7="Aula 7",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$7="Aula 7",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$7="Aula 7",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$7="Aula 7",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$7="Aula 7",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$7="Aula 7",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$7="Aula 7",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$7="Aula 7",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$7="Aula 7",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$7="Aula 7",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$7="Aula 7",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$7="Aula 7",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$7="Aula 7",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$7="Aula 7",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="I5" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$B$11="Aula 8",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$11="Aula 8",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$11="Aula 8",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$11="Aula 8",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$11="Aula 8",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$11="Aula 8",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$11="Aula 8",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$11="Aula 8",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$11="Aula 8",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$11="Aula 8",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$11="Aula 8",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$11="Aula 8",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$11="Aula 8",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$11="Aula 8",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$11="Aula 8",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$11="Aula 8",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$11="Aula 8",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$B$7="Aula 8",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$7="Aula 8",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$7="Aula 8",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$7="Aula 8",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$7="Aula 8",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$7="Aula 8",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$7="Aula 8",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$7="Aula 8",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$7="Aula 8",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$7="Aula 8",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$7="Aula 8",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$7="Aula 8",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$7="Aula 8",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$7="Aula 8",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$7="Aula 8",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$7="Aula 8",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$7="Aula 8",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="J5" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$B$11="Aula 9",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$11="Aula 9",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$11="Aula 9",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$11="Aula 9",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$11="Aula 9",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$11="Aula 9",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$11="Aula 9",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$11="Aula 9",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$11="Aula 9",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$11="Aula 9",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$11="Aula 9",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$11="Aula 9",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$11="Aula 9",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$11="Aula 9",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$11="Aula 9",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$11="Aula 9",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$11="Aula 9",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$B$7="Aula 9",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$7="Aula 9",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$7="Aula 9",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$7="Aula 9",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$7="Aula 9",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$7="Aula 9",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$7="Aula 9",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$7="Aula 9",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$7="Aula 9",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$7="Aula 9",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$7="Aula 9",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$7="Aula 9",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$7="Aula 9",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$7="Aula 9",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$7="Aula 9",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$7="Aula 9",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$7="Aula 9",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="K5" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$B$11="Lab",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$11="Lab",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$11="Lab",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$11="Lab",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$11="Lab",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$11="Lab",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$11="Lab",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$11="Lab",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$11="Lab",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$11="Lab",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$11="Lab",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$11="Lab",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$11="Lab",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$11="Lab",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$11="Lab",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$11="Lab",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$11="Lab",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$B$7="Lab",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$7="Lab",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$7="Lab",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$7="Lab",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$7="Lab",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$7="Lab",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$7="Lab",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$7="Lab",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$7="Lab",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$7="Lab",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$7="Lab",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$7="Lab",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$7="Lab",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$7="Lab",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$7="Lab",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$7="Lab",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$7="Lab",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -6219,43 +6158,43 @@
         </is>
       </c>
       <c r="B6" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$B$13="Aula 1",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$13="Aula 1",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$13="Aula 1",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$13="Aula 1",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$13="Aula 1",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$13="Aula 1",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$13="Aula 1",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$13="Aula 1",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$13="Aula 1",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$13="Aula 1",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$13="Aula 1",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$13="Aula 1",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$13="Aula 1",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$13="Aula 1",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$13="Aula 1",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$13="Aula 1",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$13="Aula 1",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$B$9="Aula 1",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$9="Aula 1",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$9="Aula 1",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$9="Aula 1",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$9="Aula 1",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$9="Aula 1",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$9="Aula 1",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$9="Aula 1",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$9="Aula 1",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$9="Aula 1",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$9="Aula 1",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$9="Aula 1",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$9="Aula 1",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$9="Aula 1",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$9="Aula 1",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$9="Aula 1",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$9="Aula 1",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="C6" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$B$13="Aula 2",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$13="Aula 2",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$13="Aula 2",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$13="Aula 2",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$13="Aula 2",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$13="Aula 2",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$13="Aula 2",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$13="Aula 2",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$13="Aula 2",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$13="Aula 2",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$13="Aula 2",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$13="Aula 2",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$13="Aula 2",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$13="Aula 2",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$13="Aula 2",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$13="Aula 2",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$13="Aula 2",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$B$9="Aula 2",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$9="Aula 2",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$9="Aula 2",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$9="Aula 2",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$9="Aula 2",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$9="Aula 2",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$9="Aula 2",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$9="Aula 2",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$9="Aula 2",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$9="Aula 2",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$9="Aula 2",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$9="Aula 2",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$9="Aula 2",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$9="Aula 2",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$9="Aula 2",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$9="Aula 2",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$9="Aula 2",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$B$13="Aula 3",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$13="Aula 3",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$13="Aula 3",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$13="Aula 3",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$13="Aula 3",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$13="Aula 3",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$13="Aula 3",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$13="Aula 3",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$13="Aula 3",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$13="Aula 3",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$13="Aula 3",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$13="Aula 3",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$13="Aula 3",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$13="Aula 3",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$13="Aula 3",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$13="Aula 3",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$13="Aula 3",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$B$9="Aula 3",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$9="Aula 3",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$9="Aula 3",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$9="Aula 3",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$9="Aula 3",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$9="Aula 3",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$9="Aula 3",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$9="Aula 3",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$9="Aula 3",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$9="Aula 3",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$9="Aula 3",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$9="Aula 3",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$9="Aula 3",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$9="Aula 3",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$9="Aula 3",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$9="Aula 3",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$9="Aula 3",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$B$13="Aula 4",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$13="Aula 4",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$13="Aula 4",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$13="Aula 4",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$13="Aula 4",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$13="Aula 4",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$13="Aula 4",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$13="Aula 4",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$13="Aula 4",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$13="Aula 4",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$13="Aula 4",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$13="Aula 4",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$13="Aula 4",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$13="Aula 4",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$13="Aula 4",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$13="Aula 4",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$13="Aula 4",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$B$9="Aula 4",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$9="Aula 4",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$9="Aula 4",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$9="Aula 4",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$9="Aula 4",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$9="Aula 4",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$9="Aula 4",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$9="Aula 4",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$9="Aula 4",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$9="Aula 4",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$9="Aula 4",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$9="Aula 4",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$9="Aula 4",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$9="Aula 4",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$9="Aula 4",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$9="Aula 4",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$9="Aula 4",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$B$13="Aula 5",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$13="Aula 5",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$13="Aula 5",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$13="Aula 5",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$13="Aula 5",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$13="Aula 5",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$13="Aula 5",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$13="Aula 5",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$13="Aula 5",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$13="Aula 5",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$13="Aula 5",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$13="Aula 5",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$13="Aula 5",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$13="Aula 5",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$13="Aula 5",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$13="Aula 5",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$13="Aula 5",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$B$9="Aula 5",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$9="Aula 5",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$9="Aula 5",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$9="Aula 5",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$9="Aula 5",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$9="Aula 5",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$9="Aula 5",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$9="Aula 5",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$9="Aula 5",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$9="Aula 5",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$9="Aula 5",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$9="Aula 5",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$9="Aula 5",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$9="Aula 5",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$9="Aula 5",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$9="Aula 5",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$9="Aula 5",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="G6" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$B$13="Aula 6",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$13="Aula 6",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$13="Aula 6",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$13="Aula 6",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$13="Aula 6",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$13="Aula 6",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$13="Aula 6",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$13="Aula 6",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$13="Aula 6",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$13="Aula 6",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$13="Aula 6",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$13="Aula 6",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$13="Aula 6",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$13="Aula 6",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$13="Aula 6",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$13="Aula 6",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$13="Aula 6",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$B$9="Aula 6",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$9="Aula 6",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$9="Aula 6",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$9="Aula 6",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$9="Aula 6",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$9="Aula 6",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$9="Aula 6",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$9="Aula 6",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$9="Aula 6",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$9="Aula 6",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$9="Aula 6",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$9="Aula 6",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$9="Aula 6",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$9="Aula 6",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$9="Aula 6",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$9="Aula 6",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$9="Aula 6",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="H6" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$B$13="Aula 7",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$13="Aula 7",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$13="Aula 7",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$13="Aula 7",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$13="Aula 7",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$13="Aula 7",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$13="Aula 7",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$13="Aula 7",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$13="Aula 7",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$13="Aula 7",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$13="Aula 7",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$13="Aula 7",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$13="Aula 7",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$13="Aula 7",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$13="Aula 7",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$13="Aula 7",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$13="Aula 7",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$B$9="Aula 7",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$9="Aula 7",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$9="Aula 7",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$9="Aula 7",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$9="Aula 7",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$9="Aula 7",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$9="Aula 7",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$9="Aula 7",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$9="Aula 7",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$9="Aula 7",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$9="Aula 7",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$9="Aula 7",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$9="Aula 7",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$9="Aula 7",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$9="Aula 7",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$9="Aula 7",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$9="Aula 7",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="I6" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$B$13="Aula 8",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$13="Aula 8",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$13="Aula 8",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$13="Aula 8",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$13="Aula 8",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$13="Aula 8",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$13="Aula 8",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$13="Aula 8",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$13="Aula 8",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$13="Aula 8",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$13="Aula 8",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$13="Aula 8",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$13="Aula 8",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$13="Aula 8",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$13="Aula 8",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$13="Aula 8",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$13="Aula 8",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$B$9="Aula 8",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$9="Aula 8",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$9="Aula 8",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$9="Aula 8",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$9="Aula 8",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$9="Aula 8",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$9="Aula 8",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$9="Aula 8",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$9="Aula 8",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$9="Aula 8",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$9="Aula 8",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$9="Aula 8",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$9="Aula 8",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$9="Aula 8",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$9="Aula 8",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$9="Aula 8",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$9="Aula 8",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="J6" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$B$13="Aula 9",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$13="Aula 9",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$13="Aula 9",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$13="Aula 9",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$13="Aula 9",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$13="Aula 9",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$13="Aula 9",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$13="Aula 9",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$13="Aula 9",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$13="Aula 9",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$13="Aula 9",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$13="Aula 9",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$13="Aula 9",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$13="Aula 9",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$13="Aula 9",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$13="Aula 9",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$13="Aula 9",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$B$9="Aula 9",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$9="Aula 9",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$9="Aula 9",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$9="Aula 9",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$9="Aula 9",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$9="Aula 9",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$9="Aula 9",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$9="Aula 9",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$9="Aula 9",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$9="Aula 9",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$9="Aula 9",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$9="Aula 9",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$9="Aula 9",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$9="Aula 9",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$9="Aula 9",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$9="Aula 9",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$9="Aula 9",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="K6" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$B$13="Lab",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$13="Lab",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$13="Lab",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$13="Lab",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$13="Lab",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$13="Lab",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$13="Lab",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$13="Lab",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$13="Lab",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$13="Lab",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$13="Lab",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$13="Lab",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$13="Lab",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$13="Lab",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$13="Lab",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$13="Lab",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$13="Lab",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$B$9="Lab",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$9="Lab",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$9="Lab",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$9="Lab",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$9="Lab",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$9="Lab",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$9="Lab",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$9="Lab",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$9="Lab",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$9="Lab",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$9="Lab",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$9="Lab",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$9="Lab",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$9="Lab",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$9="Lab",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$9="Lab",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$9="Lab",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="L6" t="inlineStr"/>
@@ -6267,43 +6206,43 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$B$15="Aula 1",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$15="Aula 1",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$15="Aula 1",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$15="Aula 1",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$15="Aula 1",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$15="Aula 1",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$15="Aula 1",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$15="Aula 1",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$15="Aula 1",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$15="Aula 1",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$15="Aula 1",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$15="Aula 1",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$15="Aula 1",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$15="Aula 1",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$15="Aula 1",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$15="Aula 1",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$15="Aula 1",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$B$11="Aula 1",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$11="Aula 1",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$11="Aula 1",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$11="Aula 1",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$11="Aula 1",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$11="Aula 1",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$11="Aula 1",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$11="Aula 1",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$11="Aula 1",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$11="Aula 1",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$11="Aula 1",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$11="Aula 1",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$11="Aula 1",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$11="Aula 1",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$11="Aula 1",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$11="Aula 1",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$11="Aula 1",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="C7" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$B$15="Aula 2",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$15="Aula 2",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$15="Aula 2",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$15="Aula 2",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$15="Aula 2",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$15="Aula 2",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$15="Aula 2",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$15="Aula 2",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$15="Aula 2",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$15="Aula 2",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$15="Aula 2",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$15="Aula 2",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$15="Aula 2",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$15="Aula 2",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$15="Aula 2",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$15="Aula 2",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$15="Aula 2",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$B$11="Aula 2",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$11="Aula 2",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$11="Aula 2",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$11="Aula 2",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$11="Aula 2",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$11="Aula 2",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$11="Aula 2",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$11="Aula 2",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$11="Aula 2",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$11="Aula 2",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$11="Aula 2",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$11="Aula 2",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$11="Aula 2",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$11="Aula 2",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$11="Aula 2",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$11="Aula 2",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$11="Aula 2",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="D7" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$B$15="Aula 3",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$15="Aula 3",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$15="Aula 3",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$15="Aula 3",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$15="Aula 3",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$15="Aula 3",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$15="Aula 3",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$15="Aula 3",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$15="Aula 3",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$15="Aula 3",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$15="Aula 3",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$15="Aula 3",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$15="Aula 3",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$15="Aula 3",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$15="Aula 3",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$15="Aula 3",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$15="Aula 3",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$B$11="Aula 3",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$11="Aula 3",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$11="Aula 3",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$11="Aula 3",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$11="Aula 3",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$11="Aula 3",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$11="Aula 3",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$11="Aula 3",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$11="Aula 3",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$11="Aula 3",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$11="Aula 3",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$11="Aula 3",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$11="Aula 3",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$11="Aula 3",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$11="Aula 3",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$11="Aula 3",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$11="Aula 3",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$B$15="Aula 4",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$15="Aula 4",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$15="Aula 4",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$15="Aula 4",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$15="Aula 4",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$15="Aula 4",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$15="Aula 4",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$15="Aula 4",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$15="Aula 4",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$15="Aula 4",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$15="Aula 4",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$15="Aula 4",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$15="Aula 4",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$15="Aula 4",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$15="Aula 4",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$15="Aula 4",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$15="Aula 4",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$B$11="Aula 4",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$11="Aula 4",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$11="Aula 4",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$11="Aula 4",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$11="Aula 4",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$11="Aula 4",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$11="Aula 4",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$11="Aula 4",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$11="Aula 4",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$11="Aula 4",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$11="Aula 4",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$11="Aula 4",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$11="Aula 4",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$11="Aula 4",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$11="Aula 4",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$11="Aula 4",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$11="Aula 4",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$B$15="Aula 5",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$15="Aula 5",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$15="Aula 5",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$15="Aula 5",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$15="Aula 5",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$15="Aula 5",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$15="Aula 5",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$15="Aula 5",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$15="Aula 5",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$15="Aula 5",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$15="Aula 5",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$15="Aula 5",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$15="Aula 5",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$15="Aula 5",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$15="Aula 5",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$15="Aula 5",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$15="Aula 5",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$B$11="Aula 5",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$11="Aula 5",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$11="Aula 5",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$11="Aula 5",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$11="Aula 5",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$11="Aula 5",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$11="Aula 5",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$11="Aula 5",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$11="Aula 5",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$11="Aula 5",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$11="Aula 5",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$11="Aula 5",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$11="Aula 5",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$11="Aula 5",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$11="Aula 5",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$11="Aula 5",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$11="Aula 5",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="G7" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$B$15="Aula 6",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$15="Aula 6",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$15="Aula 6",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$15="Aula 6",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$15="Aula 6",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$15="Aula 6",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$15="Aula 6",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$15="Aula 6",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$15="Aula 6",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$15="Aula 6",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$15="Aula 6",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$15="Aula 6",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$15="Aula 6",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$15="Aula 6",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$15="Aula 6",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$15="Aula 6",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$15="Aula 6",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$B$11="Aula 6",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$11="Aula 6",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$11="Aula 6",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$11="Aula 6",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$11="Aula 6",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$11="Aula 6",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$11="Aula 6",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$11="Aula 6",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$11="Aula 6",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$11="Aula 6",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$11="Aula 6",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$11="Aula 6",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$11="Aula 6",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$11="Aula 6",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$11="Aula 6",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$11="Aula 6",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$11="Aula 6",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="H7" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$B$15="Aula 7",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$15="Aula 7",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$15="Aula 7",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$15="Aula 7",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$15="Aula 7",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$15="Aula 7",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$15="Aula 7",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$15="Aula 7",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$15="Aula 7",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$15="Aula 7",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$15="Aula 7",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$15="Aula 7",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$15="Aula 7",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$15="Aula 7",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$15="Aula 7",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$15="Aula 7",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$15="Aula 7",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$B$11="Aula 7",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$11="Aula 7",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$11="Aula 7",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$11="Aula 7",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$11="Aula 7",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$11="Aula 7",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$11="Aula 7",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$11="Aula 7",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$11="Aula 7",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$11="Aula 7",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$11="Aula 7",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$11="Aula 7",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$11="Aula 7",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$11="Aula 7",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$11="Aula 7",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$11="Aula 7",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$11="Aula 7",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="I7" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$B$15="Aula 8",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$15="Aula 8",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$15="Aula 8",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$15="Aula 8",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$15="Aula 8",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$15="Aula 8",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$15="Aula 8",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$15="Aula 8",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$15="Aula 8",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$15="Aula 8",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$15="Aula 8",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$15="Aula 8",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$15="Aula 8",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$15="Aula 8",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$15="Aula 8",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$15="Aula 8",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$15="Aula 8",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$B$11="Aula 8",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$11="Aula 8",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$11="Aula 8",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$11="Aula 8",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$11="Aula 8",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$11="Aula 8",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$11="Aula 8",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$11="Aula 8",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$11="Aula 8",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$11="Aula 8",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$11="Aula 8",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$11="Aula 8",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$11="Aula 8",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$11="Aula 8",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$11="Aula 8",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$11="Aula 8",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$11="Aula 8",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="J7" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$B$15="Aula 9",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$15="Aula 9",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$15="Aula 9",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$15="Aula 9",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$15="Aula 9",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$15="Aula 9",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$15="Aula 9",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$15="Aula 9",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$15="Aula 9",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$15="Aula 9",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$15="Aula 9",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$15="Aula 9",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$15="Aula 9",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$15="Aula 9",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$15="Aula 9",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$15="Aula 9",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$15="Aula 9",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$B$11="Aula 9",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$11="Aula 9",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$11="Aula 9",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$11="Aula 9",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$11="Aula 9",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$11="Aula 9",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$11="Aula 9",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$11="Aula 9",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$11="Aula 9",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$11="Aula 9",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$11="Aula 9",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$11="Aula 9",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$11="Aula 9",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$11="Aula 9",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$11="Aula 9",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$11="Aula 9",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$11="Aula 9",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="K7" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$B$15="Lab",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$15="Lab",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$15="Lab",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$15="Lab",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$15="Lab",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$15="Lab",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$15="Lab",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$15="Lab",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$15="Lab",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$15="Lab",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$15="Lab",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$15="Lab",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$15="Lab",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$15="Lab",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$15="Lab",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$15="Lab",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$15="Lab",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$B$11="Lab",(D111!$A$1&amp;" "),"")&amp;IF(D211!$B$11="Lab",(D211!$A$1&amp;" "),"")&amp;IF(D311!$B$11="Lab",(D311!$A$1&amp;" "),"")&amp;IF(D411!$B$11="Lab",(D411!$A$1&amp;" "),"")&amp;IF(C111!$B$11="Lab",(C111!$A$1&amp;" "),"")&amp;IF(C121!$B$11="Lab",(C121!$A$1&amp;" "),"")&amp;IF(C122!$B$11="Lab",(C122!$A$1&amp;" "),"")&amp;IF(C211!$B$11="Lab",(C211!$A$1&amp;" "),"")&amp;IF(C212!$B$11="Lab",(C212!$A$1&amp;" "),"")&amp;IF(C311!$B$11="Lab",(C311!$A$1&amp;" "),"")&amp;IF(C312!$B$11="Lab",(C312!$A$1&amp;" "),"")&amp;IF(C411!$B$11="Lab",(C411!$A$1&amp;" "),"")&amp;IF(C412!$B$11="Lab",(C412!$A$1&amp;" "),"")&amp;IF(M111!$B$11="Lab",(M111!$A$1&amp;" "),"")&amp;IF(M211!$B$11="Lab",(M211!$A$1&amp;" "),"")&amp;IF(M311!$B$11="Lab",(M311!$A$1&amp;" "),"")&amp;IF(M411!$B$11="Lab",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="L7" t="inlineStr"/>
@@ -6381,99 +6320,59 @@
       <c r="L9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B10" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$C$5="Aula 1",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$5="Aula 1",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$5="Aula 1",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$5="Aula 1",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$5="Aula 1",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$5="Aula 1",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$5="Aula 1",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$5="Aula 1",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$5="Aula 1",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$5="Aula 1",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$5="Aula 1",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$5="Aula 1",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$5="Aula 1",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$5="Aula 1",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$5="Aula 1",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$5="Aula 1",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$5="Aula 1",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="C10" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$C$5="Aula 2",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$5="Aula 2",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$5="Aula 2",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$5="Aula 2",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$5="Aula 2",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$5="Aula 2",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$5="Aula 2",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$5="Aula 2",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$5="Aula 2",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$5="Aula 2",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$5="Aula 2",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$5="Aula 2",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$5="Aula 2",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$5="Aula 2",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$5="Aula 2",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$5="Aula 2",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$5="Aula 2",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="D10" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$C$5="Aula 3",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$5="Aula 3",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$5="Aula 3",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$5="Aula 3",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$5="Aula 3",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$5="Aula 3",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$5="Aula 3",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$5="Aula 3",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$5="Aula 3",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$5="Aula 3",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$5="Aula 3",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$5="Aula 3",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$5="Aula 3",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$5="Aula 3",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$5="Aula 3",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$5="Aula 3",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$5="Aula 3",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="E10" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$C$5="Aula 4",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$5="Aula 4",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$5="Aula 4",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$5="Aula 4",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$5="Aula 4",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$5="Aula 4",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$5="Aula 4",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$5="Aula 4",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$5="Aula 4",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$5="Aula 4",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$5="Aula 4",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$5="Aula 4",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$5="Aula 4",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$5="Aula 4",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$5="Aula 4",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$5="Aula 4",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$5="Aula 4",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="F10" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$C$5="Aula 5",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$5="Aula 5",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$5="Aula 5",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$5="Aula 5",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$5="Aula 5",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$5="Aula 5",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$5="Aula 5",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$5="Aula 5",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$5="Aula 5",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$5="Aula 5",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$5="Aula 5",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$5="Aula 5",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$5="Aula 5",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$5="Aula 5",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$5="Aula 5",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$5="Aula 5",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$5="Aula 5",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="G10" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$C$5="Aula 6",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$5="Aula 6",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$5="Aula 6",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$5="Aula 6",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$5="Aula 6",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$5="Aula 6",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$5="Aula 6",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$5="Aula 6",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$5="Aula 6",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$5="Aula 6",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$5="Aula 6",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$5="Aula 6",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$5="Aula 6",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$5="Aula 6",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$5="Aula 6",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$5="Aula 6",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$5="Aula 6",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="H10" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$C$5="Aula 7",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$5="Aula 7",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$5="Aula 7",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$5="Aula 7",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$5="Aula 7",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$5="Aula 7",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$5="Aula 7",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$5="Aula 7",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$5="Aula 7",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$5="Aula 7",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$5="Aula 7",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$5="Aula 7",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$5="Aula 7",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$5="Aula 7",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$5="Aula 7",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$5="Aula 7",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$5="Aula 7",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="I10" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$C$5="Aula 8",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$5="Aula 8",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$5="Aula 8",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$5="Aula 8",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$5="Aula 8",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$5="Aula 8",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$5="Aula 8",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$5="Aula 8",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$5="Aula 8",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$5="Aula 8",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$5="Aula 8",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$5="Aula 8",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$5="Aula 8",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$5="Aula 8",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$5="Aula 8",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$5="Aula 8",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$5="Aula 8",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="J10" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$C$5="Aula 9",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$5="Aula 9",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$5="Aula 9",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$5="Aula 9",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$5="Aula 9",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$5="Aula 9",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$5="Aula 9",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$5="Aula 9",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$5="Aula 9",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$5="Aula 9",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$5="Aula 9",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$5="Aula 9",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$5="Aula 9",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$5="Aula 9",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$5="Aula 9",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$5="Aula 9",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$5="Aula 9",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="K10" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$C$5="Lab",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$5="Lab",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$5="Lab",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$5="Lab",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$5="Lab",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$5="Lab",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$5="Lab",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$5="Lab",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$5="Lab",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$5="Lab",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$5="Lab",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$5="Lab",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$5="Lab",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$5="Lab",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$5="Lab",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$5="Lab",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$5="Lab",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>C112</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>C111</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>C113</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B11" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$C$7="Aula 1",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$7="Aula 1",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$7="Aula 1",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$7="Aula 1",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$7="Aula 1",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$7="Aula 1",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$7="Aula 1",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$7="Aula 1",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$7="Aula 1",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$7="Aula 1",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$7="Aula 1",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$7="Aula 1",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$7="Aula 1",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$7="Aula 1",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$7="Aula 1",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$7="Aula 1",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$7="Aula 1",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="C11" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$C$7="Aula 2",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$7="Aula 2",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$7="Aula 2",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$7="Aula 2",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$7="Aula 2",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$7="Aula 2",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$7="Aula 2",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$7="Aula 2",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$7="Aula 2",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$7="Aula 2",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$7="Aula 2",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$7="Aula 2",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$7="Aula 2",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$7="Aula 2",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$7="Aula 2",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$7="Aula 2",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$7="Aula 2",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="D11" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$C$7="Aula 3",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$7="Aula 3",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$7="Aula 3",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$7="Aula 3",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$7="Aula 3",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$7="Aula 3",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$7="Aula 3",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$7="Aula 3",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$7="Aula 3",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$7="Aula 3",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$7="Aula 3",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$7="Aula 3",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$7="Aula 3",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$7="Aula 3",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$7="Aula 3",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$7="Aula 3",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$7="Aula 3",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="E11" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$C$7="Aula 4",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$7="Aula 4",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$7="Aula 4",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$7="Aula 4",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$7="Aula 4",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$7="Aula 4",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$7="Aula 4",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$7="Aula 4",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$7="Aula 4",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$7="Aula 4",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$7="Aula 4",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$7="Aula 4",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$7="Aula 4",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$7="Aula 4",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$7="Aula 4",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$7="Aula 4",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$7="Aula 4",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="F11" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$C$7="Aula 5",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$7="Aula 5",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$7="Aula 5",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$7="Aula 5",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$7="Aula 5",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$7="Aula 5",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$7="Aula 5",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$7="Aula 5",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$7="Aula 5",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$7="Aula 5",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$7="Aula 5",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$7="Aula 5",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$7="Aula 5",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$7="Aula 5",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$7="Aula 5",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$7="Aula 5",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$7="Aula 5",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="G11" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$C$7="Aula 6",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$7="Aula 6",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$7="Aula 6",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$7="Aula 6",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$7="Aula 6",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$7="Aula 6",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$7="Aula 6",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$7="Aula 6",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$7="Aula 6",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$7="Aula 6",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$7="Aula 6",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$7="Aula 6",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$7="Aula 6",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$7="Aula 6",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$7="Aula 6",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$7="Aula 6",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$7="Aula 6",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="H11" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$C$7="Aula 7",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$7="Aula 7",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$7="Aula 7",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$7="Aula 7",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$7="Aula 7",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$7="Aula 7",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$7="Aula 7",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$7="Aula 7",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$7="Aula 7",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$7="Aula 7",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$7="Aula 7",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$7="Aula 7",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$7="Aula 7",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$7="Aula 7",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$7="Aula 7",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$7="Aula 7",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$7="Aula 7",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="I11" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$C$7="Aula 8",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$7="Aula 8",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$7="Aula 8",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$7="Aula 8",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$7="Aula 8",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$7="Aula 8",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$7="Aula 8",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$7="Aula 8",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$7="Aula 8",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$7="Aula 8",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$7="Aula 8",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$7="Aula 8",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$7="Aula 8",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$7="Aula 8",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$7="Aula 8",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$7="Aula 8",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$7="Aula 8",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="J11" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$C$7="Aula 9",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$7="Aula 9",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$7="Aula 9",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$7="Aula 9",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$7="Aula 9",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$7="Aula 9",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$7="Aula 9",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$7="Aula 9",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$7="Aula 9",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$7="Aula 9",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$7="Aula 9",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$7="Aula 9",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$7="Aula 9",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$7="Aula 9",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$7="Aula 9",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$7="Aula 9",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$7="Aula 9",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="K11" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$C$7="Lab",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$7="Lab",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$7="Lab",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$7="Lab",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$7="Lab",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$7="Lab",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$7="Lab",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$7="Lab",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$7="Lab",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$7="Lab",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$7="Lab",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$7="Lab",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$7="Lab",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$7="Lab",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$7="Lab",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$7="Lab",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$7="Lab",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>C111</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>C112,C113</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
     </row>
     <row r="12">
@@ -6483,43 +6382,43 @@
         </is>
       </c>
       <c r="B12" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$C$9="Aula 1",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$9="Aula 1",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$9="Aula 1",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$9="Aula 1",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$9="Aula 1",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$9="Aula 1",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$9="Aula 1",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$9="Aula 1",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$9="Aula 1",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$9="Aula 1",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$9="Aula 1",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$9="Aula 1",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$9="Aula 1",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$9="Aula 1",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$9="Aula 1",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$9="Aula 1",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$9="Aula 1",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$C$5="Aula 1",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$5="Aula 1",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$5="Aula 1",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$5="Aula 1",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$5="Aula 1",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$5="Aula 1",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$5="Aula 1",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$5="Aula 1",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$5="Aula 1",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$5="Aula 1",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$5="Aula 1",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$5="Aula 1",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$5="Aula 1",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$5="Aula 1",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$5="Aula 1",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$5="Aula 1",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$5="Aula 1",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="C12" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$C$9="Aula 2",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$9="Aula 2",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$9="Aula 2",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$9="Aula 2",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$9="Aula 2",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$9="Aula 2",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$9="Aula 2",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$9="Aula 2",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$9="Aula 2",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$9="Aula 2",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$9="Aula 2",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$9="Aula 2",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$9="Aula 2",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$9="Aula 2",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$9="Aula 2",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$9="Aula 2",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$9="Aula 2",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$C$5="Aula 2",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$5="Aula 2",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$5="Aula 2",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$5="Aula 2",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$5="Aula 2",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$5="Aula 2",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$5="Aula 2",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$5="Aula 2",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$5="Aula 2",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$5="Aula 2",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$5="Aula 2",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$5="Aula 2",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$5="Aula 2",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$5="Aula 2",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$5="Aula 2",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$5="Aula 2",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$5="Aula 2",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="D12" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$C$9="Aula 3",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$9="Aula 3",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$9="Aula 3",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$9="Aula 3",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$9="Aula 3",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$9="Aula 3",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$9="Aula 3",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$9="Aula 3",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$9="Aula 3",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$9="Aula 3",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$9="Aula 3",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$9="Aula 3",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$9="Aula 3",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$9="Aula 3",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$9="Aula 3",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$9="Aula 3",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$9="Aula 3",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$C$5="Aula 3",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$5="Aula 3",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$5="Aula 3",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$5="Aula 3",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$5="Aula 3",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$5="Aula 3",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$5="Aula 3",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$5="Aula 3",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$5="Aula 3",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$5="Aula 3",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$5="Aula 3",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$5="Aula 3",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$5="Aula 3",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$5="Aula 3",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$5="Aula 3",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$5="Aula 3",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$5="Aula 3",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="E12" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$C$9="Aula 4",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$9="Aula 4",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$9="Aula 4",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$9="Aula 4",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$9="Aula 4",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$9="Aula 4",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$9="Aula 4",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$9="Aula 4",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$9="Aula 4",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$9="Aula 4",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$9="Aula 4",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$9="Aula 4",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$9="Aula 4",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$9="Aula 4",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$9="Aula 4",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$9="Aula 4",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$9="Aula 4",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$C$5="Aula 4",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$5="Aula 4",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$5="Aula 4",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$5="Aula 4",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$5="Aula 4",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$5="Aula 4",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$5="Aula 4",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$5="Aula 4",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$5="Aula 4",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$5="Aula 4",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$5="Aula 4",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$5="Aula 4",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$5="Aula 4",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$5="Aula 4",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$5="Aula 4",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$5="Aula 4",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$5="Aula 4",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="F12" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$C$9="Aula 5",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$9="Aula 5",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$9="Aula 5",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$9="Aula 5",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$9="Aula 5",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$9="Aula 5",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$9="Aula 5",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$9="Aula 5",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$9="Aula 5",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$9="Aula 5",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$9="Aula 5",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$9="Aula 5",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$9="Aula 5",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$9="Aula 5",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$9="Aula 5",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$9="Aula 5",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$9="Aula 5",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$C$5="Aula 5",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$5="Aula 5",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$5="Aula 5",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$5="Aula 5",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$5="Aula 5",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$5="Aula 5",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$5="Aula 5",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$5="Aula 5",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$5="Aula 5",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$5="Aula 5",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$5="Aula 5",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$5="Aula 5",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$5="Aula 5",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$5="Aula 5",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$5="Aula 5",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$5="Aula 5",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$5="Aula 5",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="G12" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$C$9="Aula 6",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$9="Aula 6",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$9="Aula 6",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$9="Aula 6",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$9="Aula 6",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$9="Aula 6",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$9="Aula 6",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$9="Aula 6",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$9="Aula 6",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$9="Aula 6",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$9="Aula 6",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$9="Aula 6",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$9="Aula 6",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$9="Aula 6",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$9="Aula 6",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$9="Aula 6",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$9="Aula 6",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$C$5="Aula 6",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$5="Aula 6",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$5="Aula 6",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$5="Aula 6",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$5="Aula 6",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$5="Aula 6",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$5="Aula 6",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$5="Aula 6",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$5="Aula 6",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$5="Aula 6",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$5="Aula 6",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$5="Aula 6",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$5="Aula 6",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$5="Aula 6",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$5="Aula 6",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$5="Aula 6",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$5="Aula 6",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="H12" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$C$9="Aula 7",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$9="Aula 7",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$9="Aula 7",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$9="Aula 7",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$9="Aula 7",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$9="Aula 7",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$9="Aula 7",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$9="Aula 7",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$9="Aula 7",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$9="Aula 7",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$9="Aula 7",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$9="Aula 7",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$9="Aula 7",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$9="Aula 7",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$9="Aula 7",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$9="Aula 7",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$9="Aula 7",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$C$5="Aula 7",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$5="Aula 7",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$5="Aula 7",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$5="Aula 7",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$5="Aula 7",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$5="Aula 7",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$5="Aula 7",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$5="Aula 7",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$5="Aula 7",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$5="Aula 7",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$5="Aula 7",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$5="Aula 7",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$5="Aula 7",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$5="Aula 7",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$5="Aula 7",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$5="Aula 7",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$5="Aula 7",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="I12" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$C$9="Aula 8",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$9="Aula 8",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$9="Aula 8",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$9="Aula 8",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$9="Aula 8",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$9="Aula 8",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$9="Aula 8",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$9="Aula 8",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$9="Aula 8",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$9="Aula 8",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$9="Aula 8",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$9="Aula 8",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$9="Aula 8",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$9="Aula 8",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$9="Aula 8",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$9="Aula 8",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$9="Aula 8",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$C$5="Aula 8",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$5="Aula 8",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$5="Aula 8",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$5="Aula 8",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$5="Aula 8",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$5="Aula 8",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$5="Aula 8",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$5="Aula 8",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$5="Aula 8",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$5="Aula 8",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$5="Aula 8",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$5="Aula 8",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$5="Aula 8",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$5="Aula 8",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$5="Aula 8",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$5="Aula 8",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$5="Aula 8",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="J12" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$C$9="Aula 9",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$9="Aula 9",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$9="Aula 9",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$9="Aula 9",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$9="Aula 9",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$9="Aula 9",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$9="Aula 9",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$9="Aula 9",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$9="Aula 9",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$9="Aula 9",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$9="Aula 9",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$9="Aula 9",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$9="Aula 9",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$9="Aula 9",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$9="Aula 9",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$9="Aula 9",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$9="Aula 9",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$C$5="Aula 9",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$5="Aula 9",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$5="Aula 9",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$5="Aula 9",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$5="Aula 9",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$5="Aula 9",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$5="Aula 9",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$5="Aula 9",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$5="Aula 9",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$5="Aula 9",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$5="Aula 9",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$5="Aula 9",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$5="Aula 9",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$5="Aula 9",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$5="Aula 9",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$5="Aula 9",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$5="Aula 9",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="K12" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$C$9="Lab",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$9="Lab",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$9="Lab",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$9="Lab",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$9="Lab",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$9="Lab",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$9="Lab",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$9="Lab",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$9="Lab",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$9="Lab",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$9="Lab",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$9="Lab",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$9="Lab",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$9="Lab",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$9="Lab",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$9="Lab",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$9="Lab",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$C$5="Lab",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$5="Lab",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$5="Lab",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$5="Lab",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$5="Lab",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$5="Lab",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$5="Lab",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$5="Lab",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$5="Lab",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$5="Lab",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$5="Lab",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$5="Lab",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$5="Lab",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$5="Lab",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$5="Lab",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$5="Lab",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$5="Lab",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="L12" t="inlineStr"/>
@@ -6531,43 +6430,43 @@
         </is>
       </c>
       <c r="B13" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$C$11="Aula 1",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$11="Aula 1",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$11="Aula 1",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$11="Aula 1",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$11="Aula 1",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$11="Aula 1",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$11="Aula 1",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$11="Aula 1",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$11="Aula 1",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$11="Aula 1",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$11="Aula 1",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$11="Aula 1",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$11="Aula 1",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$11="Aula 1",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$11="Aula 1",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$11="Aula 1",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$11="Aula 1",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$C$7="Aula 1",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$7="Aula 1",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$7="Aula 1",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$7="Aula 1",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$7="Aula 1",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$7="Aula 1",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$7="Aula 1",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$7="Aula 1",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$7="Aula 1",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$7="Aula 1",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$7="Aula 1",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$7="Aula 1",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$7="Aula 1",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$7="Aula 1",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$7="Aula 1",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$7="Aula 1",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$7="Aula 1",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="C13" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$C$11="Aula 2",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$11="Aula 2",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$11="Aula 2",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$11="Aula 2",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$11="Aula 2",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$11="Aula 2",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$11="Aula 2",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$11="Aula 2",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$11="Aula 2",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$11="Aula 2",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$11="Aula 2",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$11="Aula 2",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$11="Aula 2",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$11="Aula 2",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$11="Aula 2",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$11="Aula 2",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$11="Aula 2",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$C$7="Aula 2",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$7="Aula 2",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$7="Aula 2",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$7="Aula 2",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$7="Aula 2",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$7="Aula 2",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$7="Aula 2",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$7="Aula 2",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$7="Aula 2",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$7="Aula 2",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$7="Aula 2",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$7="Aula 2",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$7="Aula 2",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$7="Aula 2",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$7="Aula 2",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$7="Aula 2",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$7="Aula 2",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="D13" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$C$11="Aula 3",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$11="Aula 3",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$11="Aula 3",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$11="Aula 3",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$11="Aula 3",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$11="Aula 3",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$11="Aula 3",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$11="Aula 3",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$11="Aula 3",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$11="Aula 3",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$11="Aula 3",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$11="Aula 3",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$11="Aula 3",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$11="Aula 3",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$11="Aula 3",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$11="Aula 3",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$11="Aula 3",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$C$7="Aula 3",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$7="Aula 3",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$7="Aula 3",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$7="Aula 3",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$7="Aula 3",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$7="Aula 3",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$7="Aula 3",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$7="Aula 3",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$7="Aula 3",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$7="Aula 3",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$7="Aula 3",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$7="Aula 3",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$7="Aula 3",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$7="Aula 3",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$7="Aula 3",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$7="Aula 3",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$7="Aula 3",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="E13" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$C$11="Aula 4",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$11="Aula 4",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$11="Aula 4",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$11="Aula 4",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$11="Aula 4",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$11="Aula 4",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$11="Aula 4",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$11="Aula 4",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$11="Aula 4",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$11="Aula 4",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$11="Aula 4",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$11="Aula 4",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$11="Aula 4",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$11="Aula 4",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$11="Aula 4",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$11="Aula 4",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$11="Aula 4",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$C$7="Aula 4",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$7="Aula 4",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$7="Aula 4",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$7="Aula 4",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$7="Aula 4",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$7="Aula 4",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$7="Aula 4",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$7="Aula 4",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$7="Aula 4",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$7="Aula 4",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$7="Aula 4",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$7="Aula 4",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$7="Aula 4",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$7="Aula 4",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$7="Aula 4",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$7="Aula 4",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$7="Aula 4",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="F13" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$C$11="Aula 5",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$11="Aula 5",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$11="Aula 5",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$11="Aula 5",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$11="Aula 5",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$11="Aula 5",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$11="Aula 5",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$11="Aula 5",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$11="Aula 5",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$11="Aula 5",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$11="Aula 5",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$11="Aula 5",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$11="Aula 5",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$11="Aula 5",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$11="Aula 5",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$11="Aula 5",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$11="Aula 5",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$C$7="Aula 5",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$7="Aula 5",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$7="Aula 5",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$7="Aula 5",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$7="Aula 5",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$7="Aula 5",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$7="Aula 5",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$7="Aula 5",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$7="Aula 5",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$7="Aula 5",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$7="Aula 5",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$7="Aula 5",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$7="Aula 5",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$7="Aula 5",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$7="Aula 5",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$7="Aula 5",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$7="Aula 5",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="G13" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$C$11="Aula 6",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$11="Aula 6",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$11="Aula 6",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$11="Aula 6",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$11="Aula 6",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$11="Aula 6",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$11="Aula 6",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$11="Aula 6",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$11="Aula 6",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$11="Aula 6",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$11="Aula 6",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$11="Aula 6",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$11="Aula 6",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$11="Aula 6",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$11="Aula 6",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$11="Aula 6",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$11="Aula 6",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$C$7="Aula 6",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$7="Aula 6",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$7="Aula 6",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$7="Aula 6",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$7="Aula 6",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$7="Aula 6",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$7="Aula 6",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$7="Aula 6",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$7="Aula 6",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$7="Aula 6",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$7="Aula 6",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$7="Aula 6",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$7="Aula 6",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$7="Aula 6",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$7="Aula 6",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$7="Aula 6",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$7="Aula 6",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="H13" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$C$11="Aula 7",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$11="Aula 7",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$11="Aula 7",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$11="Aula 7",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$11="Aula 7",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$11="Aula 7",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$11="Aula 7",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$11="Aula 7",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$11="Aula 7",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$11="Aula 7",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$11="Aula 7",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$11="Aula 7",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$11="Aula 7",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$11="Aula 7",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$11="Aula 7",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$11="Aula 7",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$11="Aula 7",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$C$7="Aula 7",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$7="Aula 7",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$7="Aula 7",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$7="Aula 7",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$7="Aula 7",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$7="Aula 7",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$7="Aula 7",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$7="Aula 7",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$7="Aula 7",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$7="Aula 7",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$7="Aula 7",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$7="Aula 7",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$7="Aula 7",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$7="Aula 7",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$7="Aula 7",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$7="Aula 7",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$7="Aula 7",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="I13" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$C$11="Aula 8",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$11="Aula 8",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$11="Aula 8",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$11="Aula 8",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$11="Aula 8",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$11="Aula 8",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$11="Aula 8",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$11="Aula 8",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$11="Aula 8",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$11="Aula 8",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$11="Aula 8",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$11="Aula 8",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$11="Aula 8",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$11="Aula 8",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$11="Aula 8",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$11="Aula 8",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$11="Aula 8",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$C$7="Aula 8",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$7="Aula 8",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$7="Aula 8",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$7="Aula 8",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$7="Aula 8",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$7="Aula 8",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$7="Aula 8",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$7="Aula 8",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$7="Aula 8",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$7="Aula 8",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$7="Aula 8",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$7="Aula 8",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$7="Aula 8",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$7="Aula 8",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$7="Aula 8",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$7="Aula 8",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$7="Aula 8",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="J13" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$C$11="Aula 9",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$11="Aula 9",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$11="Aula 9",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$11="Aula 9",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$11="Aula 9",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$11="Aula 9",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$11="Aula 9",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$11="Aula 9",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$11="Aula 9",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$11="Aula 9",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$11="Aula 9",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$11="Aula 9",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$11="Aula 9",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$11="Aula 9",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$11="Aula 9",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$11="Aula 9",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$11="Aula 9",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$C$7="Aula 9",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$7="Aula 9",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$7="Aula 9",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$7="Aula 9",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$7="Aula 9",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$7="Aula 9",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$7="Aula 9",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$7="Aula 9",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$7="Aula 9",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$7="Aula 9",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$7="Aula 9",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$7="Aula 9",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$7="Aula 9",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$7="Aula 9",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$7="Aula 9",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$7="Aula 9",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$7="Aula 9",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="K13" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$C$11="Lab",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$11="Lab",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$11="Lab",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$11="Lab",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$11="Lab",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$11="Lab",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$11="Lab",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$11="Lab",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$11="Lab",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$11="Lab",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$11="Lab",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$11="Lab",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$11="Lab",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$11="Lab",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$11="Lab",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$11="Lab",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$11="Lab",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$C$7="Lab",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$7="Lab",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$7="Lab",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$7="Lab",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$7="Lab",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$7="Lab",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$7="Lab",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$7="Lab",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$7="Lab",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$7="Lab",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$7="Lab",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$7="Lab",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$7="Lab",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$7="Lab",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$7="Lab",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$7="Lab",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$7="Lab",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="L13" t="inlineStr"/>
@@ -6579,43 +6478,43 @@
         </is>
       </c>
       <c r="B14" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$C$13="Aula 1",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$13="Aula 1",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$13="Aula 1",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$13="Aula 1",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$13="Aula 1",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$13="Aula 1",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$13="Aula 1",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$13="Aula 1",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$13="Aula 1",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$13="Aula 1",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$13="Aula 1",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$13="Aula 1",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$13="Aula 1",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$13="Aula 1",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$13="Aula 1",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$13="Aula 1",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$13="Aula 1",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$C$9="Aula 1",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$9="Aula 1",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$9="Aula 1",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$9="Aula 1",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$9="Aula 1",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$9="Aula 1",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$9="Aula 1",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$9="Aula 1",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$9="Aula 1",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$9="Aula 1",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$9="Aula 1",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$9="Aula 1",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$9="Aula 1",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$9="Aula 1",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$9="Aula 1",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$9="Aula 1",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$9="Aula 1",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="C14" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$C$13="Aula 2",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$13="Aula 2",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$13="Aula 2",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$13="Aula 2",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$13="Aula 2",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$13="Aula 2",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$13="Aula 2",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$13="Aula 2",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$13="Aula 2",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$13="Aula 2",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$13="Aula 2",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$13="Aula 2",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$13="Aula 2",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$13="Aula 2",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$13="Aula 2",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$13="Aula 2",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$13="Aula 2",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$C$9="Aula 2",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$9="Aula 2",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$9="Aula 2",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$9="Aula 2",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$9="Aula 2",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$9="Aula 2",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$9="Aula 2",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$9="Aula 2",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$9="Aula 2",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$9="Aula 2",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$9="Aula 2",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$9="Aula 2",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$9="Aula 2",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$9="Aula 2",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$9="Aula 2",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$9="Aula 2",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$9="Aula 2",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="D14" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$C$13="Aula 3",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$13="Aula 3",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$13="Aula 3",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$13="Aula 3",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$13="Aula 3",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$13="Aula 3",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$13="Aula 3",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$13="Aula 3",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$13="Aula 3",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$13="Aula 3",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$13="Aula 3",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$13="Aula 3",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$13="Aula 3",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$13="Aula 3",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$13="Aula 3",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$13="Aula 3",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$13="Aula 3",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$C$9="Aula 3",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$9="Aula 3",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$9="Aula 3",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$9="Aula 3",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$9="Aula 3",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$9="Aula 3",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$9="Aula 3",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$9="Aula 3",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$9="Aula 3",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$9="Aula 3",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$9="Aula 3",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$9="Aula 3",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$9="Aula 3",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$9="Aula 3",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$9="Aula 3",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$9="Aula 3",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$9="Aula 3",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="E14" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$C$13="Aula 4",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$13="Aula 4",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$13="Aula 4",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$13="Aula 4",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$13="Aula 4",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$13="Aula 4",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$13="Aula 4",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$13="Aula 4",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$13="Aula 4",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$13="Aula 4",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$13="Aula 4",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$13="Aula 4",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$13="Aula 4",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$13="Aula 4",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$13="Aula 4",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$13="Aula 4",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$13="Aula 4",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$C$9="Aula 4",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$9="Aula 4",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$9="Aula 4",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$9="Aula 4",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$9="Aula 4",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$9="Aula 4",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$9="Aula 4",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$9="Aula 4",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$9="Aula 4",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$9="Aula 4",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$9="Aula 4",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$9="Aula 4",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$9="Aula 4",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$9="Aula 4",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$9="Aula 4",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$9="Aula 4",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$9="Aula 4",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="F14" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$C$13="Aula 5",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$13="Aula 5",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$13="Aula 5",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$13="Aula 5",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$13="Aula 5",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$13="Aula 5",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$13="Aula 5",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$13="Aula 5",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$13="Aula 5",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$13="Aula 5",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$13="Aula 5",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$13="Aula 5",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$13="Aula 5",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$13="Aula 5",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$13="Aula 5",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$13="Aula 5",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$13="Aula 5",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$C$9="Aula 5",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$9="Aula 5",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$9="Aula 5",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$9="Aula 5",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$9="Aula 5",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$9="Aula 5",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$9="Aula 5",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$9="Aula 5",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$9="Aula 5",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$9="Aula 5",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$9="Aula 5",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$9="Aula 5",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$9="Aula 5",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$9="Aula 5",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$9="Aula 5",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$9="Aula 5",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$9="Aula 5",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="G14" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$C$13="Aula 6",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$13="Aula 6",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$13="Aula 6",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$13="Aula 6",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$13="Aula 6",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$13="Aula 6",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$13="Aula 6",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$13="Aula 6",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$13="Aula 6",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$13="Aula 6",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$13="Aula 6",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$13="Aula 6",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$13="Aula 6",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$13="Aula 6",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$13="Aula 6",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$13="Aula 6",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$13="Aula 6",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$C$9="Aula 6",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$9="Aula 6",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$9="Aula 6",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$9="Aula 6",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$9="Aula 6",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$9="Aula 6",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$9="Aula 6",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$9="Aula 6",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$9="Aula 6",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$9="Aula 6",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$9="Aula 6",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$9="Aula 6",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$9="Aula 6",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$9="Aula 6",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$9="Aula 6",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$9="Aula 6",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$9="Aula 6",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="H14" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$C$13="Aula 7",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$13="Aula 7",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$13="Aula 7",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$13="Aula 7",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$13="Aula 7",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$13="Aula 7",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$13="Aula 7",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$13="Aula 7",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$13="Aula 7",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$13="Aula 7",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$13="Aula 7",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$13="Aula 7",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$13="Aula 7",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$13="Aula 7",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$13="Aula 7",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$13="Aula 7",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$13="Aula 7",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$C$9="Aula 7",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$9="Aula 7",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$9="Aula 7",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$9="Aula 7",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$9="Aula 7",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$9="Aula 7",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$9="Aula 7",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$9="Aula 7",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$9="Aula 7",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$9="Aula 7",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$9="Aula 7",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$9="Aula 7",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$9="Aula 7",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$9="Aula 7",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$9="Aula 7",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$9="Aula 7",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$9="Aula 7",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="I14" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$C$13="Aula 8",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$13="Aula 8",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$13="Aula 8",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$13="Aula 8",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$13="Aula 8",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$13="Aula 8",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$13="Aula 8",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$13="Aula 8",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$13="Aula 8",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$13="Aula 8",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$13="Aula 8",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$13="Aula 8",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$13="Aula 8",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$13="Aula 8",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$13="Aula 8",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$13="Aula 8",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$13="Aula 8",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$C$9="Aula 8",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$9="Aula 8",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$9="Aula 8",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$9="Aula 8",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$9="Aula 8",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$9="Aula 8",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$9="Aula 8",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$9="Aula 8",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$9="Aula 8",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$9="Aula 8",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$9="Aula 8",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$9="Aula 8",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$9="Aula 8",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$9="Aula 8",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$9="Aula 8",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$9="Aula 8",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$9="Aula 8",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="J14" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$C$13="Aula 9",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$13="Aula 9",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$13="Aula 9",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$13="Aula 9",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$13="Aula 9",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$13="Aula 9",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$13="Aula 9",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$13="Aula 9",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$13="Aula 9",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$13="Aula 9",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$13="Aula 9",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$13="Aula 9",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$13="Aula 9",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$13="Aula 9",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$13="Aula 9",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$13="Aula 9",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$13="Aula 9",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$C$9="Aula 9",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$9="Aula 9",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$9="Aula 9",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$9="Aula 9",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$9="Aula 9",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$9="Aula 9",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$9="Aula 9",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$9="Aula 9",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$9="Aula 9",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$9="Aula 9",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$9="Aula 9",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$9="Aula 9",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$9="Aula 9",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$9="Aula 9",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$9="Aula 9",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$9="Aula 9",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$9="Aula 9",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="K14" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$C$13="Lab",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$13="Lab",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$13="Lab",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$13="Lab",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$13="Lab",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$13="Lab",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$13="Lab",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$13="Lab",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$13="Lab",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$13="Lab",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$13="Lab",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$13="Lab",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$13="Lab",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$13="Lab",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$13="Lab",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$13="Lab",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$13="Lab",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$C$9="Lab",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$9="Lab",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$9="Lab",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$9="Lab",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$9="Lab",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$9="Lab",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$9="Lab",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$9="Lab",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$9="Lab",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$9="Lab",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$9="Lab",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$9="Lab",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$9="Lab",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$9="Lab",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$9="Lab",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$9="Lab",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$9="Lab",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="L14" t="inlineStr"/>
@@ -6627,43 +6526,43 @@
         </is>
       </c>
       <c r="B15" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$C$15="Aula 1",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$15="Aula 1",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$15="Aula 1",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$15="Aula 1",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$15="Aula 1",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$15="Aula 1",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$15="Aula 1",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$15="Aula 1",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$15="Aula 1",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$15="Aula 1",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$15="Aula 1",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$15="Aula 1",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$15="Aula 1",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$15="Aula 1",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$15="Aula 1",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$15="Aula 1",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$15="Aula 1",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$C$11="Aula 1",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$11="Aula 1",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$11="Aula 1",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$11="Aula 1",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$11="Aula 1",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$11="Aula 1",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$11="Aula 1",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$11="Aula 1",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$11="Aula 1",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$11="Aula 1",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$11="Aula 1",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$11="Aula 1",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$11="Aula 1",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$11="Aula 1",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$11="Aula 1",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$11="Aula 1",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$11="Aula 1",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="C15" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$C$15="Aula 2",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$15="Aula 2",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$15="Aula 2",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$15="Aula 2",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$15="Aula 2",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$15="Aula 2",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$15="Aula 2",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$15="Aula 2",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$15="Aula 2",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$15="Aula 2",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$15="Aula 2",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$15="Aula 2",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$15="Aula 2",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$15="Aula 2",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$15="Aula 2",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$15="Aula 2",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$15="Aula 2",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$C$11="Aula 2",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$11="Aula 2",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$11="Aula 2",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$11="Aula 2",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$11="Aula 2",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$11="Aula 2",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$11="Aula 2",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$11="Aula 2",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$11="Aula 2",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$11="Aula 2",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$11="Aula 2",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$11="Aula 2",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$11="Aula 2",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$11="Aula 2",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$11="Aula 2",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$11="Aula 2",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$11="Aula 2",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="D15" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$C$15="Aula 3",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$15="Aula 3",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$15="Aula 3",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$15="Aula 3",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$15="Aula 3",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$15="Aula 3",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$15="Aula 3",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$15="Aula 3",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$15="Aula 3",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$15="Aula 3",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$15="Aula 3",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$15="Aula 3",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$15="Aula 3",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$15="Aula 3",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$15="Aula 3",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$15="Aula 3",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$15="Aula 3",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$C$11="Aula 3",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$11="Aula 3",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$11="Aula 3",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$11="Aula 3",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$11="Aula 3",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$11="Aula 3",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$11="Aula 3",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$11="Aula 3",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$11="Aula 3",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$11="Aula 3",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$11="Aula 3",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$11="Aula 3",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$11="Aula 3",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$11="Aula 3",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$11="Aula 3",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$11="Aula 3",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$11="Aula 3",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="E15" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$C$15="Aula 4",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$15="Aula 4",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$15="Aula 4",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$15="Aula 4",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$15="Aula 4",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$15="Aula 4",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$15="Aula 4",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$15="Aula 4",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$15="Aula 4",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$15="Aula 4",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$15="Aula 4",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$15="Aula 4",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$15="Aula 4",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$15="Aula 4",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$15="Aula 4",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$15="Aula 4",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$15="Aula 4",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$C$11="Aula 4",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$11="Aula 4",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$11="Aula 4",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$11="Aula 4",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$11="Aula 4",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$11="Aula 4",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$11="Aula 4",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$11="Aula 4",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$11="Aula 4",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$11="Aula 4",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$11="Aula 4",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$11="Aula 4",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$11="Aula 4",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$11="Aula 4",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$11="Aula 4",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$11="Aula 4",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$11="Aula 4",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="F15" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$C$15="Aula 5",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$15="Aula 5",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$15="Aula 5",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$15="Aula 5",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$15="Aula 5",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$15="Aula 5",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$15="Aula 5",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$15="Aula 5",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$15="Aula 5",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$15="Aula 5",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$15="Aula 5",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$15="Aula 5",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$15="Aula 5",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$15="Aula 5",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$15="Aula 5",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$15="Aula 5",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$15="Aula 5",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$C$11="Aula 5",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$11="Aula 5",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$11="Aula 5",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$11="Aula 5",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$11="Aula 5",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$11="Aula 5",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$11="Aula 5",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$11="Aula 5",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$11="Aula 5",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$11="Aula 5",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$11="Aula 5",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$11="Aula 5",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$11="Aula 5",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$11="Aula 5",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$11="Aula 5",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$11="Aula 5",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$11="Aula 5",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="G15" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$C$15="Aula 6",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$15="Aula 6",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$15="Aula 6",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$15="Aula 6",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$15="Aula 6",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$15="Aula 6",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$15="Aula 6",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$15="Aula 6",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$15="Aula 6",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$15="Aula 6",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$15="Aula 6",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$15="Aula 6",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$15="Aula 6",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$15="Aula 6",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$15="Aula 6",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$15="Aula 6",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$15="Aula 6",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$C$11="Aula 6",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$11="Aula 6",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$11="Aula 6",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$11="Aula 6",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$11="Aula 6",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$11="Aula 6",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$11="Aula 6",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$11="Aula 6",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$11="Aula 6",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$11="Aula 6",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$11="Aula 6",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$11="Aula 6",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$11="Aula 6",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$11="Aula 6",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$11="Aula 6",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$11="Aula 6",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$11="Aula 6",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="H15" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$C$15="Aula 7",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$15="Aula 7",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$15="Aula 7",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$15="Aula 7",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$15="Aula 7",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$15="Aula 7",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$15="Aula 7",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$15="Aula 7",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$15="Aula 7",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$15="Aula 7",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$15="Aula 7",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$15="Aula 7",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$15="Aula 7",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$15="Aula 7",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$15="Aula 7",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$15="Aula 7",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$15="Aula 7",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$C$11="Aula 7",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$11="Aula 7",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$11="Aula 7",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$11="Aula 7",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$11="Aula 7",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$11="Aula 7",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$11="Aula 7",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$11="Aula 7",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$11="Aula 7",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$11="Aula 7",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$11="Aula 7",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$11="Aula 7",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$11="Aula 7",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$11="Aula 7",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$11="Aula 7",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$11="Aula 7",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$11="Aula 7",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="I15" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$C$15="Aula 8",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$15="Aula 8",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$15="Aula 8",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$15="Aula 8",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$15="Aula 8",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$15="Aula 8",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$15="Aula 8",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$15="Aula 8",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$15="Aula 8",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$15="Aula 8",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$15="Aula 8",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$15="Aula 8",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$15="Aula 8",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$15="Aula 8",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$15="Aula 8",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$15="Aula 8",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$15="Aula 8",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$C$11="Aula 8",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$11="Aula 8",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$11="Aula 8",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$11="Aula 8",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$11="Aula 8",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$11="Aula 8",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$11="Aula 8",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$11="Aula 8",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$11="Aula 8",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$11="Aula 8",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$11="Aula 8",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$11="Aula 8",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$11="Aula 8",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$11="Aula 8",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$11="Aula 8",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$11="Aula 8",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$11="Aula 8",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="J15" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$C$15="Aula 9",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$15="Aula 9",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$15="Aula 9",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$15="Aula 9",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$15="Aula 9",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$15="Aula 9",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$15="Aula 9",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$15="Aula 9",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$15="Aula 9",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$15="Aula 9",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$15="Aula 9",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$15="Aula 9",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$15="Aula 9",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$15="Aula 9",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$15="Aula 9",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$15="Aula 9",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$15="Aula 9",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$C$11="Aula 9",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$11="Aula 9",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$11="Aula 9",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$11="Aula 9",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$11="Aula 9",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$11="Aula 9",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$11="Aula 9",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$11="Aula 9",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$11="Aula 9",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$11="Aula 9",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$11="Aula 9",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$11="Aula 9",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$11="Aula 9",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$11="Aula 9",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$11="Aula 9",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$11="Aula 9",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$11="Aula 9",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="K15" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$C$15="Lab",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$15="Lab",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$15="Lab",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$15="Lab",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$15="Lab",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$15="Lab",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$15="Lab",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$15="Lab",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$15="Lab",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$15="Lab",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$15="Lab",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$15="Lab",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$15="Lab",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$15="Lab",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$15="Lab",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$15="Lab",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$15="Lab",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$C$11="Lab",(D111!$A$1&amp;" "),"")&amp;IF(D211!$C$11="Lab",(D211!$A$1&amp;" "),"")&amp;IF(D311!$C$11="Lab",(D311!$A$1&amp;" "),"")&amp;IF(D411!$C$11="Lab",(D411!$A$1&amp;" "),"")&amp;IF(C111!$C$11="Lab",(C111!$A$1&amp;" "),"")&amp;IF(C121!$C$11="Lab",(C121!$A$1&amp;" "),"")&amp;IF(C122!$C$11="Lab",(C122!$A$1&amp;" "),"")&amp;IF(C211!$C$11="Lab",(C211!$A$1&amp;" "),"")&amp;IF(C212!$C$11="Lab",(C212!$A$1&amp;" "),"")&amp;IF(C311!$C$11="Lab",(C311!$A$1&amp;" "),"")&amp;IF(C312!$C$11="Lab",(C312!$A$1&amp;" "),"")&amp;IF(C411!$C$11="Lab",(C411!$A$1&amp;" "),"")&amp;IF(C412!$C$11="Lab",(C412!$A$1&amp;" "),"")&amp;IF(M111!$C$11="Lab",(M111!$A$1&amp;" "),"")&amp;IF(M211!$C$11="Lab",(M211!$A$1&amp;" "),"")&amp;IF(M311!$C$11="Lab",(M311!$A$1&amp;" "),"")&amp;IF(M411!$C$11="Lab",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="L15" t="inlineStr"/>
@@ -6741,99 +6640,51 @@
       <c r="L17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B18" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$D$5="Aula 1",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$5="Aula 1",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$5="Aula 1",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$5="Aula 1",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$5="Aula 1",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$5="Aula 1",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$5="Aula 1",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$5="Aula 1",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$5="Aula 1",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$5="Aula 1",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$5="Aula 1",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$5="Aula 1",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$5="Aula 1",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$5="Aula 1",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$5="Aula 1",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$5="Aula 1",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$5="Aula 1",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="C18" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$D$5="Aula 2",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$5="Aula 2",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$5="Aula 2",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$5="Aula 2",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$5="Aula 2",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$5="Aula 2",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$5="Aula 2",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$5="Aula 2",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$5="Aula 2",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$5="Aula 2",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$5="Aula 2",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$5="Aula 2",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$5="Aula 2",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$5="Aula 2",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$5="Aula 2",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$5="Aula 2",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$5="Aula 2",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="D18" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$D$5="Aula 3",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$5="Aula 3",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$5="Aula 3",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$5="Aula 3",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$5="Aula 3",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$5="Aula 3",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$5="Aula 3",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$5="Aula 3",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$5="Aula 3",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$5="Aula 3",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$5="Aula 3",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$5="Aula 3",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$5="Aula 3",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$5="Aula 3",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$5="Aula 3",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$5="Aula 3",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$5="Aula 3",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="E18" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$D$5="Aula 4",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$5="Aula 4",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$5="Aula 4",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$5="Aula 4",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$5="Aula 4",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$5="Aula 4",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$5="Aula 4",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$5="Aula 4",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$5="Aula 4",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$5="Aula 4",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$5="Aula 4",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$5="Aula 4",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$5="Aula 4",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$5="Aula 4",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$5="Aula 4",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$5="Aula 4",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$5="Aula 4",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="F18" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$D$5="Aula 5",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$5="Aula 5",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$5="Aula 5",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$5="Aula 5",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$5="Aula 5",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$5="Aula 5",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$5="Aula 5",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$5="Aula 5",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$5="Aula 5",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$5="Aula 5",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$5="Aula 5",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$5="Aula 5",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$5="Aula 5",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$5="Aula 5",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$5="Aula 5",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$5="Aula 5",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$5="Aula 5",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="G18" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$D$5="Aula 6",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$5="Aula 6",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$5="Aula 6",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$5="Aula 6",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$5="Aula 6",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$5="Aula 6",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$5="Aula 6",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$5="Aula 6",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$5="Aula 6",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$5="Aula 6",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$5="Aula 6",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$5="Aula 6",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$5="Aula 6",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$5="Aula 6",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$5="Aula 6",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$5="Aula 6",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$5="Aula 6",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="H18" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$D$5="Aula 7",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$5="Aula 7",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$5="Aula 7",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$5="Aula 7",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$5="Aula 7",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$5="Aula 7",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$5="Aula 7",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$5="Aula 7",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$5="Aula 7",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$5="Aula 7",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$5="Aula 7",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$5="Aula 7",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$5="Aula 7",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$5="Aula 7",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$5="Aula 7",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$5="Aula 7",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$5="Aula 7",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="I18" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$D$5="Aula 8",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$5="Aula 8",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$5="Aula 8",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$5="Aula 8",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$5="Aula 8",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$5="Aula 8",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$5="Aula 8",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$5="Aula 8",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$5="Aula 8",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$5="Aula 8",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$5="Aula 8",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$5="Aula 8",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$5="Aula 8",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$5="Aula 8",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$5="Aula 8",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$5="Aula 8",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$5="Aula 8",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="J18" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$D$5="Aula 9",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$5="Aula 9",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$5="Aula 9",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$5="Aula 9",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$5="Aula 9",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$5="Aula 9",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$5="Aula 9",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$5="Aula 9",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$5="Aula 9",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$5="Aula 9",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$5="Aula 9",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$5="Aula 9",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$5="Aula 9",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$5="Aula 9",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$5="Aula 9",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$5="Aula 9",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$5="Aula 9",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="K18" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$D$5="Lab",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$5="Lab",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$5="Lab",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$5="Lab",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$5="Lab",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$5="Lab",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$5="Lab",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$5="Lab",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$5="Lab",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$5="Lab",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$5="Lab",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$5="Lab",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$5="Lab",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$5="Lab",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$5="Lab",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$5="Lab",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$5="Lab",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>C112</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>C111</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>C113</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B19" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$D$7="Aula 1",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$7="Aula 1",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$7="Aula 1",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$7="Aula 1",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$7="Aula 1",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$7="Aula 1",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$7="Aula 1",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$7="Aula 1",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$7="Aula 1",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$7="Aula 1",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$7="Aula 1",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$7="Aula 1",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$7="Aula 1",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$7="Aula 1",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$7="Aula 1",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$7="Aula 1",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$7="Aula 1",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="C19" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$D$7="Aula 2",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$7="Aula 2",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$7="Aula 2",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$7="Aula 2",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$7="Aula 2",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$7="Aula 2",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$7="Aula 2",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$7="Aula 2",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$7="Aula 2",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$7="Aula 2",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$7="Aula 2",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$7="Aula 2",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$7="Aula 2",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$7="Aula 2",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$7="Aula 2",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$7="Aula 2",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$7="Aula 2",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="D19" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$D$7="Aula 3",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$7="Aula 3",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$7="Aula 3",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$7="Aula 3",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$7="Aula 3",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$7="Aula 3",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$7="Aula 3",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$7="Aula 3",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$7="Aula 3",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$7="Aula 3",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$7="Aula 3",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$7="Aula 3",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$7="Aula 3",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$7="Aula 3",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$7="Aula 3",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$7="Aula 3",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$7="Aula 3",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="E19" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$D$7="Aula 4",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$7="Aula 4",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$7="Aula 4",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$7="Aula 4",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$7="Aula 4",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$7="Aula 4",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$7="Aula 4",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$7="Aula 4",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$7="Aula 4",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$7="Aula 4",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$7="Aula 4",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$7="Aula 4",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$7="Aula 4",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$7="Aula 4",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$7="Aula 4",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$7="Aula 4",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$7="Aula 4",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="F19" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$D$7="Aula 5",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$7="Aula 5",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$7="Aula 5",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$7="Aula 5",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$7="Aula 5",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$7="Aula 5",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$7="Aula 5",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$7="Aula 5",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$7="Aula 5",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$7="Aula 5",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$7="Aula 5",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$7="Aula 5",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$7="Aula 5",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$7="Aula 5",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$7="Aula 5",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$7="Aula 5",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$7="Aula 5",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="G19" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$D$7="Aula 6",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$7="Aula 6",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$7="Aula 6",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$7="Aula 6",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$7="Aula 6",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$7="Aula 6",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$7="Aula 6",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$7="Aula 6",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$7="Aula 6",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$7="Aula 6",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$7="Aula 6",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$7="Aula 6",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$7="Aula 6",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$7="Aula 6",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$7="Aula 6",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$7="Aula 6",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$7="Aula 6",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="H19" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$D$7="Aula 7",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$7="Aula 7",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$7="Aula 7",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$7="Aula 7",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$7="Aula 7",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$7="Aula 7",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$7="Aula 7",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$7="Aula 7",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$7="Aula 7",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$7="Aula 7",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$7="Aula 7",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$7="Aula 7",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$7="Aula 7",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$7="Aula 7",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$7="Aula 7",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$7="Aula 7",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$7="Aula 7",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="I19" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$D$7="Aula 8",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$7="Aula 8",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$7="Aula 8",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$7="Aula 8",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$7="Aula 8",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$7="Aula 8",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$7="Aula 8",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$7="Aula 8",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$7="Aula 8",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$7="Aula 8",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$7="Aula 8",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$7="Aula 8",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$7="Aula 8",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$7="Aula 8",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$7="Aula 8",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$7="Aula 8",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$7="Aula 8",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="J19" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$D$7="Aula 9",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$7="Aula 9",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$7="Aula 9",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$7="Aula 9",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$7="Aula 9",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$7="Aula 9",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$7="Aula 9",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$7="Aula 9",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$7="Aula 9",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$7="Aula 9",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$7="Aula 9",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$7="Aula 9",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$7="Aula 9",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$7="Aula 9",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$7="Aula 9",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$7="Aula 9",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$7="Aula 9",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="K19" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$D$7="Lab",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$7="Lab",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$7="Lab",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$7="Lab",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$7="Lab",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$7="Lab",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$7="Lab",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$7="Lab",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$7="Lab",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$7="Lab",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$7="Lab",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$7="Lab",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$7="Lab",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$7="Lab",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$7="Lab",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$7="Lab",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$7="Lab",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
     </row>
     <row r="20">
@@ -6843,43 +6694,43 @@
         </is>
       </c>
       <c r="B20" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$D$9="Aula 1",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$9="Aula 1",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$9="Aula 1",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$9="Aula 1",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$9="Aula 1",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$9="Aula 1",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$9="Aula 1",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$9="Aula 1",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$9="Aula 1",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$9="Aula 1",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$9="Aula 1",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$9="Aula 1",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$9="Aula 1",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$9="Aula 1",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$9="Aula 1",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$9="Aula 1",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$9="Aula 1",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$D$5="Aula 1",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$5="Aula 1",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$5="Aula 1",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$5="Aula 1",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$5="Aula 1",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$5="Aula 1",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$5="Aula 1",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$5="Aula 1",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$5="Aula 1",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$5="Aula 1",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$5="Aula 1",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$5="Aula 1",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$5="Aula 1",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$5="Aula 1",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$5="Aula 1",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$5="Aula 1",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$5="Aula 1",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="C20" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$D$9="Aula 2",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$9="Aula 2",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$9="Aula 2",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$9="Aula 2",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$9="Aula 2",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$9="Aula 2",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$9="Aula 2",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$9="Aula 2",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$9="Aula 2",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$9="Aula 2",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$9="Aula 2",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$9="Aula 2",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$9="Aula 2",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$9="Aula 2",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$9="Aula 2",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$9="Aula 2",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$9="Aula 2",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$D$5="Aula 2",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$5="Aula 2",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$5="Aula 2",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$5="Aula 2",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$5="Aula 2",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$5="Aula 2",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$5="Aula 2",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$5="Aula 2",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$5="Aula 2",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$5="Aula 2",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$5="Aula 2",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$5="Aula 2",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$5="Aula 2",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$5="Aula 2",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$5="Aula 2",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$5="Aula 2",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$5="Aula 2",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="D20" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$D$9="Aula 3",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$9="Aula 3",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$9="Aula 3",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$9="Aula 3",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$9="Aula 3",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$9="Aula 3",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$9="Aula 3",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$9="Aula 3",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$9="Aula 3",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$9="Aula 3",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$9="Aula 3",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$9="Aula 3",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$9="Aula 3",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$9="Aula 3",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$9="Aula 3",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$9="Aula 3",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$9="Aula 3",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$D$5="Aula 3",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$5="Aula 3",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$5="Aula 3",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$5="Aula 3",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$5="Aula 3",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$5="Aula 3",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$5="Aula 3",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$5="Aula 3",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$5="Aula 3",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$5="Aula 3",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$5="Aula 3",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$5="Aula 3",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$5="Aula 3",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$5="Aula 3",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$5="Aula 3",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$5="Aula 3",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$5="Aula 3",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="E20" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$D$9="Aula 4",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$9="Aula 4",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$9="Aula 4",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$9="Aula 4",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$9="Aula 4",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$9="Aula 4",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$9="Aula 4",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$9="Aula 4",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$9="Aula 4",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$9="Aula 4",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$9="Aula 4",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$9="Aula 4",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$9="Aula 4",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$9="Aula 4",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$9="Aula 4",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$9="Aula 4",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$9="Aula 4",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$D$5="Aula 4",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$5="Aula 4",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$5="Aula 4",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$5="Aula 4",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$5="Aula 4",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$5="Aula 4",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$5="Aula 4",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$5="Aula 4",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$5="Aula 4",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$5="Aula 4",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$5="Aula 4",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$5="Aula 4",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$5="Aula 4",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$5="Aula 4",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$5="Aula 4",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$5="Aula 4",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$5="Aula 4",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="F20" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$D$9="Aula 5",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$9="Aula 5",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$9="Aula 5",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$9="Aula 5",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$9="Aula 5",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$9="Aula 5",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$9="Aula 5",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$9="Aula 5",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$9="Aula 5",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$9="Aula 5",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$9="Aula 5",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$9="Aula 5",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$9="Aula 5",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$9="Aula 5",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$9="Aula 5",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$9="Aula 5",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$9="Aula 5",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$D$5="Aula 5",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$5="Aula 5",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$5="Aula 5",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$5="Aula 5",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$5="Aula 5",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$5="Aula 5",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$5="Aula 5",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$5="Aula 5",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$5="Aula 5",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$5="Aula 5",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$5="Aula 5",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$5="Aula 5",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$5="Aula 5",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$5="Aula 5",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$5="Aula 5",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$5="Aula 5",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$5="Aula 5",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="G20" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$D$9="Aula 6",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$9="Aula 6",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$9="Aula 6",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$9="Aula 6",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$9="Aula 6",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$9="Aula 6",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$9="Aula 6",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$9="Aula 6",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$9="Aula 6",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$9="Aula 6",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$9="Aula 6",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$9="Aula 6",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$9="Aula 6",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$9="Aula 6",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$9="Aula 6",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$9="Aula 6",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$9="Aula 6",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$D$5="Aula 6",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$5="Aula 6",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$5="Aula 6",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$5="Aula 6",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$5="Aula 6",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$5="Aula 6",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$5="Aula 6",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$5="Aula 6",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$5="Aula 6",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$5="Aula 6",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$5="Aula 6",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$5="Aula 6",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$5="Aula 6",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$5="Aula 6",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$5="Aula 6",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$5="Aula 6",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$5="Aula 6",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="H20" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$D$9="Aula 7",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$9="Aula 7",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$9="Aula 7",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$9="Aula 7",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$9="Aula 7",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$9="Aula 7",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$9="Aula 7",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$9="Aula 7",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$9="Aula 7",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$9="Aula 7",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$9="Aula 7",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$9="Aula 7",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$9="Aula 7",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$9="Aula 7",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$9="Aula 7",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$9="Aula 7",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$9="Aula 7",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$D$5="Aula 7",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$5="Aula 7",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$5="Aula 7",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$5="Aula 7",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$5="Aula 7",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$5="Aula 7",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$5="Aula 7",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$5="Aula 7",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$5="Aula 7",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$5="Aula 7",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$5="Aula 7",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$5="Aula 7",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$5="Aula 7",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$5="Aula 7",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$5="Aula 7",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$5="Aula 7",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$5="Aula 7",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="I20" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$D$9="Aula 8",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$9="Aula 8",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$9="Aula 8",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$9="Aula 8",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$9="Aula 8",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$9="Aula 8",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$9="Aula 8",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$9="Aula 8",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$9="Aula 8",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$9="Aula 8",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$9="Aula 8",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$9="Aula 8",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$9="Aula 8",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$9="Aula 8",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$9="Aula 8",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$9="Aula 8",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$9="Aula 8",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$D$5="Aula 8",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$5="Aula 8",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$5="Aula 8",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$5="Aula 8",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$5="Aula 8",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$5="Aula 8",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$5="Aula 8",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$5="Aula 8",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$5="Aula 8",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$5="Aula 8",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$5="Aula 8",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$5="Aula 8",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$5="Aula 8",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$5="Aula 8",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$5="Aula 8",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$5="Aula 8",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$5="Aula 8",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="J20" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$D$9="Aula 9",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$9="Aula 9",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$9="Aula 9",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$9="Aula 9",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$9="Aula 9",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$9="Aula 9",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$9="Aula 9",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$9="Aula 9",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$9="Aula 9",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$9="Aula 9",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$9="Aula 9",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$9="Aula 9",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$9="Aula 9",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$9="Aula 9",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$9="Aula 9",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$9="Aula 9",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$9="Aula 9",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$D$5="Aula 9",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$5="Aula 9",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$5="Aula 9",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$5="Aula 9",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$5="Aula 9",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$5="Aula 9",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$5="Aula 9",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$5="Aula 9",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$5="Aula 9",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$5="Aula 9",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$5="Aula 9",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$5="Aula 9",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$5="Aula 9",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$5="Aula 9",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$5="Aula 9",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$5="Aula 9",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$5="Aula 9",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="K20" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$D$9="Lab",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$9="Lab",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$9="Lab",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$9="Lab",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$9="Lab",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$9="Lab",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$9="Lab",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$9="Lab",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$9="Lab",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$9="Lab",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$9="Lab",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$9="Lab",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$9="Lab",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$9="Lab",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$9="Lab",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$9="Lab",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$9="Lab",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$D$5="Lab",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$5="Lab",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$5="Lab",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$5="Lab",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$5="Lab",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$5="Lab",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$5="Lab",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$5="Lab",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$5="Lab",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$5="Lab",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$5="Lab",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$5="Lab",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$5="Lab",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$5="Lab",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$5="Lab",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$5="Lab",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$5="Lab",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="L20" t="inlineStr"/>
@@ -6891,43 +6742,43 @@
         </is>
       </c>
       <c r="B21" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$D$11="Aula 1",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$11="Aula 1",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$11="Aula 1",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$11="Aula 1",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$11="Aula 1",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$11="Aula 1",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$11="Aula 1",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$11="Aula 1",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$11="Aula 1",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$11="Aula 1",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$11="Aula 1",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$11="Aula 1",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$11="Aula 1",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$11="Aula 1",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$11="Aula 1",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$11="Aula 1",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$11="Aula 1",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$D$7="Aula 1",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$7="Aula 1",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$7="Aula 1",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$7="Aula 1",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$7="Aula 1",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$7="Aula 1",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$7="Aula 1",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$7="Aula 1",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$7="Aula 1",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$7="Aula 1",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$7="Aula 1",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$7="Aula 1",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$7="Aula 1",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$7="Aula 1",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$7="Aula 1",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$7="Aula 1",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$7="Aula 1",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="C21" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$D$11="Aula 2",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$11="Aula 2",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$11="Aula 2",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$11="Aula 2",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$11="Aula 2",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$11="Aula 2",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$11="Aula 2",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$11="Aula 2",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$11="Aula 2",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$11="Aula 2",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$11="Aula 2",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$11="Aula 2",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$11="Aula 2",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$11="Aula 2",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$11="Aula 2",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$11="Aula 2",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$11="Aula 2",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$D$7="Aula 2",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$7="Aula 2",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$7="Aula 2",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$7="Aula 2",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$7="Aula 2",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$7="Aula 2",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$7="Aula 2",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$7="Aula 2",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$7="Aula 2",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$7="Aula 2",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$7="Aula 2",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$7="Aula 2",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$7="Aula 2",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$7="Aula 2",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$7="Aula 2",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$7="Aula 2",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$7="Aula 2",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="D21" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$D$11="Aula 3",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$11="Aula 3",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$11="Aula 3",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$11="Aula 3",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$11="Aula 3",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$11="Aula 3",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$11="Aula 3",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$11="Aula 3",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$11="Aula 3",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$11="Aula 3",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$11="Aula 3",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$11="Aula 3",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$11="Aula 3",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$11="Aula 3",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$11="Aula 3",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$11="Aula 3",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$11="Aula 3",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$D$7="Aula 3",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$7="Aula 3",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$7="Aula 3",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$7="Aula 3",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$7="Aula 3",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$7="Aula 3",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$7="Aula 3",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$7="Aula 3",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$7="Aula 3",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$7="Aula 3",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$7="Aula 3",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$7="Aula 3",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$7="Aula 3",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$7="Aula 3",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$7="Aula 3",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$7="Aula 3",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$7="Aula 3",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="E21" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$D$11="Aula 4",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$11="Aula 4",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$11="Aula 4",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$11="Aula 4",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$11="Aula 4",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$11="Aula 4",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$11="Aula 4",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$11="Aula 4",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$11="Aula 4",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$11="Aula 4",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$11="Aula 4",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$11="Aula 4",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$11="Aula 4",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$11="Aula 4",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$11="Aula 4",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$11="Aula 4",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$11="Aula 4",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$D$7="Aula 4",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$7="Aula 4",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$7="Aula 4",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$7="Aula 4",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$7="Aula 4",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$7="Aula 4",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$7="Aula 4",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$7="Aula 4",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$7="Aula 4",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$7="Aula 4",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$7="Aula 4",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$7="Aula 4",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$7="Aula 4",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$7="Aula 4",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$7="Aula 4",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$7="Aula 4",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$7="Aula 4",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="F21" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$D$11="Aula 5",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$11="Aula 5",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$11="Aula 5",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$11="Aula 5",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$11="Aula 5",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$11="Aula 5",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$11="Aula 5",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$11="Aula 5",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$11="Aula 5",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$11="Aula 5",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$11="Aula 5",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$11="Aula 5",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$11="Aula 5",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$11="Aula 5",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$11="Aula 5",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$11="Aula 5",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$11="Aula 5",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$D$7="Aula 5",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$7="Aula 5",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$7="Aula 5",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$7="Aula 5",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$7="Aula 5",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$7="Aula 5",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$7="Aula 5",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$7="Aula 5",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$7="Aula 5",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$7="Aula 5",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$7="Aula 5",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$7="Aula 5",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$7="Aula 5",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$7="Aula 5",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$7="Aula 5",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$7="Aula 5",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$7="Aula 5",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="G21" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$D$11="Aula 6",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$11="Aula 6",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$11="Aula 6",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$11="Aula 6",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$11="Aula 6",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$11="Aula 6",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$11="Aula 6",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$11="Aula 6",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$11="Aula 6",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$11="Aula 6",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$11="Aula 6",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$11="Aula 6",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$11="Aula 6",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$11="Aula 6",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$11="Aula 6",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$11="Aula 6",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$11="Aula 6",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$D$7="Aula 6",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$7="Aula 6",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$7="Aula 6",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$7="Aula 6",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$7="Aula 6",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$7="Aula 6",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$7="Aula 6",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$7="Aula 6",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$7="Aula 6",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$7="Aula 6",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$7="Aula 6",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$7="Aula 6",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$7="Aula 6",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$7="Aula 6",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$7="Aula 6",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$7="Aula 6",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$7="Aula 6",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="H21" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$D$11="Aula 7",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$11="Aula 7",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$11="Aula 7",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$11="Aula 7",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$11="Aula 7",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$11="Aula 7",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$11="Aula 7",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$11="Aula 7",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$11="Aula 7",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$11="Aula 7",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$11="Aula 7",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$11="Aula 7",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$11="Aula 7",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$11="Aula 7",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$11="Aula 7",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$11="Aula 7",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$11="Aula 7",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$D$7="Aula 7",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$7="Aula 7",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$7="Aula 7",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$7="Aula 7",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$7="Aula 7",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$7="Aula 7",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$7="Aula 7",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$7="Aula 7",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$7="Aula 7",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$7="Aula 7",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$7="Aula 7",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$7="Aula 7",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$7="Aula 7",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$7="Aula 7",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$7="Aula 7",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$7="Aula 7",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$7="Aula 7",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="I21" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$D$11="Aula 8",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$11="Aula 8",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$11="Aula 8",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$11="Aula 8",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$11="Aula 8",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$11="Aula 8",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$11="Aula 8",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$11="Aula 8",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$11="Aula 8",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$11="Aula 8",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$11="Aula 8",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$11="Aula 8",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$11="Aula 8",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$11="Aula 8",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$11="Aula 8",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$11="Aula 8",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$11="Aula 8",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$D$7="Aula 8",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$7="Aula 8",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$7="Aula 8",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$7="Aula 8",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$7="Aula 8",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$7="Aula 8",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$7="Aula 8",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$7="Aula 8",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$7="Aula 8",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$7="Aula 8",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$7="Aula 8",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$7="Aula 8",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$7="Aula 8",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$7="Aula 8",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$7="Aula 8",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$7="Aula 8",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$7="Aula 8",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="J21" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$D$11="Aula 9",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$11="Aula 9",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$11="Aula 9",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$11="Aula 9",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$11="Aula 9",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$11="Aula 9",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$11="Aula 9",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$11="Aula 9",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$11="Aula 9",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$11="Aula 9",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$11="Aula 9",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$11="Aula 9",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$11="Aula 9",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$11="Aula 9",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$11="Aula 9",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$11="Aula 9",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$11="Aula 9",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$D$7="Aula 9",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$7="Aula 9",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$7="Aula 9",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$7="Aula 9",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$7="Aula 9",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$7="Aula 9",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$7="Aula 9",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$7="Aula 9",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$7="Aula 9",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$7="Aula 9",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$7="Aula 9",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$7="Aula 9",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$7="Aula 9",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$7="Aula 9",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$7="Aula 9",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$7="Aula 9",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$7="Aula 9",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="K21" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$D$11="Lab",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$11="Lab",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$11="Lab",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$11="Lab",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$11="Lab",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$11="Lab",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$11="Lab",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$11="Lab",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$11="Lab",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$11="Lab",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$11="Lab",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$11="Lab",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$11="Lab",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$11="Lab",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$11="Lab",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$11="Lab",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$11="Lab",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$D$7="Lab",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$7="Lab",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$7="Lab",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$7="Lab",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$7="Lab",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$7="Lab",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$7="Lab",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$7="Lab",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$7="Lab",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$7="Lab",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$7="Lab",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$7="Lab",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$7="Lab",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$7="Lab",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$7="Lab",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$7="Lab",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$7="Lab",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -6939,43 +6790,43 @@
         </is>
       </c>
       <c r="B22" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$D$13="Aula 1",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$13="Aula 1",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$13="Aula 1",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$13="Aula 1",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$13="Aula 1",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$13="Aula 1",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$13="Aula 1",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$13="Aula 1",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$13="Aula 1",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$13="Aula 1",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$13="Aula 1",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$13="Aula 1",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$13="Aula 1",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$13="Aula 1",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$13="Aula 1",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$13="Aula 1",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$13="Aula 1",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$D$9="Aula 1",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$9="Aula 1",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$9="Aula 1",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$9="Aula 1",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$9="Aula 1",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$9="Aula 1",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$9="Aula 1",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$9="Aula 1",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$9="Aula 1",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$9="Aula 1",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$9="Aula 1",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$9="Aula 1",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$9="Aula 1",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$9="Aula 1",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$9="Aula 1",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$9="Aula 1",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$9="Aula 1",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="C22" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$D$13="Aula 2",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$13="Aula 2",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$13="Aula 2",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$13="Aula 2",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$13="Aula 2",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$13="Aula 2",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$13="Aula 2",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$13="Aula 2",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$13="Aula 2",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$13="Aula 2",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$13="Aula 2",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$13="Aula 2",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$13="Aula 2",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$13="Aula 2",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$13="Aula 2",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$13="Aula 2",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$13="Aula 2",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$D$9="Aula 2",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$9="Aula 2",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$9="Aula 2",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$9="Aula 2",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$9="Aula 2",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$9="Aula 2",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$9="Aula 2",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$9="Aula 2",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$9="Aula 2",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$9="Aula 2",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$9="Aula 2",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$9="Aula 2",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$9="Aula 2",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$9="Aula 2",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$9="Aula 2",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$9="Aula 2",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$9="Aula 2",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="D22" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$D$13="Aula 3",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$13="Aula 3",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$13="Aula 3",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$13="Aula 3",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$13="Aula 3",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$13="Aula 3",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$13="Aula 3",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$13="Aula 3",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$13="Aula 3",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$13="Aula 3",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$13="Aula 3",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$13="Aula 3",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$13="Aula 3",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$13="Aula 3",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$13="Aula 3",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$13="Aula 3",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$13="Aula 3",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$D$9="Aula 3",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$9="Aula 3",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$9="Aula 3",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$9="Aula 3",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$9="Aula 3",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$9="Aula 3",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$9="Aula 3",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$9="Aula 3",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$9="Aula 3",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$9="Aula 3",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$9="Aula 3",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$9="Aula 3",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$9="Aula 3",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$9="Aula 3",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$9="Aula 3",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$9="Aula 3",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$9="Aula 3",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="E22" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$D$13="Aula 4",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$13="Aula 4",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$13="Aula 4",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$13="Aula 4",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$13="Aula 4",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$13="Aula 4",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$13="Aula 4",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$13="Aula 4",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$13="Aula 4",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$13="Aula 4",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$13="Aula 4",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$13="Aula 4",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$13="Aula 4",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$13="Aula 4",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$13="Aula 4",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$13="Aula 4",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$13="Aula 4",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$D$9="Aula 4",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$9="Aula 4",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$9="Aula 4",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$9="Aula 4",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$9="Aula 4",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$9="Aula 4",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$9="Aula 4",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$9="Aula 4",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$9="Aula 4",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$9="Aula 4",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$9="Aula 4",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$9="Aula 4",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$9="Aula 4",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$9="Aula 4",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$9="Aula 4",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$9="Aula 4",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$9="Aula 4",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="F22" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$D$13="Aula 5",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$13="Aula 5",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$13="Aula 5",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$13="Aula 5",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$13="Aula 5",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$13="Aula 5",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$13="Aula 5",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$13="Aula 5",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$13="Aula 5",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$13="Aula 5",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$13="Aula 5",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$13="Aula 5",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$13="Aula 5",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$13="Aula 5",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$13="Aula 5",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$13="Aula 5",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$13="Aula 5",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$D$9="Aula 5",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$9="Aula 5",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$9="Aula 5",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$9="Aula 5",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$9="Aula 5",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$9="Aula 5",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$9="Aula 5",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$9="Aula 5",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$9="Aula 5",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$9="Aula 5",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$9="Aula 5",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$9="Aula 5",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$9="Aula 5",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$9="Aula 5",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$9="Aula 5",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$9="Aula 5",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$9="Aula 5",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="G22" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$D$13="Aula 6",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$13="Aula 6",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$13="Aula 6",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$13="Aula 6",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$13="Aula 6",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$13="Aula 6",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$13="Aula 6",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$13="Aula 6",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$13="Aula 6",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$13="Aula 6",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$13="Aula 6",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$13="Aula 6",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$13="Aula 6",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$13="Aula 6",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$13="Aula 6",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$13="Aula 6",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$13="Aula 6",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$D$9="Aula 6",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$9="Aula 6",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$9="Aula 6",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$9="Aula 6",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$9="Aula 6",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$9="Aula 6",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$9="Aula 6",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$9="Aula 6",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$9="Aula 6",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$9="Aula 6",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$9="Aula 6",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$9="Aula 6",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$9="Aula 6",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$9="Aula 6",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$9="Aula 6",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$9="Aula 6",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$9="Aula 6",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="H22" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$D$13="Aula 7",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$13="Aula 7",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$13="Aula 7",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$13="Aula 7",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$13="Aula 7",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$13="Aula 7",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$13="Aula 7",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$13="Aula 7",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$13="Aula 7",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$13="Aula 7",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$13="Aula 7",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$13="Aula 7",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$13="Aula 7",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$13="Aula 7",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$13="Aula 7",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$13="Aula 7",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$13="Aula 7",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$D$9="Aula 7",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$9="Aula 7",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$9="Aula 7",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$9="Aula 7",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$9="Aula 7",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$9="Aula 7",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$9="Aula 7",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$9="Aula 7",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$9="Aula 7",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$9="Aula 7",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$9="Aula 7",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$9="Aula 7",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$9="Aula 7",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$9="Aula 7",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$9="Aula 7",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$9="Aula 7",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$9="Aula 7",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="I22" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$D$13="Aula 8",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$13="Aula 8",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$13="Aula 8",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$13="Aula 8",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$13="Aula 8",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$13="Aula 8",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$13="Aula 8",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$13="Aula 8",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$13="Aula 8",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$13="Aula 8",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$13="Aula 8",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$13="Aula 8",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$13="Aula 8",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$13="Aula 8",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$13="Aula 8",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$13="Aula 8",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$13="Aula 8",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$D$9="Aula 8",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$9="Aula 8",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$9="Aula 8",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$9="Aula 8",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$9="Aula 8",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$9="Aula 8",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$9="Aula 8",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$9="Aula 8",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$9="Aula 8",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$9="Aula 8",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$9="Aula 8",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$9="Aula 8",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$9="Aula 8",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$9="Aula 8",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$9="Aula 8",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$9="Aula 8",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$9="Aula 8",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="J22" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$D$13="Aula 9",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$13="Aula 9",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$13="Aula 9",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$13="Aula 9",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$13="Aula 9",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$13="Aula 9",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$13="Aula 9",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$13="Aula 9",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$13="Aula 9",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$13="Aula 9",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$13="Aula 9",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$13="Aula 9",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$13="Aula 9",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$13="Aula 9",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$13="Aula 9",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$13="Aula 9",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$13="Aula 9",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$D$9="Aula 9",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$9="Aula 9",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$9="Aula 9",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$9="Aula 9",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$9="Aula 9",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$9="Aula 9",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$9="Aula 9",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$9="Aula 9",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$9="Aula 9",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$9="Aula 9",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$9="Aula 9",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$9="Aula 9",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$9="Aula 9",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$9="Aula 9",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$9="Aula 9",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$9="Aula 9",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$9="Aula 9",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="K22" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$D$13="Lab",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$13="Lab",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$13="Lab",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$13="Lab",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$13="Lab",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$13="Lab",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$13="Lab",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$13="Lab",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$13="Lab",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$13="Lab",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$13="Lab",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$13="Lab",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$13="Lab",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$13="Lab",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$13="Lab",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$13="Lab",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$13="Lab",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$D$9="Lab",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$9="Lab",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$9="Lab",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$9="Lab",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$9="Lab",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$9="Lab",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$9="Lab",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$9="Lab",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$9="Lab",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$9="Lab",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$9="Lab",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$9="Lab",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$9="Lab",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$9="Lab",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$9="Lab",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$9="Lab",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$9="Lab",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="L22" t="inlineStr"/>
@@ -6987,43 +6838,43 @@
         </is>
       </c>
       <c r="B23" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$D$15="Aula 1",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$15="Aula 1",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$15="Aula 1",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$15="Aula 1",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$15="Aula 1",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$15="Aula 1",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$15="Aula 1",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$15="Aula 1",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$15="Aula 1",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$15="Aula 1",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$15="Aula 1",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$15="Aula 1",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$15="Aula 1",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$15="Aula 1",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$15="Aula 1",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$15="Aula 1",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$15="Aula 1",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$D$11="Aula 1",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$11="Aula 1",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$11="Aula 1",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$11="Aula 1",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$11="Aula 1",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$11="Aula 1",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$11="Aula 1",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$11="Aula 1",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$11="Aula 1",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$11="Aula 1",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$11="Aula 1",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$11="Aula 1",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$11="Aula 1",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$11="Aula 1",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$11="Aula 1",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$11="Aula 1",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$11="Aula 1",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="C23" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$D$15="Aula 2",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$15="Aula 2",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$15="Aula 2",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$15="Aula 2",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$15="Aula 2",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$15="Aula 2",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$15="Aula 2",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$15="Aula 2",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$15="Aula 2",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$15="Aula 2",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$15="Aula 2",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$15="Aula 2",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$15="Aula 2",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$15="Aula 2",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$15="Aula 2",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$15="Aula 2",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$15="Aula 2",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$D$11="Aula 2",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$11="Aula 2",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$11="Aula 2",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$11="Aula 2",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$11="Aula 2",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$11="Aula 2",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$11="Aula 2",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$11="Aula 2",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$11="Aula 2",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$11="Aula 2",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$11="Aula 2",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$11="Aula 2",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$11="Aula 2",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$11="Aula 2",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$11="Aula 2",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$11="Aula 2",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$11="Aula 2",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="D23" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$D$15="Aula 3",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$15="Aula 3",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$15="Aula 3",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$15="Aula 3",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$15="Aula 3",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$15="Aula 3",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$15="Aula 3",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$15="Aula 3",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$15="Aula 3",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$15="Aula 3",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$15="Aula 3",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$15="Aula 3",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$15="Aula 3",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$15="Aula 3",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$15="Aula 3",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$15="Aula 3",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$15="Aula 3",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$D$11="Aula 3",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$11="Aula 3",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$11="Aula 3",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$11="Aula 3",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$11="Aula 3",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$11="Aula 3",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$11="Aula 3",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$11="Aula 3",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$11="Aula 3",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$11="Aula 3",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$11="Aula 3",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$11="Aula 3",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$11="Aula 3",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$11="Aula 3",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$11="Aula 3",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$11="Aula 3",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$11="Aula 3",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="E23" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$D$15="Aula 4",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$15="Aula 4",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$15="Aula 4",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$15="Aula 4",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$15="Aula 4",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$15="Aula 4",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$15="Aula 4",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$15="Aula 4",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$15="Aula 4",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$15="Aula 4",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$15="Aula 4",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$15="Aula 4",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$15="Aula 4",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$15="Aula 4",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$15="Aula 4",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$15="Aula 4",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$15="Aula 4",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$D$11="Aula 4",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$11="Aula 4",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$11="Aula 4",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$11="Aula 4",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$11="Aula 4",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$11="Aula 4",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$11="Aula 4",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$11="Aula 4",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$11="Aula 4",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$11="Aula 4",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$11="Aula 4",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$11="Aula 4",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$11="Aula 4",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$11="Aula 4",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$11="Aula 4",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$11="Aula 4",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$11="Aula 4",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="F23" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$D$15="Aula 5",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$15="Aula 5",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$15="Aula 5",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$15="Aula 5",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$15="Aula 5",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$15="Aula 5",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$15="Aula 5",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$15="Aula 5",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$15="Aula 5",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$15="Aula 5",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$15="Aula 5",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$15="Aula 5",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$15="Aula 5",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$15="Aula 5",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$15="Aula 5",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$15="Aula 5",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$15="Aula 5",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$D$11="Aula 5",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$11="Aula 5",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$11="Aula 5",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$11="Aula 5",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$11="Aula 5",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$11="Aula 5",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$11="Aula 5",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$11="Aula 5",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$11="Aula 5",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$11="Aula 5",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$11="Aula 5",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$11="Aula 5",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$11="Aula 5",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$11="Aula 5",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$11="Aula 5",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$11="Aula 5",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$11="Aula 5",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="G23" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$D$15="Aula 6",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$15="Aula 6",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$15="Aula 6",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$15="Aula 6",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$15="Aula 6",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$15="Aula 6",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$15="Aula 6",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$15="Aula 6",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$15="Aula 6",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$15="Aula 6",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$15="Aula 6",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$15="Aula 6",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$15="Aula 6",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$15="Aula 6",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$15="Aula 6",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$15="Aula 6",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$15="Aula 6",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$D$11="Aula 6",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$11="Aula 6",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$11="Aula 6",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$11="Aula 6",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$11="Aula 6",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$11="Aula 6",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$11="Aula 6",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$11="Aula 6",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$11="Aula 6",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$11="Aula 6",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$11="Aula 6",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$11="Aula 6",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$11="Aula 6",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$11="Aula 6",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$11="Aula 6",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$11="Aula 6",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$11="Aula 6",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="H23" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$D$15="Aula 7",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$15="Aula 7",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$15="Aula 7",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$15="Aula 7",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$15="Aula 7",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$15="Aula 7",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$15="Aula 7",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$15="Aula 7",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$15="Aula 7",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$15="Aula 7",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$15="Aula 7",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$15="Aula 7",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$15="Aula 7",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$15="Aula 7",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$15="Aula 7",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$15="Aula 7",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$15="Aula 7",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$D$11="Aula 7",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$11="Aula 7",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$11="Aula 7",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$11="Aula 7",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$11="Aula 7",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$11="Aula 7",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$11="Aula 7",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$11="Aula 7",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$11="Aula 7",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$11="Aula 7",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$11="Aula 7",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$11="Aula 7",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$11="Aula 7",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$11="Aula 7",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$11="Aula 7",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$11="Aula 7",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$11="Aula 7",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="I23" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$D$15="Aula 8",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$15="Aula 8",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$15="Aula 8",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$15="Aula 8",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$15="Aula 8",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$15="Aula 8",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$15="Aula 8",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$15="Aula 8",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$15="Aula 8",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$15="Aula 8",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$15="Aula 8",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$15="Aula 8",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$15="Aula 8",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$15="Aula 8",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$15="Aula 8",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$15="Aula 8",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$15="Aula 8",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$D$11="Aula 8",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$11="Aula 8",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$11="Aula 8",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$11="Aula 8",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$11="Aula 8",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$11="Aula 8",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$11="Aula 8",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$11="Aula 8",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$11="Aula 8",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$11="Aula 8",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$11="Aula 8",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$11="Aula 8",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$11="Aula 8",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$11="Aula 8",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$11="Aula 8",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$11="Aula 8",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$11="Aula 8",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="J23" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$D$15="Aula 9",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$15="Aula 9",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$15="Aula 9",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$15="Aula 9",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$15="Aula 9",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$15="Aula 9",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$15="Aula 9",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$15="Aula 9",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$15="Aula 9",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$15="Aula 9",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$15="Aula 9",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$15="Aula 9",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$15="Aula 9",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$15="Aula 9",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$15="Aula 9",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$15="Aula 9",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$15="Aula 9",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$D$11="Aula 9",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$11="Aula 9",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$11="Aula 9",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$11="Aula 9",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$11="Aula 9",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$11="Aula 9",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$11="Aula 9",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$11="Aula 9",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$11="Aula 9",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$11="Aula 9",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$11="Aula 9",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$11="Aula 9",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$11="Aula 9",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$11="Aula 9",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$11="Aula 9",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$11="Aula 9",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$11="Aula 9",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="K23" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$D$15="Lab",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$15="Lab",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$15="Lab",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$15="Lab",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$15="Lab",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$15="Lab",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$15="Lab",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$15="Lab",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$15="Lab",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$15="Lab",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$15="Lab",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$15="Lab",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$15="Lab",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$15="Lab",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$15="Lab",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$15="Lab",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$15="Lab",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$D$11="Lab",(D111!$A$1&amp;" "),"")&amp;IF(D211!$D$11="Lab",(D211!$A$1&amp;" "),"")&amp;IF(D311!$D$11="Lab",(D311!$A$1&amp;" "),"")&amp;IF(D411!$D$11="Lab",(D411!$A$1&amp;" "),"")&amp;IF(C111!$D$11="Lab",(C111!$A$1&amp;" "),"")&amp;IF(C121!$D$11="Lab",(C121!$A$1&amp;" "),"")&amp;IF(C122!$D$11="Lab",(C122!$A$1&amp;" "),"")&amp;IF(C211!$D$11="Lab",(C211!$A$1&amp;" "),"")&amp;IF(C212!$D$11="Lab",(C212!$A$1&amp;" "),"")&amp;IF(C311!$D$11="Lab",(C311!$A$1&amp;" "),"")&amp;IF(C312!$D$11="Lab",(C312!$A$1&amp;" "),"")&amp;IF(C411!$D$11="Lab",(C411!$A$1&amp;" "),"")&amp;IF(C412!$D$11="Lab",(C412!$A$1&amp;" "),"")&amp;IF(M111!$D$11="Lab",(M111!$A$1&amp;" "),"")&amp;IF(M211!$D$11="Lab",(M211!$A$1&amp;" "),"")&amp;IF(M311!$D$11="Lab",(M311!$A$1&amp;" "),"")&amp;IF(M411!$D$11="Lab",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="L23" t="inlineStr"/>
@@ -7101,99 +6952,63 @@
       <c r="L25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B26" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$E$5="Aula 1",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$5="Aula 1",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$5="Aula 1",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$5="Aula 1",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$5="Aula 1",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$5="Aula 1",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$5="Aula 1",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$5="Aula 1",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$5="Aula 1",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$5="Aula 1",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$5="Aula 1",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$5="Aula 1",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$5="Aula 1",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$5="Aula 1",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$5="Aula 1",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$5="Aula 1",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$5="Aula 1",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="C26" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$E$5="Aula 2",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$5="Aula 2",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$5="Aula 2",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$5="Aula 2",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$5="Aula 2",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$5="Aula 2",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$5="Aula 2",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$5="Aula 2",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$5="Aula 2",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$5="Aula 2",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$5="Aula 2",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$5="Aula 2",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$5="Aula 2",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$5="Aula 2",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$5="Aula 2",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$5="Aula 2",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$5="Aula 2",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="D26" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$E$5="Aula 3",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$5="Aula 3",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$5="Aula 3",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$5="Aula 3",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$5="Aula 3",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$5="Aula 3",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$5="Aula 3",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$5="Aula 3",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$5="Aula 3",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$5="Aula 3",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$5="Aula 3",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$5="Aula 3",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$5="Aula 3",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$5="Aula 3",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$5="Aula 3",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$5="Aula 3",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$5="Aula 3",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="E26" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$E$5="Aula 4",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$5="Aula 4",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$5="Aula 4",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$5="Aula 4",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$5="Aula 4",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$5="Aula 4",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$5="Aula 4",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$5="Aula 4",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$5="Aula 4",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$5="Aula 4",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$5="Aula 4",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$5="Aula 4",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$5="Aula 4",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$5="Aula 4",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$5="Aula 4",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$5="Aula 4",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$5="Aula 4",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="F26" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$E$5="Aula 5",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$5="Aula 5",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$5="Aula 5",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$5="Aula 5",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$5="Aula 5",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$5="Aula 5",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$5="Aula 5",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$5="Aula 5",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$5="Aula 5",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$5="Aula 5",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$5="Aula 5",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$5="Aula 5",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$5="Aula 5",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$5="Aula 5",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$5="Aula 5",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$5="Aula 5",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$5="Aula 5",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="G26" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$E$5="Aula 6",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$5="Aula 6",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$5="Aula 6",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$5="Aula 6",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$5="Aula 6",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$5="Aula 6",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$5="Aula 6",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$5="Aula 6",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$5="Aula 6",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$5="Aula 6",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$5="Aula 6",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$5="Aula 6",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$5="Aula 6",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$5="Aula 6",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$5="Aula 6",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$5="Aula 6",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$5="Aula 6",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="H26" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$E$5="Aula 7",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$5="Aula 7",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$5="Aula 7",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$5="Aula 7",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$5="Aula 7",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$5="Aula 7",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$5="Aula 7",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$5="Aula 7",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$5="Aula 7",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$5="Aula 7",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$5="Aula 7",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$5="Aula 7",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$5="Aula 7",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$5="Aula 7",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$5="Aula 7",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$5="Aula 7",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$5="Aula 7",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="I26" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$E$5="Aula 8",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$5="Aula 8",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$5="Aula 8",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$5="Aula 8",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$5="Aula 8",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$5="Aula 8",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$5="Aula 8",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$5="Aula 8",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$5="Aula 8",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$5="Aula 8",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$5="Aula 8",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$5="Aula 8",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$5="Aula 8",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$5="Aula 8",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$5="Aula 8",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$5="Aula 8",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$5="Aula 8",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="J26" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$E$5="Aula 9",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$5="Aula 9",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$5="Aula 9",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$5="Aula 9",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$5="Aula 9",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$5="Aula 9",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$5="Aula 9",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$5="Aula 9",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$5="Aula 9",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$5="Aula 9",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$5="Aula 9",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$5="Aula 9",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$5="Aula 9",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$5="Aula 9",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$5="Aula 9",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$5="Aula 9",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$5="Aula 9",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="K26" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$E$5="Lab",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$5="Lab",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$5="Lab",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$5="Lab",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$5="Lab",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$5="Lab",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$5="Lab",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$5="Lab",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$5="Lab",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$5="Lab",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$5="Lab",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$5="Lab",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$5="Lab",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$5="Lab",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$5="Lab",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$5="Lab",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$5="Lab",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>C113</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>C112</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>C111</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B27" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$E$7="Aula 1",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$7="Aula 1",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$7="Aula 1",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$7="Aula 1",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$7="Aula 1",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$7="Aula 1",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$7="Aula 1",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$7="Aula 1",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$7="Aula 1",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$7="Aula 1",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$7="Aula 1",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$7="Aula 1",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$7="Aula 1",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$7="Aula 1",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$7="Aula 1",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$7="Aula 1",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$7="Aula 1",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="C27" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$E$7="Aula 2",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$7="Aula 2",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$7="Aula 2",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$7="Aula 2",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$7="Aula 2",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$7="Aula 2",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$7="Aula 2",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$7="Aula 2",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$7="Aula 2",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$7="Aula 2",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$7="Aula 2",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$7="Aula 2",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$7="Aula 2",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$7="Aula 2",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$7="Aula 2",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$7="Aula 2",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$7="Aula 2",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="D27" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$E$7="Aula 3",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$7="Aula 3",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$7="Aula 3",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$7="Aula 3",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$7="Aula 3",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$7="Aula 3",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$7="Aula 3",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$7="Aula 3",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$7="Aula 3",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$7="Aula 3",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$7="Aula 3",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$7="Aula 3",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$7="Aula 3",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$7="Aula 3",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$7="Aula 3",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$7="Aula 3",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$7="Aula 3",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="E27" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$E$7="Aula 4",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$7="Aula 4",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$7="Aula 4",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$7="Aula 4",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$7="Aula 4",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$7="Aula 4",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$7="Aula 4",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$7="Aula 4",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$7="Aula 4",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$7="Aula 4",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$7="Aula 4",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$7="Aula 4",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$7="Aula 4",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$7="Aula 4",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$7="Aula 4",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$7="Aula 4",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$7="Aula 4",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="F27" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$E$7="Aula 5",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$7="Aula 5",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$7="Aula 5",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$7="Aula 5",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$7="Aula 5",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$7="Aula 5",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$7="Aula 5",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$7="Aula 5",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$7="Aula 5",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$7="Aula 5",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$7="Aula 5",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$7="Aula 5",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$7="Aula 5",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$7="Aula 5",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$7="Aula 5",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$7="Aula 5",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$7="Aula 5",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="G27" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$E$7="Aula 6",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$7="Aula 6",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$7="Aula 6",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$7="Aula 6",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$7="Aula 6",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$7="Aula 6",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$7="Aula 6",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$7="Aula 6",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$7="Aula 6",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$7="Aula 6",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$7="Aula 6",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$7="Aula 6",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$7="Aula 6",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$7="Aula 6",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$7="Aula 6",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$7="Aula 6",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$7="Aula 6",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="H27" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$E$7="Aula 7",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$7="Aula 7",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$7="Aula 7",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$7="Aula 7",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$7="Aula 7",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$7="Aula 7",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$7="Aula 7",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$7="Aula 7",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$7="Aula 7",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$7="Aula 7",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$7="Aula 7",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$7="Aula 7",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$7="Aula 7",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$7="Aula 7",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$7="Aula 7",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$7="Aula 7",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$7="Aula 7",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="I27" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$E$7="Aula 8",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$7="Aula 8",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$7="Aula 8",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$7="Aula 8",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$7="Aula 8",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$7="Aula 8",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$7="Aula 8",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$7="Aula 8",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$7="Aula 8",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$7="Aula 8",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$7="Aula 8",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$7="Aula 8",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$7="Aula 8",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$7="Aula 8",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$7="Aula 8",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$7="Aula 8",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$7="Aula 8",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="J27" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$E$7="Aula 9",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$7="Aula 9",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$7="Aula 9",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$7="Aula 9",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$7="Aula 9",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$7="Aula 9",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$7="Aula 9",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$7="Aula 9",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$7="Aula 9",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$7="Aula 9",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$7="Aula 9",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$7="Aula 9",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$7="Aula 9",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$7="Aula 9",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$7="Aula 9",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$7="Aula 9",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$7="Aula 9",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="K27" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$E$7="Lab",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$7="Lab",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$7="Lab",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$7="Lab",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$7="Lab",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$7="Lab",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$7="Lab",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$7="Lab",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$7="Lab",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$7="Lab",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$7="Lab",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$7="Lab",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$7="Lab",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$7="Lab",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$7="Lab",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$7="Lab",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$7="Lab",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>C113</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>C112</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>C111</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
     </row>
     <row r="28">
@@ -7203,43 +7018,43 @@
         </is>
       </c>
       <c r="B28" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$E$9="Aula 1",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$9="Aula 1",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$9="Aula 1",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$9="Aula 1",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$9="Aula 1",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$9="Aula 1",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$9="Aula 1",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$9="Aula 1",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$9="Aula 1",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$9="Aula 1",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$9="Aula 1",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$9="Aula 1",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$9="Aula 1",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$9="Aula 1",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$9="Aula 1",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$9="Aula 1",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$9="Aula 1",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$E$5="Aula 1",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$5="Aula 1",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$5="Aula 1",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$5="Aula 1",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$5="Aula 1",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$5="Aula 1",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$5="Aula 1",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$5="Aula 1",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$5="Aula 1",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$5="Aula 1",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$5="Aula 1",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$5="Aula 1",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$5="Aula 1",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$5="Aula 1",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$5="Aula 1",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$5="Aula 1",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$5="Aula 1",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="C28" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$E$9="Aula 2",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$9="Aula 2",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$9="Aula 2",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$9="Aula 2",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$9="Aula 2",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$9="Aula 2",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$9="Aula 2",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$9="Aula 2",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$9="Aula 2",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$9="Aula 2",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$9="Aula 2",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$9="Aula 2",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$9="Aula 2",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$9="Aula 2",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$9="Aula 2",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$9="Aula 2",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$9="Aula 2",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$E$5="Aula 2",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$5="Aula 2",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$5="Aula 2",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$5="Aula 2",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$5="Aula 2",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$5="Aula 2",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$5="Aula 2",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$5="Aula 2",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$5="Aula 2",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$5="Aula 2",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$5="Aula 2",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$5="Aula 2",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$5="Aula 2",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$5="Aula 2",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$5="Aula 2",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$5="Aula 2",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$5="Aula 2",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="D28" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$E$9="Aula 3",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$9="Aula 3",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$9="Aula 3",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$9="Aula 3",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$9="Aula 3",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$9="Aula 3",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$9="Aula 3",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$9="Aula 3",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$9="Aula 3",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$9="Aula 3",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$9="Aula 3",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$9="Aula 3",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$9="Aula 3",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$9="Aula 3",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$9="Aula 3",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$9="Aula 3",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$9="Aula 3",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$E$5="Aula 3",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$5="Aula 3",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$5="Aula 3",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$5="Aula 3",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$5="Aula 3",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$5="Aula 3",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$5="Aula 3",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$5="Aula 3",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$5="Aula 3",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$5="Aula 3",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$5="Aula 3",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$5="Aula 3",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$5="Aula 3",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$5="Aula 3",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$5="Aula 3",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$5="Aula 3",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$5="Aula 3",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="E28" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$E$9="Aula 4",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$9="Aula 4",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$9="Aula 4",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$9="Aula 4",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$9="Aula 4",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$9="Aula 4",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$9="Aula 4",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$9="Aula 4",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$9="Aula 4",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$9="Aula 4",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$9="Aula 4",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$9="Aula 4",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$9="Aula 4",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$9="Aula 4",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$9="Aula 4",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$9="Aula 4",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$9="Aula 4",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$E$5="Aula 4",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$5="Aula 4",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$5="Aula 4",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$5="Aula 4",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$5="Aula 4",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$5="Aula 4",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$5="Aula 4",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$5="Aula 4",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$5="Aula 4",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$5="Aula 4",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$5="Aula 4",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$5="Aula 4",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$5="Aula 4",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$5="Aula 4",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$5="Aula 4",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$5="Aula 4",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$5="Aula 4",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="F28" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$E$9="Aula 5",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$9="Aula 5",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$9="Aula 5",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$9="Aula 5",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$9="Aula 5",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$9="Aula 5",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$9="Aula 5",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$9="Aula 5",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$9="Aula 5",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$9="Aula 5",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$9="Aula 5",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$9="Aula 5",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$9="Aula 5",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$9="Aula 5",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$9="Aula 5",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$9="Aula 5",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$9="Aula 5",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$E$5="Aula 5",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$5="Aula 5",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$5="Aula 5",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$5="Aula 5",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$5="Aula 5",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$5="Aula 5",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$5="Aula 5",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$5="Aula 5",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$5="Aula 5",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$5="Aula 5",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$5="Aula 5",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$5="Aula 5",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$5="Aula 5",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$5="Aula 5",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$5="Aula 5",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$5="Aula 5",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$5="Aula 5",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="G28" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$E$9="Aula 6",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$9="Aula 6",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$9="Aula 6",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$9="Aula 6",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$9="Aula 6",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$9="Aula 6",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$9="Aula 6",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$9="Aula 6",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$9="Aula 6",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$9="Aula 6",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$9="Aula 6",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$9="Aula 6",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$9="Aula 6",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$9="Aula 6",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$9="Aula 6",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$9="Aula 6",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$9="Aula 6",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$E$5="Aula 6",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$5="Aula 6",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$5="Aula 6",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$5="Aula 6",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$5="Aula 6",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$5="Aula 6",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$5="Aula 6",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$5="Aula 6",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$5="Aula 6",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$5="Aula 6",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$5="Aula 6",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$5="Aula 6",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$5="Aula 6",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$5="Aula 6",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$5="Aula 6",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$5="Aula 6",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$5="Aula 6",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="H28" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$E$9="Aula 7",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$9="Aula 7",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$9="Aula 7",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$9="Aula 7",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$9="Aula 7",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$9="Aula 7",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$9="Aula 7",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$9="Aula 7",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$9="Aula 7",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$9="Aula 7",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$9="Aula 7",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$9="Aula 7",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$9="Aula 7",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$9="Aula 7",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$9="Aula 7",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$9="Aula 7",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$9="Aula 7",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$E$5="Aula 7",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$5="Aula 7",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$5="Aula 7",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$5="Aula 7",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$5="Aula 7",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$5="Aula 7",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$5="Aula 7",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$5="Aula 7",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$5="Aula 7",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$5="Aula 7",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$5="Aula 7",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$5="Aula 7",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$5="Aula 7",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$5="Aula 7",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$5="Aula 7",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$5="Aula 7",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$5="Aula 7",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="I28" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$E$9="Aula 8",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$9="Aula 8",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$9="Aula 8",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$9="Aula 8",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$9="Aula 8",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$9="Aula 8",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$9="Aula 8",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$9="Aula 8",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$9="Aula 8",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$9="Aula 8",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$9="Aula 8",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$9="Aula 8",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$9="Aula 8",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$9="Aula 8",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$9="Aula 8",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$9="Aula 8",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$9="Aula 8",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$E$5="Aula 8",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$5="Aula 8",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$5="Aula 8",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$5="Aula 8",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$5="Aula 8",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$5="Aula 8",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$5="Aula 8",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$5="Aula 8",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$5="Aula 8",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$5="Aula 8",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$5="Aula 8",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$5="Aula 8",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$5="Aula 8",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$5="Aula 8",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$5="Aula 8",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$5="Aula 8",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$5="Aula 8",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="J28" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$E$9="Aula 9",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$9="Aula 9",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$9="Aula 9",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$9="Aula 9",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$9="Aula 9",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$9="Aula 9",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$9="Aula 9",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$9="Aula 9",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$9="Aula 9",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$9="Aula 9",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$9="Aula 9",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$9="Aula 9",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$9="Aula 9",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$9="Aula 9",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$9="Aula 9",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$9="Aula 9",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$9="Aula 9",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$E$5="Aula 9",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$5="Aula 9",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$5="Aula 9",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$5="Aula 9",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$5="Aula 9",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$5="Aula 9",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$5="Aula 9",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$5="Aula 9",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$5="Aula 9",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$5="Aula 9",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$5="Aula 9",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$5="Aula 9",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$5="Aula 9",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$5="Aula 9",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$5="Aula 9",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$5="Aula 9",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$5="Aula 9",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="K28" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$E$9="Lab",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$9="Lab",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$9="Lab",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$9="Lab",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$9="Lab",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$9="Lab",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$9="Lab",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$9="Lab",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$9="Lab",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$9="Lab",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$9="Lab",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$9="Lab",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$9="Lab",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$9="Lab",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$9="Lab",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$9="Lab",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$9="Lab",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$E$5="Lab",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$5="Lab",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$5="Lab",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$5="Lab",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$5="Lab",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$5="Lab",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$5="Lab",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$5="Lab",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$5="Lab",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$5="Lab",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$5="Lab",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$5="Lab",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$5="Lab",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$5="Lab",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$5="Lab",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$5="Lab",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$5="Lab",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="L28" t="inlineStr"/>
@@ -7251,43 +7066,43 @@
         </is>
       </c>
       <c r="B29" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$E$11="Aula 1",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$11="Aula 1",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$11="Aula 1",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$11="Aula 1",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$11="Aula 1",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$11="Aula 1",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$11="Aula 1",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$11="Aula 1",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$11="Aula 1",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$11="Aula 1",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$11="Aula 1",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$11="Aula 1",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$11="Aula 1",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$11="Aula 1",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$11="Aula 1",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$11="Aula 1",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$11="Aula 1",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$E$7="Aula 1",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$7="Aula 1",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$7="Aula 1",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$7="Aula 1",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$7="Aula 1",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$7="Aula 1",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$7="Aula 1",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$7="Aula 1",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$7="Aula 1",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$7="Aula 1",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$7="Aula 1",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$7="Aula 1",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$7="Aula 1",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$7="Aula 1",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$7="Aula 1",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$7="Aula 1",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$7="Aula 1",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="C29" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$E$11="Aula 2",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$11="Aula 2",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$11="Aula 2",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$11="Aula 2",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$11="Aula 2",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$11="Aula 2",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$11="Aula 2",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$11="Aula 2",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$11="Aula 2",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$11="Aula 2",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$11="Aula 2",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$11="Aula 2",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$11="Aula 2",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$11="Aula 2",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$11="Aula 2",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$11="Aula 2",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$11="Aula 2",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$E$7="Aula 2",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$7="Aula 2",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$7="Aula 2",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$7="Aula 2",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$7="Aula 2",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$7="Aula 2",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$7="Aula 2",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$7="Aula 2",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$7="Aula 2",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$7="Aula 2",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$7="Aula 2",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$7="Aula 2",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$7="Aula 2",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$7="Aula 2",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$7="Aula 2",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$7="Aula 2",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$7="Aula 2",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="D29" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$E$11="Aula 3",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$11="Aula 3",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$11="Aula 3",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$11="Aula 3",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$11="Aula 3",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$11="Aula 3",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$11="Aula 3",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$11="Aula 3",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$11="Aula 3",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$11="Aula 3",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$11="Aula 3",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$11="Aula 3",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$11="Aula 3",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$11="Aula 3",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$11="Aula 3",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$11="Aula 3",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$11="Aula 3",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$E$7="Aula 3",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$7="Aula 3",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$7="Aula 3",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$7="Aula 3",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$7="Aula 3",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$7="Aula 3",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$7="Aula 3",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$7="Aula 3",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$7="Aula 3",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$7="Aula 3",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$7="Aula 3",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$7="Aula 3",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$7="Aula 3",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$7="Aula 3",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$7="Aula 3",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$7="Aula 3",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$7="Aula 3",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="E29" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$E$11="Aula 4",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$11="Aula 4",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$11="Aula 4",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$11="Aula 4",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$11="Aula 4",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$11="Aula 4",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$11="Aula 4",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$11="Aula 4",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$11="Aula 4",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$11="Aula 4",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$11="Aula 4",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$11="Aula 4",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$11="Aula 4",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$11="Aula 4",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$11="Aula 4",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$11="Aula 4",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$11="Aula 4",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$E$7="Aula 4",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$7="Aula 4",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$7="Aula 4",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$7="Aula 4",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$7="Aula 4",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$7="Aula 4",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$7="Aula 4",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$7="Aula 4",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$7="Aula 4",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$7="Aula 4",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$7="Aula 4",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$7="Aula 4",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$7="Aula 4",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$7="Aula 4",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$7="Aula 4",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$7="Aula 4",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$7="Aula 4",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="F29" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$E$11="Aula 5",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$11="Aula 5",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$11="Aula 5",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$11="Aula 5",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$11="Aula 5",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$11="Aula 5",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$11="Aula 5",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$11="Aula 5",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$11="Aula 5",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$11="Aula 5",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$11="Aula 5",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$11="Aula 5",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$11="Aula 5",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$11="Aula 5",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$11="Aula 5",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$11="Aula 5",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$11="Aula 5",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$E$7="Aula 5",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$7="Aula 5",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$7="Aula 5",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$7="Aula 5",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$7="Aula 5",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$7="Aula 5",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$7="Aula 5",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$7="Aula 5",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$7="Aula 5",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$7="Aula 5",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$7="Aula 5",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$7="Aula 5",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$7="Aula 5",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$7="Aula 5",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$7="Aula 5",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$7="Aula 5",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$7="Aula 5",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="G29" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$E$11="Aula 6",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$11="Aula 6",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$11="Aula 6",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$11="Aula 6",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$11="Aula 6",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$11="Aula 6",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$11="Aula 6",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$11="Aula 6",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$11="Aula 6",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$11="Aula 6",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$11="Aula 6",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$11="Aula 6",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$11="Aula 6",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$11="Aula 6",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$11="Aula 6",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$11="Aula 6",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$11="Aula 6",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$E$7="Aula 6",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$7="Aula 6",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$7="Aula 6",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$7="Aula 6",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$7="Aula 6",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$7="Aula 6",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$7="Aula 6",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$7="Aula 6",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$7="Aula 6",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$7="Aula 6",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$7="Aula 6",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$7="Aula 6",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$7="Aula 6",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$7="Aula 6",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$7="Aula 6",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$7="Aula 6",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$7="Aula 6",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="H29" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$E$11="Aula 7",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$11="Aula 7",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$11="Aula 7",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$11="Aula 7",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$11="Aula 7",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$11="Aula 7",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$11="Aula 7",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$11="Aula 7",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$11="Aula 7",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$11="Aula 7",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$11="Aula 7",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$11="Aula 7",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$11="Aula 7",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$11="Aula 7",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$11="Aula 7",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$11="Aula 7",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$11="Aula 7",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$E$7="Aula 7",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$7="Aula 7",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$7="Aula 7",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$7="Aula 7",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$7="Aula 7",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$7="Aula 7",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$7="Aula 7",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$7="Aula 7",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$7="Aula 7",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$7="Aula 7",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$7="Aula 7",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$7="Aula 7",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$7="Aula 7",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$7="Aula 7",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$7="Aula 7",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$7="Aula 7",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$7="Aula 7",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="I29" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$E$11="Aula 8",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$11="Aula 8",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$11="Aula 8",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$11="Aula 8",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$11="Aula 8",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$11="Aula 8",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$11="Aula 8",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$11="Aula 8",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$11="Aula 8",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$11="Aula 8",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$11="Aula 8",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$11="Aula 8",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$11="Aula 8",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$11="Aula 8",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$11="Aula 8",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$11="Aula 8",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$11="Aula 8",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$E$7="Aula 8",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$7="Aula 8",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$7="Aula 8",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$7="Aula 8",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$7="Aula 8",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$7="Aula 8",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$7="Aula 8",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$7="Aula 8",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$7="Aula 8",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$7="Aula 8",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$7="Aula 8",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$7="Aula 8",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$7="Aula 8",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$7="Aula 8",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$7="Aula 8",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$7="Aula 8",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$7="Aula 8",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="J29" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$E$11="Aula 9",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$11="Aula 9",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$11="Aula 9",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$11="Aula 9",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$11="Aula 9",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$11="Aula 9",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$11="Aula 9",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$11="Aula 9",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$11="Aula 9",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$11="Aula 9",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$11="Aula 9",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$11="Aula 9",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$11="Aula 9",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$11="Aula 9",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$11="Aula 9",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$11="Aula 9",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$11="Aula 9",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$E$7="Aula 9",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$7="Aula 9",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$7="Aula 9",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$7="Aula 9",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$7="Aula 9",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$7="Aula 9",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$7="Aula 9",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$7="Aula 9",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$7="Aula 9",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$7="Aula 9",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$7="Aula 9",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$7="Aula 9",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$7="Aula 9",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$7="Aula 9",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$7="Aula 9",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$7="Aula 9",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$7="Aula 9",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="K29" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$E$11="Lab",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$11="Lab",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$11="Lab",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$11="Lab",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$11="Lab",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$11="Lab",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$11="Lab",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$11="Lab",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$11="Lab",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$11="Lab",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$11="Lab",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$11="Lab",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$11="Lab",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$11="Lab",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$11="Lab",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$11="Lab",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$11="Lab",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$E$7="Lab",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$7="Lab",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$7="Lab",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$7="Lab",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$7="Lab",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$7="Lab",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$7="Lab",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$7="Lab",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$7="Lab",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$7="Lab",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$7="Lab",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$7="Lab",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$7="Lab",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$7="Lab",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$7="Lab",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$7="Lab",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$7="Lab",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="L29" t="inlineStr"/>
@@ -7299,43 +7114,43 @@
         </is>
       </c>
       <c r="B30" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$E$13="Aula 1",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$13="Aula 1",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$13="Aula 1",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$13="Aula 1",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$13="Aula 1",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$13="Aula 1",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$13="Aula 1",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$13="Aula 1",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$13="Aula 1",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$13="Aula 1",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$13="Aula 1",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$13="Aula 1",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$13="Aula 1",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$13="Aula 1",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$13="Aula 1",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$13="Aula 1",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$13="Aula 1",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$E$9="Aula 1",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$9="Aula 1",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$9="Aula 1",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$9="Aula 1",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$9="Aula 1",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$9="Aula 1",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$9="Aula 1",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$9="Aula 1",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$9="Aula 1",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$9="Aula 1",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$9="Aula 1",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$9="Aula 1",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$9="Aula 1",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$9="Aula 1",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$9="Aula 1",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$9="Aula 1",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$9="Aula 1",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="C30" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$E$13="Aula 2",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$13="Aula 2",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$13="Aula 2",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$13="Aula 2",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$13="Aula 2",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$13="Aula 2",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$13="Aula 2",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$13="Aula 2",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$13="Aula 2",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$13="Aula 2",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$13="Aula 2",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$13="Aula 2",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$13="Aula 2",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$13="Aula 2",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$13="Aula 2",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$13="Aula 2",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$13="Aula 2",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$E$9="Aula 2",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$9="Aula 2",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$9="Aula 2",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$9="Aula 2",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$9="Aula 2",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$9="Aula 2",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$9="Aula 2",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$9="Aula 2",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$9="Aula 2",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$9="Aula 2",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$9="Aula 2",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$9="Aula 2",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$9="Aula 2",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$9="Aula 2",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$9="Aula 2",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$9="Aula 2",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$9="Aula 2",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="D30" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$E$13="Aula 3",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$13="Aula 3",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$13="Aula 3",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$13="Aula 3",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$13="Aula 3",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$13="Aula 3",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$13="Aula 3",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$13="Aula 3",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$13="Aula 3",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$13="Aula 3",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$13="Aula 3",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$13="Aula 3",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$13="Aula 3",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$13="Aula 3",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$13="Aula 3",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$13="Aula 3",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$13="Aula 3",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$E$9="Aula 3",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$9="Aula 3",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$9="Aula 3",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$9="Aula 3",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$9="Aula 3",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$9="Aula 3",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$9="Aula 3",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$9="Aula 3",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$9="Aula 3",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$9="Aula 3",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$9="Aula 3",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$9="Aula 3",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$9="Aula 3",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$9="Aula 3",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$9="Aula 3",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$9="Aula 3",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$9="Aula 3",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="E30" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$E$13="Aula 4",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$13="Aula 4",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$13="Aula 4",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$13="Aula 4",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$13="Aula 4",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$13="Aula 4",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$13="Aula 4",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$13="Aula 4",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$13="Aula 4",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$13="Aula 4",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$13="Aula 4",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$13="Aula 4",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$13="Aula 4",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$13="Aula 4",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$13="Aula 4",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$13="Aula 4",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$13="Aula 4",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$E$9="Aula 4",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$9="Aula 4",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$9="Aula 4",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$9="Aula 4",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$9="Aula 4",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$9="Aula 4",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$9="Aula 4",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$9="Aula 4",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$9="Aula 4",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$9="Aula 4",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$9="Aula 4",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$9="Aula 4",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$9="Aula 4",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$9="Aula 4",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$9="Aula 4",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$9="Aula 4",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$9="Aula 4",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="F30" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$E$13="Aula 5",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$13="Aula 5",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$13="Aula 5",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$13="Aula 5",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$13="Aula 5",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$13="Aula 5",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$13="Aula 5",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$13="Aula 5",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$13="Aula 5",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$13="Aula 5",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$13="Aula 5",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$13="Aula 5",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$13="Aula 5",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$13="Aula 5",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$13="Aula 5",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$13="Aula 5",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$13="Aula 5",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$E$9="Aula 5",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$9="Aula 5",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$9="Aula 5",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$9="Aula 5",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$9="Aula 5",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$9="Aula 5",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$9="Aula 5",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$9="Aula 5",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$9="Aula 5",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$9="Aula 5",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$9="Aula 5",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$9="Aula 5",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$9="Aula 5",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$9="Aula 5",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$9="Aula 5",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$9="Aula 5",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$9="Aula 5",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="G30" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$E$13="Aula 6",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$13="Aula 6",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$13="Aula 6",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$13="Aula 6",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$13="Aula 6",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$13="Aula 6",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$13="Aula 6",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$13="Aula 6",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$13="Aula 6",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$13="Aula 6",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$13="Aula 6",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$13="Aula 6",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$13="Aula 6",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$13="Aula 6",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$13="Aula 6",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$13="Aula 6",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$13="Aula 6",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$E$9="Aula 6",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$9="Aula 6",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$9="Aula 6",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$9="Aula 6",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$9="Aula 6",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$9="Aula 6",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$9="Aula 6",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$9="Aula 6",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$9="Aula 6",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$9="Aula 6",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$9="Aula 6",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$9="Aula 6",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$9="Aula 6",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$9="Aula 6",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$9="Aula 6",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$9="Aula 6",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$9="Aula 6",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="H30" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$E$13="Aula 7",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$13="Aula 7",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$13="Aula 7",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$13="Aula 7",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$13="Aula 7",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$13="Aula 7",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$13="Aula 7",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$13="Aula 7",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$13="Aula 7",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$13="Aula 7",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$13="Aula 7",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$13="Aula 7",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$13="Aula 7",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$13="Aula 7",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$13="Aula 7",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$13="Aula 7",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$13="Aula 7",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$E$9="Aula 7",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$9="Aula 7",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$9="Aula 7",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$9="Aula 7",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$9="Aula 7",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$9="Aula 7",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$9="Aula 7",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$9="Aula 7",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$9="Aula 7",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$9="Aula 7",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$9="Aula 7",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$9="Aula 7",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$9="Aula 7",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$9="Aula 7",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$9="Aula 7",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$9="Aula 7",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$9="Aula 7",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="I30" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$E$13="Aula 8",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$13="Aula 8",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$13="Aula 8",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$13="Aula 8",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$13="Aula 8",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$13="Aula 8",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$13="Aula 8",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$13="Aula 8",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$13="Aula 8",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$13="Aula 8",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$13="Aula 8",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$13="Aula 8",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$13="Aula 8",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$13="Aula 8",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$13="Aula 8",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$13="Aula 8",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$13="Aula 8",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$E$9="Aula 8",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$9="Aula 8",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$9="Aula 8",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$9="Aula 8",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$9="Aula 8",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$9="Aula 8",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$9="Aula 8",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$9="Aula 8",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$9="Aula 8",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$9="Aula 8",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$9="Aula 8",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$9="Aula 8",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$9="Aula 8",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$9="Aula 8",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$9="Aula 8",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$9="Aula 8",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$9="Aula 8",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="J30" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$E$13="Aula 9",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$13="Aula 9",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$13="Aula 9",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$13="Aula 9",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$13="Aula 9",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$13="Aula 9",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$13="Aula 9",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$13="Aula 9",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$13="Aula 9",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$13="Aula 9",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$13="Aula 9",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$13="Aula 9",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$13="Aula 9",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$13="Aula 9",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$13="Aula 9",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$13="Aula 9",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$13="Aula 9",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$E$9="Aula 9",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$9="Aula 9",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$9="Aula 9",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$9="Aula 9",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$9="Aula 9",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$9="Aula 9",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$9="Aula 9",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$9="Aula 9",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$9="Aula 9",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$9="Aula 9",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$9="Aula 9",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$9="Aula 9",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$9="Aula 9",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$9="Aula 9",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$9="Aula 9",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$9="Aula 9",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$9="Aula 9",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="K30" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$E$13="Lab",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$13="Lab",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$13="Lab",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$13="Lab",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$13="Lab",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$13="Lab",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$13="Lab",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$13="Lab",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$13="Lab",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$13="Lab",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$13="Lab",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$13="Lab",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$13="Lab",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$13="Lab",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$13="Lab",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$13="Lab",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$13="Lab",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$E$9="Lab",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$9="Lab",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$9="Lab",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$9="Lab",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$9="Lab",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$9="Lab",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$9="Lab",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$9="Lab",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$9="Lab",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$9="Lab",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$9="Lab",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$9="Lab",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$9="Lab",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$9="Lab",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$9="Lab",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$9="Lab",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$9="Lab",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="L30" t="inlineStr"/>
@@ -7347,43 +7162,43 @@
         </is>
       </c>
       <c r="B31" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$E$15="Aula 1",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$15="Aula 1",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$15="Aula 1",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$15="Aula 1",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$15="Aula 1",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$15="Aula 1",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$15="Aula 1",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$15="Aula 1",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$15="Aula 1",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$15="Aula 1",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$15="Aula 1",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$15="Aula 1",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$15="Aula 1",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$15="Aula 1",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$15="Aula 1",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$15="Aula 1",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$15="Aula 1",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$E$11="Aula 1",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$11="Aula 1",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$11="Aula 1",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$11="Aula 1",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$11="Aula 1",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$11="Aula 1",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$11="Aula 1",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$11="Aula 1",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$11="Aula 1",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$11="Aula 1",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$11="Aula 1",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$11="Aula 1",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$11="Aula 1",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$11="Aula 1",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$11="Aula 1",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$11="Aula 1",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$11="Aula 1",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="C31" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$E$15="Aula 2",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$15="Aula 2",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$15="Aula 2",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$15="Aula 2",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$15="Aula 2",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$15="Aula 2",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$15="Aula 2",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$15="Aula 2",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$15="Aula 2",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$15="Aula 2",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$15="Aula 2",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$15="Aula 2",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$15="Aula 2",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$15="Aula 2",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$15="Aula 2",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$15="Aula 2",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$15="Aula 2",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$E$11="Aula 2",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$11="Aula 2",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$11="Aula 2",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$11="Aula 2",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$11="Aula 2",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$11="Aula 2",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$11="Aula 2",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$11="Aula 2",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$11="Aula 2",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$11="Aula 2",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$11="Aula 2",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$11="Aula 2",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$11="Aula 2",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$11="Aula 2",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$11="Aula 2",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$11="Aula 2",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$11="Aula 2",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="D31" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$E$15="Aula 3",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$15="Aula 3",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$15="Aula 3",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$15="Aula 3",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$15="Aula 3",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$15="Aula 3",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$15="Aula 3",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$15="Aula 3",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$15="Aula 3",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$15="Aula 3",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$15="Aula 3",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$15="Aula 3",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$15="Aula 3",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$15="Aula 3",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$15="Aula 3",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$15="Aula 3",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$15="Aula 3",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$E$11="Aula 3",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$11="Aula 3",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$11="Aula 3",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$11="Aula 3",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$11="Aula 3",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$11="Aula 3",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$11="Aula 3",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$11="Aula 3",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$11="Aula 3",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$11="Aula 3",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$11="Aula 3",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$11="Aula 3",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$11="Aula 3",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$11="Aula 3",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$11="Aula 3",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$11="Aula 3",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$11="Aula 3",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="E31" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$E$15="Aula 4",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$15="Aula 4",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$15="Aula 4",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$15="Aula 4",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$15="Aula 4",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$15="Aula 4",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$15="Aula 4",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$15="Aula 4",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$15="Aula 4",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$15="Aula 4",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$15="Aula 4",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$15="Aula 4",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$15="Aula 4",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$15="Aula 4",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$15="Aula 4",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$15="Aula 4",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$15="Aula 4",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$E$11="Aula 4",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$11="Aula 4",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$11="Aula 4",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$11="Aula 4",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$11="Aula 4",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$11="Aula 4",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$11="Aula 4",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$11="Aula 4",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$11="Aula 4",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$11="Aula 4",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$11="Aula 4",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$11="Aula 4",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$11="Aula 4",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$11="Aula 4",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$11="Aula 4",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$11="Aula 4",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$11="Aula 4",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="F31" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$E$15="Aula 5",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$15="Aula 5",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$15="Aula 5",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$15="Aula 5",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$15="Aula 5",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$15="Aula 5",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$15="Aula 5",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$15="Aula 5",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$15="Aula 5",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$15="Aula 5",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$15="Aula 5",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$15="Aula 5",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$15="Aula 5",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$15="Aula 5",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$15="Aula 5",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$15="Aula 5",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$15="Aula 5",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$E$11="Aula 5",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$11="Aula 5",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$11="Aula 5",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$11="Aula 5",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$11="Aula 5",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$11="Aula 5",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$11="Aula 5",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$11="Aula 5",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$11="Aula 5",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$11="Aula 5",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$11="Aula 5",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$11="Aula 5",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$11="Aula 5",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$11="Aula 5",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$11="Aula 5",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$11="Aula 5",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$11="Aula 5",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="G31" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$E$15="Aula 6",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$15="Aula 6",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$15="Aula 6",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$15="Aula 6",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$15="Aula 6",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$15="Aula 6",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$15="Aula 6",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$15="Aula 6",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$15="Aula 6",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$15="Aula 6",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$15="Aula 6",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$15="Aula 6",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$15="Aula 6",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$15="Aula 6",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$15="Aula 6",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$15="Aula 6",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$15="Aula 6",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$E$11="Aula 6",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$11="Aula 6",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$11="Aula 6",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$11="Aula 6",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$11="Aula 6",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$11="Aula 6",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$11="Aula 6",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$11="Aula 6",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$11="Aula 6",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$11="Aula 6",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$11="Aula 6",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$11="Aula 6",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$11="Aula 6",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$11="Aula 6",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$11="Aula 6",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$11="Aula 6",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$11="Aula 6",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="H31" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$E$15="Aula 7",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$15="Aula 7",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$15="Aula 7",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$15="Aula 7",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$15="Aula 7",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$15="Aula 7",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$15="Aula 7",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$15="Aula 7",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$15="Aula 7",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$15="Aula 7",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$15="Aula 7",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$15="Aula 7",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$15="Aula 7",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$15="Aula 7",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$15="Aula 7",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$15="Aula 7",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$15="Aula 7",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$E$11="Aula 7",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$11="Aula 7",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$11="Aula 7",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$11="Aula 7",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$11="Aula 7",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$11="Aula 7",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$11="Aula 7",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$11="Aula 7",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$11="Aula 7",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$11="Aula 7",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$11="Aula 7",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$11="Aula 7",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$11="Aula 7",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$11="Aula 7",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$11="Aula 7",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$11="Aula 7",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$11="Aula 7",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="I31" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$E$15="Aula 8",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$15="Aula 8",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$15="Aula 8",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$15="Aula 8",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$15="Aula 8",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$15="Aula 8",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$15="Aula 8",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$15="Aula 8",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$15="Aula 8",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$15="Aula 8",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$15="Aula 8",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$15="Aula 8",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$15="Aula 8",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$15="Aula 8",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$15="Aula 8",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$15="Aula 8",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$15="Aula 8",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$E$11="Aula 8",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$11="Aula 8",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$11="Aula 8",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$11="Aula 8",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$11="Aula 8",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$11="Aula 8",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$11="Aula 8",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$11="Aula 8",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$11="Aula 8",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$11="Aula 8",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$11="Aula 8",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$11="Aula 8",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$11="Aula 8",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$11="Aula 8",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$11="Aula 8",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$11="Aula 8",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$11="Aula 8",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="J31" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$E$15="Aula 9",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$15="Aula 9",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$15="Aula 9",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$15="Aula 9",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$15="Aula 9",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$15="Aula 9",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$15="Aula 9",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$15="Aula 9",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$15="Aula 9",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$15="Aula 9",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$15="Aula 9",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$15="Aula 9",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$15="Aula 9",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$15="Aula 9",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$15="Aula 9",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$15="Aula 9",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$15="Aula 9",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$E$11="Aula 9",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$11="Aula 9",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$11="Aula 9",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$11="Aula 9",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$11="Aula 9",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$11="Aula 9",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$11="Aula 9",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$11="Aula 9",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$11="Aula 9",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$11="Aula 9",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$11="Aula 9",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$11="Aula 9",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$11="Aula 9",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$11="Aula 9",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$11="Aula 9",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$11="Aula 9",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$11="Aula 9",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="K31" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$E$15="Lab",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$15="Lab",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$15="Lab",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$15="Lab",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$15="Lab",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$15="Lab",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$15="Lab",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$15="Lab",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$15="Lab",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$15="Lab",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$15="Lab",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$15="Lab",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$15="Lab",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$15="Lab",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$15="Lab",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$15="Lab",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$15="Lab",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$E$11="Lab",(D111!$A$1&amp;" "),"")&amp;IF(D211!$E$11="Lab",(D211!$A$1&amp;" "),"")&amp;IF(D311!$E$11="Lab",(D311!$A$1&amp;" "),"")&amp;IF(D411!$E$11="Lab",(D411!$A$1&amp;" "),"")&amp;IF(C111!$E$11="Lab",(C111!$A$1&amp;" "),"")&amp;IF(C121!$E$11="Lab",(C121!$A$1&amp;" "),"")&amp;IF(C122!$E$11="Lab",(C122!$A$1&amp;" "),"")&amp;IF(C211!$E$11="Lab",(C211!$A$1&amp;" "),"")&amp;IF(C212!$E$11="Lab",(C212!$A$1&amp;" "),"")&amp;IF(C311!$E$11="Lab",(C311!$A$1&amp;" "),"")&amp;IF(C312!$E$11="Lab",(C312!$A$1&amp;" "),"")&amp;IF(C411!$E$11="Lab",(C411!$A$1&amp;" "),"")&amp;IF(C412!$E$11="Lab",(C412!$A$1&amp;" "),"")&amp;IF(M111!$E$11="Lab",(M111!$A$1&amp;" "),"")&amp;IF(M211!$E$11="Lab",(M211!$A$1&amp;" "),"")&amp;IF(M311!$E$11="Lab",(M311!$A$1&amp;" "),"")&amp;IF(M411!$E$11="Lab",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="L31" t="inlineStr"/>
@@ -7461,98 +7276,42 @@
       <c r="L33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="A34" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B34" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$F$5="Aula 1",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$5="Aula 1",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$5="Aula 1",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$5="Aula 1",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$5="Aula 1",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$5="Aula 1",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$5="Aula 1",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$5="Aula 1",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$5="Aula 1",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$5="Aula 1",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$5="Aula 1",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$5="Aula 1",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$5="Aula 1",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$5="Aula 1",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$5="Aula 1",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$5="Aula 1",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$5="Aula 1",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="C34" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$F$5="Aula 2",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$5="Aula 2",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$5="Aula 2",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$5="Aula 2",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$5="Aula 2",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$5="Aula 2",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$5="Aula 2",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$5="Aula 2",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$5="Aula 2",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$5="Aula 2",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$5="Aula 2",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$5="Aula 2",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$5="Aula 2",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$5="Aula 2",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$5="Aula 2",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$5="Aula 2",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$5="Aula 2",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="D34" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$F$5="Aula 3",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$5="Aula 3",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$5="Aula 3",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$5="Aula 3",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$5="Aula 3",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$5="Aula 3",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$5="Aula 3",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$5="Aula 3",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$5="Aula 3",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$5="Aula 3",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$5="Aula 3",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$5="Aula 3",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$5="Aula 3",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$5="Aula 3",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$5="Aula 3",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$5="Aula 3",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$5="Aula 3",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="E34" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$F$5="Aula 4",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$5="Aula 4",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$5="Aula 4",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$5="Aula 4",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$5="Aula 4",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$5="Aula 4",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$5="Aula 4",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$5="Aula 4",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$5="Aula 4",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$5="Aula 4",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$5="Aula 4",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$5="Aula 4",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$5="Aula 4",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$5="Aula 4",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$5="Aula 4",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$5="Aula 4",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$5="Aula 4",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="F34" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$F$5="Aula 5",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$5="Aula 5",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$5="Aula 5",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$5="Aula 5",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$5="Aula 5",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$5="Aula 5",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$5="Aula 5",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$5="Aula 5",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$5="Aula 5",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$5="Aula 5",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$5="Aula 5",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$5="Aula 5",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$5="Aula 5",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$5="Aula 5",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$5="Aula 5",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$5="Aula 5",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$5="Aula 5",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="G34" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$F$5="Aula 6",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$5="Aula 6",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$5="Aula 6",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$5="Aula 6",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$5="Aula 6",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$5="Aula 6",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$5="Aula 6",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$5="Aula 6",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$5="Aula 6",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$5="Aula 6",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$5="Aula 6",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$5="Aula 6",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$5="Aula 6",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$5="Aula 6",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$5="Aula 6",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$5="Aula 6",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$5="Aula 6",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="H34" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$F$5="Aula 7",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$5="Aula 7",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$5="Aula 7",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$5="Aula 7",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$5="Aula 7",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$5="Aula 7",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$5="Aula 7",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$5="Aula 7",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$5="Aula 7",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$5="Aula 7",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$5="Aula 7",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$5="Aula 7",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$5="Aula 7",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$5="Aula 7",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$5="Aula 7",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$5="Aula 7",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$5="Aula 7",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="I34" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$F$5="Aula 8",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$5="Aula 8",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$5="Aula 8",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$5="Aula 8",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$5="Aula 8",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$5="Aula 8",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$5="Aula 8",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$5="Aula 8",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$5="Aula 8",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$5="Aula 8",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$5="Aula 8",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$5="Aula 8",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$5="Aula 8",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$5="Aula 8",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$5="Aula 8",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$5="Aula 8",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$5="Aula 8",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="J34" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$F$5="Aula 9",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$5="Aula 9",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$5="Aula 9",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$5="Aula 9",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$5="Aula 9",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$5="Aula 9",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$5="Aula 9",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$5="Aula 9",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$5="Aula 9",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$5="Aula 9",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$5="Aula 9",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$5="Aula 9",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$5="Aula 9",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$5="Aula 9",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$5="Aula 9",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$5="Aula 9",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$5="Aula 9",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="K34" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$F$5="Lab",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$5="Lab",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$5="Lab",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$5="Lab",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$5="Lab",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$5="Lab",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$5="Lab",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$5="Lab",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$5="Lab",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$5="Lab",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$5="Lab",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$5="Lab",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$5="Lab",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$5="Lab",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$5="Lab",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$5="Lab",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$5="Lab",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="A35" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B35" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$F$7="Aula 1",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$7="Aula 1",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$7="Aula 1",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$7="Aula 1",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$7="Aula 1",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$7="Aula 1",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$7="Aula 1",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$7="Aula 1",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$7="Aula 1",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$7="Aula 1",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$7="Aula 1",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$7="Aula 1",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$7="Aula 1",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$7="Aula 1",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$7="Aula 1",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$7="Aula 1",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$7="Aula 1",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="C35" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$F$7="Aula 2",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$7="Aula 2",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$7="Aula 2",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$7="Aula 2",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$7="Aula 2",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$7="Aula 2",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$7="Aula 2",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$7="Aula 2",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$7="Aula 2",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$7="Aula 2",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$7="Aula 2",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$7="Aula 2",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$7="Aula 2",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$7="Aula 2",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$7="Aula 2",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$7="Aula 2",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$7="Aula 2",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="D35" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$F$7="Aula 3",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$7="Aula 3",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$7="Aula 3",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$7="Aula 3",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$7="Aula 3",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$7="Aula 3",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$7="Aula 3",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$7="Aula 3",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$7="Aula 3",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$7="Aula 3",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$7="Aula 3",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$7="Aula 3",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$7="Aula 3",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$7="Aula 3",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$7="Aula 3",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$7="Aula 3",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$7="Aula 3",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="E35" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$F$7="Aula 4",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$7="Aula 4",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$7="Aula 4",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$7="Aula 4",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$7="Aula 4",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$7="Aula 4",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$7="Aula 4",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$7="Aula 4",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$7="Aula 4",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$7="Aula 4",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$7="Aula 4",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$7="Aula 4",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$7="Aula 4",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$7="Aula 4",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$7="Aula 4",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$7="Aula 4",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$7="Aula 4",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="F35" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$F$7="Aula 5",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$7="Aula 5",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$7="Aula 5",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$7="Aula 5",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$7="Aula 5",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$7="Aula 5",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$7="Aula 5",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$7="Aula 5",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$7="Aula 5",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$7="Aula 5",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$7="Aula 5",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$7="Aula 5",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$7="Aula 5",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$7="Aula 5",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$7="Aula 5",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$7="Aula 5",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$7="Aula 5",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="G35" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$F$7="Aula 6",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$7="Aula 6",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$7="Aula 6",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$7="Aula 6",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$7="Aula 6",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$7="Aula 6",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$7="Aula 6",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$7="Aula 6",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$7="Aula 6",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$7="Aula 6",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$7="Aula 6",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$7="Aula 6",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$7="Aula 6",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$7="Aula 6",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$7="Aula 6",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$7="Aula 6",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$7="Aula 6",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="H35" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$F$7="Aula 7",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$7="Aula 7",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$7="Aula 7",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$7="Aula 7",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$7="Aula 7",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$7="Aula 7",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$7="Aula 7",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$7="Aula 7",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$7="Aula 7",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$7="Aula 7",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$7="Aula 7",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$7="Aula 7",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$7="Aula 7",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$7="Aula 7",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$7="Aula 7",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$7="Aula 7",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$7="Aula 7",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="I35" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$F$7="Aula 8",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$7="Aula 8",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$7="Aula 8",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$7="Aula 8",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$7="Aula 8",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$7="Aula 8",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$7="Aula 8",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$7="Aula 8",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$7="Aula 8",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$7="Aula 8",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$7="Aula 8",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$7="Aula 8",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$7="Aula 8",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$7="Aula 8",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$7="Aula 8",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$7="Aula 8",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$7="Aula 8",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="J35" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$F$7="Aula 9",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$7="Aula 9",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$7="Aula 9",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$7="Aula 9",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$7="Aula 9",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$7="Aula 9",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$7="Aula 9",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$7="Aula 9",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$7="Aula 9",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$7="Aula 9",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$7="Aula 9",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$7="Aula 9",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$7="Aula 9",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$7="Aula 9",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$7="Aula 9",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$7="Aula 9",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$7="Aula 9",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
-      </c>
-      <c r="K35" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$F$7="Lab",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$7="Lab",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$7="Lab",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$7="Lab",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$7="Lab",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$7="Lab",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$7="Lab",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$7="Lab",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$7="Lab",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$7="Lab",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$7="Lab",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$7="Lab",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$7="Lab",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$7="Lab",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$7="Lab",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$7="Lab",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$7="Lab",(M411!$A$1&amp;" "),""))," ",",")</f>
-        <v/>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>C112</t>
+        </is>
       </c>
       <c r="L35" t="inlineStr"/>
     </row>
@@ -7563,43 +7322,43 @@
         </is>
       </c>
       <c r="B36" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$F$9="Aula 1",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$9="Aula 1",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$9="Aula 1",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$9="Aula 1",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$9="Aula 1",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$9="Aula 1",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$9="Aula 1",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$9="Aula 1",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$9="Aula 1",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$9="Aula 1",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$9="Aula 1",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$9="Aula 1",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$9="Aula 1",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$9="Aula 1",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$9="Aula 1",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$9="Aula 1",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$9="Aula 1",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$F$5="Aula 1",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$5="Aula 1",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$5="Aula 1",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$5="Aula 1",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$5="Aula 1",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$5="Aula 1",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$5="Aula 1",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$5="Aula 1",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$5="Aula 1",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$5="Aula 1",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$5="Aula 1",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$5="Aula 1",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$5="Aula 1",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$5="Aula 1",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$5="Aula 1",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$5="Aula 1",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$5="Aula 1",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="C36" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$F$9="Aula 2",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$9="Aula 2",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$9="Aula 2",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$9="Aula 2",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$9="Aula 2",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$9="Aula 2",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$9="Aula 2",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$9="Aula 2",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$9="Aula 2",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$9="Aula 2",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$9="Aula 2",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$9="Aula 2",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$9="Aula 2",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$9="Aula 2",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$9="Aula 2",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$9="Aula 2",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$9="Aula 2",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$F$5="Aula 2",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$5="Aula 2",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$5="Aula 2",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$5="Aula 2",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$5="Aula 2",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$5="Aula 2",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$5="Aula 2",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$5="Aula 2",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$5="Aula 2",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$5="Aula 2",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$5="Aula 2",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$5="Aula 2",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$5="Aula 2",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$5="Aula 2",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$5="Aula 2",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$5="Aula 2",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$5="Aula 2",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="D36" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$F$9="Aula 3",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$9="Aula 3",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$9="Aula 3",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$9="Aula 3",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$9="Aula 3",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$9="Aula 3",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$9="Aula 3",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$9="Aula 3",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$9="Aula 3",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$9="Aula 3",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$9="Aula 3",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$9="Aula 3",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$9="Aula 3",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$9="Aula 3",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$9="Aula 3",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$9="Aula 3",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$9="Aula 3",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$F$5="Aula 3",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$5="Aula 3",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$5="Aula 3",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$5="Aula 3",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$5="Aula 3",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$5="Aula 3",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$5="Aula 3",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$5="Aula 3",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$5="Aula 3",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$5="Aula 3",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$5="Aula 3",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$5="Aula 3",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$5="Aula 3",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$5="Aula 3",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$5="Aula 3",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$5="Aula 3",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$5="Aula 3",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="E36" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$F$9="Aula 4",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$9="Aula 4",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$9="Aula 4",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$9="Aula 4",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$9="Aula 4",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$9="Aula 4",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$9="Aula 4",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$9="Aula 4",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$9="Aula 4",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$9="Aula 4",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$9="Aula 4",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$9="Aula 4",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$9="Aula 4",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$9="Aula 4",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$9="Aula 4",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$9="Aula 4",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$9="Aula 4",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$F$5="Aula 4",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$5="Aula 4",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$5="Aula 4",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$5="Aula 4",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$5="Aula 4",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$5="Aula 4",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$5="Aula 4",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$5="Aula 4",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$5="Aula 4",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$5="Aula 4",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$5="Aula 4",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$5="Aula 4",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$5="Aula 4",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$5="Aula 4",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$5="Aula 4",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$5="Aula 4",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$5="Aula 4",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="F36" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$F$9="Aula 5",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$9="Aula 5",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$9="Aula 5",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$9="Aula 5",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$9="Aula 5",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$9="Aula 5",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$9="Aula 5",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$9="Aula 5",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$9="Aula 5",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$9="Aula 5",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$9="Aula 5",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$9="Aula 5",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$9="Aula 5",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$9="Aula 5",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$9="Aula 5",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$9="Aula 5",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$9="Aula 5",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$F$5="Aula 5",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$5="Aula 5",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$5="Aula 5",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$5="Aula 5",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$5="Aula 5",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$5="Aula 5",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$5="Aula 5",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$5="Aula 5",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$5="Aula 5",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$5="Aula 5",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$5="Aula 5",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$5="Aula 5",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$5="Aula 5",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$5="Aula 5",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$5="Aula 5",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$5="Aula 5",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$5="Aula 5",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="G36" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$F$9="Aula 6",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$9="Aula 6",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$9="Aula 6",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$9="Aula 6",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$9="Aula 6",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$9="Aula 6",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$9="Aula 6",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$9="Aula 6",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$9="Aula 6",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$9="Aula 6",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$9="Aula 6",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$9="Aula 6",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$9="Aula 6",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$9="Aula 6",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$9="Aula 6",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$9="Aula 6",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$9="Aula 6",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$F$5="Aula 6",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$5="Aula 6",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$5="Aula 6",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$5="Aula 6",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$5="Aula 6",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$5="Aula 6",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$5="Aula 6",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$5="Aula 6",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$5="Aula 6",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$5="Aula 6",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$5="Aula 6",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$5="Aula 6",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$5="Aula 6",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$5="Aula 6",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$5="Aula 6",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$5="Aula 6",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$5="Aula 6",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="H36" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$F$9="Aula 7",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$9="Aula 7",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$9="Aula 7",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$9="Aula 7",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$9="Aula 7",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$9="Aula 7",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$9="Aula 7",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$9="Aula 7",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$9="Aula 7",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$9="Aula 7",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$9="Aula 7",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$9="Aula 7",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$9="Aula 7",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$9="Aula 7",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$9="Aula 7",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$9="Aula 7",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$9="Aula 7",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$F$5="Aula 7",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$5="Aula 7",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$5="Aula 7",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$5="Aula 7",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$5="Aula 7",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$5="Aula 7",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$5="Aula 7",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$5="Aula 7",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$5="Aula 7",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$5="Aula 7",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$5="Aula 7",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$5="Aula 7",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$5="Aula 7",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$5="Aula 7",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$5="Aula 7",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$5="Aula 7",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$5="Aula 7",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="I36" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$F$9="Aula 8",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$9="Aula 8",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$9="Aula 8",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$9="Aula 8",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$9="Aula 8",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$9="Aula 8",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$9="Aula 8",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$9="Aula 8",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$9="Aula 8",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$9="Aula 8",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$9="Aula 8",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$9="Aula 8",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$9="Aula 8",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$9="Aula 8",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$9="Aula 8",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$9="Aula 8",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$9="Aula 8",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$F$5="Aula 8",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$5="Aula 8",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$5="Aula 8",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$5="Aula 8",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$5="Aula 8",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$5="Aula 8",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$5="Aula 8",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$5="Aula 8",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$5="Aula 8",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$5="Aula 8",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$5="Aula 8",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$5="Aula 8",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$5="Aula 8",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$5="Aula 8",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$5="Aula 8",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$5="Aula 8",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$5="Aula 8",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="J36" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$F$9="Aula 9",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$9="Aula 9",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$9="Aula 9",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$9="Aula 9",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$9="Aula 9",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$9="Aula 9",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$9="Aula 9",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$9="Aula 9",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$9="Aula 9",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$9="Aula 9",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$9="Aula 9",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$9="Aula 9",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$9="Aula 9",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$9="Aula 9",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$9="Aula 9",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$9="Aula 9",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$9="Aula 9",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$F$5="Aula 9",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$5="Aula 9",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$5="Aula 9",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$5="Aula 9",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$5="Aula 9",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$5="Aula 9",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$5="Aula 9",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$5="Aula 9",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$5="Aula 9",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$5="Aula 9",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$5="Aula 9",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$5="Aula 9",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$5="Aula 9",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$5="Aula 9",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$5="Aula 9",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$5="Aula 9",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$5="Aula 9",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="K36" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$F$9="Lab",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$9="Lab",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$9="Lab",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$9="Lab",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$9="Lab",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$9="Lab",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$9="Lab",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$9="Lab",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$9="Lab",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$9="Lab",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$9="Lab",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$9="Lab",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$9="Lab",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$9="Lab",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$9="Lab",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$9="Lab",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$9="Lab",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$F$5="Lab",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$5="Lab",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$5="Lab",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$5="Lab",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$5="Lab",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$5="Lab",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$5="Lab",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$5="Lab",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$5="Lab",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$5="Lab",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$5="Lab",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$5="Lab",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$5="Lab",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$5="Lab",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$5="Lab",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$5="Lab",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$5="Lab",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="L36" t="inlineStr"/>
@@ -7611,43 +7370,43 @@
         </is>
       </c>
       <c r="B37" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$F$11="Aula 1",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$11="Aula 1",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$11="Aula 1",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$11="Aula 1",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$11="Aula 1",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$11="Aula 1",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$11="Aula 1",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$11="Aula 1",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$11="Aula 1",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$11="Aula 1",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$11="Aula 1",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$11="Aula 1",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$11="Aula 1",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$11="Aula 1",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$11="Aula 1",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$11="Aula 1",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$11="Aula 1",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$F$7="Aula 1",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$7="Aula 1",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$7="Aula 1",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$7="Aula 1",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$7="Aula 1",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$7="Aula 1",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$7="Aula 1",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$7="Aula 1",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$7="Aula 1",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$7="Aula 1",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$7="Aula 1",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$7="Aula 1",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$7="Aula 1",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$7="Aula 1",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$7="Aula 1",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$7="Aula 1",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$7="Aula 1",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="C37" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$F$11="Aula 2",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$11="Aula 2",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$11="Aula 2",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$11="Aula 2",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$11="Aula 2",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$11="Aula 2",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$11="Aula 2",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$11="Aula 2",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$11="Aula 2",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$11="Aula 2",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$11="Aula 2",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$11="Aula 2",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$11="Aula 2",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$11="Aula 2",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$11="Aula 2",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$11="Aula 2",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$11="Aula 2",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$F$7="Aula 2",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$7="Aula 2",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$7="Aula 2",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$7="Aula 2",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$7="Aula 2",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$7="Aula 2",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$7="Aula 2",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$7="Aula 2",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$7="Aula 2",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$7="Aula 2",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$7="Aula 2",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$7="Aula 2",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$7="Aula 2",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$7="Aula 2",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$7="Aula 2",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$7="Aula 2",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$7="Aula 2",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="D37" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$F$11="Aula 3",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$11="Aula 3",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$11="Aula 3",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$11="Aula 3",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$11="Aula 3",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$11="Aula 3",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$11="Aula 3",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$11="Aula 3",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$11="Aula 3",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$11="Aula 3",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$11="Aula 3",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$11="Aula 3",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$11="Aula 3",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$11="Aula 3",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$11="Aula 3",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$11="Aula 3",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$11="Aula 3",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$F$7="Aula 3",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$7="Aula 3",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$7="Aula 3",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$7="Aula 3",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$7="Aula 3",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$7="Aula 3",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$7="Aula 3",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$7="Aula 3",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$7="Aula 3",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$7="Aula 3",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$7="Aula 3",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$7="Aula 3",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$7="Aula 3",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$7="Aula 3",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$7="Aula 3",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$7="Aula 3",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$7="Aula 3",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="E37" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$F$11="Aula 4",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$11="Aula 4",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$11="Aula 4",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$11="Aula 4",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$11="Aula 4",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$11="Aula 4",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$11="Aula 4",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$11="Aula 4",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$11="Aula 4",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$11="Aula 4",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$11="Aula 4",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$11="Aula 4",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$11="Aula 4",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$11="Aula 4",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$11="Aula 4",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$11="Aula 4",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$11="Aula 4",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$F$7="Aula 4",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$7="Aula 4",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$7="Aula 4",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$7="Aula 4",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$7="Aula 4",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$7="Aula 4",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$7="Aula 4",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$7="Aula 4",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$7="Aula 4",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$7="Aula 4",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$7="Aula 4",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$7="Aula 4",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$7="Aula 4",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$7="Aula 4",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$7="Aula 4",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$7="Aula 4",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$7="Aula 4",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="F37" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$F$11="Aula 5",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$11="Aula 5",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$11="Aula 5",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$11="Aula 5",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$11="Aula 5",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$11="Aula 5",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$11="Aula 5",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$11="Aula 5",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$11="Aula 5",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$11="Aula 5",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$11="Aula 5",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$11="Aula 5",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$11="Aula 5",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$11="Aula 5",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$11="Aula 5",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$11="Aula 5",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$11="Aula 5",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$F$7="Aula 5",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$7="Aula 5",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$7="Aula 5",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$7="Aula 5",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$7="Aula 5",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$7="Aula 5",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$7="Aula 5",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$7="Aula 5",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$7="Aula 5",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$7="Aula 5",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$7="Aula 5",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$7="Aula 5",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$7="Aula 5",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$7="Aula 5",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$7="Aula 5",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$7="Aula 5",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$7="Aula 5",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="G37" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$F$11="Aula 6",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$11="Aula 6",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$11="Aula 6",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$11="Aula 6",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$11="Aula 6",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$11="Aula 6",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$11="Aula 6",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$11="Aula 6",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$11="Aula 6",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$11="Aula 6",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$11="Aula 6",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$11="Aula 6",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$11="Aula 6",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$11="Aula 6",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$11="Aula 6",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$11="Aula 6",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$11="Aula 6",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$F$7="Aula 6",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$7="Aula 6",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$7="Aula 6",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$7="Aula 6",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$7="Aula 6",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$7="Aula 6",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$7="Aula 6",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$7="Aula 6",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$7="Aula 6",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$7="Aula 6",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$7="Aula 6",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$7="Aula 6",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$7="Aula 6",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$7="Aula 6",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$7="Aula 6",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$7="Aula 6",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$7="Aula 6",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="H37" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$F$11="Aula 7",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$11="Aula 7",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$11="Aula 7",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$11="Aula 7",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$11="Aula 7",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$11="Aula 7",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$11="Aula 7",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$11="Aula 7",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$11="Aula 7",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$11="Aula 7",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$11="Aula 7",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$11="Aula 7",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$11="Aula 7",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$11="Aula 7",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$11="Aula 7",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$11="Aula 7",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$11="Aula 7",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$F$7="Aula 7",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$7="Aula 7",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$7="Aula 7",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$7="Aula 7",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$7="Aula 7",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$7="Aula 7",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$7="Aula 7",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$7="Aula 7",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$7="Aula 7",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$7="Aula 7",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$7="Aula 7",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$7="Aula 7",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$7="Aula 7",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$7="Aula 7",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$7="Aula 7",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$7="Aula 7",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$7="Aula 7",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="I37" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$F$11="Aula 8",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$11="Aula 8",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$11="Aula 8",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$11="Aula 8",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$11="Aula 8",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$11="Aula 8",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$11="Aula 8",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$11="Aula 8",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$11="Aula 8",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$11="Aula 8",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$11="Aula 8",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$11="Aula 8",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$11="Aula 8",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$11="Aula 8",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$11="Aula 8",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$11="Aula 8",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$11="Aula 8",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$F$7="Aula 8",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$7="Aula 8",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$7="Aula 8",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$7="Aula 8",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$7="Aula 8",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$7="Aula 8",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$7="Aula 8",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$7="Aula 8",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$7="Aula 8",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$7="Aula 8",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$7="Aula 8",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$7="Aula 8",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$7="Aula 8",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$7="Aula 8",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$7="Aula 8",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$7="Aula 8",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$7="Aula 8",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="J37" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$F$11="Aula 9",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$11="Aula 9",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$11="Aula 9",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$11="Aula 9",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$11="Aula 9",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$11="Aula 9",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$11="Aula 9",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$11="Aula 9",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$11="Aula 9",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$11="Aula 9",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$11="Aula 9",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$11="Aula 9",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$11="Aula 9",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$11="Aula 9",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$11="Aula 9",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$11="Aula 9",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$11="Aula 9",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$F$7="Aula 9",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$7="Aula 9",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$7="Aula 9",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$7="Aula 9",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$7="Aula 9",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$7="Aula 9",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$7="Aula 9",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$7="Aula 9",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$7="Aula 9",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$7="Aula 9",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$7="Aula 9",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$7="Aula 9",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$7="Aula 9",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$7="Aula 9",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$7="Aula 9",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$7="Aula 9",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$7="Aula 9",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="K37" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$F$11="Lab",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$11="Lab",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$11="Lab",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$11="Lab",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$11="Lab",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$11="Lab",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$11="Lab",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$11="Lab",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$11="Lab",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$11="Lab",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$11="Lab",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$11="Lab",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$11="Lab",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$11="Lab",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$11="Lab",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$11="Lab",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$11="Lab",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$F$7="Lab",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$7="Lab",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$7="Lab",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$7="Lab",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$7="Lab",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$7="Lab",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$7="Lab",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$7="Lab",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$7="Lab",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$7="Lab",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$7="Lab",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$7="Lab",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$7="Lab",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$7="Lab",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$7="Lab",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$7="Lab",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$7="Lab",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="L37" t="inlineStr"/>
@@ -7659,43 +7418,43 @@
         </is>
       </c>
       <c r="B38" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$F$13="Aula 1",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$13="Aula 1",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$13="Aula 1",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$13="Aula 1",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$13="Aula 1",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$13="Aula 1",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$13="Aula 1",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$13="Aula 1",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$13="Aula 1",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$13="Aula 1",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$13="Aula 1",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$13="Aula 1",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$13="Aula 1",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$13="Aula 1",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$13="Aula 1",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$13="Aula 1",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$13="Aula 1",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$F$9="Aula 1",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$9="Aula 1",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$9="Aula 1",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$9="Aula 1",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$9="Aula 1",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$9="Aula 1",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$9="Aula 1",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$9="Aula 1",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$9="Aula 1",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$9="Aula 1",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$9="Aula 1",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$9="Aula 1",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$9="Aula 1",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$9="Aula 1",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$9="Aula 1",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$9="Aula 1",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$9="Aula 1",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="C38" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$F$13="Aula 2",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$13="Aula 2",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$13="Aula 2",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$13="Aula 2",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$13="Aula 2",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$13="Aula 2",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$13="Aula 2",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$13="Aula 2",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$13="Aula 2",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$13="Aula 2",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$13="Aula 2",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$13="Aula 2",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$13="Aula 2",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$13="Aula 2",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$13="Aula 2",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$13="Aula 2",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$13="Aula 2",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$F$9="Aula 2",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$9="Aula 2",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$9="Aula 2",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$9="Aula 2",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$9="Aula 2",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$9="Aula 2",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$9="Aula 2",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$9="Aula 2",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$9="Aula 2",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$9="Aula 2",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$9="Aula 2",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$9="Aula 2",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$9="Aula 2",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$9="Aula 2",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$9="Aula 2",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$9="Aula 2",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$9="Aula 2",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="D38" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$F$13="Aula 3",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$13="Aula 3",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$13="Aula 3",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$13="Aula 3",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$13="Aula 3",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$13="Aula 3",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$13="Aula 3",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$13="Aula 3",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$13="Aula 3",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$13="Aula 3",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$13="Aula 3",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$13="Aula 3",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$13="Aula 3",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$13="Aula 3",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$13="Aula 3",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$13="Aula 3",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$13="Aula 3",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$F$9="Aula 3",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$9="Aula 3",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$9="Aula 3",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$9="Aula 3",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$9="Aula 3",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$9="Aula 3",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$9="Aula 3",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$9="Aula 3",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$9="Aula 3",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$9="Aula 3",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$9="Aula 3",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$9="Aula 3",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$9="Aula 3",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$9="Aula 3",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$9="Aula 3",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$9="Aula 3",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$9="Aula 3",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="E38" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$F$13="Aula 4",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$13="Aula 4",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$13="Aula 4",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$13="Aula 4",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$13="Aula 4",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$13="Aula 4",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$13="Aula 4",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$13="Aula 4",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$13="Aula 4",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$13="Aula 4",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$13="Aula 4",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$13="Aula 4",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$13="Aula 4",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$13="Aula 4",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$13="Aula 4",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$13="Aula 4",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$13="Aula 4",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$F$9="Aula 4",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$9="Aula 4",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$9="Aula 4",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$9="Aula 4",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$9="Aula 4",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$9="Aula 4",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$9="Aula 4",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$9="Aula 4",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$9="Aula 4",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$9="Aula 4",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$9="Aula 4",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$9="Aula 4",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$9="Aula 4",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$9="Aula 4",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$9="Aula 4",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$9="Aula 4",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$9="Aula 4",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="F38" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$F$13="Aula 5",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$13="Aula 5",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$13="Aula 5",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$13="Aula 5",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$13="Aula 5",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$13="Aula 5",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$13="Aula 5",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$13="Aula 5",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$13="Aula 5",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$13="Aula 5",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$13="Aula 5",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$13="Aula 5",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$13="Aula 5",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$13="Aula 5",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$13="Aula 5",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$13="Aula 5",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$13="Aula 5",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$F$9="Aula 5",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$9="Aula 5",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$9="Aula 5",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$9="Aula 5",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$9="Aula 5",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$9="Aula 5",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$9="Aula 5",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$9="Aula 5",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$9="Aula 5",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$9="Aula 5",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$9="Aula 5",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$9="Aula 5",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$9="Aula 5",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$9="Aula 5",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$9="Aula 5",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$9="Aula 5",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$9="Aula 5",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="G38" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$F$13="Aula 6",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$13="Aula 6",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$13="Aula 6",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$13="Aula 6",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$13="Aula 6",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$13="Aula 6",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$13="Aula 6",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$13="Aula 6",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$13="Aula 6",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$13="Aula 6",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$13="Aula 6",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$13="Aula 6",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$13="Aula 6",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$13="Aula 6",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$13="Aula 6",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$13="Aula 6",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$13="Aula 6",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$F$9="Aula 6",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$9="Aula 6",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$9="Aula 6",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$9="Aula 6",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$9="Aula 6",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$9="Aula 6",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$9="Aula 6",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$9="Aula 6",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$9="Aula 6",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$9="Aula 6",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$9="Aula 6",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$9="Aula 6",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$9="Aula 6",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$9="Aula 6",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$9="Aula 6",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$9="Aula 6",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$9="Aula 6",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="H38" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$F$13="Aula 7",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$13="Aula 7",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$13="Aula 7",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$13="Aula 7",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$13="Aula 7",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$13="Aula 7",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$13="Aula 7",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$13="Aula 7",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$13="Aula 7",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$13="Aula 7",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$13="Aula 7",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$13="Aula 7",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$13="Aula 7",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$13="Aula 7",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$13="Aula 7",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$13="Aula 7",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$13="Aula 7",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$F$9="Aula 7",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$9="Aula 7",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$9="Aula 7",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$9="Aula 7",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$9="Aula 7",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$9="Aula 7",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$9="Aula 7",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$9="Aula 7",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$9="Aula 7",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$9="Aula 7",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$9="Aula 7",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$9="Aula 7",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$9="Aula 7",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$9="Aula 7",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$9="Aula 7",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$9="Aula 7",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$9="Aula 7",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="I38" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$F$13="Aula 8",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$13="Aula 8",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$13="Aula 8",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$13="Aula 8",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$13="Aula 8",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$13="Aula 8",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$13="Aula 8",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$13="Aula 8",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$13="Aula 8",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$13="Aula 8",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$13="Aula 8",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$13="Aula 8",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$13="Aula 8",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$13="Aula 8",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$13="Aula 8",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$13="Aula 8",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$13="Aula 8",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$F$9="Aula 8",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$9="Aula 8",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$9="Aula 8",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$9="Aula 8",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$9="Aula 8",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$9="Aula 8",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$9="Aula 8",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$9="Aula 8",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$9="Aula 8",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$9="Aula 8",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$9="Aula 8",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$9="Aula 8",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$9="Aula 8",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$9="Aula 8",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$9="Aula 8",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$9="Aula 8",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$9="Aula 8",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="J38" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$F$13="Aula 9",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$13="Aula 9",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$13="Aula 9",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$13="Aula 9",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$13="Aula 9",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$13="Aula 9",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$13="Aula 9",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$13="Aula 9",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$13="Aula 9",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$13="Aula 9",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$13="Aula 9",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$13="Aula 9",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$13="Aula 9",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$13="Aula 9",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$13="Aula 9",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$13="Aula 9",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$13="Aula 9",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$F$9="Aula 9",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$9="Aula 9",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$9="Aula 9",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$9="Aula 9",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$9="Aula 9",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$9="Aula 9",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$9="Aula 9",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$9="Aula 9",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$9="Aula 9",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$9="Aula 9",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$9="Aula 9",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$9="Aula 9",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$9="Aula 9",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$9="Aula 9",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$9="Aula 9",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$9="Aula 9",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$9="Aula 9",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="K38" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$F$13="Lab",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$13="Lab",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$13="Lab",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$13="Lab",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$13="Lab",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$13="Lab",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$13="Lab",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$13="Lab",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$13="Lab",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$13="Lab",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$13="Lab",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$13="Lab",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$13="Lab",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$13="Lab",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$13="Lab",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$13="Lab",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$13="Lab",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$F$9="Lab",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$9="Lab",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$9="Lab",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$9="Lab",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$9="Lab",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$9="Lab",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$9="Lab",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$9="Lab",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$9="Lab",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$9="Lab",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$9="Lab",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$9="Lab",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$9="Lab",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$9="Lab",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$9="Lab",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$9="Lab",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$9="Lab",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -7707,43 +7466,43 @@
         </is>
       </c>
       <c r="B39" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$F$15="Aula 1",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$15="Aula 1",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$15="Aula 1",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$15="Aula 1",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$15="Aula 1",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$15="Aula 1",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$15="Aula 1",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$15="Aula 1",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$15="Aula 1",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$15="Aula 1",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$15="Aula 1",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$15="Aula 1",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$15="Aula 1",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$15="Aula 1",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$15="Aula 1",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$15="Aula 1",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$15="Aula 1",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$F$11="Aula 1",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$11="Aula 1",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$11="Aula 1",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$11="Aula 1",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$11="Aula 1",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$11="Aula 1",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$11="Aula 1",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$11="Aula 1",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$11="Aula 1",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$11="Aula 1",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$11="Aula 1",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$11="Aula 1",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$11="Aula 1",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$11="Aula 1",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$11="Aula 1",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$11="Aula 1",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$11="Aula 1",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="C39" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$F$15="Aula 2",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$15="Aula 2",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$15="Aula 2",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$15="Aula 2",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$15="Aula 2",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$15="Aula 2",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$15="Aula 2",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$15="Aula 2",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$15="Aula 2",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$15="Aula 2",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$15="Aula 2",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$15="Aula 2",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$15="Aula 2",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$15="Aula 2",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$15="Aula 2",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$15="Aula 2",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$15="Aula 2",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$F$11="Aula 2",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$11="Aula 2",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$11="Aula 2",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$11="Aula 2",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$11="Aula 2",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$11="Aula 2",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$11="Aula 2",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$11="Aula 2",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$11="Aula 2",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$11="Aula 2",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$11="Aula 2",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$11="Aula 2",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$11="Aula 2",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$11="Aula 2",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$11="Aula 2",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$11="Aula 2",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$11="Aula 2",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="D39" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$F$15="Aula 3",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$15="Aula 3",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$15="Aula 3",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$15="Aula 3",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$15="Aula 3",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$15="Aula 3",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$15="Aula 3",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$15="Aula 3",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$15="Aula 3",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$15="Aula 3",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$15="Aula 3",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$15="Aula 3",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$15="Aula 3",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$15="Aula 3",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$15="Aula 3",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$15="Aula 3",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$15="Aula 3",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$F$11="Aula 3",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$11="Aula 3",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$11="Aula 3",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$11="Aula 3",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$11="Aula 3",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$11="Aula 3",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$11="Aula 3",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$11="Aula 3",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$11="Aula 3",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$11="Aula 3",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$11="Aula 3",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$11="Aula 3",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$11="Aula 3",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$11="Aula 3",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$11="Aula 3",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$11="Aula 3",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$11="Aula 3",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="E39" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$F$15="Aula 4",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$15="Aula 4",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$15="Aula 4",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$15="Aula 4",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$15="Aula 4",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$15="Aula 4",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$15="Aula 4",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$15="Aula 4",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$15="Aula 4",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$15="Aula 4",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$15="Aula 4",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$15="Aula 4",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$15="Aula 4",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$15="Aula 4",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$15="Aula 4",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$15="Aula 4",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$15="Aula 4",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$F$11="Aula 4",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$11="Aula 4",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$11="Aula 4",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$11="Aula 4",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$11="Aula 4",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$11="Aula 4",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$11="Aula 4",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$11="Aula 4",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$11="Aula 4",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$11="Aula 4",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$11="Aula 4",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$11="Aula 4",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$11="Aula 4",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$11="Aula 4",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$11="Aula 4",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$11="Aula 4",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$11="Aula 4",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="F39" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$F$15="Aula 5",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$15="Aula 5",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$15="Aula 5",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$15="Aula 5",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$15="Aula 5",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$15="Aula 5",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$15="Aula 5",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$15="Aula 5",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$15="Aula 5",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$15="Aula 5",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$15="Aula 5",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$15="Aula 5",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$15="Aula 5",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$15="Aula 5",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$15="Aula 5",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$15="Aula 5",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$15="Aula 5",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$F$11="Aula 5",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$11="Aula 5",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$11="Aula 5",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$11="Aula 5",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$11="Aula 5",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$11="Aula 5",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$11="Aula 5",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$11="Aula 5",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$11="Aula 5",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$11="Aula 5",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$11="Aula 5",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$11="Aula 5",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$11="Aula 5",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$11="Aula 5",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$11="Aula 5",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$11="Aula 5",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$11="Aula 5",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="G39" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$F$15="Aula 6",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$15="Aula 6",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$15="Aula 6",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$15="Aula 6",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$15="Aula 6",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$15="Aula 6",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$15="Aula 6",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$15="Aula 6",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$15="Aula 6",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$15="Aula 6",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$15="Aula 6",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$15="Aula 6",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$15="Aula 6",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$15="Aula 6",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$15="Aula 6",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$15="Aula 6",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$15="Aula 6",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$F$11="Aula 6",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$11="Aula 6",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$11="Aula 6",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$11="Aula 6",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$11="Aula 6",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$11="Aula 6",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$11="Aula 6",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$11="Aula 6",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$11="Aula 6",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$11="Aula 6",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$11="Aula 6",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$11="Aula 6",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$11="Aula 6",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$11="Aula 6",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$11="Aula 6",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$11="Aula 6",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$11="Aula 6",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="H39" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$F$15="Aula 7",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$15="Aula 7",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$15="Aula 7",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$15="Aula 7",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$15="Aula 7",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$15="Aula 7",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$15="Aula 7",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$15="Aula 7",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$15="Aula 7",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$15="Aula 7",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$15="Aula 7",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$15="Aula 7",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$15="Aula 7",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$15="Aula 7",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$15="Aula 7",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$15="Aula 7",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$15="Aula 7",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$F$11="Aula 7",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$11="Aula 7",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$11="Aula 7",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$11="Aula 7",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$11="Aula 7",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$11="Aula 7",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$11="Aula 7",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$11="Aula 7",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$11="Aula 7",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$11="Aula 7",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$11="Aula 7",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$11="Aula 7",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$11="Aula 7",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$11="Aula 7",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$11="Aula 7",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$11="Aula 7",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$11="Aula 7",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="I39" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$F$15="Aula 8",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$15="Aula 8",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$15="Aula 8",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$15="Aula 8",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$15="Aula 8",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$15="Aula 8",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$15="Aula 8",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$15="Aula 8",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$15="Aula 8",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$15="Aula 8",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$15="Aula 8",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$15="Aula 8",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$15="Aula 8",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$15="Aula 8",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$15="Aula 8",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$15="Aula 8",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$15="Aula 8",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$F$11="Aula 8",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$11="Aula 8",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$11="Aula 8",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$11="Aula 8",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$11="Aula 8",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$11="Aula 8",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$11="Aula 8",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$11="Aula 8",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$11="Aula 8",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$11="Aula 8",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$11="Aula 8",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$11="Aula 8",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$11="Aula 8",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$11="Aula 8",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$11="Aula 8",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$11="Aula 8",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$11="Aula 8",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="J39" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$F$15="Aula 9",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$15="Aula 9",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$15="Aula 9",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$15="Aula 9",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$15="Aula 9",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$15="Aula 9",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$15="Aula 9",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$15="Aula 9",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$15="Aula 9",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$15="Aula 9",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$15="Aula 9",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$15="Aula 9",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$15="Aula 9",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$15="Aula 9",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$15="Aula 9",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$15="Aula 9",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$15="Aula 9",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$F$11="Aula 9",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$11="Aula 9",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$11="Aula 9",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$11="Aula 9",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$11="Aula 9",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$11="Aula 9",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$11="Aula 9",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$11="Aula 9",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$11="Aula 9",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$11="Aula 9",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$11="Aula 9",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$11="Aula 9",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$11="Aula 9",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$11="Aula 9",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$11="Aula 9",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$11="Aula 9",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$11="Aula 9",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="K39" s="2">
-        <f>SUBSTITUTE(TRIM(IF(D111!$F$15="Lab",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$15="Lab",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$15="Lab",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$15="Lab",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$15="Lab",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$15="Lab",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$15="Lab",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$15="Lab",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$15="Lab",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$15="Lab",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$15="Lab",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$15="Lab",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$15="Lab",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$15="Lab",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$15="Lab",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$15="Lab",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$15="Lab",(M411!$A$1&amp;" "),""))," ",",")</f>
+        <f>SUBSTITUTE(TRIM(IF(D111!$F$11="Lab",(D111!$A$1&amp;" "),"")&amp;IF(D211!$F$11="Lab",(D211!$A$1&amp;" "),"")&amp;IF(D311!$F$11="Lab",(D311!$A$1&amp;" "),"")&amp;IF(D411!$F$11="Lab",(D411!$A$1&amp;" "),"")&amp;IF(C111!$F$11="Lab",(C111!$A$1&amp;" "),"")&amp;IF(C121!$F$11="Lab",(C121!$A$1&amp;" "),"")&amp;IF(C122!$F$11="Lab",(C122!$A$1&amp;" "),"")&amp;IF(C211!$F$11="Lab",(C211!$A$1&amp;" "),"")&amp;IF(C212!$F$11="Lab",(C212!$A$1&amp;" "),"")&amp;IF(C311!$F$11="Lab",(C311!$A$1&amp;" "),"")&amp;IF(C312!$F$11="Lab",(C312!$A$1&amp;" "),"")&amp;IF(C411!$F$11="Lab",(C411!$A$1&amp;" "),"")&amp;IF(C412!$F$11="Lab",(C412!$A$1&amp;" "),"")&amp;IF(M111!$F$11="Lab",(M111!$A$1&amp;" "),"")&amp;IF(M211!$F$11="Lab",(M211!$A$1&amp;" "),"")&amp;IF(M311!$F$11="Lab",(M311!$A$1&amp;" "),"")&amp;IF(M411!$F$11="Lab",(M411!$A$1&amp;" "),""))," ",",")</f>
         <v/>
       </c>
       <c r="L39" t="inlineStr"/>
@@ -7759,7 +7518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8137,14 +7896,11 @@
       </c>
       <c r="F10" s="1" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" s="2">
-        <f>COUNTA($H$4:$H$9)</f>
-        <v/>
-      </c>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr">
         <is>
@@ -8177,11 +7933,11 @@
       </c>
       <c r="F11" s="3" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="2" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -8218,11 +7974,11 @@
       </c>
       <c r="F12" s="1" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -8255,11 +8011,11 @@
       </c>
       <c r="F13" s="3" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr"/>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="2" t="inlineStr"/>
-      <c r="L13" s="2" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -8296,11 +8052,11 @@
       </c>
       <c r="F14" s="1" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr"/>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr"/>
-      <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="2" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -8329,32 +8085,27 @@
       </c>
       <c r="F15" s="3" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="2" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" s="2" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
     </row>
-    <row r="16">
-      <c r="G16">
-        <f>"Total:"</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="F17">
-        <f>"Sigma Frec:"</f>
-        <v/>
-      </c>
-      <c r="G17">
-        <f>SUM($J$4:$J$9)</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
+  <conditionalFormatting sqref="I4:I9">
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
+      <formula>L4&gt;J4</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="0">
+      <formula>L4=J4</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="2" stopIfTrue="0">
+      <formula>L4&lt;J4</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8365,7 +8116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8811,14 +8562,11 @@
       <c r="E10" s="1" t="inlineStr"/>
       <c r="F10" s="1" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" s="2">
-        <f>COUNTA($H$4:$H$9)</f>
-        <v/>
-      </c>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr">
         <is>
@@ -8835,11 +8583,11 @@
       <c r="E11" s="3" t="inlineStr"/>
       <c r="F11" s="3" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="2" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -8860,11 +8608,11 @@
       <c r="E12" s="1" t="inlineStr"/>
       <c r="F12" s="1" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -8881,11 +8629,11 @@
       <c r="E13" s="3" t="inlineStr"/>
       <c r="F13" s="3" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr"/>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="2" t="inlineStr"/>
-      <c r="L13" s="2" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -8906,13 +8654,13 @@
       <c r="E14" s="1" t="inlineStr"/>
       <c r="F14" s="1" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr"/>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr"/>
-      <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="2" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" s="2" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
@@ -8923,32 +8671,27 @@
       <c r="E15" s="3" t="inlineStr"/>
       <c r="F15" s="3" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="2" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" s="2" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
     </row>
-    <row r="16">
-      <c r="G16">
-        <f>"Total:"</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="F17">
-        <f>"Sigma Frec:"</f>
-        <v/>
-      </c>
-      <c r="G17">
-        <f>SUM($J$4:$J$9)</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
+  <conditionalFormatting sqref="I4:I9">
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
+      <formula>L4&gt;J4</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="0">
+      <formula>L4=J4</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="2" stopIfTrue="0">
+      <formula>L4&lt;J4</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8959,7 +8702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9397,14 +9140,11 @@
       <c r="E10" s="1" t="inlineStr"/>
       <c r="F10" s="1" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" s="2">
-        <f>COUNTA($H$4:$H$9)</f>
-        <v/>
-      </c>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr">
         <is>
@@ -9421,11 +9161,11 @@
       <c r="E11" s="3" t="inlineStr"/>
       <c r="F11" s="3" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="2" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -9446,11 +9186,11 @@
       <c r="E12" s="1" t="inlineStr"/>
       <c r="F12" s="1" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -9467,11 +9207,11 @@
       <c r="E13" s="3" t="inlineStr"/>
       <c r="F13" s="3" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr"/>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="2" t="inlineStr"/>
-      <c r="L13" s="2" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -9492,13 +9232,13 @@
       <c r="E14" s="1" t="inlineStr"/>
       <c r="F14" s="1" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr"/>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr"/>
-      <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="2" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" s="2" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
@@ -9509,32 +9249,27 @@
       <c r="E15" s="3" t="inlineStr"/>
       <c r="F15" s="3" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="2" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" s="2" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
     </row>
-    <row r="16">
-      <c r="G16">
-        <f>"Total:"</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="F17">
-        <f>"Sigma Frec:"</f>
-        <v/>
-      </c>
-      <c r="G17">
-        <f>SUM($J$4:$J$9)</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
+  <conditionalFormatting sqref="I4:I9">
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
+      <formula>L4&gt;J4</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="0">
+      <formula>L4=J4</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="2" stopIfTrue="0">
+      <formula>L4&lt;J4</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10019,14 +9754,11 @@
       <c r="E10" s="1" t="inlineStr"/>
       <c r="F10" s="1" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" s="2">
-        <f>COUNTA($H$4:$H$9)</f>
-        <v/>
-      </c>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr">
         <is>
@@ -10043,11 +9775,11 @@
       <c r="E11" s="3" t="inlineStr"/>
       <c r="F11" s="3" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="2" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -10068,11 +9800,11 @@
       <c r="E12" s="1" t="inlineStr"/>
       <c r="F12" s="1" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -10089,11 +9821,11 @@
       <c r="E13" s="3" t="inlineStr"/>
       <c r="F13" s="3" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr"/>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="2" t="inlineStr"/>
-      <c r="L13" s="2" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -10114,11 +9846,11 @@
       <c r="E14" s="1" t="inlineStr"/>
       <c r="F14" s="1" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr"/>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr"/>
-      <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="2" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -10135,11 +9867,11 @@
       <c r="E15" s="3" t="inlineStr"/>
       <c r="F15" s="3" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="2" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -10155,17 +9887,14 @@
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
-      <c r="G16">
-        <f>"Total:"</f>
-        <v/>
-      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>Aula 6</t>
         </is>
@@ -10178,21 +9907,15 @@
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
-      <c r="F17">
-        <f>"Sigma Frec:"</f>
-        <v/>
-      </c>
-      <c r="G17">
-        <f>SUM($J$4:$J$9)</f>
-        <v/>
-      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>Lab</t>
         </is>
@@ -10200,6 +9923,17 @@
       <c r="O17" t="inlineStr"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="I4:I9">
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
+      <formula>L4&gt;J4</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="0">
+      <formula>L4=J4</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="2" stopIfTrue="0">
+      <formula>L4&lt;J4</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10684,14 +10418,11 @@
       <c r="E10" s="1" t="inlineStr"/>
       <c r="F10" s="1" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" s="2">
-        <f>COUNTA($H$4:$H$9)</f>
-        <v/>
-      </c>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr">
         <is>
@@ -10708,11 +10439,11 @@
       <c r="E11" s="3" t="inlineStr"/>
       <c r="F11" s="3" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="2" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -10733,11 +10464,11 @@
       <c r="E12" s="1" t="inlineStr"/>
       <c r="F12" s="1" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -10754,11 +10485,11 @@
       <c r="E13" s="3" t="inlineStr"/>
       <c r="F13" s="3" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr"/>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="2" t="inlineStr"/>
-      <c r="L13" s="2" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -10779,11 +10510,11 @@
       <c r="E14" s="1" t="inlineStr"/>
       <c r="F14" s="1" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr"/>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr"/>
-      <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="2" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -10800,11 +10531,11 @@
       <c r="E15" s="3" t="inlineStr"/>
       <c r="F15" s="3" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="2" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -10820,17 +10551,14 @@
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
-      <c r="G16">
-        <f>"Total:"</f>
-        <v/>
-      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>Aula 5</t>
         </is>
@@ -10843,21 +10571,15 @@
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
-      <c r="F17">
-        <f>"Sigma Frec:"</f>
-        <v/>
-      </c>
-      <c r="G17">
-        <f>SUM($J$4:$J$9)</f>
-        <v/>
-      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>Aula 5</t>
         </is>
@@ -10865,6 +10587,17 @@
       <c r="O17" t="inlineStr"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="I4:I9">
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
+      <formula>L4&gt;J4</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="0">
+      <formula>L4=J4</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="2" stopIfTrue="0">
+      <formula>L4&lt;J4</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11349,14 +11082,11 @@
       <c r="E10" s="1" t="inlineStr"/>
       <c r="F10" s="1" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" s="2">
-        <f>COUNTA($H$4:$H$9)</f>
-        <v/>
-      </c>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr">
         <is>
@@ -11373,11 +11103,11 @@
       <c r="E11" s="3" t="inlineStr"/>
       <c r="F11" s="3" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="2" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -11398,11 +11128,11 @@
       <c r="E12" s="1" t="inlineStr"/>
       <c r="F12" s="1" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -11419,11 +11149,11 @@
       <c r="E13" s="3" t="inlineStr"/>
       <c r="F13" s="3" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr"/>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="2" t="inlineStr"/>
-      <c r="L13" s="2" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -11444,11 +11174,11 @@
       <c r="E14" s="1" t="inlineStr"/>
       <c r="F14" s="1" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr"/>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr"/>
-      <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="2" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -11465,11 +11195,11 @@
       <c r="E15" s="3" t="inlineStr"/>
       <c r="F15" s="3" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="2" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -11485,17 +11215,14 @@
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
-      <c r="G16">
-        <f>"Total:"</f>
-        <v/>
-      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>Aula 1</t>
         </is>
@@ -11508,21 +11235,15 @@
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
-      <c r="F17">
-        <f>"Sigma Frec:"</f>
-        <v/>
-      </c>
-      <c r="G17">
-        <f>SUM($J$4:$J$9)</f>
-        <v/>
-      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>Aula 5</t>
         </is>
@@ -11530,6 +11251,17 @@
       <c r="O17" t="inlineStr"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="I4:I9">
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
+      <formula>L4&gt;J4</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="0">
+      <formula>L4=J4</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="2" stopIfTrue="0">
+      <formula>L4&lt;J4</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11540,7 +11272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -11922,14 +11654,11 @@
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" s="2">
-        <f>COUNTA($H$4:$H$9)</f>
-        <v/>
-      </c>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr">
         <is>
@@ -11966,11 +11695,11 @@
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="2" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -12011,11 +11740,11 @@
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -12052,11 +11781,11 @@
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr"/>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="2" t="inlineStr"/>
-      <c r="L13" s="2" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -12089,11 +11818,11 @@
       <c r="E14" s="1" t="inlineStr"/>
       <c r="F14" s="1" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr"/>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr"/>
-      <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="2" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -12118,11 +11847,11 @@
       <c r="E15" s="3" t="inlineStr"/>
       <c r="F15" s="3" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="2" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -12131,23 +11860,18 @@
       </c>
       <c r="O15" t="inlineStr"/>
     </row>
-    <row r="16">
-      <c r="G16">
-        <f>"Total:"</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="F17">
-        <f>"Sigma Frec:"</f>
-        <v/>
-      </c>
-      <c r="G17">
-        <f>SUM($J$4:$J$9)</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
+  <conditionalFormatting sqref="I4:I9">
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
+      <formula>L4&gt;J4</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="0">
+      <formula>L4=J4</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="2" stopIfTrue="0">
+      <formula>L4&lt;J4</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12158,7 +11882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -12540,14 +12264,11 @@
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" s="2">
-        <f>COUNTA($H$4:$H$9)</f>
-        <v/>
-      </c>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr">
         <is>
@@ -12584,11 +12305,11 @@
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="2" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -12629,11 +12350,11 @@
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -12670,11 +12391,11 @@
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr"/>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="2" t="inlineStr"/>
-      <c r="L13" s="2" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -12707,11 +12428,11 @@
       <c r="E14" s="1" t="inlineStr"/>
       <c r="F14" s="1" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr"/>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr"/>
-      <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="2" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -12736,11 +12457,11 @@
       <c r="E15" s="3" t="inlineStr"/>
       <c r="F15" s="3" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="2" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -12749,23 +12470,18 @@
       </c>
       <c r="O15" t="inlineStr"/>
     </row>
-    <row r="16">
-      <c r="G16">
-        <f>"Total:"</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="F17">
-        <f>"Sigma Frec:"</f>
-        <v/>
-      </c>
-      <c r="G17">
-        <f>SUM($J$4:$J$9)</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
+  <conditionalFormatting sqref="I4:I9">
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
+      <formula>L4&gt;J4</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="0">
+      <formula>L4=J4</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="2" stopIfTrue="0">
+      <formula>L4&lt;J4</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>